--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -11,58 +11,22 @@
     <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -129,7 +93,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -156,12 +120,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -172,17 +130,23 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -190,20 +154,13 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -231,15 +188,15 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="15">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -251,14 +208,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -276,10 +233,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -290,13 +247,30 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="none">
+      <x:top style="thin">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="none">
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -451,37 +425,37 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -490,16 +464,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -508,67 +479,78 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -580,20 +562,20 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -601,6 +583,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -864,190 +850,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46049.5962615741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2115,188 +2097,184 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+      <x:c r="H6" s="13">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46066.6040162037</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3364,190 +3342,186 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46078.2888888889</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46078.2901041667</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="J6" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46089.2508680556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s"/>
+      <x:c r="C7" s="16" t="s"/>
+      <x:c r="D7" s="16" t="s"/>
+      <x:c r="E7" s="16" t="s"/>
+      <x:c r="F7" s="16" t="s"/>
+      <x:c r="G7" s="16" t="s"/>
+      <x:c r="H7" s="16" t="s"/>
+      <x:c r="I7" s="16" t="s"/>
+      <x:c r="J7" s="16" t="s"/>
+      <x:c r="K7" s="16" t="s"/>
+      <x:c r="L7" s="16" t="s"/>
+      <x:c r="M7" s="16" t="s"/>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s"/>
-      <x:c r="D9" s="15" t="s"/>
-      <x:c r="E9" s="16" t="s"/>
-      <x:c r="F9" s="16" t="s"/>
+      <x:c r="B9" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="s"/>
+      <x:c r="D9" s="18" t="s"/>
+      <x:c r="E9" s="19" t="s"/>
+      <x:c r="F9" s="19" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="17" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="s"/>
-      <x:c r="D10" s="18" t="s"/>
-      <x:c r="E10" s="18" t="s"/>
-      <x:c r="F10" s="19" t="s">
-        <x:v>23</x:v>
+      <x:c r="B10" s="20" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="21" t="s"/>
+      <x:c r="F10" s="22" t="s">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="20" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="21" t="s"/>
-      <x:c r="D11" s="21" t="s"/>
-      <x:c r="E11" s="21" t="s"/>
-      <x:c r="F11" s="22" t="n">
+      <x:c r="B11" s="23" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="24" t="s"/>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="24" t="s"/>
-      <x:c r="F12" s="25" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,9 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>EVALUATOR SUMMARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EVALUATOR EDGE</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -154,7 +157,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="18"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -188,7 +191,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -233,10 +236,10 @@
       <x:right style="none">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -247,30 +250,13 @@
       <x:left style="none">
         <x:color rgb="FF000000"/>
       </x:left>
-      <x:right style="none">
+      <x:right style="thick">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
+      <x:top style="none">
         <x:color rgb="FF000000"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
-    </x:border>
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="thick">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="thin">
+      <x:bottom style="none">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -452,10 +438,13 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -464,22 +453,19 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -546,11 +532,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -562,11 +552,7 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -574,8 +560,12 @@
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -583,10 +573,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -835,7 +821,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -852,7 +840,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46023</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -915,22 +903,22 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46049.5725925926</x:v>
@@ -939,7 +927,7 @@
         <x:v>46049.5726273148</x:v>
       </x:c>
       <x:c r="J6" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
@@ -948,7 +936,7 @@
         <x:v>46049.5962615741</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -984,14 +972,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -1000,41 +986,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2015,13 +2009,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2082,7 +2077,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -2099,7 +2096,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="3" t="s"/>
       <x:c r="B3" s="3">
-        <x:v>46054</x:v>
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s"/>
       <x:c r="D3" s="3" t="s"/>
@@ -2162,20 +2159,20 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s"/>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46066.6004513889</x:v>
@@ -2184,7 +2181,7 @@
         <x:v>46066.6024652778</x:v>
       </x:c>
       <x:c r="J6" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
         <x:v>130</x:v>
@@ -2193,7 +2190,7 @@
         <x:v>46066.6040162037</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -2229,14 +2226,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -2245,41 +2240,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3260,13 +3263,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3327,7 +3331,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -3407,22 +3413,22 @@
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H6" s="13">
         <x:v>46078.2888888889</x:v>
@@ -3431,7 +3437,7 @@
         <x:v>46078.2901041667</x:v>
       </x:c>
       <x:c r="J6" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
@@ -3440,7 +3446,7 @@
         <x:v>46089.2508680556</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
@@ -3476,14 +3482,12 @@
       <x:c r="L8" s="9" t="s"/>
       <x:c r="M8" s="9" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="17" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="s"/>
-      <x:c r="D9" s="18" t="s"/>
-      <x:c r="E9" s="19" t="s"/>
-      <x:c r="F9" s="19" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
       <x:c r="G9" s="9" t="s"/>
       <x:c r="H9" s="9" t="s"/>
       <x:c r="I9" s="9" t="s"/>
@@ -3492,41 +3496,49 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="21" t="s"/>
-      <x:c r="F10" s="22" t="s">
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="n">
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="26" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4507,13 +4519,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
-    <x:mergeCell ref="B11:E11"/>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -469,7 +469,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -505,27 +505,31 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -901,7 +905,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -957,20 +961,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -988,44 +992,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2157,7 +2161,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -2211,20 +2215,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2242,44 +2246,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3411,7 +3415,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -3467,20 +3471,20 @@
       <x:c r="M7" s="16" t="s"/>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="17" t="s"/>
+      <x:c r="C8" s="17" t="s"/>
+      <x:c r="D8" s="17" t="s"/>
+      <x:c r="E8" s="17" t="s"/>
+      <x:c r="F8" s="17" t="s"/>
+      <x:c r="G8" s="17" t="s"/>
+      <x:c r="H8" s="17" t="s"/>
+      <x:c r="I8" s="17" t="s"/>
+      <x:c r="J8" s="17" t="s"/>
+      <x:c r="K8" s="17" t="s"/>
+      <x:c r="L8" s="17" t="s"/>
+      <x:c r="M8" s="17" t="s"/>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3498,44 +3502,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
+      <x:c r="B11" s="18" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -875,7 +875,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -945,7 +945,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -2131,7 +2131,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2199,7 +2199,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>
@@ -3385,7 +3385,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3455,7 +3455,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s"/>
       <x:c r="C7" s="16" t="s"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,12 +24,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR EDGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -96,7 +132,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -141,15 +177,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -164,6 +200,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -411,27 +454,24 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -453,10 +493,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -469,7 +512,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -500,36 +543,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -556,15 +583,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -877,18 +904,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -906,75 +921,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46049.5725925926</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46049.5726273148</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46049.5962615741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46049.5725925926</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46049.5726273148</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46049.5962615741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -992,44 +1019,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>12</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2133,18 +2160,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2162,73 +2177,85 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s"/>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46066.6004513889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46066.6024652778</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46066.6040162037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s"/>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46066.6004513889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46066.6024652778</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46066.6040162037</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -2246,44 +2273,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>12</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3387,18 +3414,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3416,75 +3431,87 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s"/>
-      <x:c r="C7" s="16" t="s"/>
-      <x:c r="D7" s="16" t="s"/>
-      <x:c r="E7" s="16" t="s"/>
-      <x:c r="F7" s="16" t="s"/>
-      <x:c r="G7" s="16" t="s"/>
-      <x:c r="H7" s="16" t="s"/>
-      <x:c r="I7" s="16" t="s"/>
-      <x:c r="J7" s="16" t="s"/>
-      <x:c r="K7" s="16" t="s"/>
-      <x:c r="L7" s="16" t="s"/>
-      <x:c r="M7" s="16" t="s"/>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="17" t="s"/>
-      <x:c r="C8" s="17" t="s"/>
-      <x:c r="D8" s="17" t="s"/>
-      <x:c r="E8" s="17" t="s"/>
-      <x:c r="F8" s="17" t="s"/>
-      <x:c r="G8" s="17" t="s"/>
-      <x:c r="H8" s="17" t="s"/>
-      <x:c r="I8" s="17" t="s"/>
-      <x:c r="J8" s="17" t="s"/>
-      <x:c r="K8" s="17" t="s"/>
-      <x:c r="L8" s="17" t="s"/>
-      <x:c r="M8" s="17" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B9" s="9" t="s"/>
@@ -3502,44 +3529,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s"/>
+      <x:c r="D11" s="15" t="s"/>
+      <x:c r="E11" s="16" t="s"/>
+      <x:c r="F11" s="16" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>12</x:v>
+      <x:c r="B12" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="19" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="B13" s="20" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,12 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR EDGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XIV | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -104,6 +107,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>XIV | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -119,6 +125,9 @@
     <x:t>test</x:t>
   </x:si>
   <x:si>
+    <x:t>XIV | March 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-06446</x:t>
   </x:si>
   <x:si>
@@ -132,7 +141,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -172,6 +181,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -443,14 +476,23 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -463,56 +505,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -543,67 +585,79 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -832,58 +886,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -926,81 +980,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="J8" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>21</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1019,44 +1073,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2043,7 +2097,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -2088,58 +2142,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2182,79 +2236,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s"/>
-      <x:c r="E8" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="J8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46066.6040162037</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>21</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2273,44 +2327,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3297,7 +3351,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>
@@ -3342,58 +3396,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3436,81 +3490,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="12">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I8" s="12">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46089.2508680556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>21</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -3529,44 +3583,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s"/>
-      <x:c r="D11" s="15" t="s"/>
-      <x:c r="E11" s="16" t="s"/>
-      <x:c r="F11" s="16" t="s"/>
+      <x:c r="B11" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="19" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="n">
+      <x:c r="B13" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+      <x:c r="B14" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4553,7 +4607,7 @@
   <x:mergeCells count="7">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B11:F11"/>
     <x:mergeCell ref="B12:E12"/>
     <x:mergeCell ref="B13:E13"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -69,6 +69,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -138,10 +174,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="15">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -186,15 +224,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -210,15 +240,15 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -233,13 +263,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -476,26 +499,26 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -505,56 +528,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -585,79 +611,91 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -886,78 +924,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -978,7 +1028,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1018,104 +1068,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46049.5725925926</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46049.5726273148</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J10" s="16" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46049.5962615741</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2094,14 +2181,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2142,78 +2230,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2234,7 +2334,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2274,102 +2374,139 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C8" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="F10" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
         <x:v>46066.6004513889</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I10" s="17">
         <x:v>46066.6024652778</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="J10" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L10" s="19">
         <x:v>46066.6040162037</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="15" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3348,14 +3485,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3396,78 +3534,90 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28" ht="22" customHeight="1">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s"/>
-      <x:c r="D3" s="12" t="s"/>
-      <x:c r="E3" s="12" t="s"/>
-      <x:c r="F3" s="12" t="s"/>
-      <x:c r="G3" s="12" t="s"/>
-      <x:c r="H3" s="12" t="s"/>
-      <x:c r="I3" s="12" t="s"/>
-      <x:c r="J3" s="12" t="s"/>
-      <x:c r="K3" s="12" t="s"/>
-      <x:c r="L3" s="12" t="s"/>
-      <x:c r="M3" s="12" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28">
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="s"/>
+      <x:c r="D5" s="12" t="s"/>
+      <x:c r="E5" s="12" t="s"/>
+      <x:c r="F5" s="12" t="s"/>
+      <x:c r="G5" s="12" t="s"/>
+      <x:c r="H5" s="12" t="s"/>
+      <x:c r="I5" s="12" t="s"/>
+      <x:c r="J5" s="12" t="s"/>
+      <x:c r="K5" s="12" t="s"/>
+      <x:c r="L5" s="12" t="s"/>
+      <x:c r="M5" s="12" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3488,7 +3638,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3528,104 +3678,141 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="14" t="s"/>
+      <x:c r="C9" s="14" t="s"/>
+      <x:c r="D9" s="14" t="s"/>
+      <x:c r="E9" s="14" t="s"/>
+      <x:c r="F9" s="14" t="s"/>
+      <x:c r="G9" s="14" t="s"/>
+      <x:c r="H9" s="14" t="s"/>
+      <x:c r="I9" s="14" t="s"/>
+      <x:c r="J9" s="14" t="s"/>
+      <x:c r="K9" s="14" t="s"/>
+      <x:c r="L9" s="14" t="s"/>
+      <x:c r="M9" s="14" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4604,14 +4791,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -69,42 +69,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -179,7 +143,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -223,14 +187,6 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -245,10 +201,18 @@
       <x:family val="2"/>
     </x:font>
     <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -263,6 +227,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -507,16 +478,16 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -528,24 +499,21 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -564,10 +532,13 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -580,7 +551,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -611,28 +582,20 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -647,10 +610,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -675,15 +634,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1028,7 +987,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1068,138 +1027,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="15">
+        <x:v>46049.5725925926</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46049.5726273148</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46049.5962615741</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46049.5725925926</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46049.5726273148</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46049.5962615741</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>37</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2301,7 +2223,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -2334,7 +2256,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2374,136 +2296,99 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="9" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D8" s="9" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46066.6004513889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46066.6024652778</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46066.6040162037</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46066.6004513889</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46066.6024652778</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46066.6040162037</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>37</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3605,7 +3490,7 @@
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="12" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="12" t="s"/>
       <x:c r="D5" s="12" t="s"/>
@@ -3638,7 +3523,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3678,138 +3563,101 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
+      <x:c r="F8" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
+        <x:v>46078.2888888889</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46078.2901041667</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="15">
+        <x:v>46089.2508680556</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="14" t="s"/>
-      <x:c r="C9" s="14" t="s"/>
-      <x:c r="D9" s="14" t="s"/>
-      <x:c r="E9" s="14" t="s"/>
-      <x:c r="F9" s="14" t="s"/>
-      <x:c r="G9" s="14" t="s"/>
-      <x:c r="H9" s="14" t="s"/>
-      <x:c r="I9" s="14" t="s"/>
-      <x:c r="J9" s="14" t="s"/>
-      <x:c r="K9" s="14" t="s"/>
-      <x:c r="L9" s="14" t="s"/>
-      <x:c r="M9" s="14" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="H10" s="17">
-        <x:v>46078.2888888889</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>46078.2901041667</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>46089.2508680556</x:v>
-      </x:c>
-      <x:c r="M10" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
+      <x:c r="B13" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="s"/>
+      <x:c r="D13" s="18" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="19" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
-        <x:v>37</x:v>
+      <x:c r="B14" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="s"/>
+      <x:c r="D14" s="21" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="22" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -1081,50 +1081,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2108,10 +2108,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -2348,50 +2348,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3375,10 +3375,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
@@ -3617,50 +3617,50 @@
       <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="17" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="s"/>
-      <x:c r="D13" s="18" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="19" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="s"/>
-      <x:c r="D14" s="21" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="22" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4644,10 +4644,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -1048,10 +1048,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46049.5725925926</x:v>
+        <x:v>46049.5726010069</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46049.5726273148</x:v>
+        <x:v>46049.5726341898</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>21</x:v>
@@ -1060,7 +1060,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46049.5962615741</x:v>
+        <x:v>46049.5962660532</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
@@ -2315,10 +2315,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46066.6004513889</x:v>
+        <x:v>46066.6004589236</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46066.6024652778</x:v>
+        <x:v>46066.6024709375</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>32</x:v>
@@ -2327,7 +2327,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46066.6040162037</x:v>
+        <x:v>46066.6040195139</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>
@@ -3584,10 +3584,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46078.2888888889</x:v>
+        <x:v>46078.2888967361</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46078.2901041667</x:v>
+        <x:v>46078.2901145602</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>32</x:v>
@@ -3596,7 +3596,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L8" s="15">
-        <x:v>46089.2508680556</x:v>
+        <x:v>46089.2508762037</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>22</x:v>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -126,6 +126,24 @@
   </x:si>
   <x:si>
     <x:t>XIV | March 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1161-496</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07584</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1160-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-07583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1159-185</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-06446</x:t>
@@ -470,7 +488,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="27">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -550,8 +568,14 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -656,6 +680,26 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -3565,103 +3609,201 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="31">
+        <x:v>46106.5066742245</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46106.5082381134</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="33">
+        <x:v>46106.5099302546</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D9" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F9" s="29" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H9" s="31">
+        <x:v>46105.676846794</x:v>
+      </x:c>
+      <x:c r="I9" s="31">
+        <x:v>46106.5084437037</x:v>
+      </x:c>
+      <x:c r="J9" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="33">
+        <x:v>46106.5101144792</x:v>
+      </x:c>
+      <x:c r="M9" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H10" s="31">
+        <x:v>46105.6741278125</x:v>
+      </x:c>
+      <x:c r="I10" s="31">
+        <x:v>46106.5086548727</x:v>
+      </x:c>
+      <x:c r="J10" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="33">
+        <x:v>46106.5103567593</x:v>
+      </x:c>
+      <x:c r="M10" s="29" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H11" s="31">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I11" s="31">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L11" s="33">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="20" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
+        <x:v>25</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="23" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
-        <x:v>1</x:v>
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4644,10 +4786,10 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -1031,7 +1031,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2300,7 +2300,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2340,7 +2340,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>28</x:v>
@@ -3567,7 +3567,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -3607,7 +3607,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="29" t="s">
         <x:v>15</x:v>
@@ -3646,7 +3646,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3684,7 +3684,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -3722,7 +3722,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR EDGE</x:t>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -24,15 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>EVALUATOR EDGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIV | January 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -107,9 +104,6 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
-    <x:t>XIV | February 2026</x:t>
-  </x:si>
-  <x:si>
     <x:t>Amateur Radio Station Permit to PURCHASE/POSSESS</x:t>
   </x:si>
   <x:si>
@@ -123,9 +117,6 @@
   </x:si>
   <x:si>
     <x:t>test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>XIV | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-07610</x:t>
@@ -488,7 +479,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="29">
+  <x:cellStyleXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -505,6 +496,9 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -575,7 +569,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -611,6 +605,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -997,20 +995,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1033,81 +1031,81 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="15" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="s">
+      <x:c r="F8" s="15" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>46049.5726010069</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46049.5726341898</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46049.5726010069</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46049.5726341898</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="K8" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>46049.5962660532</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L8" s="15">
-        <x:v>46049.5962660532</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -1126,44 +1124,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2266,20 +2264,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2302,79 +2300,79 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="14" t="s">
+      <x:c r="B8" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s"/>
+      <x:c r="E8" s="15" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="s">
+      <x:c r="G8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s"/>
-      <x:c r="E8" s="14" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="14" t="s">
+      <x:c r="H8" s="16">
+        <x:v>46066.6004589236</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46066.6024709375</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H8" s="15">
-        <x:v>46066.6004589236</x:v>
-      </x:c>
-      <x:c r="I8" s="15">
-        <x:v>46066.6024709375</x:v>
-      </x:c>
-      <x:c r="J8" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="15">
+      <x:c r="L8" s="16">
         <x:v>46066.6040195139</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
@@ -2393,44 +2391,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="s"/>
-      <x:c r="D11" s="18" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="19" t="s"/>
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="21" t="s"/>
-      <x:c r="F12" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="n">
+      <x:c r="B13" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3533,20 +3531,20 @@
     </x:row>
     <x:row r="5" spans="1:28" ht="22" customHeight="1">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="12" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C5" s="12" t="s"/>
-      <x:c r="D5" s="12" t="s"/>
-      <x:c r="E5" s="12" t="s"/>
-      <x:c r="F5" s="12" t="s"/>
-      <x:c r="G5" s="12" t="s"/>
-      <x:c r="H5" s="12" t="s"/>
-      <x:c r="I5" s="12" t="s"/>
-      <x:c r="J5" s="12" t="s"/>
-      <x:c r="K5" s="12" t="s"/>
-      <x:c r="L5" s="12" t="s"/>
-      <x:c r="M5" s="12" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46082</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3569,238 +3567,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="13" t="s">
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="13" t="s">
+      <x:c r="D7" s="14" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="13" t="s">
+      <x:c r="E7" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="s">
+      <x:c r="F7" s="14" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="s">
+      <x:c r="G7" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="s">
+      <x:c r="H7" s="14" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H7" s="13" t="s">
+      <x:c r="I7" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I7" s="13" t="s">
+      <x:c r="J7" s="14" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J7" s="13" t="s">
+      <x:c r="K7" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="s">
+      <x:c r="L7" s="14" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L7" s="13" t="s">
+      <x:c r="M7" s="14" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="M7" s="13" t="s">
-        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="29" t="s">
+      <x:c r="B8" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="29" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
+      <x:c r="E8" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E8" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F8" s="29" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G8" s="29" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H8" s="31">
+      <x:c r="F8" s="30" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H8" s="32">
         <x:v>46106.5066742245</x:v>
       </x:c>
-      <x:c r="I8" s="31">
+      <x:c r="I8" s="32">
         <x:v>46106.5082381134</x:v>
       </x:c>
-      <x:c r="J8" s="30" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="J8" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="33">
+      <x:c r="L8" s="34">
         <x:v>46106.5099302546</x:v>
       </x:c>
-      <x:c r="M8" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M8" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="29" t="s">
+      <x:c r="B9" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C9" s="29" t="s">
+      <x:c r="D9" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D9" s="30" t="s">
+      <x:c r="E9" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F9" s="29" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G9" s="29" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H9" s="31">
+      <x:c r="F9" s="30" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
         <x:v>46105.676846794</x:v>
       </x:c>
-      <x:c r="I9" s="31">
+      <x:c r="I9" s="32">
         <x:v>46106.5084437037</x:v>
       </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
+      <x:c r="J9" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="33">
+      <x:c r="L9" s="34">
         <x:v>46106.5101144792</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="29" t="s">
+      <x:c r="B10" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="s">
+      <x:c r="D10" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="E10" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E10" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F10" s="29" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G10" s="29" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H10" s="31">
+      <x:c r="F10" s="30" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
         <x:v>46105.6741278125</x:v>
       </x:c>
-      <x:c r="I10" s="31">
+      <x:c r="I10" s="32">
         <x:v>46106.5086548727</x:v>
       </x:c>
-      <x:c r="J10" s="30" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
+      <x:c r="J10" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="33">
+      <x:c r="L10" s="34">
         <x:v>46106.5103567593</x:v>
       </x:c>
-      <x:c r="M10" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="29" t="s">
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="29" t="s">
+      <x:c r="D11" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
+      <x:c r="E11" s="30" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E11" s="29" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F11" s="29" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G11" s="29" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="H11" s="31">
+      <x:c r="F11" s="30" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I11" s="31">
+      <x:c r="I11" s="32">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
+      <x:c r="J11" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="33">
+      <x:c r="L11" s="34">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M11" s="29" t="s">
-        <x:v>22</x:v>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="17" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="s"/>
-      <x:c r="D14" s="18" t="s"/>
-      <x:c r="E14" s="19" t="s"/>
-      <x:c r="F14" s="19" t="s"/>
+      <x:c r="B14" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="20" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+      <x:c r="B15" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="21" t="s"/>
-      <x:c r="F15" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
+      <x:c r="B17" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -9,6 +9,7 @@
     <x:sheet name="January 2026" sheetId="7" r:id="rId7"/>
     <x:sheet name="February 2026" sheetId="8" r:id="rId8"/>
     <x:sheet name="March 2026" sheetId="9" r:id="rId9"/>
+    <x:sheet name="April 2026" sheetId="10" r:id="rId10"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -141,6 +142,24 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1085-817</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amateur Radio Operator Certificate (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDWARD LANCE LORILLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sarphil subdivision celica, s, Baungon, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1220-376</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4802,4 +4821,1273 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46118.3222074537</x:v>
+      </x:c>
+      <x:c r="I8" s="16">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K8" s="17" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="L8" s="16">
+        <x:v>46118.3241166898</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -160,6 +160,120 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08037-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1226-211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08039-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1227-973</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AASXXCXC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08041-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1229-879</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASDQWE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08042-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1230-779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08040-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1228-788</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4993,113 +5107,527 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="30" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="30" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="31" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="32">
         <x:v>46118.3222074537</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="32">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="31" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="33" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="34">
         <x:v>46118.3241166898</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H9" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J9" s="31" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="34">
+        <x:v>46118.7577859143</x:v>
+      </x:c>
+      <x:c r="M9" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F10" s="30" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G10" s="30" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H10" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I10" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J10" s="31" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L10" s="34">
+        <x:v>46118.743899213</x:v>
+      </x:c>
+      <x:c r="M10" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="B11" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D11" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F11" s="30" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H11" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L11" s="34">
+        <x:v>46118.4241364815</x:v>
+      </x:c>
+      <x:c r="M11" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>24</x:v>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D12" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F12" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H12" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K12" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L12" s="34">
+        <x:v>46118.3476865394</x:v>
+      </x:c>
+      <x:c r="M12" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
-        <x:v>1</x:v>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D13" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K13" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L13" s="34">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M13" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F14" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K14" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L14" s="34">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M14" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F15" s="30" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="K15" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L15" s="34">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M15" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F16" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H16" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K16" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L16" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M16" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D17" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F17" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K17" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L17" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M17" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D18" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F18" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K18" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L18" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M18" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D19" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F19" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K19" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L19" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M19" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C22" s="19" t="s"/>
+      <x:c r="D22" s="19" t="s"/>
+      <x:c r="E22" s="20" t="s"/>
+      <x:c r="F22" s="20" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="s"/>
+      <x:c r="D23" s="22" t="s"/>
+      <x:c r="E23" s="22" t="s"/>
+      <x:c r="F23" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="s"/>
+      <x:c r="D24" s="25" t="s"/>
+      <x:c r="E24" s="25" t="s"/>
+      <x:c r="F24" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="s"/>
+      <x:c r="D25" s="25" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="24" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="s"/>
+      <x:c r="D26" s="25" t="s"/>
+      <x:c r="E26" s="25" t="s"/>
+      <x:c r="F26" s="26" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C27" s="28" t="s"/>
+      <x:c r="D27" s="28" t="s"/>
+      <x:c r="E27" s="28" t="s"/>
+      <x:c r="F27" s="29" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6067,15 +6595,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B22:F22"/>
+    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -160,6 +160,24 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08044</x:t>
@@ -5164,10 +5182,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>47</x:v>
@@ -5176,7 +5194,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -5202,10 +5220,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>50</x:v>
@@ -5214,7 +5232,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5240,10 +5258,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>53</x:v>
@@ -5252,7 +5270,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5278,10 +5296,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>56</x:v>
@@ -5290,7 +5308,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5298,10 +5316,10 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D13" s="31" t="s">
         <x:v>16</x:v>
@@ -5310,25 +5328,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H13" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H13" s="32">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I13" s="32">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J13" s="31" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="K13" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5336,10 +5354,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="30" t="s">
-        <x:v>62</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="31" t="s">
         <x:v>16</x:v>
@@ -5348,25 +5366,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G14" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5374,10 +5392,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D15" s="31" t="s">
         <x:v>16</x:v>
@@ -5386,25 +5404,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5412,10 +5430,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D16" s="31" t="s">
         <x:v>16</x:v>
@@ -5424,25 +5442,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="H16" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5450,10 +5468,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D17" s="31" t="s">
         <x:v>16</x:v>
@@ -5462,25 +5480,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H17" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="G17" s="30" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H17" s="32">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I17" s="32">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J17" s="31" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5488,10 +5506,10 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>16</x:v>
@@ -5500,25 +5518,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="G18" s="30" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5526,10 +5544,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C19" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D19" s="31" t="s">
         <x:v>16</x:v>
@@ -5544,10 +5562,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>82</x:v>
@@ -5556,80 +5574,154 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="18" t="s">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D20" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F20" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K20" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L20" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M20" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D21" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F21" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="K21" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L21" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M21" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C22" s="19" t="s"/>
-      <x:c r="D22" s="19" t="s"/>
-      <x:c r="E22" s="20" t="s"/>
-      <x:c r="F22" s="20" t="s"/>
+      <x:c r="C24" s="19" t="s"/>
+      <x:c r="D24" s="19" t="s"/>
+      <x:c r="E24" s="20" t="s"/>
+      <x:c r="F24" s="20" t="s"/>
     </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="21" t="s">
+    <x:row r="25" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B25" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C23" s="22" t="s"/>
-      <x:c r="D23" s="22" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="23" t="s">
+      <x:c r="C25" s="22" t="s"/>
+      <x:c r="D25" s="22" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C24" s="25" t="s"/>
-      <x:c r="D24" s="25" t="s"/>
-      <x:c r="E24" s="25" t="s"/>
-      <x:c r="F24" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C25" s="25" t="s"/>
-      <x:c r="D25" s="25" t="s"/>
-      <x:c r="E25" s="25" t="s"/>
-      <x:c r="F25" s="26" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="24" t="s">
-        <x:v>57</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="25" t="s"/>
       <x:c r="D26" s="25" t="s"/>
       <x:c r="E26" s="25" t="s"/>
       <x:c r="F26" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="s"/>
+      <x:c r="D27" s="25" t="s"/>
+      <x:c r="E27" s="25" t="s"/>
+      <x:c r="F27" s="26" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="24" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="s"/>
+      <x:c r="D28" s="25" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="26" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="27" t="s">
+    <x:row r="29" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B29" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C27" s="28" t="s"/>
-      <x:c r="D27" s="28" t="s"/>
-      <x:c r="E27" s="28" t="s"/>
-      <x:c r="F27" s="29" t="n">
-        <x:v>12</x:v>
+      <x:c r="C29" s="28" t="s"/>
+      <x:c r="D29" s="28" t="s"/>
+      <x:c r="E29" s="28" t="s"/>
+      <x:c r="F29" s="29" t="n">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6600,12 +6692,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B24:F24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -160,6 +160,15 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1220-376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08048</x:t>
@@ -5182,10 +5191,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>47</x:v>
@@ -5194,7 +5203,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -5220,10 +5229,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>50</x:v>
@@ -5232,7 +5241,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5258,10 +5267,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>53</x:v>
@@ -5270,7 +5279,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5296,10 +5305,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>56</x:v>
@@ -5308,7 +5317,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5334,10 +5343,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>59</x:v>
@@ -5346,7 +5355,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5372,10 +5381,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>62</x:v>
@@ -5384,7 +5393,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5392,10 +5401,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="31" t="s">
         <x:v>16</x:v>
@@ -5404,25 +5413,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="K15" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5430,10 +5439,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D16" s="31" t="s">
         <x:v>16</x:v>
@@ -5442,25 +5451,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5468,7 +5477,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
         <x:v>71</x:v>
@@ -5486,19 +5495,19 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5506,10 +5515,10 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>16</x:v>
@@ -5518,25 +5527,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="H18" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5544,10 +5553,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C19" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D19" s="31" t="s">
         <x:v>16</x:v>
@@ -5556,25 +5565,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="H19" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="H19" s="32">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I19" s="32">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5582,10 +5591,10 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C20" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D20" s="31" t="s">
         <x:v>16</x:v>
@@ -5594,25 +5603,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="H20" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5620,10 +5629,10 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C21" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D21" s="31" t="s">
         <x:v>16</x:v>
@@ -5632,77 +5641,104 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>88</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="30" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D22" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E22" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F22" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K22" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L22" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M22" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="18" t="s">
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C24" s="19" t="s"/>
-      <x:c r="D24" s="19" t="s"/>
-      <x:c r="E24" s="20" t="s"/>
-      <x:c r="F24" s="20" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B25" s="21" t="s">
+      <x:c r="C25" s="19" t="s"/>
+      <x:c r="D25" s="19" t="s"/>
+      <x:c r="E25" s="20" t="s"/>
+      <x:c r="F25" s="20" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="s"/>
-      <x:c r="D25" s="22" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="23" t="s">
+      <x:c r="C26" s="22" t="s"/>
+      <x:c r="D26" s="22" t="s"/>
+      <x:c r="E26" s="22" t="s"/>
+      <x:c r="F26" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C26" s="25" t="s"/>
-      <x:c r="D26" s="25" t="s"/>
-      <x:c r="E26" s="25" t="s"/>
-      <x:c r="F26" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="25" t="s"/>
       <x:c r="D27" s="25" t="s"/>
       <x:c r="E27" s="25" t="s"/>
       <x:c r="F27" s="26" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
       <x:c r="B28" s="24" t="s">
-        <x:v>63</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="25" t="s"/>
       <x:c r="D28" s="25" t="s"/>
@@ -5711,18 +5747,28 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B29" s="27" t="s">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="24" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="s"/>
+      <x:c r="D29" s="25" t="s"/>
+      <x:c r="E29" s="25" t="s"/>
+      <x:c r="F29" s="26" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B30" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C29" s="28" t="s"/>
-      <x:c r="D29" s="28" t="s"/>
-      <x:c r="E29" s="28" t="s"/>
-      <x:c r="F29" s="29" t="n">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C30" s="28" t="s"/>
+      <x:c r="D30" s="28" t="s"/>
+      <x:c r="E30" s="28" t="s"/>
+      <x:c r="F30" s="29" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6692,12 +6738,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B24:F24"/>
-    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -162,6 +162,126 @@
     <x:t>61-4-2026-1220-376</x:t>
   </x:si>
   <x:si>
+    <x:t>Amateur Radio Station Permit to PURCHASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZXCASD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-ROXIV-08090-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1241-111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
   </x:si>
   <x:si>
@@ -171,60 +291,6 @@
     <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -282,25 +348,28 @@
     <x:t>61-4-2026-1228-788</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08045-26</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
-    <x:t>MPDP-ROXIV-08034-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1223-617</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123431</x:t>
+    <x:t>MPDP-ROXIV-08088-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1239-459</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5173,37 +5242,35 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="s"/>
       <x:c r="E9" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F9" s="30" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G9" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5290592824</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5300361458</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K9" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5304719792</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -5223,25 +5290,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F10" s="30" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="30" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5261,25 +5328,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5299,10 +5366,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G12" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="32">
         <x:v>46118.7562945255</x:v>
@@ -5311,7 +5378,7 @@
         <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
@@ -5337,25 +5404,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G13" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5375,25 +5442,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G14" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5413,25 +5480,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G15" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5439,10 +5506,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D16" s="31" t="s">
         <x:v>16</x:v>
@@ -5457,19 +5524,19 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5477,10 +5544,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D17" s="31" t="s">
         <x:v>16</x:v>
@@ -5489,25 +5556,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="H17" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5515,10 +5582,10 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>16</x:v>
@@ -5527,25 +5594,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="K18" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5553,10 +5620,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D19" s="31" t="s">
         <x:v>16</x:v>
@@ -5565,25 +5632,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5591,10 +5658,10 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D20" s="31" t="s">
         <x:v>16</x:v>
@@ -5603,25 +5670,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5629,10 +5696,10 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D21" s="31" t="s">
         <x:v>16</x:v>
@@ -5641,25 +5708,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5667,10 +5734,10 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D22" s="31" t="s">
         <x:v>16</x:v>
@@ -5679,105 +5746,411 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D23" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E23" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F23" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K23" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L23" s="34">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M23" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D24" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F24" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K24" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L24" s="34">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M24" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C25" s="19" t="s"/>
-      <x:c r="D25" s="19" t="s"/>
-      <x:c r="E25" s="20" t="s"/>
-      <x:c r="F25" s="20" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="s"/>
-      <x:c r="D26" s="22" t="s"/>
-      <x:c r="E26" s="22" t="s"/>
-      <x:c r="F26" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C27" s="25" t="s"/>
-      <x:c r="D27" s="25" t="s"/>
-      <x:c r="E27" s="25" t="s"/>
-      <x:c r="F27" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C28" s="25" t="s"/>
-      <x:c r="D28" s="25" t="s"/>
-      <x:c r="E28" s="25" t="s"/>
-      <x:c r="F28" s="26" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="24" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C29" s="25" t="s"/>
-      <x:c r="D29" s="25" t="s"/>
-      <x:c r="E29" s="25" t="s"/>
-      <x:c r="F29" s="26" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C30" s="28" t="s"/>
-      <x:c r="D30" s="28" t="s"/>
-      <x:c r="E30" s="28" t="s"/>
-      <x:c r="F30" s="29" t="n">
-        <x:v>15</x:v>
+      <x:c r="B25" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D25" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F25" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="K25" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L25" s="34">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M25" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D26" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E26" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F26" s="30" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H26" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K26" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L26" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M26" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D27" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E27" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F27" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K27" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L27" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M27" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D28" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E28" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F28" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="K28" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L28" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M28" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D29" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E29" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F29" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="H29" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K29" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L29" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M29" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D30" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E30" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F30" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H30" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K30" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L30" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M30" s="30" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C33" s="19" t="s"/>
+      <x:c r="D33" s="19" t="s"/>
+      <x:c r="E33" s="20" t="s"/>
+      <x:c r="F33" s="20" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C34" s="22" t="s"/>
+      <x:c r="D34" s="22" t="s"/>
+      <x:c r="E34" s="22" t="s"/>
+      <x:c r="F34" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C35" s="25" t="s"/>
+      <x:c r="D35" s="25" t="s"/>
+      <x:c r="E35" s="25" t="s"/>
+      <x:c r="F35" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="24" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C36" s="25" t="s"/>
+      <x:c r="D36" s="25" t="s"/>
+      <x:c r="E36" s="25" t="s"/>
+      <x:c r="F36" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C37" s="25" t="s"/>
+      <x:c r="D37" s="25" t="s"/>
+      <x:c r="E37" s="25" t="s"/>
+      <x:c r="F37" s="26" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="24" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C38" s="25" t="s"/>
+      <x:c r="D38" s="25" t="s"/>
+      <x:c r="E38" s="25" t="s"/>
+      <x:c r="F38" s="26" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C39" s="28" t="s"/>
+      <x:c r="D39" s="28" t="s"/>
+      <x:c r="E39" s="28" t="s"/>
+      <x:c r="F39" s="29" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -6733,17 +7106,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B25:F25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
-    <x:mergeCell ref="B28:E28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B33:F33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -204,6 +204,15 @@
     <x:t>zxcasdqweq2</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -213,13 +222,19 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08048</x:t>
@@ -231,6 +246,42 @@
     <x:t>123wezxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
   </x:si>
   <x:si>
@@ -240,10 +291,28 @@
     <x:t>zczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
@@ -253,42 +322,6 @@
   </x:si>
   <x:si>
     <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5410,10 +5443,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>61</x:v>
@@ -5422,7 +5455,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5448,10 +5481,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>64</x:v>
@@ -5460,7 +5493,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5486,10 +5519,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>67</x:v>
@@ -5498,7 +5531,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5524,19 +5557,19 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5556,25 +5589,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="H17" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="H17" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I17" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J17" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5600,10 +5633,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>75</x:v>
@@ -5612,7 +5645,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5752,10 +5785,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>87</x:v>
@@ -5764,7 +5797,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5772,10 +5805,10 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D23" s="31" t="s">
         <x:v>16</x:v>
@@ -5784,25 +5817,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H23" s="32">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I23" s="32">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5810,10 +5843,10 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D24" s="31" t="s">
         <x:v>16</x:v>
@@ -5822,25 +5855,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -5848,10 +5881,10 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D25" s="31" t="s">
         <x:v>16</x:v>
@@ -5860,25 +5893,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>99</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5886,10 +5919,10 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D26" s="31" t="s">
         <x:v>16</x:v>
@@ -5898,25 +5931,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -5924,10 +5957,10 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C27" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D27" s="31" t="s">
         <x:v>16</x:v>
@@ -5936,25 +5969,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -5962,10 +5995,10 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C28" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D28" s="31" t="s">
         <x:v>16</x:v>
@@ -5974,25 +6007,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>110</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6000,7 +6033,7 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s">
         <x:v>107</x:v>
@@ -6012,25 +6045,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6038,10 +6071,10 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C30" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D30" s="31" t="s">
         <x:v>16</x:v>
@@ -6050,111 +6083,259 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="H30" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="H30" s="32">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I30" s="32">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D31" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E31" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F31" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H31" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K31" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L31" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M31" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D32" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E32" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F32" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H32" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I32" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="K32" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L32" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M32" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="18" t="s">
+      <x:c r="B33" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D33" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E33" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F33" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H33" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I33" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J33" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K33" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L33" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M33" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D34" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E34" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F34" s="30" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H34" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K34" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L34" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M34" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C33" s="19" t="s"/>
-      <x:c r="D33" s="19" t="s"/>
-      <x:c r="E33" s="20" t="s"/>
-      <x:c r="F33" s="20" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="21" t="s">
+      <x:c r="C37" s="19" t="s"/>
+      <x:c r="D37" s="19" t="s"/>
+      <x:c r="E37" s="20" t="s"/>
+      <x:c r="F37" s="20" t="s"/>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B38" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C34" s="22" t="s"/>
-      <x:c r="D34" s="22" t="s"/>
-      <x:c r="E34" s="22" t="s"/>
-      <x:c r="F34" s="23" t="s">
+      <x:c r="C38" s="22" t="s"/>
+      <x:c r="D38" s="22" t="s"/>
+      <x:c r="E38" s="22" t="s"/>
+      <x:c r="F38" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="24" t="s">
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C35" s="25" t="s"/>
-      <x:c r="D35" s="25" t="s"/>
-      <x:c r="E35" s="25" t="s"/>
-      <x:c r="F35" s="26" t="n">
+      <x:c r="C39" s="25" t="s"/>
+      <x:c r="D39" s="25" t="s"/>
+      <x:c r="E39" s="25" t="s"/>
+      <x:c r="F39" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="24" t="s">
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C36" s="25" t="s"/>
-      <x:c r="D36" s="25" t="s"/>
-      <x:c r="E36" s="25" t="s"/>
-      <x:c r="F36" s="26" t="n">
+      <x:c r="C40" s="25" t="s"/>
+      <x:c r="D40" s="25" t="s"/>
+      <x:c r="E40" s="25" t="s"/>
+      <x:c r="F40" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="24" t="s">
+    <x:row r="41" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B41" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C37" s="25" t="s"/>
-      <x:c r="D37" s="25" t="s"/>
-      <x:c r="E37" s="25" t="s"/>
-      <x:c r="F37" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B38" s="24" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C38" s="25" t="s"/>
-      <x:c r="D38" s="25" t="s"/>
-      <x:c r="E38" s="25" t="s"/>
-      <x:c r="F38" s="26" t="n">
+      <x:c r="C41" s="25" t="s"/>
+      <x:c r="D41" s="25" t="s"/>
+      <x:c r="E41" s="25" t="s"/>
+      <x:c r="F41" s="26" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B42" s="24" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C42" s="25" t="s"/>
+      <x:c r="D42" s="25" t="s"/>
+      <x:c r="E42" s="25" t="s"/>
+      <x:c r="F42" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="27" t="s">
+    <x:row r="43" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B43" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C39" s="28" t="s"/>
-      <x:c r="D39" s="28" t="s"/>
-      <x:c r="E39" s="28" t="s"/>
-      <x:c r="F39" s="29" t="n">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C43" s="28" t="s"/>
+      <x:c r="D43" s="28" t="s"/>
+      <x:c r="E43" s="28" t="s"/>
+      <x:c r="F43" s="29" t="n">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7111,13 +7292,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B33:F33"/>
-    <x:mergeCell ref="B34:E34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
-    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B37:F37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B42:E42"/>
+    <x:mergeCell ref="B43:E43"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -213,6 +213,15 @@
     <x:t>123qwe123qwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -222,6 +231,21 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
   </x:si>
   <x:si>
@@ -231,19 +255,46 @@
     <x:t>asdqwe123</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
@@ -255,22 +306,13 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
@@ -282,46 +324,16 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -384,6 +396,12 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08034-26</x:t>
   </x:si>
   <x:si>
@@ -391,12 +409,6 @@
   </x:si>
   <x:si>
     <x:t>123431</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08045-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5481,10 +5493,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>64</x:v>
@@ -5493,7 +5505,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5519,10 +5531,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>67</x:v>
@@ -5531,7 +5543,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5595,10 +5607,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>72</x:v>
@@ -5607,7 +5619,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5633,10 +5645,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>75</x:v>
@@ -5645,7 +5657,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5671,10 +5683,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>78</x:v>
@@ -5683,7 +5695,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5709,10 +5721,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>81</x:v>
@@ -5721,7 +5733,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5747,10 +5759,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>84</x:v>
@@ -5759,7 +5771,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5785,10 +5797,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>87</x:v>
@@ -5797,7 +5809,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5823,19 +5835,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5855,25 +5867,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="H24" s="32">
+        <x:v>46119.7297941435</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46119.731450544</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -5893,25 +5905,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
+      <x:c r="H25" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="H25" s="32">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I25" s="32">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J25" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5937,10 +5949,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
         <x:v>98</x:v>
@@ -5949,7 +5961,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -5957,10 +5969,10 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D27" s="31" t="s">
         <x:v>16</x:v>
@@ -5969,25 +5981,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>103</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -5995,10 +6007,10 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="31" t="s">
         <x:v>16</x:v>
@@ -6007,25 +6019,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6033,10 +6045,10 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D29" s="31" t="s">
         <x:v>16</x:v>
@@ -6045,25 +6057,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6071,10 +6083,10 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C30" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D30" s="31" t="s">
         <x:v>16</x:v>
@@ -6083,25 +6095,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6109,10 +6121,10 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C31" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D31" s="31" t="s">
         <x:v>16</x:v>
@@ -6121,25 +6133,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6147,10 +6159,10 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C32" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D32" s="31" t="s">
         <x:v>16</x:v>
@@ -6159,25 +6171,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7372774306</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7373236806</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6185,10 +6197,10 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C33" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D33" s="31" t="s">
         <x:v>16</x:v>
@@ -6197,25 +6209,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6223,10 +6235,10 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C34" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D34" s="31" t="s">
         <x:v>16</x:v>
@@ -6235,109 +6247,183 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="G34" s="30" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="18" t="s">
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B35" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D35" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E35" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F35" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H35" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I35" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="K35" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L35" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M35" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D36" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E36" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F36" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H36" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K36" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L36" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M36" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B39" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C37" s="19" t="s"/>
-      <x:c r="D37" s="19" t="s"/>
-      <x:c r="E37" s="20" t="s"/>
-      <x:c r="F37" s="20" t="s"/>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B38" s="21" t="s">
+      <x:c r="C39" s="19" t="s"/>
+      <x:c r="D39" s="19" t="s"/>
+      <x:c r="E39" s="20" t="s"/>
+      <x:c r="F39" s="20" t="s"/>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B40" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C38" s="22" t="s"/>
-      <x:c r="D38" s="22" t="s"/>
-      <x:c r="E38" s="22" t="s"/>
-      <x:c r="F38" s="23" t="s">
+      <x:c r="C40" s="22" t="s"/>
+      <x:c r="D40" s="22" t="s"/>
+      <x:c r="E40" s="22" t="s"/>
+      <x:c r="F40" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B39" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C39" s="25" t="s"/>
-      <x:c r="D39" s="25" t="s"/>
-      <x:c r="E39" s="25" t="s"/>
-      <x:c r="F39" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B40" s="24" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C40" s="25" t="s"/>
-      <x:c r="D40" s="25" t="s"/>
-      <x:c r="E40" s="25" t="s"/>
-      <x:c r="F40" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="18" customHeight="1">
       <x:c r="B41" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C41" s="25" t="s"/>
       <x:c r="D41" s="25" t="s"/>
       <x:c r="E41" s="25" t="s"/>
       <x:c r="F41" s="26" t="n">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="18" customHeight="1">
       <x:c r="B42" s="24" t="s">
-        <x:v>99</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C42" s="25" t="s"/>
       <x:c r="D42" s="25" t="s"/>
       <x:c r="E42" s="25" t="s"/>
       <x:c r="F42" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B43" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="s"/>
+      <x:c r="D43" s="25" t="s"/>
+      <x:c r="E43" s="25" t="s"/>
+      <x:c r="F43" s="26" t="n">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B44" s="24" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C44" s="25" t="s"/>
+      <x:c r="D44" s="25" t="s"/>
+      <x:c r="E44" s="25" t="s"/>
+      <x:c r="F44" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B43" s="27" t="s">
+    <x:row r="45" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B45" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C43" s="28" t="s"/>
-      <x:c r="D43" s="28" t="s"/>
-      <x:c r="E43" s="28" t="s"/>
-      <x:c r="F43" s="29" t="n">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C45" s="28" t="s"/>
+      <x:c r="D45" s="28" t="s"/>
+      <x:c r="E45" s="28" t="s"/>
+      <x:c r="F45" s="29" t="n">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7292,13 +7378,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B37:F37"/>
-    <x:mergeCell ref="B38:E38"/>
-    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B39:F39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
     <x:mergeCell ref="B42:E42"/>
     <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B44:E44"/>
+    <x:mergeCell ref="B45:E45"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -222,6 +222,21 @@
     <x:t>123wezxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -231,12 +246,6 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -246,13 +255,46 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08092</x:t>
@@ -264,6 +306,12 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
@@ -273,13 +321,10 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08097</x:t>
@@ -297,43 +342,25 @@
     <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5531,10 +5558,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>67</x:v>
@@ -5543,7 +5570,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5607,10 +5634,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>72</x:v>
@@ -5619,7 +5646,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5645,10 +5672,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>75</x:v>
@@ -5657,7 +5684,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5683,10 +5710,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>78</x:v>
@@ -5695,7 +5722,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5721,10 +5748,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>81</x:v>
@@ -5733,7 +5760,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5759,10 +5786,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>84</x:v>
@@ -5771,7 +5798,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5797,10 +5824,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>87</x:v>
@@ -5809,7 +5836,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5835,19 +5862,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5873,10 +5900,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>92</x:v>
@@ -5885,7 +5912,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -5911,19 +5938,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5943,25 +5970,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="H26" s="32">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -5981,25 +6008,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6019,25 +6046,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="H28" s="32">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6045,10 +6072,10 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D29" s="31" t="s">
         <x:v>16</x:v>
@@ -6057,25 +6084,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>107</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6083,10 +6110,10 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D30" s="31" t="s">
         <x:v>16</x:v>
@@ -6095,25 +6122,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6121,10 +6148,10 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D31" s="31" t="s">
         <x:v>16</x:v>
@@ -6133,25 +6160,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6159,10 +6186,10 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D32" s="31" t="s">
         <x:v>16</x:v>
@@ -6171,25 +6198,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>118</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6197,10 +6224,10 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C33" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D33" s="31" t="s">
         <x:v>16</x:v>
@@ -6209,25 +6236,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6235,10 +6262,10 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C34" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D34" s="31" t="s">
         <x:v>16</x:v>
@@ -6247,16 +6274,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
         <x:v>30</x:v>
@@ -6265,7 +6292,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6273,10 +6300,10 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C35" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D35" s="31" t="s">
         <x:v>16</x:v>
@@ -6285,25 +6312,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6311,10 +6338,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C36" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D36" s="31" t="s">
         <x:v>16</x:v>
@@ -6323,111 +6350,259 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7372774306</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7373236806</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B37" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D37" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E37" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F37" s="30" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H37" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I37" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J37" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K37" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L37" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M37" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B38" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C38" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D38" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E38" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F38" s="30" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H38" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K38" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L38" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M38" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="18" t="s">
+      <x:c r="B39" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C39" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D39" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E39" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F39" s="30" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G39" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H39" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I39" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K39" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L39" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M39" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B40" s="30" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C40" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D40" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E40" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F40" s="30" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H40" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I40" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K40" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L40" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M40" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C39" s="19" t="s"/>
-      <x:c r="D39" s="19" t="s"/>
-      <x:c r="E39" s="20" t="s"/>
-      <x:c r="F39" s="20" t="s"/>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B40" s="21" t="s">
+      <x:c r="C43" s="19" t="s"/>
+      <x:c r="D43" s="19" t="s"/>
+      <x:c r="E43" s="20" t="s"/>
+      <x:c r="F43" s="20" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B44" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C40" s="22" t="s"/>
-      <x:c r="D40" s="22" t="s"/>
-      <x:c r="E40" s="22" t="s"/>
-      <x:c r="F40" s="23" t="s">
+      <x:c r="C44" s="22" t="s"/>
+      <x:c r="D44" s="22" t="s"/>
+      <x:c r="E44" s="22" t="s"/>
+      <x:c r="F44" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B41" s="24" t="s">
+    <x:row r="45" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B45" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C41" s="25" t="s"/>
-      <x:c r="D41" s="25" t="s"/>
-      <x:c r="E41" s="25" t="s"/>
-      <x:c r="F41" s="26" t="n">
+      <x:c r="C45" s="25" t="s"/>
+      <x:c r="D45" s="25" t="s"/>
+      <x:c r="E45" s="25" t="s"/>
+      <x:c r="F45" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B42" s="24" t="s">
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C42" s="25" t="s"/>
-      <x:c r="D42" s="25" t="s"/>
-      <x:c r="E42" s="25" t="s"/>
-      <x:c r="F42" s="26" t="n">
+      <x:c r="C46" s="25" t="s"/>
+      <x:c r="D46" s="25" t="s"/>
+      <x:c r="E46" s="25" t="s"/>
+      <x:c r="F46" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B43" s="24" t="s">
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C43" s="25" t="s"/>
-      <x:c r="D43" s="25" t="s"/>
-      <x:c r="E43" s="25" t="s"/>
-      <x:c r="F43" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B44" s="24" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="C44" s="25" t="s"/>
-      <x:c r="D44" s="25" t="s"/>
-      <x:c r="E44" s="25" t="s"/>
-      <x:c r="F44" s="26" t="n">
+      <x:c r="C47" s="25" t="s"/>
+      <x:c r="D47" s="25" t="s"/>
+      <x:c r="E47" s="25" t="s"/>
+      <x:c r="F47" s="26" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="24" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C48" s="25" t="s"/>
+      <x:c r="D48" s="25" t="s"/>
+      <x:c r="E48" s="25" t="s"/>
+      <x:c r="F48" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B45" s="27" t="s">
+    <x:row r="49" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B49" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C45" s="28" t="s"/>
-      <x:c r="D45" s="28" t="s"/>
-      <x:c r="E45" s="28" t="s"/>
-      <x:c r="F45" s="29" t="n">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C49" s="28" t="s"/>
+      <x:c r="D49" s="28" t="s"/>
+      <x:c r="E49" s="28" t="s"/>
+      <x:c r="F49" s="29" t="n">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
     <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7378,13 +7553,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B39:F39"/>
-    <x:mergeCell ref="B40:E40"/>
-    <x:mergeCell ref="B41:E41"/>
-    <x:mergeCell ref="B42:E42"/>
-    <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B43:F43"/>
     <x:mergeCell ref="B44:E44"/>
     <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B47:E47"/>
+    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B49:E49"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -246,6 +246,33 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -255,13 +282,19 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08120</x:t>
@@ -273,13 +306,28 @@
     <x:t>test123</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08118</x:t>
@@ -288,22 +336,31 @@
     <x:t>61-4-2026-1256-775</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
@@ -312,55 +369,13 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5672,10 +5687,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>75</x:v>
@@ -5684,7 +5699,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5710,10 +5725,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>78</x:v>
@@ -5722,7 +5737,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5748,10 +5763,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>81</x:v>
@@ -5760,7 +5775,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5786,10 +5801,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>84</x:v>
@@ -5798,7 +5813,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5824,10 +5839,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>87</x:v>
@@ -5836,7 +5851,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5862,19 +5877,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5900,10 +5915,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>92</x:v>
@@ -5912,7 +5927,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -5938,19 +5953,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5970,25 +5985,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6008,10 +6023,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H27" s="32">
         <x:v>46119.8029380671</x:v>
@@ -6046,25 +6061,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6090,19 +6105,19 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6128,19 +6143,19 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6166,10 +6181,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
         <x:v>109</x:v>
@@ -6178,7 +6193,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6204,19 +6219,19 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6224,10 +6239,10 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D33" s="31" t="s">
         <x:v>16</x:v>
@@ -6236,25 +6251,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>116</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6262,10 +6277,10 @@
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D34" s="31" t="s">
         <x:v>16</x:v>
@@ -6274,25 +6289,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6300,10 +6315,10 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C35" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D35" s="31" t="s">
         <x:v>16</x:v>
@@ -6312,25 +6327,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H35" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I35" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="G35" s="30" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="H35" s="32">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I35" s="32">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J35" s="31" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6338,10 +6353,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C36" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D36" s="31" t="s">
         <x:v>16</x:v>
@@ -6350,25 +6365,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>127</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6376,10 +6391,10 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C37" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D37" s="31" t="s">
         <x:v>16</x:v>
@@ -6388,25 +6403,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6414,10 +6429,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C38" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D38" s="31" t="s">
         <x:v>16</x:v>
@@ -6426,25 +6441,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="H38" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="G38" s="30" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H38" s="32">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I38" s="32">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6452,10 +6467,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C39" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D39" s="31" t="s">
         <x:v>16</x:v>
@@ -6470,19 +6485,19 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>136</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6490,10 +6505,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C40" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D40" s="31" t="s">
         <x:v>16</x:v>
@@ -6508,103 +6523,177 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="18" t="s">
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B41" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C41" s="30" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D41" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E41" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F41" s="30" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G41" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H41" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I41" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="K41" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L41" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M41" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B42" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C42" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D42" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E42" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F42" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G42" s="30" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H42" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I42" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K42" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L42" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M42" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C43" s="19" t="s"/>
-      <x:c r="D43" s="19" t="s"/>
-      <x:c r="E43" s="20" t="s"/>
-      <x:c r="F43" s="20" t="s"/>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B44" s="21" t="s">
+      <x:c r="C45" s="19" t="s"/>
+      <x:c r="D45" s="19" t="s"/>
+      <x:c r="E45" s="20" t="s"/>
+      <x:c r="F45" s="20" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C44" s="22" t="s"/>
-      <x:c r="D44" s="22" t="s"/>
-      <x:c r="E44" s="22" t="s"/>
-      <x:c r="F44" s="23" t="s">
+      <x:c r="C46" s="22" t="s"/>
+      <x:c r="D46" s="22" t="s"/>
+      <x:c r="E46" s="22" t="s"/>
+      <x:c r="F46" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C45" s="25" t="s"/>
-      <x:c r="D45" s="25" t="s"/>
-      <x:c r="E45" s="25" t="s"/>
-      <x:c r="F45" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="24" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C46" s="25" t="s"/>
-      <x:c r="D46" s="25" t="s"/>
-      <x:c r="E46" s="25" t="s"/>
-      <x:c r="F46" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C47" s="25" t="s"/>
       <x:c r="D47" s="25" t="s"/>
       <x:c r="E47" s="25" t="s"/>
       <x:c r="F47" s="26" t="n">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="24" t="s">
-        <x:v>112</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C48" s="25" t="s"/>
       <x:c r="D48" s="25" t="s"/>
       <x:c r="E48" s="25" t="s"/>
       <x:c r="F48" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C49" s="25" t="s"/>
+      <x:c r="D49" s="25" t="s"/>
+      <x:c r="E49" s="25" t="s"/>
+      <x:c r="F49" s="26" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="24" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C50" s="25" t="s"/>
+      <x:c r="D50" s="25" t="s"/>
+      <x:c r="E50" s="25" t="s"/>
+      <x:c r="F50" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B49" s="27" t="s">
+    <x:row r="51" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B51" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C49" s="28" t="s"/>
-      <x:c r="D49" s="28" t="s"/>
-      <x:c r="E49" s="28" t="s"/>
-      <x:c r="F49" s="29" t="n">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C51" s="28" t="s"/>
+      <x:c r="D51" s="28" t="s"/>
+      <x:c r="E51" s="28" t="s"/>
+      <x:c r="F51" s="29" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
     <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7553,13 +7642,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B43:F43"/>
-    <x:mergeCell ref="B44:E44"/>
-    <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B45:F45"/>
     <x:mergeCell ref="B46:E46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
+    <x:mergeCell ref="B50:E50"/>
+    <x:mergeCell ref="B51:E51"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,6 +177,12 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08033</x:t>
   </x:si>
   <x:si>
@@ -237,6 +243,15 @@
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -264,6 +279,42 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
   </x:si>
   <x:si>
@@ -273,13 +324,43 @@
     <x:t>zcx</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
@@ -291,91 +372,16 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5383,19 +5389,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5415,25 +5421,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="H11" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="H11" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I11" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J11" s="31" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5453,25 +5459,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="H12" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I12" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J12" s="31" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5491,25 +5497,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="H13" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="H13" s="32">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I13" s="32">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J13" s="31" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5529,25 +5535,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="H14" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="H14" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I14" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J14" s="31" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5567,25 +5573,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5605,25 +5611,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5649,19 +5655,19 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5681,25 +5687,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="H18" s="32">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5719,25 +5725,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="H19" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="H19" s="32">
-        <x:v>46119.542956794</x:v>
-      </x:c>
-      <x:c r="I19" s="32">
-        <x:v>46119.5456356481</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5757,25 +5763,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="H20" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5795,25 +5801,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="H21" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5833,25 +5839,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5871,25 +5877,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="H23" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="H23" s="32">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I23" s="32">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5953,10 +5959,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
         <x:v>95</x:v>
@@ -5965,7 +5971,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5991,19 +5997,19 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6067,19 +6073,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>98</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6105,19 +6111,19 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6149,7 +6155,7 @@
         <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
@@ -6257,19 +6263,19 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6289,25 +6295,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="H34" s="32">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="G34" s="30" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="H34" s="32">
-        <x:v>46121.0999663542</x:v>
-      </x:c>
-      <x:c r="I34" s="32">
-        <x:v>46121.1007466204</x:v>
-      </x:c>
-      <x:c r="J34" s="31" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6315,10 +6321,10 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D35" s="31" t="s">
         <x:v>16</x:v>
@@ -6327,25 +6333,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>121</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6353,10 +6359,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C36" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D36" s="31" t="s">
         <x:v>16</x:v>
@@ -6365,25 +6371,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H36" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="G36" s="30" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H36" s="32">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I36" s="32">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J36" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6391,10 +6397,10 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C37" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D37" s="31" t="s">
         <x:v>16</x:v>
@@ -6403,25 +6409,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G37" s="30" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G37" s="30" t="s">
-        <x:v>127</x:v>
-      </x:c>
       <x:c r="H37" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>128</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6429,10 +6435,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C38" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D38" s="31" t="s">
         <x:v>16</x:v>
@@ -6441,25 +6447,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H38" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="G38" s="30" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H38" s="32">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I38" s="32">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6467,10 +6473,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C39" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D39" s="31" t="s">
         <x:v>16</x:v>
@@ -6479,25 +6485,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G39" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H39" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I39" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J39" s="31" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="G39" s="30" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H39" s="32">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I39" s="32">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J39" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6505,10 +6511,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C40" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D40" s="31" t="s">
         <x:v>16</x:v>
@@ -6517,25 +6523,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G40" s="30" t="s">
-        <x:v>138</x:v>
-      </x:c>
       <x:c r="H40" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6543,10 +6549,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C41" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D41" s="31" t="s">
         <x:v>16</x:v>
@@ -6561,19 +6567,19 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>141</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6581,10 +6587,10 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C42" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D42" s="31" t="s">
         <x:v>16</x:v>
@@ -6593,66 +6599,93 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G42" s="30" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="G42" s="30" t="s">
+      <x:c r="H42" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I42" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J42" s="31" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="H42" s="32">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I42" s="32">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J42" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C43" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D43" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E43" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F43" s="30" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G43" s="30" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="H43" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I43" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J43" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K43" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L43" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M43" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="18" t="s">
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C45" s="19" t="s"/>
-      <x:c r="D45" s="19" t="s"/>
-      <x:c r="E45" s="20" t="s"/>
-      <x:c r="F45" s="20" t="s"/>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="21" t="s">
+      <x:c r="C46" s="19" t="s"/>
+      <x:c r="D46" s="19" t="s"/>
+      <x:c r="E46" s="20" t="s"/>
+      <x:c r="F46" s="20" t="s"/>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B47" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C46" s="22" t="s"/>
-      <x:c r="D46" s="22" t="s"/>
-      <x:c r="E46" s="22" t="s"/>
-      <x:c r="F46" s="23" t="s">
+      <x:c r="C47" s="22" t="s"/>
+      <x:c r="D47" s="22" t="s"/>
+      <x:c r="E47" s="22" t="s"/>
+      <x:c r="F47" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C47" s="25" t="s"/>
-      <x:c r="D47" s="25" t="s"/>
-      <x:c r="E47" s="25" t="s"/>
-      <x:c r="F47" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="24" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C48" s="25" t="s"/>
       <x:c r="D48" s="25" t="s"/>
@@ -6663,38 +6696,48 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C49" s="25" t="s"/>
       <x:c r="D49" s="25" t="s"/>
       <x:c r="E49" s="25" t="s"/>
       <x:c r="F49" s="26" t="n">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="24" t="s">
-        <x:v>117</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="25" t="s"/>
       <x:c r="D50" s="25" t="s"/>
       <x:c r="E50" s="25" t="s"/>
       <x:c r="F50" s="26" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="24" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C51" s="25" t="s"/>
+      <x:c r="D51" s="25" t="s"/>
+      <x:c r="E51" s="25" t="s"/>
+      <x:c r="F51" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B51" s="27" t="s">
+    <x:row r="52" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B52" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C51" s="28" t="s"/>
-      <x:c r="D51" s="28" t="s"/>
-      <x:c r="E51" s="28" t="s"/>
-      <x:c r="F51" s="29" t="n">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C52" s="28" t="s"/>
+      <x:c r="D52" s="28" t="s"/>
+      <x:c r="E52" s="28" t="s"/>
+      <x:c r="F52" s="29" t="n">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
     <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7642,13 +7685,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B45:F45"/>
-    <x:mergeCell ref="B46:E46"/>
+    <x:mergeCell ref="B46:F46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
+    <x:mergeCell ref="B52:E52"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,126 +177,165 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08120</x:t>
   </x:si>
   <x:si>
@@ -315,13 +354,13 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -336,54 +375,33 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -444,19 +462,19 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08045-26</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1233-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08034-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1223-617</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123431</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5389,19 +5407,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5421,25 +5439,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5459,25 +5477,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G12" s="30" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5497,25 +5515,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G13" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5535,25 +5553,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G14" s="30" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5573,25 +5591,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G15" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5611,25 +5629,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G16" s="30" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>69</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5655,19 +5673,19 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5687,25 +5705,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5725,25 +5743,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5763,25 +5781,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5801,25 +5819,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5839,25 +5857,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5877,25 +5895,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>89</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5921,10 +5939,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>92</x:v>
@@ -5933,7 +5951,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -5959,19 +5977,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -5991,25 +6009,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="H26" s="32">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46119.5434206134</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46119.545474919</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6029,25 +6047,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
+      <x:c r="H27" s="32">
+        <x:v>46119.7254171991</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46119.7262936574</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6073,19 +6091,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6111,19 +6129,19 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6143,25 +6161,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6181,25 +6199,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6219,16 +6237,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
         <x:v>49</x:v>
@@ -6237,7 +6255,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6257,25 +6275,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6295,10 +6313,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H34" s="32">
         <x:v>46119.8017436343</x:v>
@@ -6307,7 +6325,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
@@ -6333,25 +6351,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6359,10 +6377,10 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D36" s="31" t="s">
         <x:v>16</x:v>
@@ -6371,25 +6389,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="H36" s="32">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H36" s="32">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I36" s="32">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J36" s="31" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="K36" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6397,10 +6415,10 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D37" s="31" t="s">
         <x:v>16</x:v>
@@ -6409,25 +6427,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6435,10 +6453,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C38" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D38" s="31" t="s">
         <x:v>16</x:v>
@@ -6447,25 +6465,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G38" s="30" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="H38" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I38" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J38" s="31" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="H38" s="32">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I38" s="32">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J38" s="31" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6473,10 +6491,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C39" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D39" s="31" t="s">
         <x:v>16</x:v>
@@ -6485,25 +6503,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G39" s="30" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="G39" s="30" t="s">
-        <x:v>133</x:v>
-      </x:c>
       <x:c r="H39" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>134</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6511,10 +6529,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C40" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D40" s="31" t="s">
         <x:v>16</x:v>
@@ -6523,25 +6541,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H40" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I40" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J40" s="31" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="G40" s="30" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H40" s="32">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I40" s="32">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J40" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6549,10 +6567,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C41" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D41" s="31" t="s">
         <x:v>16</x:v>
@@ -6561,25 +6579,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G41" s="30" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="G41" s="30" t="s">
+      <x:c r="H41" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I41" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="H41" s="32">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I41" s="32">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J41" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6587,10 +6605,10 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C42" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D42" s="31" t="s">
         <x:v>16</x:v>
@@ -6599,25 +6617,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>143</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6625,10 +6643,10 @@
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
       <x:c r="B43" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C43" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D43" s="31" t="s">
         <x:v>16</x:v>
@@ -6637,109 +6655,183 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.439490081</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="18" t="s">
+    <x:row r="44" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B44" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C44" s="30" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D44" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E44" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F44" s="30" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G44" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H44" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I44" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J44" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K44" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L44" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M44" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="30" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C45" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D45" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E45" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F45" s="30" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G45" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H45" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I45" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J45" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K45" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L45" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M45" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B48" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C46" s="19" t="s"/>
-      <x:c r="D46" s="19" t="s"/>
-      <x:c r="E46" s="20" t="s"/>
-      <x:c r="F46" s="20" t="s"/>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B47" s="21" t="s">
+      <x:c r="C48" s="19" t="s"/>
+      <x:c r="D48" s="19" t="s"/>
+      <x:c r="E48" s="20" t="s"/>
+      <x:c r="F48" s="20" t="s"/>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B49" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C47" s="22" t="s"/>
-      <x:c r="D47" s="22" t="s"/>
-      <x:c r="E47" s="22" t="s"/>
-      <x:c r="F47" s="23" t="s">
+      <x:c r="C49" s="22" t="s"/>
+      <x:c r="D49" s="22" t="s"/>
+      <x:c r="E49" s="22" t="s"/>
+      <x:c r="F49" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C48" s="25" t="s"/>
-      <x:c r="D48" s="25" t="s"/>
-      <x:c r="E48" s="25" t="s"/>
-      <x:c r="F48" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="24" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C49" s="25" t="s"/>
-      <x:c r="D49" s="25" t="s"/>
-      <x:c r="E49" s="25" t="s"/>
-      <x:c r="F49" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C50" s="25" t="s"/>
       <x:c r="D50" s="25" t="s"/>
       <x:c r="E50" s="25" t="s"/>
       <x:c r="F50" s="26" t="n">
-        <x:v>26</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="24" t="s">
-        <x:v>119</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C51" s="25" t="s"/>
       <x:c r="D51" s="25" t="s"/>
       <x:c r="E51" s="25" t="s"/>
       <x:c r="F51" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="s"/>
+      <x:c r="D52" s="25" t="s"/>
+      <x:c r="E52" s="25" t="s"/>
+      <x:c r="F52" s="26" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B53" s="24" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C53" s="25" t="s"/>
+      <x:c r="D53" s="25" t="s"/>
+      <x:c r="E53" s="25" t="s"/>
+      <x:c r="F53" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B52" s="27" t="s">
+    <x:row r="54" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B54" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C52" s="28" t="s"/>
-      <x:c r="D52" s="28" t="s"/>
-      <x:c r="E52" s="28" t="s"/>
-      <x:c r="F52" s="29" t="n">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C54" s="28" t="s"/>
+      <x:c r="D54" s="28" t="s"/>
+      <x:c r="E54" s="28" t="s"/>
+      <x:c r="F54" s="29" t="n">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7685,13 +7777,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B46:F46"/>
-    <x:mergeCell ref="B47:E47"/>
-    <x:mergeCell ref="B48:E48"/>
+    <x:mergeCell ref="B48:F48"/>
     <x:mergeCell ref="B49:E49"/>
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
+    <x:mergeCell ref="B54:E54"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,6 +177,111 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08033</x:t>
   </x:si>
   <x:si>
@@ -186,91 +291,19 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08087</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1238-244</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
@@ -282,19 +315,61 @@
     <x:t>zczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
@@ -306,100 +381,73 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5407,10 +5455,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>52</x:v>
@@ -5419,7 +5467,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5445,10 +5493,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>55</x:v>
@@ -5457,7 +5505,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5483,10 +5531,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>58</x:v>
@@ -5495,7 +5543,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5521,10 +5569,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>61</x:v>
@@ -5533,7 +5581,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5559,10 +5607,10 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>64</x:v>
@@ -5571,7 +5619,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5597,19 +5645,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>67</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5629,25 +5677,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5673,10 +5721,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>72</x:v>
@@ -5685,7 +5733,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5711,10 +5759,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>75</x:v>
@@ -5723,7 +5771,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5749,10 +5797,10 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>78</x:v>
@@ -5761,7 +5809,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5787,10 +5835,10 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
         <x:v>81</x:v>
@@ -5799,7 +5847,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5825,10 +5873,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
         <x:v>84</x:v>
@@ -5837,7 +5885,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5863,10 +5911,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>87</x:v>
@@ -5875,7 +5923,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5901,19 +5949,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5939,10 +5987,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
         <x:v>92</x:v>
@@ -5951,7 +5999,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -5977,19 +6025,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6009,25 +6057,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>97</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6053,10 +6101,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
         <x:v>100</x:v>
@@ -6065,7 +6113,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6091,19 +6139,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6129,10 +6177,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
         <x:v>105</x:v>
@@ -6141,7 +6189,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6167,10 +6215,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
         <x:v>108</x:v>
@@ -6179,7 +6227,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6205,10 +6253,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
         <x:v>111</x:v>
@@ -6217,7 +6265,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6243,19 +6291,19 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6275,25 +6323,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6313,25 +6361,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>100</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6351,25 +6399,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>108</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6389,25 +6437,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>122</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6427,25 +6475,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>108</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6453,10 +6501,10 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D38" s="31" t="s">
         <x:v>16</x:v>
@@ -6465,25 +6513,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6491,10 +6539,10 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D39" s="31" t="s">
         <x:v>16</x:v>
@@ -6509,19 +6557,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6529,10 +6577,10 @@
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D40" s="31" t="s">
         <x:v>16</x:v>
@@ -6541,25 +6589,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G40" s="30" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G40" s="30" t="s">
-        <x:v>135</x:v>
-      </x:c>
       <x:c r="H40" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>136</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6567,10 +6615,10 @@
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D41" s="31" t="s">
         <x:v>16</x:v>
@@ -6579,25 +6627,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>140</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6605,10 +6653,10 @@
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D42" s="31" t="s">
         <x:v>16</x:v>
@@ -6617,25 +6665,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6643,10 +6691,10 @@
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
       <x:c r="B43" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D43" s="31" t="s">
         <x:v>16</x:v>
@@ -6655,25 +6703,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>147</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -6681,10 +6729,10 @@
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C44" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D44" s="31" t="s">
         <x:v>16</x:v>
@@ -6693,25 +6741,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -6719,10 +6767,10 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
       <x:c r="B45" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C45" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D45" s="31" t="s">
         <x:v>16</x:v>
@@ -6731,113 +6779,335 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B46" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C46" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D46" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E46" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F46" s="30" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G46" s="30" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H46" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I46" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J46" s="31" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="K46" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L46" s="34">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M46" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B47" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D47" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E47" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F47" s="30" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G47" s="30" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H47" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I47" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J47" s="31" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="K47" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L47" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M47" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="18" t="s">
+      <x:c r="B48" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D48" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E48" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F48" s="30" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G48" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="H48" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I48" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K48" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L48" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M48" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B49" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D49" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E49" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F49" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G49" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H49" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I49" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K49" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L49" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M49" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B50" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D50" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E50" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F50" s="30" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="G50" s="30" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="H50" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I50" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K50" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L50" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M50" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B51" s="30" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D51" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E51" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F51" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="G51" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="H51" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I51" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K51" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L51" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M51" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B54" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C48" s="19" t="s"/>
-      <x:c r="D48" s="19" t="s"/>
-      <x:c r="E48" s="20" t="s"/>
-      <x:c r="F48" s="20" t="s"/>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B49" s="21" t="s">
+      <x:c r="C54" s="19" t="s"/>
+      <x:c r="D54" s="19" t="s"/>
+      <x:c r="E54" s="20" t="s"/>
+      <x:c r="F54" s="20" t="s"/>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B55" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C49" s="22" t="s"/>
-      <x:c r="D49" s="22" t="s"/>
-      <x:c r="E49" s="22" t="s"/>
-      <x:c r="F49" s="23" t="s">
+      <x:c r="C55" s="22" t="s"/>
+      <x:c r="D55" s="22" t="s"/>
+      <x:c r="E55" s="22" t="s"/>
+      <x:c r="F55" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="24" t="s">
+    <x:row r="56" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B56" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C50" s="25" t="s"/>
-      <x:c r="D50" s="25" t="s"/>
-      <x:c r="E50" s="25" t="s"/>
-      <x:c r="F50" s="26" t="n">
+      <x:c r="C56" s="25" t="s"/>
+      <x:c r="D56" s="25" t="s"/>
+      <x:c r="E56" s="25" t="s"/>
+      <x:c r="F56" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="24" t="s">
+    <x:row r="57" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B57" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C51" s="25" t="s"/>
-      <x:c r="D51" s="25" t="s"/>
-      <x:c r="E51" s="25" t="s"/>
-      <x:c r="F51" s="26" t="n">
+      <x:c r="C57" s="25" t="s"/>
+      <x:c r="D57" s="25" t="s"/>
+      <x:c r="E57" s="25" t="s"/>
+      <x:c r="F57" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="24" t="s">
+    <x:row r="58" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B58" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C52" s="25" t="s"/>
-      <x:c r="D52" s="25" t="s"/>
-      <x:c r="E52" s="25" t="s"/>
-      <x:c r="F52" s="26" t="n">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="24" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C53" s="25" t="s"/>
-      <x:c r="D53" s="25" t="s"/>
-      <x:c r="E53" s="25" t="s"/>
-      <x:c r="F53" s="26" t="n">
+      <x:c r="C58" s="25" t="s"/>
+      <x:c r="D58" s="25" t="s"/>
+      <x:c r="E58" s="25" t="s"/>
+      <x:c r="F58" s="26" t="n">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B59" s="24" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C59" s="25" t="s"/>
+      <x:c r="D59" s="25" t="s"/>
+      <x:c r="E59" s="25" t="s"/>
+      <x:c r="F59" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B54" s="27" t="s">
+    <x:row r="60" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B60" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C54" s="28" t="s"/>
-      <x:c r="D54" s="28" t="s"/>
-      <x:c r="E54" s="28" t="s"/>
-      <x:c r="F54" s="29" t="n">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C60" s="28" t="s"/>
+      <x:c r="D60" s="28" t="s"/>
+      <x:c r="E60" s="28" t="s"/>
+      <x:c r="F60" s="29" t="n">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
     <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
@@ -7777,13 +8047,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B48:F48"/>
-    <x:mergeCell ref="B49:E49"/>
-    <x:mergeCell ref="B50:E50"/>
-    <x:mergeCell ref="B51:E51"/>
-    <x:mergeCell ref="B52:E52"/>
-    <x:mergeCell ref="B53:E53"/>
-    <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B54:F54"/>
+    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
+    <x:mergeCell ref="B57:E57"/>
+    <x:mergeCell ref="B58:E58"/>
+    <x:mergeCell ref="B59:E59"/>
+    <x:mergeCell ref="B60:E60"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,22 +177,52 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08095</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1246-201</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08093</x:t>
@@ -222,12 +252,6 @@
     <x:t>zdd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08089</x:t>
   </x:si>
   <x:si>
@@ -237,6 +261,12 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08082</x:t>
   </x:si>
   <x:si>
@@ -291,34 +321,88 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -330,19 +414,70 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08147</x:t>
@@ -354,24 +489,6 @@
     <x:t>zxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
   </x:si>
   <x:si>
@@ -381,73 +498,10 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -510,6 +564,12 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08034-26</x:t>
   </x:si>
   <x:si>
@@ -517,12 +577,6 @@
   </x:si>
   <x:si>
     <x:t>123431</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08045-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5455,10 +5509,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>52</x:v>
@@ -5467,7 +5521,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5531,10 +5585,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>58</x:v>
@@ -5543,7 +5597,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5569,19 +5623,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>61</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5601,25 +5655,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5639,25 +5693,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H15" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="G15" s="30" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5677,25 +5731,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5715,25 +5769,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="H17" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I17" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J17" s="31" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="H17" s="32">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I17" s="32">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J17" s="31" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5753,25 +5807,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="H18" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5791,25 +5845,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="H19" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="H19" s="32">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I19" s="32">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5829,25 +5883,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="H20" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>81</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5867,25 +5921,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="G21" s="30" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5905,25 +5959,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="G22" s="30" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5943,25 +5997,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="G23" s="30" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H23" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I23" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -5981,25 +6035,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="H24" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46119.729231331</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46119.7316308565</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6019,25 +6073,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
+      <x:c r="H25" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="H25" s="32">
-        <x:v>46119.5439653357</x:v>
-      </x:c>
-      <x:c r="I25" s="32">
-        <x:v>46119.5452984143</x:v>
-      </x:c>
-      <x:c r="J25" s="31" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6057,25 +6111,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="H26" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46119.8017436343</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46119.8048384144</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6101,19 +6155,19 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>100</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6133,16 +6187,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="H28" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
         <x:v>49</x:v>
@@ -6151,7 +6205,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6171,25 +6225,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="H29" s="32">
+        <x:v>46119.7297941435</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46119.731450544</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="H29" s="32">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I29" s="32">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6209,25 +6263,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="H30" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6247,25 +6301,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H31" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="G31" s="30" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46119.7297941435</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46119.731450544</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6285,25 +6339,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6323,25 +6377,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>117</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6361,25 +6415,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6399,25 +6453,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6437,25 +6491,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>126</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6475,25 +6529,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6513,25 +6567,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6551,25 +6605,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>111</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6589,25 +6643,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G40" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6627,25 +6681,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>111</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6665,25 +6719,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6703,25 +6757,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -6729,10 +6783,10 @@
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
       <x:c r="B44" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D44" s="31" t="s">
         <x:v>16</x:v>
@@ -6741,25 +6795,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>145</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -6767,10 +6821,10 @@
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
       <x:c r="B45" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D45" s="31" t="s">
         <x:v>16</x:v>
@@ -6779,25 +6833,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -6805,10 +6859,10 @@
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
       <x:c r="B46" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C46" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D46" s="31" t="s">
         <x:v>16</x:v>
@@ -6817,25 +6871,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>152</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -6843,10 +6897,10 @@
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
       <x:c r="B47" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C47" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D47" s="31" t="s">
         <x:v>16</x:v>
@@ -6855,25 +6909,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>154</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>156</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -6881,10 +6935,10 @@
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
       <x:c r="B48" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C48" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D48" s="31" t="s">
         <x:v>16</x:v>
@@ -6893,25 +6947,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -6919,10 +6973,10 @@
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
       <x:c r="B49" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D49" s="31" t="s">
         <x:v>16</x:v>
@@ -6931,25 +6985,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -6957,10 +7011,10 @@
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
       <x:c r="B50" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D50" s="31" t="s">
         <x:v>16</x:v>
@@ -6969,25 +7023,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -6995,10 +7049,10 @@
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
       <x:c r="B51" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D51" s="31" t="s">
         <x:v>16</x:v>
@@ -7007,115 +7061,411 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B52" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D52" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E52" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F52" s="30" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G52" s="30" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="H52" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I52" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="K52" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L52" s="34">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M52" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B53" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C53" s="30" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D53" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E53" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F53" s="30" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G53" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="H53" s="32">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I53" s="32">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J53" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K53" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L53" s="34">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M53" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="18" t="s">
+      <x:c r="B54" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C54" s="30" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="D54" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E54" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F54" s="30" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="G54" s="30" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="H54" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I54" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J54" s="31" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="K54" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L54" s="34">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M54" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B55" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C55" s="30" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D55" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E55" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F55" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G55" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H55" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I55" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="K55" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L55" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M55" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B56" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C56" s="30" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="D56" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E56" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F56" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G56" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H56" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I56" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K56" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L56" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M56" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B57" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C57" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D57" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E57" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F57" s="30" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H57" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I57" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K57" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L57" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M57" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B58" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C58" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D58" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E58" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F58" s="30" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G58" s="30" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="H58" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I58" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="K58" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L58" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M58" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B59" s="30" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C59" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D59" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E59" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F59" s="30" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H59" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K59" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L59" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M59" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B62" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C54" s="19" t="s"/>
-      <x:c r="D54" s="19" t="s"/>
-      <x:c r="E54" s="20" t="s"/>
-      <x:c r="F54" s="20" t="s"/>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B55" s="21" t="s">
+      <x:c r="C62" s="19" t="s"/>
+      <x:c r="D62" s="19" t="s"/>
+      <x:c r="E62" s="20" t="s"/>
+      <x:c r="F62" s="20" t="s"/>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B63" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C55" s="22" t="s"/>
-      <x:c r="D55" s="22" t="s"/>
-      <x:c r="E55" s="22" t="s"/>
-      <x:c r="F55" s="23" t="s">
+      <x:c r="C63" s="22" t="s"/>
+      <x:c r="D63" s="22" t="s"/>
+      <x:c r="E63" s="22" t="s"/>
+      <x:c r="F63" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B56" s="24" t="s">
+    <x:row r="64" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B64" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C56" s="25" t="s"/>
-      <x:c r="D56" s="25" t="s"/>
-      <x:c r="E56" s="25" t="s"/>
-      <x:c r="F56" s="26" t="n">
+      <x:c r="C64" s="25" t="s"/>
+      <x:c r="D64" s="25" t="s"/>
+      <x:c r="E64" s="25" t="s"/>
+      <x:c r="F64" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B57" s="24" t="s">
+    <x:row r="65" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B65" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C57" s="25" t="s"/>
-      <x:c r="D57" s="25" t="s"/>
-      <x:c r="E57" s="25" t="s"/>
-      <x:c r="F57" s="26" t="n">
+      <x:c r="C65" s="25" t="s"/>
+      <x:c r="D65" s="25" t="s"/>
+      <x:c r="E65" s="25" t="s"/>
+      <x:c r="F65" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B58" s="24" t="s">
+    <x:row r="66" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B66" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C58" s="25" t="s"/>
-      <x:c r="D58" s="25" t="s"/>
-      <x:c r="E58" s="25" t="s"/>
-      <x:c r="F58" s="26" t="n">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B59" s="24" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="C59" s="25" t="s"/>
-      <x:c r="D59" s="25" t="s"/>
-      <x:c r="E59" s="25" t="s"/>
-      <x:c r="F59" s="26" t="n">
+      <x:c r="C66" s="25" t="s"/>
+      <x:c r="D66" s="25" t="s"/>
+      <x:c r="E66" s="25" t="s"/>
+      <x:c r="F66" s="26" t="n">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B67" s="24" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C67" s="25" t="s"/>
+      <x:c r="D67" s="25" t="s"/>
+      <x:c r="E67" s="25" t="s"/>
+      <x:c r="F67" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B60" s="27" t="s">
+    <x:row r="68" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B68" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C60" s="28" t="s"/>
-      <x:c r="D60" s="28" t="s"/>
-      <x:c r="E60" s="28" t="s"/>
-      <x:c r="F60" s="29" t="n">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C68" s="28" t="s"/>
+      <x:c r="D68" s="28" t="s"/>
+      <x:c r="E68" s="28" t="s"/>
+      <x:c r="F68" s="29" t="n">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
     <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8047,13 +8397,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B54:F54"/>
-    <x:mergeCell ref="B55:E55"/>
-    <x:mergeCell ref="B56:E56"/>
-    <x:mergeCell ref="B57:E57"/>
-    <x:mergeCell ref="B58:E58"/>
-    <x:mergeCell ref="B59:E59"/>
-    <x:mergeCell ref="B60:E60"/>
+    <x:mergeCell ref="B62:F62"/>
+    <x:mergeCell ref="B63:E63"/>
+    <x:mergeCell ref="B64:E64"/>
+    <x:mergeCell ref="B65:E65"/>
+    <x:mergeCell ref="B66:E66"/>
+    <x:mergeCell ref="B67:E67"/>
+    <x:mergeCell ref="B68:E68"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,6 +177,30 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
@@ -186,13 +210,10 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08097</x:t>
@@ -321,10 +342,19 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -333,19 +363,55 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08173</x:t>
@@ -357,6 +423,12 @@
     <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
   </x:si>
   <x:si>
@@ -375,6 +447,33 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
   </x:si>
   <x:si>
@@ -384,16 +483,46 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
@@ -402,18 +531,6 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
@@ -427,81 +544,6 @@
   </x:si>
   <x:si>
     <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5509,19 +5551,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5585,19 +5627,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5617,25 +5659,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="H13" s="32">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I13" s="32">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J13" s="31" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="H13" s="32">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I13" s="32">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J13" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5661,10 +5703,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>52</x:v>
@@ -5673,7 +5715,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5699,10 +5741,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>65</x:v>
@@ -5711,7 +5753,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5737,19 +5779,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>68</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5769,25 +5811,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5807,25 +5849,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H18" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="G18" s="30" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5845,25 +5887,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H19" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="G19" s="30" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H19" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I19" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5883,25 +5925,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H20" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I20" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J20" s="31" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="G20" s="30" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H20" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I20" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J20" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5921,25 +5963,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="H21" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -5959,25 +6001,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="H22" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -5997,25 +6039,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>88</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6035,25 +6077,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H24" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="G24" s="30" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6073,25 +6115,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H25" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="G25" s="30" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H25" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I25" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J25" s="31" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6111,25 +6153,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H26" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I26" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="G26" s="30" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H26" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I26" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J26" s="31" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6149,25 +6191,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G27" s="30" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6187,25 +6229,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="H28" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6231,10 +6273,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
         <x:v>104</x:v>
@@ -6243,7 +6285,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6275,7 +6317,7 @@
         <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>104</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
@@ -6307,10 +6349,10 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
         <x:v>109</x:v>
@@ -6319,7 +6361,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6345,19 +6387,19 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>104</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6383,19 +6425,19 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6415,25 +6457,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>104</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6453,25 +6495,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>118</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6491,25 +6533,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6529,25 +6571,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>104</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6567,25 +6609,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6605,25 +6647,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>128</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6649,19 +6691,19 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6681,25 +6723,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>133</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6725,19 +6767,19 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>125</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6763,10 +6805,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
         <x:v>49</x:v>
@@ -6775,7 +6817,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -6801,19 +6843,19 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>140</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -6833,16 +6875,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G45" s="30" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="G45" s="30" t="s">
-        <x:v>142</x:v>
-      </x:c>
       <x:c r="H45" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
         <x:v>30</x:v>
@@ -6851,7 +6893,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -6871,25 +6913,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G46" s="30" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G46" s="30" t="s">
-        <x:v>144</x:v>
-      </x:c>
       <x:c r="H46" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -6909,25 +6951,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="G47" s="30" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="G47" s="30" t="s">
-        <x:v>146</x:v>
-      </x:c>
       <x:c r="H47" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>147</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -6947,25 +6989,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G48" s="30" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H48" s="32">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I48" s="32">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J48" s="31" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="G48" s="30" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H48" s="32">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I48" s="32">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J48" s="31" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -6985,25 +7027,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="G49" s="30" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H49" s="32">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I49" s="32">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="G49" s="30" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H49" s="32">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I49" s="32">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J49" s="31" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -7023,25 +7065,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G50" s="30" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H50" s="32">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I50" s="32">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J50" s="31" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="G50" s="30" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H50" s="32">
-        <x:v>46121.2464636111</x:v>
-      </x:c>
-      <x:c r="I50" s="32">
-        <x:v>46121.3217277662</x:v>
-      </x:c>
-      <x:c r="J50" s="31" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -7061,25 +7103,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G51" s="30" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H51" s="32">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I51" s="32">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J51" s="31" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="G51" s="30" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="H51" s="32">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I51" s="32">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J51" s="31" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -7087,10 +7129,10 @@
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
       <x:c r="B52" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C52" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="31" t="s">
         <x:v>16</x:v>
@@ -7099,25 +7141,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -7125,10 +7167,10 @@
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
       <x:c r="B53" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C53" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D53" s="31" t="s">
         <x:v>16</x:v>
@@ -7137,25 +7179,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7163,10 +7205,10 @@
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
       <x:c r="B54" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D54" s="31" t="s">
         <x:v>16</x:v>
@@ -7175,25 +7217,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>170</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7201,10 +7243,10 @@
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
       <x:c r="B55" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D55" s="31" t="s">
         <x:v>16</x:v>
@@ -7213,25 +7255,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>174</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7239,10 +7281,10 @@
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
       <x:c r="B56" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C56" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D56" s="31" t="s">
         <x:v>16</x:v>
@@ -7251,25 +7293,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G56" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7277,10 +7319,10 @@
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
       <x:c r="B57" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C57" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D57" s="31" t="s">
         <x:v>16</x:v>
@@ -7289,25 +7331,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G57" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7315,10 +7357,10 @@
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
       <x:c r="B58" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C58" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D58" s="31" t="s">
         <x:v>16</x:v>
@@ -7327,25 +7369,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G58" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>183</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7353,10 +7395,10 @@
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
       <x:c r="B59" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C59" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D59" s="31" t="s">
         <x:v>16</x:v>
@@ -7365,113 +7407,335 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G59" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B60" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C60" s="30" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D60" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E60" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F60" s="30" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H60" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I60" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="K60" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L60" s="34">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M60" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B61" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C61" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D61" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E61" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F61" s="30" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G61" s="30" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="H61" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I61" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J61" s="31" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="K61" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L61" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M61" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="18" t="s">
+      <x:c r="B62" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C62" s="30" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D62" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E62" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F62" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G62" s="30" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H62" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I62" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K62" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L62" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M62" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B63" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C63" s="30" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D63" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E63" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F63" s="30" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G63" s="30" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H63" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I63" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K63" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L63" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M63" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B64" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C64" s="30" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D64" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E64" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F64" s="30" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G64" s="30" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H64" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I64" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="K64" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L64" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M64" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B65" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C65" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D65" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E65" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F65" s="30" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="G65" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="H65" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I65" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K65" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L65" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M65" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B68" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C62" s="19" t="s"/>
-      <x:c r="D62" s="19" t="s"/>
-      <x:c r="E62" s="20" t="s"/>
-      <x:c r="F62" s="20" t="s"/>
-    </x:row>
-    <x:row r="63" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B63" s="21" t="s">
+      <x:c r="C68" s="19" t="s"/>
+      <x:c r="D68" s="19" t="s"/>
+      <x:c r="E68" s="20" t="s"/>
+      <x:c r="F68" s="20" t="s"/>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B69" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C63" s="22" t="s"/>
-      <x:c r="D63" s="22" t="s"/>
-      <x:c r="E63" s="22" t="s"/>
-      <x:c r="F63" s="23" t="s">
+      <x:c r="C69" s="22" t="s"/>
+      <x:c r="D69" s="22" t="s"/>
+      <x:c r="E69" s="22" t="s"/>
+      <x:c r="F69" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B64" s="24" t="s">
+    <x:row r="70" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B70" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C64" s="25" t="s"/>
-      <x:c r="D64" s="25" t="s"/>
-      <x:c r="E64" s="25" t="s"/>
-      <x:c r="F64" s="26" t="n">
+      <x:c r="C70" s="25" t="s"/>
+      <x:c r="D70" s="25" t="s"/>
+      <x:c r="E70" s="25" t="s"/>
+      <x:c r="F70" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B65" s="24" t="s">
+    <x:row r="71" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B71" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C65" s="25" t="s"/>
-      <x:c r="D65" s="25" t="s"/>
-      <x:c r="E65" s="25" t="s"/>
-      <x:c r="F65" s="26" t="n">
+      <x:c r="C71" s="25" t="s"/>
+      <x:c r="D71" s="25" t="s"/>
+      <x:c r="E71" s="25" t="s"/>
+      <x:c r="F71" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B66" s="24" t="s">
+    <x:row r="72" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B72" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C66" s="25" t="s"/>
-      <x:c r="D66" s="25" t="s"/>
-      <x:c r="E66" s="25" t="s"/>
-      <x:c r="F66" s="26" t="n">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B67" s="24" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C67" s="25" t="s"/>
-      <x:c r="D67" s="25" t="s"/>
-      <x:c r="E67" s="25" t="s"/>
-      <x:c r="F67" s="26" t="n">
+      <x:c r="C72" s="25" t="s"/>
+      <x:c r="D72" s="25" t="s"/>
+      <x:c r="E72" s="25" t="s"/>
+      <x:c r="F72" s="26" t="n">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B73" s="24" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C73" s="25" t="s"/>
+      <x:c r="D73" s="25" t="s"/>
+      <x:c r="E73" s="25" t="s"/>
+      <x:c r="F73" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B68" s="27" t="s">
+    <x:row r="74" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B74" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C68" s="28" t="s"/>
-      <x:c r="D68" s="28" t="s"/>
-      <x:c r="E68" s="28" t="s"/>
-      <x:c r="F68" s="29" t="n">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C74" s="28" t="s"/>
+      <x:c r="D74" s="28" t="s"/>
+      <x:c r="E74" s="28" t="s"/>
+      <x:c r="F74" s="29" t="n">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
     <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8397,13 +8661,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B62:F62"/>
-    <x:mergeCell ref="B63:E63"/>
-    <x:mergeCell ref="B64:E64"/>
-    <x:mergeCell ref="B65:E65"/>
-    <x:mergeCell ref="B66:E66"/>
-    <x:mergeCell ref="B67:E67"/>
-    <x:mergeCell ref="B68:E68"/>
+    <x:mergeCell ref="B68:F68"/>
+    <x:mergeCell ref="B69:E69"/>
+    <x:mergeCell ref="B70:E70"/>
+    <x:mergeCell ref="B71:E71"/>
+    <x:mergeCell ref="B72:E72"/>
+    <x:mergeCell ref="B73:E73"/>
+    <x:mergeCell ref="B74:E74"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,6 +177,30 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
@@ -186,13 +210,10 @@
     <x:t>zxcasdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
@@ -342,34 +363,76 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08118</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1256-775</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08179</x:t>
@@ -387,46 +450,73 @@
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08177</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08172</x:t>
@@ -435,10 +525,49 @@
     <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -447,103 +576,19 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5551,19 +5596,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5583,25 +5628,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G11" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="H11" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I11" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J11" s="31" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="H11" s="32">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I11" s="32">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J11" s="31" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5621,25 +5666,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="H12" s="32">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I12" s="32">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J12" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5665,19 +5710,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5703,19 +5748,19 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5741,19 +5786,19 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5773,25 +5818,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G16" s="30" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="H16" s="32">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I16" s="32">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J16" s="31" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="H16" s="32">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I16" s="32">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J16" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5817,10 +5862,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>60</x:v>
@@ -5829,7 +5874,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5855,10 +5900,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>72</x:v>
@@ -5867,7 +5912,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5893,19 +5938,19 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5925,25 +5970,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G20" s="30" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -5963,25 +6008,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G21" s="30" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H21" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I21" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J21" s="31" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="G21" s="30" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H21" s="32">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I21" s="32">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J21" s="31" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6001,25 +6046,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G22" s="30" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H22" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I22" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J22" s="31" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="G22" s="30" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H22" s="32">
-        <x:v>46119.5267212153</x:v>
-      </x:c>
-      <x:c r="I22" s="32">
-        <x:v>46119.5274664236</x:v>
-      </x:c>
-      <x:c r="J22" s="31" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6039,25 +6084,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G23" s="30" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H23" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I23" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J23" s="31" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="G23" s="30" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H23" s="32">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I23" s="32">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J23" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6077,25 +6122,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G24" s="30" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="H24" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I24" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J24" s="31" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="H24" s="32">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I24" s="32">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J24" s="31" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6115,25 +6160,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G25" s="30" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
+      <x:c r="H25" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I25" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J25" s="31" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="H25" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I25" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J25" s="31" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6153,25 +6198,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G26" s="30" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6191,25 +6236,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G27" s="30" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H27" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J27" s="31" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G27" s="30" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H27" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I27" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J27" s="31" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6229,25 +6274,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H28" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="G28" s="30" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6267,25 +6312,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H29" s="32">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="G29" s="30" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H29" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I29" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6305,25 +6350,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H30" s="32">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="G30" s="30" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H30" s="32">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I30" s="32">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6343,25 +6388,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="H31" s="32">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6381,25 +6426,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
+      <x:c r="H32" s="32">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I32" s="32">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="H32" s="32">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I32" s="32">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J32" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6463,19 +6508,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>117</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6495,25 +6540,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G35" s="30" t="s">
-        <x:v>119</x:v>
-      </x:c>
       <x:c r="H35" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6533,25 +6578,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G36" s="30" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="H36" s="32">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I36" s="32">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J36" s="31" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="H36" s="32">
-        <x:v>46122.6182774306</x:v>
-      </x:c>
-      <x:c r="I36" s="32">
-        <x:v>46122.6193276968</x:v>
-      </x:c>
-      <x:c r="J36" s="31" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6577,19 +6622,19 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6609,25 +6654,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6647,25 +6692,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>84</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6685,25 +6730,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G40" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6723,16 +6768,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
         <x:v>30</x:v>
@@ -6741,7 +6786,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6761,25 +6806,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6799,25 +6844,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -6837,25 +6882,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>52</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -6875,16 +6920,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
         <x:v>30</x:v>
@@ -6893,7 +6938,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -6913,25 +6958,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -6951,25 +6996,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -6989,25 +7034,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>148</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -7027,25 +7072,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>151</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -7065,25 +7110,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>154</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -7103,25 +7148,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>157</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -7141,25 +7186,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -7179,25 +7224,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7217,25 +7262,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>163</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>165</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7255,25 +7300,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>109</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7293,25 +7338,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G56" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7331,25 +7376,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G57" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>172</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7357,10 +7402,10 @@
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
       <x:c r="B58" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D58" s="31" t="s">
         <x:v>16</x:v>
@@ -7369,25 +7414,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G58" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>177</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7395,10 +7440,10 @@
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
       <x:c r="B59" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C59" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D59" s="31" t="s">
         <x:v>16</x:v>
@@ -7407,25 +7452,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G59" s="30" t="s">
+      <x:c r="H59" s="32">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H59" s="32">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I59" s="32">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J59" s="31" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="K59" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -7433,10 +7478,10 @@
     </x:row>
     <x:row r="60" spans="1:28" ht="30" customHeight="1">
       <x:c r="B60" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C60" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D60" s="31" t="s">
         <x:v>16</x:v>
@@ -7445,25 +7490,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G60" s="30" t="s">
-        <x:v>183</x:v>
-      </x:c>
       <x:c r="H60" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
-        <x:v>184</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -7471,10 +7516,10 @@
     </x:row>
     <x:row r="61" spans="1:28" ht="30" customHeight="1">
       <x:c r="B61" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D61" s="31" t="s">
         <x:v>16</x:v>
@@ -7483,25 +7528,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G61" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>188</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -7509,10 +7554,10 @@
     </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
       <x:c r="B62" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C62" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D62" s="31" t="s">
         <x:v>16</x:v>
@@ -7521,25 +7566,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G62" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -7547,10 +7592,10 @@
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
       <x:c r="B63" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C63" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D63" s="31" t="s">
         <x:v>16</x:v>
@@ -7559,25 +7604,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G63" s="30" t="s">
-        <x:v>194</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -7585,10 +7630,10 @@
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
       <x:c r="B64" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C64" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="D64" s="31" t="s">
         <x:v>16</x:v>
@@ -7597,25 +7642,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="30" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G64" s="30" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="G64" s="30" t="s">
-        <x:v>196</x:v>
-      </x:c>
       <x:c r="H64" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
-        <x:v>197</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K64" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -7623,10 +7668,10 @@
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
       <x:c r="B65" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C65" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D65" s="31" t="s">
         <x:v>16</x:v>
@@ -7635,112 +7680,297 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G65" s="30" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="G65" s="30" t="s">
+      <x:c r="H65" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I65" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="H65" s="32">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I65" s="32">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J65" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B66" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C66" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D66" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E66" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F66" s="30" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H66" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I66" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="K66" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L66" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M66" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B67" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C67" s="30" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="D67" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E67" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F67" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G67" s="30" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H67" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I67" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J67" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K67" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L67" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M67" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B68" s="18" t="s">
+      <x:c r="B68" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C68" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D68" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E68" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F68" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H68" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I68" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K68" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L68" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M68" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B69" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C69" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D69" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E69" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F69" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="H69" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I69" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="K69" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L69" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M69" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B70" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C70" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D70" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E70" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F70" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H70" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I70" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K70" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L70" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M70" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B73" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C68" s="19" t="s"/>
-      <x:c r="D68" s="19" t="s"/>
-      <x:c r="E68" s="20" t="s"/>
-      <x:c r="F68" s="20" t="s"/>
-    </x:row>
-    <x:row r="69" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B69" s="21" t="s">
+      <x:c r="C73" s="19" t="s"/>
+      <x:c r="D73" s="19" t="s"/>
+      <x:c r="E73" s="20" t="s"/>
+      <x:c r="F73" s="20" t="s"/>
+    </x:row>
+    <x:row r="74" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B74" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C69" s="22" t="s"/>
-      <x:c r="D69" s="22" t="s"/>
-      <x:c r="E69" s="22" t="s"/>
-      <x:c r="F69" s="23" t="s">
+      <x:c r="C74" s="22" t="s"/>
+      <x:c r="D74" s="22" t="s"/>
+      <x:c r="E74" s="22" t="s"/>
+      <x:c r="F74" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B70" s="24" t="s">
+    <x:row r="75" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B75" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C70" s="25" t="s"/>
-      <x:c r="D70" s="25" t="s"/>
-      <x:c r="E70" s="25" t="s"/>
-      <x:c r="F70" s="26" t="n">
+      <x:c r="C75" s="25" t="s"/>
+      <x:c r="D75" s="25" t="s"/>
+      <x:c r="E75" s="25" t="s"/>
+      <x:c r="F75" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B71" s="24" t="s">
+    <x:row r="76" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B76" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C71" s="25" t="s"/>
-      <x:c r="D71" s="25" t="s"/>
-      <x:c r="E71" s="25" t="s"/>
-      <x:c r="F71" s="26" t="n">
+      <x:c r="C76" s="25" t="s"/>
+      <x:c r="D76" s="25" t="s"/>
+      <x:c r="E76" s="25" t="s"/>
+      <x:c r="F76" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B72" s="24" t="s">
+    <x:row r="77" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B77" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C72" s="25" t="s"/>
-      <x:c r="D72" s="25" t="s"/>
-      <x:c r="E72" s="25" t="s"/>
-      <x:c r="F72" s="26" t="n">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B73" s="24" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="C73" s="25" t="s"/>
-      <x:c r="D73" s="25" t="s"/>
-      <x:c r="E73" s="25" t="s"/>
-      <x:c r="F73" s="26" t="n">
+      <x:c r="C77" s="25" t="s"/>
+      <x:c r="D77" s="25" t="s"/>
+      <x:c r="E77" s="25" t="s"/>
+      <x:c r="F77" s="26" t="n">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B78" s="24" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C78" s="25" t="s"/>
+      <x:c r="D78" s="25" t="s"/>
+      <x:c r="E78" s="25" t="s"/>
+      <x:c r="F78" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B74" s="27" t="s">
+    <x:row r="79" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B79" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C74" s="28" t="s"/>
-      <x:c r="D74" s="28" t="s"/>
-      <x:c r="E74" s="28" t="s"/>
-      <x:c r="F74" s="29" t="n">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C79" s="28" t="s"/>
+      <x:c r="D79" s="28" t="s"/>
+      <x:c r="E79" s="28" t="s"/>
+      <x:c r="F79" s="29" t="n">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
     <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8661,13 +8891,13 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B68:F68"/>
-    <x:mergeCell ref="B69:E69"/>
-    <x:mergeCell ref="B70:E70"/>
-    <x:mergeCell ref="B71:E71"/>
-    <x:mergeCell ref="B72:E72"/>
-    <x:mergeCell ref="B73:E73"/>
+    <x:mergeCell ref="B73:F73"/>
     <x:mergeCell ref="B74:E74"/>
+    <x:mergeCell ref="B75:E75"/>
+    <x:mergeCell ref="B76:E76"/>
+    <x:mergeCell ref="B77:E77"/>
+    <x:mergeCell ref="B78:E78"/>
+    <x:mergeCell ref="B79:E79"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -177,19 +177,88 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -201,34 +270,22 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
@@ -363,34 +420,139 @@
     <x:t>123437</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -411,6 +573,51 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
   </x:si>
   <x:si>
@@ -420,13 +627,28 @@
     <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08180</x:t>
@@ -435,13 +657,10 @@
     <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08178</x:t>
@@ -450,13 +669,28 @@
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08176</x:t>
@@ -465,132 +699,6 @@
     <x:t>61-4-2026-1288-384</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -670,6 +778,36 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1239-459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permit to PURCHASE/POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAASD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROXIV-08193-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1304-273</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqweqaas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AASD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1305-075</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sasdqwe</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -5596,19 +5734,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5634,19 +5772,19 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5666,25 +5804,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="30" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="H12" s="32">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I12" s="32">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J12" s="31" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H12" s="32">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I12" s="32">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J12" s="31" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K12" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5704,25 +5842,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G13" s="30" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="H13" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5742,25 +5880,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G14" s="30" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H14" s="32">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I14" s="32">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J14" s="31" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="G14" s="30" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="H14" s="32">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I14" s="32">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J14" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5780,25 +5918,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G15" s="30" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="H15" s="32">
+        <x:v>46119.8017436343</x:v>
+      </x:c>
+      <x:c r="I15" s="32">
+        <x:v>46119.8048384144</x:v>
+      </x:c>
+      <x:c r="J15" s="31" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="H15" s="32">
-        <x:v>46119.8023724884</x:v>
-      </x:c>
-      <x:c r="I15" s="32">
-        <x:v>46119.8046602662</x:v>
-      </x:c>
-      <x:c r="J15" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5824,19 +5962,19 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5856,25 +5994,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G17" s="30" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -5894,25 +6032,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G18" s="30" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="H18" s="32">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I18" s="32">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J18" s="31" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="H18" s="32">
-        <x:v>46119.729231331</x:v>
-      </x:c>
-      <x:c r="I18" s="32">
-        <x:v>46119.7316308565</x:v>
-      </x:c>
-      <x:c r="J18" s="31" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -5932,25 +6070,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G19" s="30" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="H19" s="32">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I19" s="32">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J19" s="31" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="H19" s="32">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I19" s="32">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J19" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -5976,19 +6114,19 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6008,25 +6146,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6046,25 +6184,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6084,25 +6222,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6122,25 +6260,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>88</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6166,10 +6304,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
         <x:v>91</x:v>
@@ -6178,7 +6316,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6204,19 +6342,19 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6242,19 +6380,19 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>96</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6274,25 +6412,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G28" s="30" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="H28" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I28" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J28" s="31" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="H28" s="32">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I28" s="32">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J28" s="31" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6312,25 +6450,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G29" s="30" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="H29" s="32">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I29" s="32">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J29" s="31" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="H29" s="32">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I29" s="32">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J29" s="31" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6350,25 +6488,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="G30" s="30" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="H30" s="32">
+        <x:v>46119.542956794</x:v>
+      </x:c>
+      <x:c r="I30" s="32">
+        <x:v>46119.5456356481</x:v>
+      </x:c>
+      <x:c r="J30" s="31" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="H30" s="32">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I30" s="32">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J30" s="31" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6388,25 +6526,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G31" s="30" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="H31" s="32">
+        <x:v>46119.5424612384</x:v>
+      </x:c>
+      <x:c r="I31" s="32">
+        <x:v>46119.5457934491</x:v>
+      </x:c>
+      <x:c r="J31" s="31" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="H31" s="32">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I31" s="32">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J31" s="31" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6426,25 +6564,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
+      <x:c r="H32" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I32" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J32" s="31" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="H32" s="32">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I32" s="32">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J32" s="31" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6464,25 +6602,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G33" s="30" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G33" s="30" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="H33" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>114</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6502,25 +6640,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G34" s="30" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H34" s="32">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I34" s="32">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J34" s="31" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="G34" s="30" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H34" s="32">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I34" s="32">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J34" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6540,25 +6678,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G35" s="30" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G35" s="30" t="s">
+      <x:c r="H35" s="32">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I35" s="32">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J35" s="31" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="H35" s="32">
-        <x:v>46120.2362105324</x:v>
-      </x:c>
-      <x:c r="I35" s="32">
-        <x:v>46120.5226826273</x:v>
-      </x:c>
-      <x:c r="J35" s="31" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6584,10 +6722,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
         <x:v>121</x:v>
@@ -6596,7 +6734,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6622,10 +6760,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
         <x:v>124</x:v>
@@ -6634,7 +6772,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6660,10 +6798,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46123.061368912</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
         <x:v>127</x:v>
@@ -6672,7 +6810,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6698,10 +6836,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
         <x:v>130</x:v>
@@ -6710,7 +6848,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6736,19 +6874,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>133</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6768,25 +6906,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G41" s="30" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G41" s="30" t="s">
+      <x:c r="H41" s="32">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I41" s="32">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J41" s="31" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="H41" s="32">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I41" s="32">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J41" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6812,10 +6950,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
         <x:v>138</x:v>
@@ -6824,7 +6962,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6850,10 +6988,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
         <x:v>30</x:v>
@@ -6862,7 +7000,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -6888,10 +7026,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
         <x:v>143</x:v>
@@ -6900,7 +7038,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -6926,19 +7064,19 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -6958,25 +7096,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>148</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -7002,19 +7140,19 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>91</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -7034,25 +7172,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -7072,25 +7210,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -7110,25 +7248,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -7148,25 +7286,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>160</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -7186,25 +7324,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -7224,25 +7362,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7262,25 +7400,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7300,25 +7438,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7338,25 +7476,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G56" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7376,25 +7514,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G57" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7414,25 +7552,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G58" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7452,25 +7590,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G59" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
-        <x:v>180</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -7490,25 +7628,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G60" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
-        <x:v>60</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -7528,25 +7666,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G61" s="30" t="s">
-        <x:v>184</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -7566,25 +7704,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G62" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
-        <x:v>187</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -7592,10 +7730,10 @@
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
       <x:c r="B63" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C63" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D63" s="31" t="s">
         <x:v>16</x:v>
@@ -7604,25 +7742,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G63" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>192</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -7630,10 +7768,10 @@
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
       <x:c r="B64" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C64" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D64" s="31" t="s">
         <x:v>16</x:v>
@@ -7642,25 +7780,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="30" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G64" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K64" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -7668,10 +7806,10 @@
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
       <x:c r="B65" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C65" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D65" s="31" t="s">
         <x:v>16</x:v>
@@ -7686,19 +7824,19 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
         <x:v>199</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -7706,10 +7844,10 @@
     </x:row>
     <x:row r="66" spans="1:28" ht="30" customHeight="1">
       <x:c r="B66" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C66" s="30" t="s">
-        <x:v>200</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D66" s="31" t="s">
         <x:v>16</x:v>
@@ -7718,25 +7856,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="G66" s="30" t="s">
+      <x:c r="H66" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I66" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="H66" s="32">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I66" s="32">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J66" s="31" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="K66" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -7744,10 +7882,10 @@
     </x:row>
     <x:row r="67" spans="1:28" ht="30" customHeight="1">
       <x:c r="B67" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C67" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D67" s="31" t="s">
         <x:v>16</x:v>
@@ -7756,25 +7894,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G67" s="30" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H67" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -7782,10 +7920,10 @@
     </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
       <x:c r="B68" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C68" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D68" s="31" t="s">
         <x:v>16</x:v>
@@ -7794,25 +7932,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G68" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="H68" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I68" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J68" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -7820,10 +7958,10 @@
     </x:row>
     <x:row r="69" spans="1:28" ht="30" customHeight="1">
       <x:c r="B69" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C69" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D69" s="31" t="s">
         <x:v>16</x:v>
@@ -7832,25 +7970,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="H69" s="32">
+        <x:v>46122.7261372338</x:v>
+      </x:c>
+      <x:c r="I69" s="32">
+        <x:v>46122.727234375</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="G69" s="30" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="H69" s="32">
-        <x:v>46118.439490081</x:v>
-      </x:c>
-      <x:c r="I69" s="32">
-        <x:v>46118.4395309375</x:v>
-      </x:c>
-      <x:c r="J69" s="31" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="K69" s="33" t="n">
-        <x:v>3530</x:v>
-      </x:c>
       <x:c r="L69" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -7858,10 +7996,10 @@
     </x:row>
     <x:row r="70" spans="1:28" ht="30" customHeight="1">
       <x:c r="B70" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C70" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D70" s="31" t="s">
         <x:v>16</x:v>
@@ -7870,124 +8008,697 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G70" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="H70" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I70" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J70" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B71" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C71" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D71" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E71" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F71" s="30" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H71" s="32">
+        <x:v>46122.6795081481</x:v>
+      </x:c>
+      <x:c r="I71" s="32">
+        <x:v>46122.6802186921</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K71" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L71" s="34">
+        <x:v>46122.6809879398</x:v>
+      </x:c>
+      <x:c r="M71" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B72" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C72" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D72" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E72" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F72" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="H72" s="32">
+        <x:v>46122.6182774306</x:v>
+      </x:c>
+      <x:c r="I72" s="32">
+        <x:v>46122.6193276968</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K72" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L72" s="34">
+        <x:v>46122.6199813426</x:v>
+      </x:c>
+      <x:c r="M72" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="73" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B73" s="18" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C73" s="19" t="s"/>
-      <x:c r="D73" s="19" t="s"/>
-      <x:c r="E73" s="20" t="s"/>
-      <x:c r="F73" s="20" t="s"/>
-    </x:row>
-    <x:row r="74" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B74" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C74" s="22" t="s"/>
-      <x:c r="D74" s="22" t="s"/>
-      <x:c r="E74" s="22" t="s"/>
-      <x:c r="F74" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B75" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C75" s="25" t="s"/>
-      <x:c r="D75" s="25" t="s"/>
-      <x:c r="E75" s="25" t="s"/>
-      <x:c r="F75" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B76" s="24" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C76" s="25" t="s"/>
-      <x:c r="D76" s="25" t="s"/>
-      <x:c r="E76" s="25" t="s"/>
-      <x:c r="F76" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B77" s="24" t="s">
+      <x:c r="B73" s="30" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C77" s="25" t="s"/>
-      <x:c r="D77" s="25" t="s"/>
-      <x:c r="E77" s="25" t="s"/>
-      <x:c r="F77" s="26" t="n">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B78" s="24" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="C78" s="25" t="s"/>
-      <x:c r="D78" s="25" t="s"/>
-      <x:c r="E78" s="25" t="s"/>
-      <x:c r="F78" s="26" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B79" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C79" s="28" t="s"/>
-      <x:c r="D79" s="28" t="s"/>
-      <x:c r="E79" s="28" t="s"/>
-      <x:c r="F79" s="29" t="n">
-        <x:v>63</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C73" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D73" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E73" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F73" s="30" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H73" s="32">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I73" s="32">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J73" s="31" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="K73" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L73" s="34">
+        <x:v>46124.7056197917</x:v>
+      </x:c>
+      <x:c r="M73" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B74" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C74" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D74" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E74" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F74" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="H74" s="32">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I74" s="32">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J74" s="31" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="K74" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L74" s="34">
+        <x:v>46122.5928339699</x:v>
+      </x:c>
+      <x:c r="M74" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B75" s="30" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C75" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D75" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E75" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F75" s="30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="H75" s="32">
+        <x:v>46122.5945434491</x:v>
+      </x:c>
+      <x:c r="I75" s="32">
+        <x:v>46122.5999534606</x:v>
+      </x:c>
+      <x:c r="J75" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K75" s="33" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L75" s="34">
+        <x:v>46122.6007489699</x:v>
+      </x:c>
+      <x:c r="M75" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B76" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C76" s="30" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D76" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E76" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F76" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="H76" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I76" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="K76" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L76" s="34">
+        <x:v>46118.5806122685</x:v>
+      </x:c>
+      <x:c r="M76" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B77" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C77" s="30" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="D77" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E77" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F77" s="30" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="H77" s="32">
+        <x:v>46118.6064654514</x:v>
+      </x:c>
+      <x:c r="I77" s="32">
+        <x:v>46118.6065117477</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K77" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L77" s="34">
+        <x:v>46118.6077792245</x:v>
+      </x:c>
+      <x:c r="M77" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B78" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C78" s="30" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="D78" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E78" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F78" s="30" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G78" s="30" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H78" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I78" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J78" s="31" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="K78" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L78" s="34">
+        <x:v>46118.7054991898</x:v>
+      </x:c>
+      <x:c r="M78" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B79" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C79" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="D79" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E79" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F79" s="30" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G79" s="30" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H79" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I79" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J79" s="31" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="K79" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L79" s="34">
+        <x:v>46118.7388858565</x:v>
+      </x:c>
+      <x:c r="M79" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B80" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C80" s="30" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D80" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E80" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F80" s="30" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G80" s="30" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="H80" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I80" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J80" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K80" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L80" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M80" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B81" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C81" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D81" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E81" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F81" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G81" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H81" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I81" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J81" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K81" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L81" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M81" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B82" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C82" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="D82" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E82" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F82" s="30" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G82" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H82" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I82" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J82" s="31" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="K82" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L82" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M82" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B83" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C83" s="30" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D83" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E83" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F83" s="30" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="H83" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I83" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K83" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L83" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M83" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B84" s="30" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C84" s="30" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="D84" s="31" t="s"/>
+      <x:c r="E84" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F84" s="30" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H84" s="32">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I84" s="32">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="K84" s="33" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L84" s="34">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M84" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B85" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C85" s="30" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D85" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E85" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F85" s="30" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G85" s="30" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="H85" s="32">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I85" s="32">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J85" s="31" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="K85" s="33" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L85" s="34">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M85" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B88" s="18" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C88" s="19" t="s"/>
+      <x:c r="D88" s="19" t="s"/>
+      <x:c r="E88" s="20" t="s"/>
+      <x:c r="F88" s="20" t="s"/>
+    </x:row>
+    <x:row r="89" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B89" s="21" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C89" s="22" t="s"/>
+      <x:c r="D89" s="22" t="s"/>
+      <x:c r="E89" s="22" t="s"/>
+      <x:c r="F89" s="23" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B90" s="24" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C90" s="25" t="s"/>
+      <x:c r="D90" s="25" t="s"/>
+      <x:c r="E90" s="25" t="s"/>
+      <x:c r="F90" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B91" s="24" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C91" s="25" t="s"/>
+      <x:c r="D91" s="25" t="s"/>
+      <x:c r="E91" s="25" t="s"/>
+      <x:c r="F91" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B92" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C92" s="25" t="s"/>
+      <x:c r="D92" s="25" t="s"/>
+      <x:c r="E92" s="25" t="s"/>
+      <x:c r="F92" s="26" t="n">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B93" s="24" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C93" s="25" t="s"/>
+      <x:c r="D93" s="25" t="s"/>
+      <x:c r="E93" s="25" t="s"/>
+      <x:c r="F93" s="26" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B94" s="24" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C94" s="25" t="s"/>
+      <x:c r="D94" s="25" t="s"/>
+      <x:c r="E94" s="25" t="s"/>
+      <x:c r="F94" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B95" s="24" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C95" s="25" t="s"/>
+      <x:c r="D95" s="25" t="s"/>
+      <x:c r="E95" s="25" t="s"/>
+      <x:c r="F95" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B96" s="27" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C96" s="28" t="s"/>
+      <x:c r="D96" s="28" t="s"/>
+      <x:c r="E96" s="28" t="s"/>
+      <x:c r="F96" s="29" t="n">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
     <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
@@ -8886,18 +9597,20 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="13">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B73:F73"/>
-    <x:mergeCell ref="B74:E74"/>
-    <x:mergeCell ref="B75:E75"/>
-    <x:mergeCell ref="B76:E76"/>
-    <x:mergeCell ref="B77:E77"/>
-    <x:mergeCell ref="B78:E78"/>
-    <x:mergeCell ref="B79:E79"/>
+    <x:mergeCell ref="B88:F88"/>
+    <x:mergeCell ref="B89:E89"/>
+    <x:mergeCell ref="B90:E90"/>
+    <x:mergeCell ref="B91:E91"/>
+    <x:mergeCell ref="B92:E92"/>
+    <x:mergeCell ref="B93:E93"/>
+    <x:mergeCell ref="B94:E94"/>
+    <x:mergeCell ref="B95:E95"/>
+    <x:mergeCell ref="B96:E96"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -165,6 +165,18 @@
     <x:t>Amateur Radio Station Permit to PURCHASE</x:t>
   </x:si>
   <x:si>
+    <x:t>CHING'S COLLECTION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-ROXIV-08261-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1320-150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdadasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZXCASD</x:t>
   </x:si>
   <x:si>
@@ -177,6 +189,51 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
@@ -213,52 +270,199 @@
     <x:t>test123</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -270,418 +474,259 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08175</x:t>
@@ -5687,7 +5732,7 @@
       </x:c>
       <x:c r="D9" s="31" t="s"/>
       <x:c r="E9" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="30" t="s">
         <x:v>47</x:v>
@@ -5696,10 +5741,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H9" s="32">
-        <x:v>46119.5290592824</x:v>
+        <x:v>46126.0027495833</x:v>
       </x:c>
       <x:c r="I9" s="32">
-        <x:v>46119.5300361458</x:v>
+        <x:v>46126.1631260764</x:v>
       </x:c>
       <x:c r="J9" s="31" t="s">
         <x:v>49</x:v>
@@ -5708,7 +5753,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L9" s="34">
-        <x:v>46119.5304719792</x:v>
+        <x:v>46126.177127963</x:v>
       </x:c>
       <x:c r="M9" s="30" t="s">
         <x:v>21</x:v>
@@ -5716,37 +5761,35 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="30" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="30" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="s">
-        <x:v>16</x:v>
-      </x:c>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D10" s="31" t="s"/>
       <x:c r="E10" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F10" s="30" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G10" s="30" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.5290592824</x:v>
       </x:c>
       <x:c r="I10" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46119.5300361458</x:v>
       </x:c>
       <x:c r="J10" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K10" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L10" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46119.5304719792</x:v>
       </x:c>
       <x:c r="M10" s="30" t="s">
         <x:v>21</x:v>
@@ -5757,34 +5800,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="30" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5795,34 +5838,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="30" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G12" s="30" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K12" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5833,34 +5876,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D13" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="30" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="30" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K13" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5871,34 +5914,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G14" s="30" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K14" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5918,25 +5961,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G15" s="30" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K15" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5956,25 +5999,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G16" s="30" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -5994,25 +6037,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -6032,25 +6075,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -6070,25 +6113,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6108,25 +6151,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6146,25 +6189,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>80</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6184,25 +6227,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6222,25 +6265,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>86</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6260,25 +6303,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6298,25 +6341,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6336,25 +6379,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6374,25 +6417,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>64</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6412,25 +6455,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>98</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6450,25 +6493,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>101</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6488,25 +6531,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6526,25 +6569,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>107</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6564,25 +6607,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>110</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6608,19 +6651,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6640,25 +6683,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6678,25 +6721,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6716,25 +6759,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6754,25 +6797,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6792,25 +6835,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>127</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6836,10 +6879,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
         <x:v>130</x:v>
@@ -6848,7 +6891,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6874,19 +6917,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6906,25 +6949,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6944,25 +6987,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -6982,25 +7025,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -7020,25 +7063,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -7058,25 +7101,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -7096,25 +7139,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46124.701771875</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -7134,25 +7177,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>151</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -7172,25 +7215,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>154</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -7210,25 +7253,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -7248,25 +7291,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -7286,25 +7329,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G51" s="30" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -7324,25 +7367,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -7362,25 +7405,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G53" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>61</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7400,25 +7443,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G54" s="30" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7438,25 +7481,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>171</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>172</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7476,25 +7519,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G56" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>175</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7514,25 +7557,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G57" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>178</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7552,25 +7595,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G58" s="30" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>181</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7590,25 +7633,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G59" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
-        <x:v>184</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -7628,25 +7671,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G60" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -7666,25 +7709,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G61" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -7704,25 +7747,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="G62" s="30" t="s">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -7742,25 +7785,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G63" s="30" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -7780,25 +7823,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G64" s="30" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K64" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -7818,25 +7861,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="30" t="s">
-        <x:v>197</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G65" s="30" t="s">
-        <x:v>198</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>199</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -7856,25 +7899,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
-        <x:v>200</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="G66" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="H66" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I66" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J66" s="31" t="s">
-        <x:v>202</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -7894,25 +7937,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G67" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H67" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -7932,25 +7975,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
-        <x:v>205</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G68" s="30" t="s">
-        <x:v>206</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H68" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I68" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J68" s="31" t="s">
-        <x:v>207</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -7970,25 +8013,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G69" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H69" s="32">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I69" s="32">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J69" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -8008,25 +8051,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G70" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H70" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I70" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J70" s="31" t="s">
-        <x:v>110</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
@@ -8046,25 +8089,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
-        <x:v>212</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="G71" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="H71" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I71" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J71" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -8084,25 +8127,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G72" s="30" t="s">
-        <x:v>215</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H72" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I72" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J72" s="31" t="s">
-        <x:v>56</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -8122,25 +8165,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G73" s="30" t="s">
-        <x:v>217</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H73" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I73" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J73" s="31" t="s">
-        <x:v>218</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M73" s="30" t="s">
         <x:v>21</x:v>
@@ -8160,25 +8203,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G74" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H74" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I74" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J74" s="31" t="s">
-        <x:v>221</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K74" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M74" s="30" t="s">
         <x:v>21</x:v>
@@ -8198,25 +8241,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G75" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="H75" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I75" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J75" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K75" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M75" s="30" t="s">
         <x:v>21</x:v>
@@ -8224,10 +8267,10 @@
     </x:row>
     <x:row r="76" spans="1:28" ht="30" customHeight="1">
       <x:c r="B76" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D76" s="31" t="s">
         <x:v>16</x:v>
@@ -8236,25 +8279,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="G76" s="30" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="H76" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I76" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J76" s="31" t="s">
-        <x:v>228</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -8262,10 +8305,10 @@
     </x:row>
     <x:row r="77" spans="1:28" ht="30" customHeight="1">
       <x:c r="B77" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C77" s="30" t="s">
-        <x:v>229</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D77" s="31" t="s">
         <x:v>16</x:v>
@@ -8280,19 +8323,19 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="H77" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I77" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J77" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K77" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M77" s="30" t="s">
         <x:v>21</x:v>
@@ -8300,10 +8343,10 @@
     </x:row>
     <x:row r="78" spans="1:28" ht="30" customHeight="1">
       <x:c r="B78" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C78" s="30" t="s">
-        <x:v>232</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D78" s="31" t="s">
         <x:v>16</x:v>
@@ -8312,25 +8355,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="30" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G78" s="30" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G78" s="30" t="s">
-        <x:v>234</x:v>
-      </x:c>
       <x:c r="H78" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I78" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J78" s="31" t="s">
-        <x:v>235</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K78" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M78" s="30" t="s">
         <x:v>21</x:v>
@@ -8338,10 +8381,10 @@
     </x:row>
     <x:row r="79" spans="1:28" ht="30" customHeight="1">
       <x:c r="B79" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C79" s="30" t="s">
-        <x:v>236</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D79" s="31" t="s">
         <x:v>16</x:v>
@@ -8350,25 +8393,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F79" s="30" t="s">
-        <x:v>237</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G79" s="30" t="s">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H79" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I79" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J79" s="31" t="s">
-        <x:v>239</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K79" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M79" s="30" t="s">
         <x:v>21</x:v>
@@ -8376,10 +8419,10 @@
     </x:row>
     <x:row r="80" spans="1:28" ht="30" customHeight="1">
       <x:c r="B80" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C80" s="30" t="s">
-        <x:v>240</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D80" s="31" t="s">
         <x:v>16</x:v>
@@ -8388,25 +8431,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="30" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G80" s="30" t="s">
-        <x:v>242</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H80" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I80" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J80" s="31" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K80" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M80" s="30" t="s">
         <x:v>21</x:v>
@@ -8414,10 +8457,10 @@
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
       <x:c r="B81" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C81" s="30" t="s">
-        <x:v>243</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D81" s="31" t="s">
         <x:v>16</x:v>
@@ -8426,25 +8469,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F81" s="30" t="s">
-        <x:v>244</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G81" s="30" t="s">
-        <x:v>245</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H81" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I81" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J81" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K81" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L81" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M81" s="30" t="s">
         <x:v>21</x:v>
@@ -8452,10 +8495,10 @@
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
       <x:c r="B82" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C82" s="30" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="D82" s="31" t="s">
         <x:v>16</x:v>
@@ -8464,25 +8507,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F82" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G82" s="30" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G82" s="30" t="s">
-        <x:v>247</x:v>
-      </x:c>
       <x:c r="H82" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I82" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J82" s="31" t="s">
-        <x:v>248</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K82" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L82" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M82" s="30" t="s">
         <x:v>21</x:v>
@@ -8490,10 +8533,10 @@
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
       <x:c r="B83" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C83" s="30" t="s">
-        <x:v>46</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D83" s="31" t="s">
         <x:v>16</x:v>
@@ -8502,25 +8545,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="G83" s="30" t="s">
+      <x:c r="H83" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I83" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="H83" s="32">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I83" s="32">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J83" s="31" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="K83" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L83" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M83" s="30" t="s">
         <x:v>21</x:v>
@@ -8528,35 +8571,37 @@
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
       <x:c r="B84" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C84" s="30" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="C84" s="30" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="D84" s="31" t="s"/>
+      <x:c r="D84" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E84" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="30" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="G84" s="30" t="s">
+      <x:c r="H84" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I84" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="H84" s="32">
-        <x:v>46124.1588481829</x:v>
-      </x:c>
-      <x:c r="I84" s="32">
-        <x:v>46124.1588689236</x:v>
-      </x:c>
-      <x:c r="J84" s="31" t="s">
-        <x:v>255</x:v>
-      </x:c>
       <x:c r="K84" s="33" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L84" s="34">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M84" s="30" t="s">
         <x:v>21</x:v>
@@ -8564,122 +8609,255 @@
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
       <x:c r="B85" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C85" s="30" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D85" s="31" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E85" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G85" s="30" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H85" s="32">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I85" s="32">
-        <x:v>46023</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J85" s="31" t="s">
-        <x:v>260</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K85" s="33" t="n">
-        <x:v>3100</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L85" s="34">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M85" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B86" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C86" s="30" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D86" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E86" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F86" s="30" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G86" s="30" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H86" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I86" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J86" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K86" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L86" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M86" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B87" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C87" s="30" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D87" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E87" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F87" s="30" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="G87" s="30" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="H87" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I87" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J87" s="31" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="K87" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L87" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M87" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B88" s="18" t="s">
+      <x:c r="B88" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C88" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D88" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E88" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F88" s="30" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G88" s="30" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H88" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I88" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J88" s="31" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K88" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L88" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M88" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B89" s="30" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C89" s="30" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D89" s="31" t="s"/>
+      <x:c r="E89" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F89" s="30" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G89" s="30" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H89" s="32">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I89" s="32">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J89" s="31" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="K89" s="33" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L89" s="34">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M89" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B90" s="30" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C90" s="30" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D90" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E90" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F90" s="30" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G90" s="30" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H90" s="32">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I90" s="32">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J90" s="31" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="K90" s="33" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L90" s="34">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M90" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B93" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C88" s="19" t="s"/>
-      <x:c r="D88" s="19" t="s"/>
-      <x:c r="E88" s="20" t="s"/>
-      <x:c r="F88" s="20" t="s"/>
-    </x:row>
-    <x:row r="89" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B89" s="21" t="s">
+      <x:c r="C93" s="19" t="s"/>
+      <x:c r="D93" s="19" t="s"/>
+      <x:c r="E93" s="20" t="s"/>
+      <x:c r="F93" s="20" t="s"/>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B94" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C89" s="22" t="s"/>
-      <x:c r="D89" s="22" t="s"/>
-      <x:c r="E89" s="22" t="s"/>
-      <x:c r="F89" s="23" t="s">
+      <x:c r="C94" s="22" t="s"/>
+      <x:c r="D94" s="22" t="s"/>
+      <x:c r="E94" s="22" t="s"/>
+      <x:c r="F94" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B90" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C90" s="25" t="s"/>
-      <x:c r="D90" s="25" t="s"/>
-      <x:c r="E90" s="25" t="s"/>
-      <x:c r="F90" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B91" s="24" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C91" s="25" t="s"/>
-      <x:c r="D91" s="25" t="s"/>
-      <x:c r="E91" s="25" t="s"/>
-      <x:c r="F91" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B92" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C92" s="25" t="s"/>
-      <x:c r="D92" s="25" t="s"/>
-      <x:c r="E92" s="25" t="s"/>
-      <x:c r="F92" s="26" t="n">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B93" s="24" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="C93" s="25" t="s"/>
-      <x:c r="D93" s="25" t="s"/>
-      <x:c r="E93" s="25" t="s"/>
-      <x:c r="F93" s="26" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B94" s="24" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="C94" s="25" t="s"/>
-      <x:c r="D94" s="25" t="s"/>
-      <x:c r="E94" s="25" t="s"/>
-      <x:c r="F94" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:28" ht="18" customHeight="1">
       <x:c r="B95" s="24" t="s">
-        <x:v>256</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C95" s="25" t="s"/>
       <x:c r="D95" s="25" t="s"/>
@@ -8688,22 +8866,72 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B96" s="27" t="s">
+    <x:row r="96" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B96" s="24" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C96" s="25" t="s"/>
+      <x:c r="D96" s="25" t="s"/>
+      <x:c r="E96" s="25" t="s"/>
+      <x:c r="F96" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B97" s="24" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C97" s="25" t="s"/>
+      <x:c r="D97" s="25" t="s"/>
+      <x:c r="E97" s="25" t="s"/>
+      <x:c r="F97" s="26" t="n">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B98" s="24" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C98" s="25" t="s"/>
+      <x:c r="D98" s="25" t="s"/>
+      <x:c r="E98" s="25" t="s"/>
+      <x:c r="F98" s="26" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B99" s="24" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C99" s="25" t="s"/>
+      <x:c r="D99" s="25" t="s"/>
+      <x:c r="E99" s="25" t="s"/>
+      <x:c r="F99" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B100" s="24" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C100" s="25" t="s"/>
+      <x:c r="D100" s="25" t="s"/>
+      <x:c r="E100" s="25" t="s"/>
+      <x:c r="F100" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B101" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C96" s="28" t="s"/>
-      <x:c r="D96" s="28" t="s"/>
-      <x:c r="E96" s="28" t="s"/>
-      <x:c r="F96" s="29" t="n">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C101" s="28" t="s"/>
+      <x:c r="D101" s="28" t="s"/>
+      <x:c r="E101" s="28" t="s"/>
+      <x:c r="F101" s="29" t="n">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
     <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
@@ -9602,15 +9830,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B88:F88"/>
-    <x:mergeCell ref="B89:E89"/>
-    <x:mergeCell ref="B90:E90"/>
-    <x:mergeCell ref="B91:E91"/>
-    <x:mergeCell ref="B92:E92"/>
-    <x:mergeCell ref="B93:E93"/>
+    <x:mergeCell ref="B93:F93"/>
     <x:mergeCell ref="B94:E94"/>
     <x:mergeCell ref="B95:E95"/>
     <x:mergeCell ref="B96:E96"/>
+    <x:mergeCell ref="B97:E97"/>
+    <x:mergeCell ref="B98:E98"/>
+    <x:mergeCell ref="B99:E99"/>
+    <x:mergeCell ref="B100:E100"/>
+    <x:mergeCell ref="B101:E101"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -198,6 +198,15 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08296</x:t>
   </x:si>
   <x:si>
@@ -216,13 +225,322 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08215</x:t>
@@ -234,235 +552,73 @@
     <x:t>zxcsd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -474,97 +630,46 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08190</x:t>
@@ -573,43 +678,40 @@
     <x:t>61-4-2026-1301-555</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
@@ -621,13 +723,34 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08181</x:t>
@@ -639,55 +762,22 @@
     <x:t>tesg213</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08179</x:t>
@@ -703,45 +793,6 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5853,10 +5904,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>59</x:v>
@@ -5865,7 +5916,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5891,10 +5942,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>62</x:v>
@@ -5903,7 +5954,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5929,10 +5980,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>65</x:v>
@@ -5941,7 +5992,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -5952,13 +6003,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D15" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
         <x:v>66</x:v>
@@ -5967,10 +6018,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>68</x:v>
@@ -5979,7 +6030,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -5990,13 +6041,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
         <x:v>69</x:v>
@@ -6005,19 +6056,19 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K16" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -6028,34 +6079,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D17" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G17" s="30" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K17" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -6066,34 +6117,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D18" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="30" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G18" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -6104,34 +6155,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="30" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D19" s="31" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="30" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G19" s="30" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K19" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6151,25 +6202,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="30" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G20" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>80</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6189,25 +6240,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6227,16 +6278,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G22" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I22" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
         <x:v>85</x:v>
@@ -6245,7 +6296,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M22" s="30" t="s">
         <x:v>21</x:v>
@@ -6265,25 +6316,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I23" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M23" s="30" t="s">
         <x:v>21</x:v>
@@ -6303,25 +6354,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="32">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I24" s="32">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J24" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K24" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="34">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M24" s="30" t="s">
         <x:v>21</x:v>
@@ -6341,25 +6392,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6379,25 +6430,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6417,25 +6468,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="G27" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H27" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I27" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J27" s="31" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K27" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M27" s="30" t="s">
         <x:v>21</x:v>
@@ -6455,25 +6506,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G28" s="30" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H28" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I28" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J28" s="31" t="s">
-        <x:v>62</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K28" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M28" s="30" t="s">
         <x:v>21</x:v>
@@ -6493,25 +6544,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G29" s="30" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H29" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I29" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J29" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="K29" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M29" s="30" t="s">
         <x:v>21</x:v>
@@ -6531,25 +6582,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="G30" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6569,25 +6620,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6607,25 +6658,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="30" t="s">
-        <x:v>109</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="G32" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H32" s="32">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I32" s="32">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J32" s="31" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K32" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M32" s="30" t="s">
         <x:v>21</x:v>
@@ -6645,25 +6696,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G33" s="30" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>113</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6683,25 +6734,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>116</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6721,25 +6772,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6759,25 +6810,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="G36" s="30" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K36" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6797,25 +6848,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G37" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="K37" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6835,25 +6886,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G38" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K38" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6873,25 +6924,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="30" t="s">
-        <x:v>128</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G39" s="30" t="s">
-        <x:v>129</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
-        <x:v>130</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K39" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6911,25 +6962,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="30" t="s">
-        <x:v>131</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G40" s="30" t="s">
-        <x:v>132</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
-        <x:v>133</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K40" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -6949,25 +7000,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="30" t="s">
-        <x:v>134</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G41" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
-        <x:v>136</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K41" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -6987,25 +7038,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="30" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G42" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
-        <x:v>139</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K42" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -7025,25 +7076,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="30" t="s">
-        <x:v>140</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G43" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>142</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -7063,25 +7114,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>145</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -7101,25 +7152,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -7139,25 +7190,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G46" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K46" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -7177,25 +7228,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="30" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G47" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K47" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -7215,25 +7266,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G48" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -7253,25 +7304,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G49" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H49" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I49" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>159</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -7291,25 +7342,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G50" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>162</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -7335,19 +7386,19 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46124.701771875</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -7367,25 +7418,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G52" s="30" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H52" s="32">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I52" s="32">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J52" s="31" t="s">
-        <x:v>167</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -7411,19 +7462,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>170</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7443,25 +7494,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="30" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G54" s="30" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="G54" s="30" t="s">
-        <x:v>172</x:v>
-      </x:c>
       <x:c r="H54" s="32">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>173</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7481,25 +7532,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G55" s="30" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H55" s="32">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I55" s="32">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="G55" s="30" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="H55" s="32">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I55" s="32">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J55" s="31" t="s">
-        <x:v>176</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7519,25 +7570,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="30" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G56" s="30" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H56" s="32">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I56" s="32">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J56" s="31" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="G56" s="30" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="H56" s="32">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I56" s="32">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J56" s="31" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7557,25 +7608,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="H57" s="32">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I57" s="32">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J57" s="31" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="G57" s="30" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="H57" s="32">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I57" s="32">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J57" s="31" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7595,25 +7646,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G58" s="30" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G58" s="30" t="s">
-        <x:v>183</x:v>
-      </x:c>
       <x:c r="H58" s="32">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46122.244317963</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>80</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7633,25 +7684,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="G59" s="30" t="s">
+      <x:c r="H59" s="32">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="H59" s="32">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I59" s="32">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J59" s="31" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -7677,10 +7728,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
         <x:v>188</x:v>
@@ -7689,7 +7740,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -7715,10 +7766,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
         <x:v>191</x:v>
@@ -7727,7 +7778,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -7753,10 +7804,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
         <x:v>194</x:v>
@@ -7765,7 +7816,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -7791,10 +7842,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46123.061368912</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
         <x:v>197</x:v>
@@ -7803,7 +7854,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -7829,10 +7880,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
         <x:v>200</x:v>
@@ -7841,7 +7892,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -7867,10 +7918,10 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
         <x:v>203</x:v>
@@ -7879,7 +7930,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -7905,19 +7956,19 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="H66" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I66" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J66" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -7943,10 +7994,10 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H67" s="32">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
         <x:v>208</x:v>
@@ -7955,7 +8006,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -7981,19 +8032,19 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="H68" s="32">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I68" s="32">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J68" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -8013,25 +8064,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="G69" s="30" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="H69" s="32">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I69" s="32">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J69" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -8051,25 +8102,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G70" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H70" s="32">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I70" s="32">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J70" s="31" t="s">
-        <x:v>215</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
@@ -8089,25 +8140,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="G71" s="30" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="H71" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I71" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J71" s="31" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -8127,25 +8178,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G72" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H72" s="32">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I72" s="32">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J72" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -8165,25 +8216,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G73" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H73" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I73" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J73" s="31" t="s">
-        <x:v>223</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M73" s="30" t="s">
         <x:v>21</x:v>
@@ -8203,25 +8254,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G74" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H74" s="32">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I74" s="32">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J74" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K74" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M74" s="30" t="s">
         <x:v>21</x:v>
@@ -8241,25 +8292,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G75" s="30" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H75" s="32">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I75" s="32">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J75" s="31" t="s">
-        <x:v>125</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K75" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M75" s="30" t="s">
         <x:v>21</x:v>
@@ -8279,25 +8330,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G76" s="30" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H76" s="32">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I76" s="32">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J76" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -8317,25 +8368,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F77" s="30" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="G77" s="30" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="H77" s="32">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I77" s="32">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J77" s="31" t="s">
-        <x:v>75</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K77" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M77" s="30" t="s">
         <x:v>21</x:v>
@@ -8355,25 +8406,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="30" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="G78" s="30" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="H78" s="32">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I78" s="32">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J78" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K78" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="34">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M78" s="30" t="s">
         <x:v>21</x:v>
@@ -8393,25 +8444,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F79" s="30" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="G79" s="30" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="H79" s="32">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I79" s="32">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J79" s="31" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K79" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="34">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M79" s="30" t="s">
         <x:v>21</x:v>
@@ -8431,16 +8482,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="30" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="G80" s="30" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="H80" s="32">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I80" s="32">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J80" s="31" t="s">
         <x:v>30</x:v>
@@ -8449,7 +8500,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M80" s="30" t="s">
         <x:v>21</x:v>
@@ -8457,10 +8508,10 @@
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
       <x:c r="B81" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C81" s="30" t="s">
-        <x:v>240</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D81" s="31" t="s">
         <x:v>16</x:v>
@@ -8469,25 +8520,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F81" s="30" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G81" s="30" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="H81" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I81" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J81" s="31" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="K81" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M81" s="30" t="s">
         <x:v>21</x:v>
@@ -8495,10 +8546,10 @@
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
       <x:c r="B82" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C82" s="30" t="s">
-        <x:v>244</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D82" s="31" t="s">
         <x:v>16</x:v>
@@ -8513,19 +8564,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="H82" s="32">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I82" s="32">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J82" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="K82" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M82" s="30" t="s">
         <x:v>21</x:v>
@@ -8533,10 +8584,10 @@
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
       <x:c r="B83" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C83" s="30" t="s">
-        <x:v>247</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D83" s="31" t="s">
         <x:v>16</x:v>
@@ -8545,25 +8596,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="G83" s="30" t="s">
-        <x:v>249</x:v>
-      </x:c>
       <x:c r="H83" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I83" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J83" s="31" t="s">
-        <x:v>250</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K83" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M83" s="30" t="s">
         <x:v>21</x:v>
@@ -8571,10 +8622,10 @@
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
       <x:c r="B84" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C84" s="30" t="s">
-        <x:v>251</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D84" s="31" t="s">
         <x:v>16</x:v>
@@ -8583,25 +8634,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="30" t="s">
-        <x:v>252</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G84" s="30" t="s">
-        <x:v>253</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H84" s="32">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I84" s="32">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J84" s="31" t="s">
-        <x:v>254</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K84" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M84" s="30" t="s">
         <x:v>21</x:v>
@@ -8609,10 +8660,10 @@
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
       <x:c r="B85" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C85" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D85" s="31" t="s">
         <x:v>16</x:v>
@@ -8621,25 +8672,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G85" s="30" t="s">
-        <x:v>257</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H85" s="32">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I85" s="32">
-        <x:v>46118.647188044</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J85" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="K85" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M85" s="30" t="s">
         <x:v>21</x:v>
@@ -8647,10 +8698,10 @@
     </x:row>
     <x:row r="86" spans="1:28" ht="30" customHeight="1">
       <x:c r="B86" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C86" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D86" s="31" t="s">
         <x:v>16</x:v>
@@ -8659,25 +8710,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="30" t="s">
-        <x:v>259</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G86" s="30" t="s">
-        <x:v>260</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H86" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I86" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J86" s="31" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="K86" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M86" s="30" t="s">
         <x:v>21</x:v>
@@ -8685,10 +8736,10 @@
     </x:row>
     <x:row r="87" spans="1:28" ht="30" customHeight="1">
       <x:c r="B87" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C87" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="D87" s="31" t="s">
         <x:v>16</x:v>
@@ -8697,25 +8748,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="30" t="s">
-        <x:v>261</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G87" s="30" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H87" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.5788871875</x:v>
       </x:c>
       <x:c r="I87" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.5789284722</x:v>
       </x:c>
       <x:c r="J87" s="31" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K87" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L87" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M87" s="30" t="s">
         <x:v>21</x:v>
@@ -8723,10 +8774,10 @@
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
       <x:c r="B88" s="30" t="s">
-        <x:v>239</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C88" s="30" t="s">
-        <x:v>50</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D88" s="31" t="s">
         <x:v>16</x:v>
@@ -8735,25 +8786,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="30" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G88" s="30" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H88" s="32">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I88" s="32">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J88" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K88" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L88" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M88" s="30" t="s">
         <x:v>21</x:v>
@@ -8761,35 +8812,37 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="30" t="s">
-        <x:v>266</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C89" s="30" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D89" s="31" t="s"/>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="D89" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E89" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="30" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G89" s="30" t="s">
-        <x:v>269</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="H89" s="32">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I89" s="32">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J89" s="31" t="s">
-        <x:v>270</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="K89" s="33" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L89" s="34">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M89" s="30" t="s">
         <x:v>21</x:v>
@@ -8797,147 +8850,367 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="30" t="s">
-        <x:v>271</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C90" s="30" t="s">
-        <x:v>272</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D90" s="31" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E90" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="30" t="s">
-        <x:v>273</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G90" s="30" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H90" s="32">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46118.7372774306</x:v>
       </x:c>
       <x:c r="I90" s="32">
-        <x:v>46023</x:v>
+        <x:v>46118.7373236806</x:v>
       </x:c>
       <x:c r="J90" s="31" t="s">
-        <x:v>275</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="K90" s="33" t="n">
-        <x:v>3100</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="34">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M90" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B91" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C91" s="30" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D91" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E91" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F91" s="30" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G91" s="30" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H91" s="32">
+        <x:v>46118.6471475926</x:v>
+      </x:c>
+      <x:c r="I91" s="32">
+        <x:v>46118.647188044</x:v>
+      </x:c>
+      <x:c r="J91" s="31" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K91" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L91" s="34">
+        <x:v>46118.6489296181</x:v>
+      </x:c>
+      <x:c r="M91" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B92" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C92" s="30" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D92" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E92" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F92" s="30" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="G92" s="30" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="H92" s="32">
+        <x:v>46118.7761679514</x:v>
+      </x:c>
+      <x:c r="I92" s="32">
+        <x:v>46118.7762103819</x:v>
+      </x:c>
+      <x:c r="J92" s="31" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K92" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L92" s="34">
+        <x:v>46118.7774822107</x:v>
+      </x:c>
+      <x:c r="M92" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B93" s="18" t="s">
+      <x:c r="B93" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C93" s="30" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D93" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E93" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F93" s="30" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G93" s="30" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H93" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I93" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J93" s="31" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="K93" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L93" s="34">
+        <x:v>46118.4416909375</x:v>
+      </x:c>
+      <x:c r="M93" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B94" s="30" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C94" s="30" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D94" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E94" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F94" s="30" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G94" s="30" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H94" s="32">
+        <x:v>46119.4833706713</x:v>
+      </x:c>
+      <x:c r="I94" s="32">
+        <x:v>46119.4833991435</x:v>
+      </x:c>
+      <x:c r="J94" s="31" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K94" s="33" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L94" s="34">
+        <x:v>46119.4846717477</x:v>
+      </x:c>
+      <x:c r="M94" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B95" s="30" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C95" s="30" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D95" s="31" t="s"/>
+      <x:c r="E95" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F95" s="30" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G95" s="30" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H95" s="32">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I95" s="32">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J95" s="31" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="K95" s="33" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L95" s="34">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M95" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B96" s="30" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C96" s="30" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="D96" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E96" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F96" s="30" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="G96" s="30" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="H96" s="32">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I96" s="32">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J96" s="31" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="K96" s="33" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L96" s="34">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M96" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B99" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C93" s="19" t="s"/>
-      <x:c r="D93" s="19" t="s"/>
-      <x:c r="E93" s="20" t="s"/>
-      <x:c r="F93" s="20" t="s"/>
-    </x:row>
-    <x:row r="94" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B94" s="21" t="s">
+      <x:c r="C99" s="19" t="s"/>
+      <x:c r="D99" s="19" t="s"/>
+      <x:c r="E99" s="20" t="s"/>
+      <x:c r="F99" s="20" t="s"/>
+    </x:row>
+    <x:row r="100" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B100" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C94" s="22" t="s"/>
-      <x:c r="D94" s="22" t="s"/>
-      <x:c r="E94" s="22" t="s"/>
-      <x:c r="F94" s="23" t="s">
+      <x:c r="C100" s="22" t="s"/>
+      <x:c r="D100" s="22" t="s"/>
+      <x:c r="E100" s="22" t="s"/>
+      <x:c r="F100" s="23" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B95" s="24" t="s">
+    <x:row r="101" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B101" s="24" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C95" s="25" t="s"/>
-      <x:c r="D95" s="25" t="s"/>
-      <x:c r="E95" s="25" t="s"/>
-      <x:c r="F95" s="26" t="n">
+      <x:c r="C101" s="25" t="s"/>
+      <x:c r="D101" s="25" t="s"/>
+      <x:c r="E101" s="25" t="s"/>
+      <x:c r="F101" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B96" s="24" t="s">
+    <x:row r="102" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B102" s="24" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C96" s="25" t="s"/>
-      <x:c r="D96" s="25" t="s"/>
-      <x:c r="E96" s="25" t="s"/>
-      <x:c r="F96" s="26" t="n">
+      <x:c r="C102" s="25" t="s"/>
+      <x:c r="D102" s="25" t="s"/>
+      <x:c r="E102" s="25" t="s"/>
+      <x:c r="F102" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B97" s="24" t="s">
+    <x:row r="103" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B103" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C97" s="25" t="s"/>
-      <x:c r="D97" s="25" t="s"/>
-      <x:c r="E97" s="25" t="s"/>
-      <x:c r="F97" s="26" t="n">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B98" s="24" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="C98" s="25" t="s"/>
-      <x:c r="D98" s="25" t="s"/>
-      <x:c r="E98" s="25" t="s"/>
-      <x:c r="F98" s="26" t="n">
+      <x:c r="C103" s="25" t="s"/>
+      <x:c r="D103" s="25" t="s"/>
+      <x:c r="E103" s="25" t="s"/>
+      <x:c r="F103" s="26" t="n">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B104" s="24" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C104" s="25" t="s"/>
+      <x:c r="D104" s="25" t="s"/>
+      <x:c r="E104" s="25" t="s"/>
+      <x:c r="F104" s="26" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B99" s="24" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="C99" s="25" t="s"/>
-      <x:c r="D99" s="25" t="s"/>
-      <x:c r="E99" s="25" t="s"/>
-      <x:c r="F99" s="26" t="n">
+    <x:row r="105" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B105" s="24" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C105" s="25" t="s"/>
+      <x:c r="D105" s="25" t="s"/>
+      <x:c r="E105" s="25" t="s"/>
+      <x:c r="F105" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B100" s="24" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="C100" s="25" t="s"/>
-      <x:c r="D100" s="25" t="s"/>
-      <x:c r="E100" s="25" t="s"/>
-      <x:c r="F100" s="26" t="n">
+    <x:row r="106" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B106" s="24" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C106" s="25" t="s"/>
+      <x:c r="D106" s="25" t="s"/>
+      <x:c r="E106" s="25" t="s"/>
+      <x:c r="F106" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B101" s="27" t="s">
+    <x:row r="107" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B107" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C101" s="28" t="s"/>
-      <x:c r="D101" s="28" t="s"/>
-      <x:c r="E101" s="28" t="s"/>
-      <x:c r="F101" s="29" t="n">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C107" s="28" t="s"/>
+      <x:c r="D107" s="28" t="s"/>
+      <x:c r="E107" s="28" t="s"/>
+      <x:c r="F107" s="29" t="n">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
     <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
@@ -9830,15 +10103,15 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B93:F93"/>
-    <x:mergeCell ref="B94:E94"/>
-    <x:mergeCell ref="B95:E95"/>
-    <x:mergeCell ref="B96:E96"/>
-    <x:mergeCell ref="B97:E97"/>
-    <x:mergeCell ref="B98:E98"/>
-    <x:mergeCell ref="B99:E99"/>
+    <x:mergeCell ref="B99:F99"/>
     <x:mergeCell ref="B100:E100"/>
     <x:mergeCell ref="B101:E101"/>
+    <x:mergeCell ref="B102:E102"/>
+    <x:mergeCell ref="B103:E103"/>
+    <x:mergeCell ref="B104:E104"/>
+    <x:mergeCell ref="B105:E105"/>
+    <x:mergeCell ref="B106:E106"/>
+    <x:mergeCell ref="B107:E107"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -198,6 +198,24 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08292</x:t>
   </x:si>
   <x:si>
@@ -207,24 +225,6 @@
     <x:t>sczxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08337</x:t>
   </x:si>
   <x:si>
@@ -531,105 +531,111 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08189</x:t>
   </x:si>
   <x:si>
@@ -663,6 +669,48 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
   </x:si>
   <x:si>
@@ -672,10 +720,40 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
@@ -687,70 +765,31 @@
     <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08181</x:t>
@@ -760,39 +799,6 @@
   </x:si>
   <x:si>
     <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5904,10 +5910,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>59</x:v>
@@ -5916,7 +5922,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5980,10 +5986,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>65</x:v>
@@ -5992,7 +5998,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -6746,7 +6752,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
@@ -7316,7 +7322,7 @@
         <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J49" s="31" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
@@ -7462,19 +7468,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7500,19 +7506,19 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7532,25 +7538,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G55" s="30" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H55" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I55" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J55" s="31" t="s">
-        <x:v>174</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7576,10 +7582,10 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
         <x:v>177</x:v>
@@ -7588,7 +7594,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7614,10 +7620,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="H57" s="32">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
         <x:v>180</x:v>
@@ -7626,7 +7632,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7652,19 +7658,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H58" s="32">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I58" s="32">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J58" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7684,25 +7690,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="G59" s="30" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="H59" s="32">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I59" s="32">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J59" s="31" t="s">
-        <x:v>185</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -7728,10 +7734,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="H60" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I60" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J60" s="31" t="s">
         <x:v>188</x:v>
@@ -7740,7 +7746,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -7766,10 +7772,10 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="H61" s="32">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
         <x:v>191</x:v>
@@ -7778,7 +7784,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -7804,10 +7810,10 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H62" s="32">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I62" s="32">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J62" s="31" t="s">
         <x:v>194</x:v>
@@ -7816,7 +7822,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -7842,10 +7848,10 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="H63" s="32">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I63" s="32">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J63" s="31" t="s">
         <x:v>197</x:v>
@@ -7854,7 +7860,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -7880,10 +7886,10 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="H64" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I64" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J64" s="31" t="s">
         <x:v>200</x:v>
@@ -7892,7 +7898,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -7918,19 +7924,19 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="H65" s="32">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I65" s="32">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J65" s="31" t="s">
-        <x:v>203</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -7950,25 +7956,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G66" s="30" t="s">
+      <x:c r="H66" s="32">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I66" s="32">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="H66" s="32">
-        <x:v>46124.1449755903</x:v>
-      </x:c>
-      <x:c r="I66" s="32">
-        <x:v>46124.1465040046</x:v>
-      </x:c>
-      <x:c r="J66" s="31" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -7994,19 +8000,19 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H67" s="32">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
-        <x:v>208</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -8026,25 +8032,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G68" s="30" t="s">
+      <x:c r="H68" s="32">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I68" s="32">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="H68" s="32">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I68" s="32">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J68" s="31" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -8064,25 +8070,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G69" s="30" t="s">
+      <x:c r="H69" s="32">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I69" s="32">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J69" s="31" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="H69" s="32">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I69" s="32">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J69" s="31" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -8102,10 +8108,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="G70" s="30" t="s">
-        <x:v>216</x:v>
       </x:c>
       <x:c r="H70" s="32">
         <x:v>46124.150742662</x:v>
@@ -8140,25 +8146,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G71" s="30" t="s">
+      <x:c r="H71" s="32">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I71" s="32">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="H71" s="32">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I71" s="32">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J71" s="31" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -8178,10 +8184,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="G72" s="30" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="H72" s="32">
         <x:v>46122.3767795718</x:v>
@@ -8190,7 +8196,7 @@
         <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J72" s="31" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
@@ -8216,10 +8222,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="G73" s="30" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="H73" s="32">
         <x:v>46122.3879258681</x:v>
@@ -8254,10 +8260,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="G74" s="30" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="H74" s="32">
         <x:v>46122.3885020718</x:v>
@@ -8292,10 +8298,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="G75" s="30" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="H75" s="32">
         <x:v>46122.3974322338</x:v>
@@ -8330,25 +8336,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G76" s="30" t="s">
+      <x:c r="H76" s="32">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I76" s="32">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="H76" s="32">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I76" s="32">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J76" s="31" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -8368,10 +8374,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F77" s="30" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="G77" s="30" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="H77" s="32">
         <x:v>46122.5623107755</x:v>
@@ -8406,10 +8412,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="30" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G78" s="30" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="G78" s="30" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="H78" s="32">
         <x:v>46122.5911383796</x:v>
@@ -8418,7 +8424,7 @@
         <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J78" s="31" t="s">
-        <x:v>236</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K78" s="33" t="n">
         <x:v>210</x:v>
@@ -8444,25 +8450,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F79" s="30" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G79" s="30" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G79" s="30" t="s">
-        <x:v>238</x:v>
-      </x:c>
       <x:c r="H79" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I79" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J79" s="31" t="s">
-        <x:v>239</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K79" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M79" s="30" t="s">
         <x:v>21</x:v>
@@ -8482,25 +8488,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="30" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G80" s="30" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="H80" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I80" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J80" s="31" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="G80" s="30" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="H80" s="32">
-        <x:v>46126.5341923727</x:v>
-      </x:c>
-      <x:c r="I80" s="32">
-        <x:v>46126.5348242708</x:v>
-      </x:c>
-      <x:c r="J80" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K80" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="34">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M80" s="30" t="s">
         <x:v>21</x:v>
@@ -8520,25 +8526,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F81" s="30" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G81" s="30" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G81" s="30" t="s">
-        <x:v>243</x:v>
-      </x:c>
       <x:c r="H81" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I81" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J81" s="31" t="s">
-        <x:v>244</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K81" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M81" s="30" t="s">
         <x:v>21</x:v>
@@ -8558,25 +8564,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F82" s="30" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G82" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="H82" s="32">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I82" s="32">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J82" s="31" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="G82" s="30" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H82" s="32">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I82" s="32">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J82" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K82" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="34">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M82" s="30" t="s">
         <x:v>21</x:v>
@@ -8596,10 +8602,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="30" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="G83" s="30" t="s">
-        <x:v>248</x:v>
       </x:c>
       <x:c r="H83" s="32">
         <x:v>46122.6182774306</x:v>
@@ -8634,10 +8640,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="30" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="G84" s="30" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="H84" s="32">
         <x:v>46122.6795081481</x:v>
@@ -8672,10 +8678,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="30" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G85" s="30" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="G85" s="30" t="s">
-        <x:v>252</x:v>
       </x:c>
       <x:c r="H85" s="32">
         <x:v>46122.6819179514</x:v>
@@ -8684,7 +8690,7 @@
         <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J85" s="31" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K85" s="33" t="n">
         <x:v>210</x:v>
@@ -8710,10 +8716,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="30" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G86" s="30" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="G86" s="30" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="H86" s="32">
         <x:v>46122.7261372338</x:v>
@@ -8736,10 +8742,10 @@
     </x:row>
     <x:row r="87" spans="1:28" ht="30" customHeight="1">
       <x:c r="B87" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C87" s="30" t="s">
-        <x:v>257</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D87" s="31" t="s">
         <x:v>16</x:v>
@@ -8748,25 +8754,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G87" s="30" t="s">
-        <x:v>259</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="H87" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I87" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J87" s="31" t="s">
-        <x:v>260</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="K87" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M87" s="30" t="s">
         <x:v>21</x:v>
@@ -8774,10 +8780,10 @@
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
       <x:c r="B88" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C88" s="30" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D88" s="31" t="s">
         <x:v>16</x:v>
@@ -8786,25 +8792,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="30" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G88" s="30" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H88" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I88" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J88" s="31" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="G88" s="30" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="H88" s="32">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I88" s="32">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J88" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K88" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L88" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M88" s="30" t="s">
         <x:v>21</x:v>
@@ -8812,10 +8818,10 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C89" s="30" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D89" s="31" t="s">
         <x:v>16</x:v>
@@ -8824,25 +8830,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="30" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G89" s="30" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="G89" s="30" t="s">
-        <x:v>266</x:v>
-      </x:c>
       <x:c r="H89" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I89" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J89" s="31" t="s">
-        <x:v>267</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K89" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L89" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M89" s="30" t="s">
         <x:v>21</x:v>
@@ -8850,10 +8856,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C90" s="30" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D90" s="31" t="s">
         <x:v>16</x:v>
@@ -8862,25 +8868,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="30" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="G90" s="30" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="H90" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I90" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J90" s="31" t="s">
         <x:v>269</x:v>
-      </x:c>
-      <x:c r="G90" s="30" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H90" s="32">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I90" s="32">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J90" s="31" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="K90" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M90" s="30" t="s">
         <x:v>21</x:v>
@@ -8888,10 +8894,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C91" s="30" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D91" s="31" t="s">
         <x:v>16</x:v>
@@ -8900,25 +8906,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F91" s="30" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G91" s="30" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H91" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I91" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J91" s="31" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="G91" s="30" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H91" s="32">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I91" s="32">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J91" s="31" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K91" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M91" s="30" t="s">
         <x:v>21</x:v>
@@ -8926,10 +8932,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C92" s="30" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D92" s="31" t="s">
         <x:v>16</x:v>
@@ -8938,25 +8944,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F92" s="30" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G92" s="30" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="G92" s="30" t="s">
-        <x:v>277</x:v>
-      </x:c>
       <x:c r="H92" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I92" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J92" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K92" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M92" s="30" t="s">
         <x:v>21</x:v>
@@ -8964,10 +8970,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C93" s="30" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D93" s="31" t="s">
         <x:v>16</x:v>
@@ -8982,19 +8988,19 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H93" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I93" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J93" s="31" t="s">
-        <x:v>280</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K93" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M93" s="30" t="s">
         <x:v>21</x:v>
@@ -9002,10 +9008,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C94" s="30" t="s">
-        <x:v>50</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D94" s="31" t="s">
         <x:v>16</x:v>
@@ -9014,25 +9020,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F94" s="30" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G94" s="30" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="G94" s="30" t="s">
+      <x:c r="H94" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I94" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J94" s="31" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="H94" s="32">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I94" s="32">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J94" s="31" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K94" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M94" s="30" t="s">
         <x:v>21</x:v>
@@ -9040,35 +9046,37 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="30" t="s">
-        <x:v>283</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C95" s="30" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D95" s="31" t="s"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D95" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E95" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F95" s="30" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="G95" s="30" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="H95" s="32">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I95" s="32">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J95" s="31" t="s">
-        <x:v>287</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K95" s="33" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="34">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M95" s="30" t="s">
         <x:v>21</x:v>
@@ -9076,122 +9084,147 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="30" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C96" s="30" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D96" s="31" t="s">
-        <x:v>41</x:v>
-      </x:c>
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D96" s="31" t="s"/>
       <x:c r="E96" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F96" s="30" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="G96" s="30" t="s">
-        <x:v>291</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H96" s="32">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I96" s="32">
-        <x:v>46023</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J96" s="31" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="K96" s="33" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L96" s="34">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M96" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B97" s="30" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="C97" s="30" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="D97" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E97" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F97" s="30" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G97" s="30" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H97" s="32">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I97" s="32">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J97" s="31" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="K97" s="33" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L97" s="34">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M97" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="99" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B99" s="18" t="s">
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B100" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C99" s="19" t="s"/>
-      <x:c r="D99" s="19" t="s"/>
-      <x:c r="E99" s="20" t="s"/>
-      <x:c r="F99" s="20" t="s"/>
-    </x:row>
-    <x:row r="100" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B100" s="21" t="s">
+      <x:c r="C100" s="19" t="s"/>
+      <x:c r="D100" s="19" t="s"/>
+      <x:c r="E100" s="20" t="s"/>
+      <x:c r="F100" s="20" t="s"/>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B101" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C100" s="22" t="s"/>
-      <x:c r="D100" s="22" t="s"/>
-      <x:c r="E100" s="22" t="s"/>
-      <x:c r="F100" s="23" t="s">
+      <x:c r="C101" s="22" t="s"/>
+      <x:c r="D101" s="22" t="s"/>
+      <x:c r="E101" s="22" t="s"/>
+      <x:c r="F101" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B101" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C101" s="25" t="s"/>
-      <x:c r="D101" s="25" t="s"/>
-      <x:c r="E101" s="25" t="s"/>
-      <x:c r="F101" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:28" ht="18" customHeight="1">
       <x:c r="B102" s="24" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C102" s="25" t="s"/>
       <x:c r="D102" s="25" t="s"/>
       <x:c r="E102" s="25" t="s"/>
       <x:c r="F102" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:28" ht="18" customHeight="1">
       <x:c r="B103" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C103" s="25" t="s"/>
       <x:c r="D103" s="25" t="s"/>
       <x:c r="E103" s="25" t="s"/>
       <x:c r="F103" s="26" t="n">
-        <x:v>76</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:28" ht="18" customHeight="1">
       <x:c r="B104" s="24" t="s">
-        <x:v>256</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C104" s="25" t="s"/>
       <x:c r="D104" s="25" t="s"/>
       <x:c r="E104" s="25" t="s"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
       <x:c r="B105" s="24" t="s">
-        <x:v>283</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C105" s="25" t="s"/>
       <x:c r="D105" s="25" t="s"/>
       <x:c r="E105" s="25" t="s"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="24" t="s">
-        <x:v>288</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C106" s="25" t="s"/>
       <x:c r="D106" s="25" t="s"/>
@@ -9200,18 +9233,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B107" s="27" t="s">
+    <x:row r="107" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B107" s="24" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="C107" s="25" t="s"/>
+      <x:c r="D107" s="25" t="s"/>
+      <x:c r="E107" s="25" t="s"/>
+      <x:c r="F107" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B108" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C107" s="28" t="s"/>
-      <x:c r="D107" s="28" t="s"/>
-      <x:c r="E107" s="28" t="s"/>
-      <x:c r="F107" s="29" t="n">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C108" s="28" t="s"/>
+      <x:c r="D108" s="28" t="s"/>
+      <x:c r="E108" s="28" t="s"/>
+      <x:c r="F108" s="29" t="n">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
     <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10103,8 +10146,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B99:F99"/>
-    <x:mergeCell ref="B100:E100"/>
+    <x:mergeCell ref="B100:F100"/>
     <x:mergeCell ref="B101:E101"/>
     <x:mergeCell ref="B102:E102"/>
     <x:mergeCell ref="B103:E103"/>
@@ -10112,6 +10154,7 @@
     <x:mergeCell ref="B105:E105"/>
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
+    <x:mergeCell ref="B108:E108"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="295">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -189,6 +189,69 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08219</x:t>
   </x:si>
   <x:si>
@@ -198,15 +261,6 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08296</x:t>
   </x:si>
   <x:si>
@@ -216,58 +270,13 @@
     <x:t>zxcasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1325-890</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdxzcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -276,43 +285,70 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1255-384</x:t>
   </x:si>
   <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08147</x:t>
@@ -324,54 +360,27 @@
     <x:t>zxc</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08152</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1273-639</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08137</x:t>
   </x:si>
   <x:si>
@@ -486,13 +495,10 @@
     <x:t>zsd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08094</x:t>
@@ -525,10 +531,10 @@
     <x:t>xzczxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
@@ -537,6 +543,96 @@
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
   </x:si>
   <x:si>
@@ -546,79 +642,34 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08191</x:t>
@@ -630,34 +681,40 @@
     <x:t>scawdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -669,10 +726,37 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08183</x:t>
@@ -684,76 +768,28 @@
     <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
@@ -765,40 +801,10 @@
     <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08178</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -5872,19 +5878,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="32">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I11" s="32">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J11" s="31" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="K11" s="33" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L11" s="34">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M11" s="30" t="s">
         <x:v>21</x:v>
@@ -5910,10 +5916,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="32">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I12" s="32">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J12" s="31" t="s">
         <x:v>59</x:v>
@@ -5922,7 +5928,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="34">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M12" s="30" t="s">
         <x:v>21</x:v>
@@ -5948,10 +5954,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="32">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I13" s="32">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J13" s="31" t="s">
         <x:v>62</x:v>
@@ -5960,7 +5966,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="34">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M13" s="30" t="s">
         <x:v>21</x:v>
@@ -5986,10 +5992,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="32">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I14" s="32">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J14" s="31" t="s">
         <x:v>65</x:v>
@@ -5998,7 +6004,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="34">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M14" s="30" t="s">
         <x:v>21</x:v>
@@ -6024,10 +6030,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="32">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I15" s="32">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J15" s="31" t="s">
         <x:v>68</x:v>
@@ -6036,7 +6042,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="34">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M15" s="30" t="s">
         <x:v>21</x:v>
@@ -6062,10 +6068,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="32">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I16" s="32">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J16" s="31" t="s">
         <x:v>71</x:v>
@@ -6074,7 +6080,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="34">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M16" s="30" t="s">
         <x:v>21</x:v>
@@ -6100,10 +6106,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="32">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I17" s="32">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J17" s="31" t="s">
         <x:v>74</x:v>
@@ -6112,7 +6118,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="34">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M17" s="30" t="s">
         <x:v>21</x:v>
@@ -6138,19 +6144,19 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H18" s="32">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I18" s="32">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J18" s="31" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L18" s="34">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M18" s="30" t="s">
         <x:v>21</x:v>
@@ -6176,10 +6182,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="32">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I19" s="32">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J19" s="31" t="s">
         <x:v>80</x:v>
@@ -6188,7 +6194,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="34">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M19" s="30" t="s">
         <x:v>21</x:v>
@@ -6214,19 +6220,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H20" s="32">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I20" s="32">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J20" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K20" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="34">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M20" s="30" t="s">
         <x:v>21</x:v>
@@ -6246,25 +6252,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G21" s="30" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H21" s="32">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I21" s="32">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J21" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K21" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="34">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M21" s="30" t="s">
         <x:v>21</x:v>
@@ -6296,7 +6302,7 @@
         <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J22" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K22" s="33" t="n">
         <x:v>210</x:v>
@@ -6322,10 +6328,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G23" s="30" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="32">
         <x:v>46120.2374046412</x:v>
@@ -6334,7 +6340,7 @@
         <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J23" s="31" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K23" s="33" t="n">
         <x:v>210</x:v>
@@ -6360,10 +6366,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G24" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H24" s="32">
         <x:v>46120.7129542245</x:v>
@@ -6398,25 +6404,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="30" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G25" s="30" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="32">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I25" s="32">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J25" s="31" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K25" s="33" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="34">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M25" s="30" t="s">
         <x:v>21</x:v>
@@ -6442,10 +6448,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="32">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I26" s="32">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J26" s="31" t="s">
         <x:v>98</x:v>
@@ -6454,7 +6460,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="34">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M26" s="30" t="s">
         <x:v>21</x:v>
@@ -6594,19 +6600,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H30" s="32">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I30" s="32">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J30" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="34">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M30" s="30" t="s">
         <x:v>21</x:v>
@@ -6626,25 +6632,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G31" s="30" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H31" s="32">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I31" s="32">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J31" s="31" t="s">
-        <x:v>112</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K31" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="34">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M31" s="30" t="s">
         <x:v>21</x:v>
@@ -6708,19 +6714,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="32">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I33" s="32">
-        <x:v>46121.228379213</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J33" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K33" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="34">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M33" s="30" t="s">
         <x:v>21</x:v>
@@ -6740,25 +6746,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G34" s="30" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H34" s="32">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I34" s="32">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J34" s="31" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="34">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M34" s="30" t="s">
         <x:v>21</x:v>
@@ -6778,25 +6784,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G35" s="30" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="32">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I35" s="32">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J35" s="31" t="s">
-        <x:v>121</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K35" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="34">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M35" s="30" t="s">
         <x:v>21</x:v>
@@ -6822,10 +6828,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="32">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I36" s="32">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J36" s="31" t="s">
         <x:v>124</x:v>
@@ -6834,7 +6840,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="34">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M36" s="30" t="s">
         <x:v>21</x:v>
@@ -6860,10 +6866,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="32">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I37" s="32">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J37" s="31" t="s">
         <x:v>127</x:v>
@@ -6872,7 +6878,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="34">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M37" s="30" t="s">
         <x:v>21</x:v>
@@ -6898,10 +6904,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="H38" s="32">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I38" s="32">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J38" s="31" t="s">
         <x:v>130</x:v>
@@ -6910,7 +6916,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="34">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M38" s="30" t="s">
         <x:v>21</x:v>
@@ -6936,10 +6942,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H39" s="32">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I39" s="32">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J39" s="31" t="s">
         <x:v>133</x:v>
@@ -6948,7 +6954,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="34">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M39" s="30" t="s">
         <x:v>21</x:v>
@@ -6974,10 +6980,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="H40" s="32">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I40" s="32">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J40" s="31" t="s">
         <x:v>136</x:v>
@@ -6986,7 +6992,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="34">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M40" s="30" t="s">
         <x:v>21</x:v>
@@ -7012,10 +7018,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="H41" s="32">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I41" s="32">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="31" t="s">
         <x:v>139</x:v>
@@ -7024,7 +7030,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="34">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M41" s="30" t="s">
         <x:v>21</x:v>
@@ -7050,10 +7056,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="H42" s="32">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I42" s="32">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J42" s="31" t="s">
         <x:v>142</x:v>
@@ -7062,7 +7068,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="34">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M42" s="30" t="s">
         <x:v>21</x:v>
@@ -7088,19 +7094,19 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="H43" s="32">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I43" s="32">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J43" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="K43" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="34">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M43" s="30" t="s">
         <x:v>21</x:v>
@@ -7120,25 +7126,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G44" s="30" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H44" s="32">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I44" s="32">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J44" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K44" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="34">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M44" s="30" t="s">
         <x:v>21</x:v>
@@ -7158,25 +7164,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G45" s="30" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H45" s="32">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I45" s="32">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J45" s="31" t="s">
-        <x:v>149</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K45" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="34">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M45" s="30" t="s">
         <x:v>21</x:v>
@@ -7202,10 +7208,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="H46" s="32">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I46" s="32">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J46" s="31" t="s">
         <x:v>152</x:v>
@@ -7214,7 +7220,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="34">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M46" s="30" t="s">
         <x:v>21</x:v>
@@ -7240,10 +7246,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H47" s="32">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I47" s="32">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J47" s="31" t="s">
         <x:v>155</x:v>
@@ -7252,7 +7258,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="34">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M47" s="30" t="s">
         <x:v>21</x:v>
@@ -7278,19 +7284,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H48" s="32">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I48" s="32">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J48" s="31" t="s">
-        <x:v>158</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K48" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="34">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M48" s="30" t="s">
         <x:v>21</x:v>
@@ -7310,25 +7316,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="30" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G49" s="30" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="G49" s="30" t="s">
+      <x:c r="H49" s="32">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I49" s="32">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J49" s="31" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="H49" s="32">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I49" s="32">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J49" s="31" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="K49" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="34">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M49" s="30" t="s">
         <x:v>21</x:v>
@@ -7354,19 +7360,19 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H50" s="32">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I50" s="32">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J50" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K50" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="34">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M50" s="30" t="s">
         <x:v>21</x:v>
@@ -7392,19 +7398,19 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="H51" s="32">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I51" s="32">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J51" s="31" t="s">
-        <x:v>165</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K51" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="34">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M51" s="30" t="s">
         <x:v>21</x:v>
@@ -7424,25 +7430,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="30" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="G52" s="30" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G52" s="30" t="s">
+      <x:c r="H52" s="32">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I52" s="32">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J52" s="31" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="H52" s="32">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I52" s="32">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J52" s="31" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K52" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="34">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M52" s="30" t="s">
         <x:v>21</x:v>
@@ -7468,19 +7474,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="32">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I53" s="32">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J53" s="31" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K53" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="34">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M53" s="30" t="s">
         <x:v>21</x:v>
@@ -7506,19 +7512,19 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="H54" s="32">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I54" s="32">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J54" s="31" t="s">
-        <x:v>172</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K54" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="34">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M54" s="30" t="s">
         <x:v>21</x:v>
@@ -7538,25 +7544,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="30" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G55" s="30" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="G55" s="30" t="s">
+      <x:c r="H55" s="32">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I55" s="32">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J55" s="31" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="H55" s="32">
-        <x:v>46126.5341923727</x:v>
-      </x:c>
-      <x:c r="I55" s="32">
-        <x:v>46126.5348242708</x:v>
-      </x:c>
-      <x:c r="J55" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K55" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="34">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M55" s="30" t="s">
         <x:v>21</x:v>
@@ -7582,19 +7588,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="32">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I56" s="32">
-        <x:v>46124.704475463</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J56" s="31" t="s">
-        <x:v>177</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K56" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="34">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M56" s="30" t="s">
         <x:v>21</x:v>
@@ -7614,25 +7620,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="30" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="G57" s="30" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="G57" s="30" t="s">
-        <x:v>179</x:v>
-      </x:c>
       <x:c r="H57" s="32">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I57" s="32">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J57" s="31" t="s">
-        <x:v>180</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K57" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="34">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M57" s="30" t="s">
         <x:v>21</x:v>
@@ -7652,25 +7658,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="30" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G58" s="30" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H58" s="32">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I58" s="32">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J58" s="31" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="G58" s="30" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="H58" s="32">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I58" s="32">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J58" s="31" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="K58" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="34">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M58" s="30" t="s">
         <x:v>21</x:v>
@@ -7690,25 +7696,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="30" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G59" s="30" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="H59" s="32">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I59" s="32">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J59" s="31" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="G59" s="30" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="H59" s="32">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I59" s="32">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J59" s="31" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K59" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="34">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M59" s="30" t="s">
         <x:v>21</x:v>
@@ -7728,25 +7734,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="30" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="G60" s="30" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="G60" s="30" t="s">
+      <x:c r="H60" s="32">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I60" s="32">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J60" s="31" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="H60" s="32">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I60" s="32">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J60" s="31" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="K60" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="34">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M60" s="30" t="s">
         <x:v>21</x:v>
@@ -7766,25 +7772,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="30" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G61" s="30" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="G61" s="30" t="s">
-        <x:v>190</x:v>
-      </x:c>
       <x:c r="H61" s="32">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I61" s="32">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J61" s="31" t="s">
-        <x:v>191</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K61" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="34">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M61" s="30" t="s">
         <x:v>21</x:v>
@@ -7804,25 +7810,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="30" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G62" s="30" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="H62" s="32">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I62" s="32">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J62" s="31" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G62" s="30" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="H62" s="32">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I62" s="32">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J62" s="31" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="K62" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="34">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M62" s="30" t="s">
         <x:v>21</x:v>
@@ -7842,25 +7848,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="30" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G63" s="30" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="H63" s="32">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I63" s="32">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J63" s="31" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="G63" s="30" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H63" s="32">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I63" s="32">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J63" s="31" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="K63" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="34">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M63" s="30" t="s">
         <x:v>21</x:v>
@@ -7880,25 +7886,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="30" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G64" s="30" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="H64" s="32">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I64" s="32">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J64" s="31" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="G64" s="30" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="H64" s="32">
-        <x:v>46124.1512647338</x:v>
-      </x:c>
-      <x:c r="I64" s="32">
-        <x:v>46124.1530803935</x:v>
-      </x:c>
-      <x:c r="J64" s="31" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="K64" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="34">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M64" s="30" t="s">
         <x:v>21</x:v>
@@ -7918,25 +7924,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="30" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G65" s="30" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H65" s="32">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I65" s="32">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J65" s="31" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="G65" s="30" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H65" s="32">
-        <x:v>46122.3569147569</x:v>
-      </x:c>
-      <x:c r="I65" s="32">
-        <x:v>46122.3577305324</x:v>
-      </x:c>
-      <x:c r="J65" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K65" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="34">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M65" s="30" t="s">
         <x:v>21</x:v>
@@ -7956,25 +7962,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="30" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G66" s="30" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G66" s="30" t="s">
+      <x:c r="H66" s="32">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I66" s="32">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J66" s="31" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="H66" s="32">
-        <x:v>46124.1487218981</x:v>
-      </x:c>
-      <x:c r="I66" s="32">
-        <x:v>46124.1494313773</x:v>
-      </x:c>
-      <x:c r="J66" s="31" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="34">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M66" s="30" t="s">
         <x:v>21</x:v>
@@ -7994,25 +8000,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="30" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G67" s="30" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="G67" s="30" t="s">
-        <x:v>207</x:v>
-      </x:c>
       <x:c r="H67" s="32">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I67" s="32">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J67" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K67" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="34">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M67" s="30" t="s">
         <x:v>21</x:v>
@@ -8032,25 +8038,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="30" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="G68" s="30" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G68" s="30" t="s">
+      <x:c r="H68" s="32">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I68" s="32">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J68" s="31" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="H68" s="32">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I68" s="32">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J68" s="31" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="K68" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="34">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M68" s="30" t="s">
         <x:v>21</x:v>
@@ -8070,25 +8076,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="30" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G69" s="30" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="G69" s="30" t="s">
-        <x:v>212</x:v>
-      </x:c>
       <x:c r="H69" s="32">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I69" s="32">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J69" s="31" t="s">
-        <x:v>213</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K69" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="34">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M69" s="30" t="s">
         <x:v>21</x:v>
@@ -8108,25 +8114,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="30" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G70" s="30" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H70" s="32">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I70" s="32">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J70" s="31" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="G70" s="30" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="H70" s="32">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I70" s="32">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J70" s="31" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K70" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="34">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M70" s="30" t="s">
         <x:v>21</x:v>
@@ -8146,25 +8152,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F71" s="30" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="G71" s="30" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="G71" s="30" t="s">
+      <x:c r="H71" s="32">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I71" s="32">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J71" s="31" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="H71" s="32">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I71" s="32">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J71" s="31" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="K71" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="34">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M71" s="30" t="s">
         <x:v>21</x:v>
@@ -8184,25 +8190,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="30" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G72" s="30" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G72" s="30" t="s">
+      <x:c r="H72" s="32">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I72" s="32">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J72" s="31" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="H72" s="32">
-        <x:v>46122.3767795718</x:v>
-      </x:c>
-      <x:c r="I72" s="32">
-        <x:v>46122.3776183449</x:v>
-      </x:c>
-      <x:c r="J72" s="31" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="K72" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="34">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M72" s="30" t="s">
         <x:v>21</x:v>
@@ -8222,10 +8228,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="30" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G73" s="30" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="G73" s="30" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="H73" s="32">
         <x:v>46122.3879258681</x:v>
@@ -8234,7 +8240,7 @@
         <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J73" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K73" s="33" t="n">
         <x:v>210</x:v>
@@ -8260,10 +8266,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="30" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G74" s="30" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="G74" s="30" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="H74" s="32">
         <x:v>46122.3885020718</x:v>
@@ -8298,10 +8304,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="30" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G75" s="30" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="G75" s="30" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="H75" s="32">
         <x:v>46122.3974322338</x:v>
@@ -8310,7 +8316,7 @@
         <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J75" s="31" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K75" s="33" t="n">
         <x:v>210</x:v>
@@ -8336,25 +8342,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F76" s="30" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G76" s="30" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="G76" s="30" t="s">
+      <x:c r="H76" s="32">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I76" s="32">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J76" s="31" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="H76" s="32">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I76" s="32">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J76" s="31" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="K76" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="34">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M76" s="30" t="s">
         <x:v>21</x:v>
@@ -8374,25 +8380,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F77" s="30" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G77" s="30" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G77" s="30" t="s">
+      <x:c r="H77" s="32">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I77" s="32">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J77" s="31" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="H77" s="32">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I77" s="32">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J77" s="31" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="K77" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="34">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M77" s="30" t="s">
         <x:v>21</x:v>
@@ -8494,19 +8500,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H80" s="32">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I80" s="32">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J80" s="31" t="s">
-        <x:v>240</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K80" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="34">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M80" s="30" t="s">
         <x:v>21</x:v>
@@ -8526,25 +8532,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F81" s="30" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G81" s="30" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G81" s="30" t="s">
-        <x:v>242</x:v>
-      </x:c>
       <x:c r="H81" s="32">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I81" s="32">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J81" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K81" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="34">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M81" s="30" t="s">
         <x:v>21</x:v>
@@ -8564,25 +8570,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F82" s="30" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G82" s="30" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="G82" s="30" t="s">
-        <x:v>244</x:v>
-      </x:c>
       <x:c r="H82" s="32">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I82" s="32">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J82" s="31" t="s">
-        <x:v>245</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K82" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="34">
-        <x:v>46123.049084375</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M82" s="30" t="s">
         <x:v>21</x:v>
@@ -8602,25 +8608,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="30" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G83" s="30" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H83" s="32">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I83" s="32">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J83" s="31" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="G83" s="30" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="H83" s="32">
-        <x:v>46122.6182774306</x:v>
-      </x:c>
-      <x:c r="I83" s="32">
-        <x:v>46122.6193276968</x:v>
-      </x:c>
-      <x:c r="J83" s="31" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K83" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="34">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M83" s="30" t="s">
         <x:v>21</x:v>
@@ -8640,25 +8646,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="30" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G84" s="30" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="G84" s="30" t="s">
+      <x:c r="H84" s="32">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I84" s="32">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J84" s="31" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="H84" s="32">
-        <x:v>46122.6795081481</x:v>
-      </x:c>
-      <x:c r="I84" s="32">
-        <x:v>46122.6802186921</x:v>
-      </x:c>
-      <x:c r="J84" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K84" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="34">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M84" s="30" t="s">
         <x:v>21</x:v>
@@ -8684,19 +8690,19 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="H85" s="32">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I85" s="32">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J85" s="31" t="s">
-        <x:v>252</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K85" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="34">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M85" s="30" t="s">
         <x:v>21</x:v>
@@ -8716,25 +8722,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="30" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="G86" s="30" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="G86" s="30" t="s">
+      <x:c r="H86" s="32">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I86" s="32">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J86" s="31" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="H86" s="32">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I86" s="32">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J86" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K86" s="33" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="34">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M86" s="30" t="s">
         <x:v>21</x:v>
@@ -8760,10 +8766,10 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="H87" s="32">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I87" s="32">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J87" s="31" t="s">
         <x:v>257</x:v>
@@ -8772,7 +8778,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="34">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M87" s="30" t="s">
         <x:v>21</x:v>
@@ -8780,10 +8786,10 @@
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
       <x:c r="B88" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C88" s="30" t="s">
-        <x:v>259</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D88" s="31" t="s">
         <x:v>16</x:v>
@@ -8792,25 +8798,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="30" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G88" s="30" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="H88" s="32">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I88" s="32">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J88" s="31" t="s">
-        <x:v>262</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K88" s="33" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="34">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M88" s="30" t="s">
         <x:v>21</x:v>
@@ -8818,10 +8824,10 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C89" s="30" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D89" s="31" t="s">
         <x:v>16</x:v>
@@ -8830,25 +8836,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="30" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="G89" s="30" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="H89" s="32">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I89" s="32">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J89" s="31" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="G89" s="30" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="H89" s="32">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I89" s="32">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J89" s="31" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K89" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L89" s="34">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M89" s="30" t="s">
         <x:v>21</x:v>
@@ -8856,10 +8862,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C90" s="30" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D90" s="31" t="s">
         <x:v>16</x:v>
@@ -8868,25 +8874,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="30" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G90" s="30" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="G90" s="30" t="s">
-        <x:v>268</x:v>
-      </x:c>
       <x:c r="H90" s="32">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I90" s="32">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J90" s="31" t="s">
-        <x:v>269</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K90" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="34">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M90" s="30" t="s">
         <x:v>21</x:v>
@@ -8894,10 +8900,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C91" s="30" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="D91" s="31" t="s">
         <x:v>16</x:v>
@@ -8906,25 +8912,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F91" s="30" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G91" s="30" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H91" s="32">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I91" s="32">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J91" s="31" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="G91" s="30" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H91" s="32">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I91" s="32">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J91" s="31" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="K91" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="34">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M91" s="30" t="s">
         <x:v>21</x:v>
@@ -8932,10 +8938,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C92" s="30" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D92" s="31" t="s">
         <x:v>16</x:v>
@@ -8944,25 +8950,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F92" s="30" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G92" s="30" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H92" s="32">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I92" s="32">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J92" s="31" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="G92" s="30" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H92" s="32">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I92" s="32">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J92" s="31" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K92" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="34">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M92" s="30" t="s">
         <x:v>21</x:v>
@@ -8970,10 +8976,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C93" s="30" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D93" s="31" t="s">
         <x:v>16</x:v>
@@ -8982,25 +8988,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F93" s="30" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G93" s="30" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G93" s="30" t="s">
-        <x:v>279</x:v>
-      </x:c>
       <x:c r="H93" s="32">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I93" s="32">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J93" s="31" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K93" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="34">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M93" s="30" t="s">
         <x:v>21</x:v>
@@ -9008,10 +9014,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C94" s="30" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D94" s="31" t="s">
         <x:v>16</x:v>
@@ -9026,19 +9032,19 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="H94" s="32">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I94" s="32">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J94" s="31" t="s">
-        <x:v>282</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K94" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="34">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M94" s="30" t="s">
         <x:v>21</x:v>
@@ -9046,10 +9052,10 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="30" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C95" s="30" t="s">
-        <x:v>50</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="D95" s="31" t="s">
         <x:v>16</x:v>
@@ -9058,25 +9064,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F95" s="30" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G95" s="30" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="G95" s="30" t="s">
+      <x:c r="H95" s="32">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I95" s="32">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J95" s="31" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="H95" s="32">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I95" s="32">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J95" s="31" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K95" s="33" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="34">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M95" s="30" t="s">
         <x:v>21</x:v>
@@ -9084,35 +9090,37 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="30" t="s">
-        <x:v>285</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C96" s="30" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="D96" s="31" t="s"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D96" s="31" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E96" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F96" s="30" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="G96" s="30" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="H96" s="32">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I96" s="32">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J96" s="31" t="s">
-        <x:v>289</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K96" s="33" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="34">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M96" s="30" t="s">
         <x:v>21</x:v>
@@ -9120,122 +9128,147 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="30" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C97" s="30" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="D97" s="31" t="s">
-        <x:v>41</x:v>
-      </x:c>
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="D97" s="31" t="s"/>
       <x:c r="E97" s="30" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F97" s="30" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G97" s="30" t="s">
-        <x:v>293</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H97" s="32">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I97" s="32">
-        <x:v>46023</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J97" s="31" t="s">
-        <x:v>294</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K97" s="33" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L97" s="34">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M97" s="30" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B98" s="30" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C98" s="30" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D98" s="31" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E98" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F98" s="30" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G98" s="30" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H98" s="32">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I98" s="32">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J98" s="31" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K98" s="33" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L98" s="34">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M98" s="30" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B100" s="18" t="s">
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B101" s="18" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C100" s="19" t="s"/>
-      <x:c r="D100" s="19" t="s"/>
-      <x:c r="E100" s="20" t="s"/>
-      <x:c r="F100" s="20" t="s"/>
-    </x:row>
-    <x:row r="101" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B101" s="21" t="s">
+      <x:c r="C101" s="19" t="s"/>
+      <x:c r="D101" s="19" t="s"/>
+      <x:c r="E101" s="20" t="s"/>
+      <x:c r="F101" s="20" t="s"/>
+    </x:row>
+    <x:row r="102" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B102" s="21" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C101" s="22" t="s"/>
-      <x:c r="D101" s="22" t="s"/>
-      <x:c r="E101" s="22" t="s"/>
-      <x:c r="F101" s="23" t="s">
+      <x:c r="C102" s="22" t="s"/>
+      <x:c r="D102" s="22" t="s"/>
+      <x:c r="E102" s="22" t="s"/>
+      <x:c r="F102" s="23" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B102" s="24" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C102" s="25" t="s"/>
-      <x:c r="D102" s="25" t="s"/>
-      <x:c r="E102" s="25" t="s"/>
-      <x:c r="F102" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:28" ht="18" customHeight="1">
       <x:c r="B103" s="24" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C103" s="25" t="s"/>
       <x:c r="D103" s="25" t="s"/>
       <x:c r="E103" s="25" t="s"/>
       <x:c r="F103" s="26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:28" ht="18" customHeight="1">
       <x:c r="B104" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C104" s="25" t="s"/>
       <x:c r="D104" s="25" t="s"/>
       <x:c r="E104" s="25" t="s"/>
       <x:c r="F104" s="26" t="n">
-        <x:v>77</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
       <x:c r="B105" s="24" t="s">
-        <x:v>258</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C105" s="25" t="s"/>
       <x:c r="D105" s="25" t="s"/>
       <x:c r="E105" s="25" t="s"/>
       <x:c r="F105" s="26" t="n">
-        <x:v>8</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="24" t="s">
-        <x:v>285</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C106" s="25" t="s"/>
       <x:c r="D106" s="25" t="s"/>
       <x:c r="E106" s="25" t="s"/>
       <x:c r="F106" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="24" t="s">
-        <x:v>290</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C107" s="25" t="s"/>
       <x:c r="D107" s="25" t="s"/>
@@ -9244,18 +9277,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B108" s="27" t="s">
+    <x:row r="108" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B108" s="24" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C108" s="25" t="s"/>
+      <x:c r="D108" s="25" t="s"/>
+      <x:c r="E108" s="25" t="s"/>
+      <x:c r="F108" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B109" s="27" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C108" s="28" t="s"/>
-      <x:c r="D108" s="28" t="s"/>
-      <x:c r="E108" s="28" t="s"/>
-      <x:c r="F108" s="29" t="n">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C109" s="28" t="s"/>
+      <x:c r="D109" s="28" t="s"/>
+      <x:c r="E109" s="28" t="s"/>
+      <x:c r="F109" s="29" t="n">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
     <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10146,8 +10189,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B100:F100"/>
-    <x:mergeCell ref="B101:E101"/>
+    <x:mergeCell ref="B101:F101"/>
     <x:mergeCell ref="B102:E102"/>
     <x:mergeCell ref="B103:E103"/>
     <x:mergeCell ref="B104:E104"/>
@@ -10155,6 +10197,7 @@
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
+    <x:mergeCell ref="B109:E109"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -927,7 +927,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -967,14 +967,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1254,7 +1246,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="30">
+  <x:cellStyleXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1265,16 +1257,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1286,65 +1275,65 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1379,99 +1368,95 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1773,17 +1758,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1806,80 +1791,80 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>46049.5726010069</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>46049.5726341898</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>46049.5962660532</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1899,44 +1884,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -3042,17 +3027,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3075,78 +3060,78 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s"/>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="D8" s="14" t="s"/>
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="15">
         <x:v>46066.6004589236</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="15">
         <x:v>46066.6024709375</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="15">
         <x:v>46066.6040195139</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -3166,44 +3151,44 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C11" s="18" t="s"/>
+      <x:c r="D11" s="18" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="19" t="s"/>
     </x:row>
     <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+      <x:c r="B12" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+      <x:c r="B13" s="23" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+      <x:c r="B14" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -4309,17 +4294,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4342,238 +4327,238 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46106.5066742245</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46106.5082381134</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46106.5099302546</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s">
+      <x:c r="D9" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="E9" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46105.676846794</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46106.5084437037</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46106.5101144792</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s">
+      <x:c r="D10" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="E10" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46105.6741278125</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>46106.5086548727</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46106.5103567593</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46078.2888967361</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46078.2901145602</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46089.2508762037</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="18" t="s">
+      <x:c r="B14" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="20" t="s"/>
+      <x:c r="C14" s="18" t="s"/>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="19" t="s"/>
+      <x:c r="F14" s="19" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="21" t="s"/>
+      <x:c r="F15" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+      <x:c r="B16" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+      <x:c r="B17" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -5676,17 +5661,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5709,3593 +5694,3593 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="29" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="31" t="s">
+      <x:c r="D8" s="30" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="29" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H8" s="32">
+      <x:c r="H8" s="31">
         <x:v>46118.3222074537</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="31">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="31" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K8" s="33" t="n">
+      <x:c r="K8" s="32" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="L8" s="34">
+      <x:c r="L8" s="33">
         <x:v>46118.3241166898</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M8" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="30" t="s">
+      <x:c r="B9" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C9" s="30" t="s">
+      <x:c r="C9" s="29" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="s"/>
-      <x:c r="E9" s="30" t="s">
+      <x:c r="D9" s="30" t="s"/>
+      <x:c r="E9" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="F9" s="29" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="G9" s="29" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="H9" s="32">
+      <x:c r="H9" s="31">
         <x:v>46126.0027495833</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="31">
         <x:v>46126.1631260764</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="K9" s="33" t="n">
+      <x:c r="K9" s="32" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L9" s="34">
+      <x:c r="L9" s="33">
         <x:v>46126.177127963</x:v>
       </x:c>
-      <x:c r="M9" s="30" t="s">
+      <x:c r="M9" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="30" t="s">
+      <x:c r="B10" s="29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="C10" s="29" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D10" s="31" t="s"/>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="D10" s="30" t="s"/>
+      <x:c r="E10" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="F10" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="G10" s="29" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H10" s="32">
+      <x:c r="H10" s="31">
         <x:v>46119.5290592824</x:v>
       </x:c>
-      <x:c r="I10" s="32">
+      <x:c r="I10" s="31">
         <x:v>46119.5300361458</x:v>
       </x:c>
-      <x:c r="J10" s="31" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K10" s="33" t="n">
+      <x:c r="K10" s="32" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L10" s="34">
+      <x:c r="L10" s="33">
         <x:v>46119.5304719792</x:v>
       </x:c>
-      <x:c r="M10" s="30" t="s">
+      <x:c r="M10" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="30" t="s">
+      <x:c r="B11" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="C11" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D11" s="31" t="s">
+      <x:c r="D11" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="E11" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="F11" s="29" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="G11" s="29" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H11" s="32">
+      <x:c r="H11" s="31">
         <x:v>46126.4798427199</x:v>
       </x:c>
-      <x:c r="I11" s="32">
+      <x:c r="I11" s="31">
         <x:v>46126.4809562153</x:v>
       </x:c>
-      <x:c r="J11" s="31" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="K11" s="33" t="n">
+      <x:c r="K11" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L11" s="34">
+      <x:c r="L11" s="33">
         <x:v>46126.4814216667</x:v>
       </x:c>
-      <x:c r="M11" s="30" t="s">
+      <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="30" t="s">
+      <x:c r="B12" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="C12" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D12" s="31" t="s">
+      <x:c r="D12" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="E12" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="F12" s="29" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="s">
+      <x:c r="G12" s="29" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="H12" s="32">
+      <x:c r="H12" s="31">
         <x:v>46126.4716621296</x:v>
       </x:c>
-      <x:c r="I12" s="32">
+      <x:c r="I12" s="31">
         <x:v>46126.4737503704</x:v>
       </x:c>
-      <x:c r="J12" s="31" t="s">
+      <x:c r="J12" s="30" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="K12" s="33" t="n">
+      <x:c r="K12" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="34">
+      <x:c r="L12" s="33">
         <x:v>46126.4748429977</x:v>
       </x:c>
-      <x:c r="M12" s="30" t="s">
+      <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="30" t="s">
+      <x:c r="B13" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="C13" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D13" s="31" t="s">
+      <x:c r="D13" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="E13" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F13" s="30" t="s">
+      <x:c r="F13" s="29" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G13" s="30" t="s">
+      <x:c r="G13" s="29" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H13" s="32">
+      <x:c r="H13" s="31">
         <x:v>46126.455832662</x:v>
       </x:c>
-      <x:c r="I13" s="32">
+      <x:c r="I13" s="31">
         <x:v>46126.4740829051</x:v>
       </x:c>
-      <x:c r="J13" s="31" t="s">
+      <x:c r="J13" s="30" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="K13" s="33" t="n">
+      <x:c r="K13" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L13" s="34">
+      <x:c r="L13" s="33">
         <x:v>46126.4751368866</x:v>
       </x:c>
-      <x:c r="M13" s="30" t="s">
+      <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="30" t="s">
+      <x:c r="B14" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="C14" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D14" s="31" t="s">
+      <x:c r="D14" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="E14" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F14" s="30" t="s">
+      <x:c r="F14" s="29" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G14" s="30" t="s">
+      <x:c r="G14" s="29" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H14" s="32">
+      <x:c r="H14" s="31">
         <x:v>46126.4485157523</x:v>
       </x:c>
-      <x:c r="I14" s="32">
+      <x:c r="I14" s="31">
         <x:v>46126.4527227431</x:v>
       </x:c>
-      <x:c r="J14" s="31" t="s">
+      <x:c r="J14" s="30" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K14" s="33" t="n">
+      <x:c r="K14" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L14" s="34">
+      <x:c r="L14" s="33">
         <x:v>46126.4533495949</x:v>
       </x:c>
-      <x:c r="M14" s="30" t="s">
+      <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="30" t="s">
+      <x:c r="B15" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s">
+      <x:c r="C15" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D15" s="31" t="s">
+      <x:c r="D15" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="E15" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F15" s="30" t="s">
+      <x:c r="F15" s="29" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G15" s="30" t="s">
+      <x:c r="G15" s="29" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H15" s="32">
+      <x:c r="H15" s="31">
         <x:v>46126.4381590509</x:v>
       </x:c>
-      <x:c r="I15" s="32">
+      <x:c r="I15" s="31">
         <x:v>46126.4434486343</x:v>
       </x:c>
-      <x:c r="J15" s="31" t="s">
+      <x:c r="J15" s="30" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="K15" s="33" t="n">
+      <x:c r="K15" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L15" s="34">
+      <x:c r="L15" s="33">
         <x:v>46126.444417662</x:v>
       </x:c>
-      <x:c r="M15" s="30" t="s">
+      <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="30" t="s">
+      <x:c r="B16" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s">
+      <x:c r="C16" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D16" s="31" t="s">
+      <x:c r="D16" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="E16" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F16" s="30" t="s">
+      <x:c r="F16" s="29" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="s">
+      <x:c r="G16" s="29" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H16" s="32">
+      <x:c r="H16" s="31">
         <x:v>46126.1914900926</x:v>
       </x:c>
-      <x:c r="I16" s="32">
+      <x:c r="I16" s="31">
         <x:v>46126.2594011574</x:v>
       </x:c>
-      <x:c r="J16" s="31" t="s">
+      <x:c r="J16" s="30" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="K16" s="33" t="n">
+      <x:c r="K16" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L16" s="34">
+      <x:c r="L16" s="33">
         <x:v>46126.2601296875</x:v>
       </x:c>
-      <x:c r="M16" s="30" t="s">
+      <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="30" t="s">
+      <x:c r="B17" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s">
+      <x:c r="C17" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D17" s="31" t="s">
+      <x:c r="D17" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="E17" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F17" s="30" t="s">
+      <x:c r="F17" s="29" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G17" s="30" t="s">
+      <x:c r="G17" s="29" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="H17" s="32">
+      <x:c r="H17" s="31">
         <x:v>46126.1388059144</x:v>
       </x:c>
-      <x:c r="I17" s="32">
+      <x:c r="I17" s="31">
         <x:v>46126.1498425347</x:v>
       </x:c>
-      <x:c r="J17" s="31" t="s">
+      <x:c r="J17" s="30" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K17" s="33" t="n">
+      <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L17" s="34">
+      <x:c r="L17" s="33">
         <x:v>46126.176386169</x:v>
       </x:c>
-      <x:c r="M17" s="30" t="s">
+      <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="30" t="s">
+      <x:c r="C18" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D18" s="31" t="s">
+      <x:c r="D18" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="30" t="s">
+      <x:c r="E18" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F18" s="30" t="s">
+      <x:c r="F18" s="29" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G18" s="30" t="s">
+      <x:c r="G18" s="29" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="H18" s="32">
+      <x:c r="H18" s="31">
         <x:v>46124.9835281713</x:v>
       </x:c>
-      <x:c r="I18" s="32">
+      <x:c r="I18" s="31">
         <x:v>46125.0608962963</x:v>
       </x:c>
-      <x:c r="J18" s="31" t="s">
+      <x:c r="J18" s="30" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="K18" s="33" t="n">
+      <x:c r="K18" s="32" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L18" s="34">
+      <x:c r="L18" s="33">
         <x:v>46126.1641622569</x:v>
       </x:c>
-      <x:c r="M18" s="30" t="s">
+      <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="30" t="s">
+      <x:c r="B19" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C19" s="30" t="s">
+      <x:c r="C19" s="29" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D19" s="31" t="s">
+      <x:c r="D19" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="30" t="s">
+      <x:c r="E19" s="29" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F19" s="30" t="s">
+      <x:c r="F19" s="29" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G19" s="30" t="s">
+      <x:c r="G19" s="29" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="H19" s="32">
+      <x:c r="H19" s="31">
         <x:v>46126.2608066551</x:v>
       </x:c>
-      <x:c r="I19" s="32">
+      <x:c r="I19" s="31">
         <x:v>46126.2618529282</x:v>
       </x:c>
-      <x:c r="J19" s="31" t="s">
+      <x:c r="J19" s="30" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="K19" s="33" t="n">
+      <x:c r="K19" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L19" s="34">
+      <x:c r="L19" s="33">
         <x:v>46126.2624254167</x:v>
       </x:c>
-      <x:c r="M19" s="30" t="s">
+      <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="30" t="s">
+      <x:c r="B20" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s">
+      <x:c r="C20" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D20" s="31" t="s">
+      <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="30" t="s">
+      <x:c r="E20" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F20" s="30" t="s">
+      <x:c r="F20" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G20" s="30" t="s">
+      <x:c r="G20" s="29" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H20" s="32">
+      <x:c r="H20" s="31">
         <x:v>46121.0999663542</x:v>
       </x:c>
-      <x:c r="I20" s="32">
+      <x:c r="I20" s="31">
         <x:v>46121.1007466204</x:v>
       </x:c>
-      <x:c r="J20" s="31" t="s">
+      <x:c r="J20" s="30" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="K20" s="33" t="n">
+      <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L20" s="34">
+      <x:c r="L20" s="33">
         <x:v>46121.1027298958</x:v>
       </x:c>
-      <x:c r="M20" s="30" t="s">
+      <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="30" t="s">
+      <x:c r="B21" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s">
+      <x:c r="C21" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D21" s="31" t="s">
+      <x:c r="D21" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E21" s="30" t="s">
+      <x:c r="E21" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F21" s="30" t="s">
+      <x:c r="F21" s="29" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G21" s="30" t="s">
+      <x:c r="G21" s="29" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H21" s="32">
+      <x:c r="H21" s="31">
         <x:v>46119.8029380671</x:v>
       </x:c>
-      <x:c r="I21" s="32">
+      <x:c r="I21" s="31">
         <x:v>46120.5237086343</x:v>
       </x:c>
-      <x:c r="J21" s="31" t="s">
+      <x:c r="J21" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K21" s="33" t="n">
+      <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L21" s="34">
+      <x:c r="L21" s="33">
         <x:v>46120.5257164468</x:v>
       </x:c>
-      <x:c r="M21" s="30" t="s">
+      <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="30" t="s">
+      <x:c r="B22" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s">
+      <x:c r="C22" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D22" s="31" t="s">
+      <x:c r="D22" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="30" t="s">
+      <x:c r="E22" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F22" s="30" t="s">
+      <x:c r="F22" s="29" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G22" s="30" t="s">
+      <x:c r="G22" s="29" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="H22" s="32">
+      <x:c r="H22" s="31">
         <x:v>46120.2362105324</x:v>
       </x:c>
-      <x:c r="I22" s="32">
+      <x:c r="I22" s="31">
         <x:v>46120.5226826273</x:v>
       </x:c>
-      <x:c r="J22" s="31" t="s">
+      <x:c r="J22" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K22" s="33" t="n">
+      <x:c r="K22" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L22" s="34">
+      <x:c r="L22" s="33">
         <x:v>46120.5252627315</x:v>
       </x:c>
-      <x:c r="M22" s="30" t="s">
+      <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="30" t="s">
+      <x:c r="B23" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s">
+      <x:c r="C23" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D23" s="31" t="s">
+      <x:c r="D23" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="30" t="s">
+      <x:c r="E23" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F23" s="30" t="s">
+      <x:c r="F23" s="29" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G23" s="30" t="s">
+      <x:c r="G23" s="29" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H23" s="32">
+      <x:c r="H23" s="31">
         <x:v>46120.2374046412</x:v>
       </x:c>
-      <x:c r="I23" s="32">
+      <x:c r="I23" s="31">
         <x:v>46120.5224942245</x:v>
       </x:c>
-      <x:c r="J23" s="31" t="s">
+      <x:c r="J23" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="K23" s="33" t="n">
+      <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L23" s="34">
+      <x:c r="L23" s="33">
         <x:v>46120.5250032292</x:v>
       </x:c>
-      <x:c r="M23" s="30" t="s">
+      <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="30" t="s">
+      <x:c r="B24" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s">
+      <x:c r="C24" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D24" s="31" t="s">
+      <x:c r="D24" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="30" t="s">
+      <x:c r="E24" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F24" s="30" t="s">
+      <x:c r="F24" s="29" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G24" s="30" t="s">
+      <x:c r="G24" s="29" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="H24" s="32">
+      <x:c r="H24" s="31">
         <x:v>46120.7129542245</x:v>
       </x:c>
-      <x:c r="I24" s="32">
+      <x:c r="I24" s="31">
         <x:v>46121.100944213</x:v>
       </x:c>
-      <x:c r="J24" s="31" t="s">
+      <x:c r="J24" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K24" s="33" t="n">
+      <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L24" s="34">
+      <x:c r="L24" s="33">
         <x:v>46121.1029720949</x:v>
       </x:c>
-      <x:c r="M24" s="30" t="s">
+      <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="30" t="s">
+      <x:c r="B25" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C25" s="30" t="s">
+      <x:c r="C25" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D25" s="31" t="s">
+      <x:c r="D25" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E25" s="30" t="s">
+      <x:c r="E25" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F25" s="30" t="s">
+      <x:c r="F25" s="29" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G25" s="30" t="s">
+      <x:c r="G25" s="29" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H25" s="32">
+      <x:c r="H25" s="31">
         <x:v>46120.2349196412</x:v>
       </x:c>
-      <x:c r="I25" s="32">
+      <x:c r="I25" s="31">
         <x:v>46120.5229746296</x:v>
       </x:c>
-      <x:c r="J25" s="31" t="s">
+      <x:c r="J25" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K25" s="33" t="n">
+      <x:c r="K25" s="32" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="34">
+      <x:c r="L25" s="33">
         <x:v>46120.5255047106</x:v>
       </x:c>
-      <x:c r="M25" s="30" t="s">
+      <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="30" t="s">
+      <x:c r="B26" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C26" s="30" t="s">
+      <x:c r="C26" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="s">
+      <x:c r="D26" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E26" s="30" t="s">
+      <x:c r="E26" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F26" s="30" t="s">
+      <x:c r="F26" s="29" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G26" s="30" t="s">
+      <x:c r="G26" s="29" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="H26" s="32">
+      <x:c r="H26" s="31">
         <x:v>46121.5183984954</x:v>
       </x:c>
-      <x:c r="I26" s="32">
+      <x:c r="I26" s="31">
         <x:v>46122.2061737153</x:v>
       </x:c>
-      <x:c r="J26" s="31" t="s">
+      <x:c r="J26" s="30" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="K26" s="33" t="n">
+      <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L26" s="34">
+      <x:c r="L26" s="33">
         <x:v>46122.2307100926</x:v>
       </x:c>
-      <x:c r="M26" s="30" t="s">
+      <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="30" t="s">
+      <x:c r="B27" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s">
+      <x:c r="C27" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D27" s="31" t="s">
+      <x:c r="D27" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E27" s="30" t="s">
+      <x:c r="E27" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F27" s="30" t="s">
+      <x:c r="F27" s="29" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G27" s="30" t="s">
+      <x:c r="G27" s="29" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H27" s="32">
+      <x:c r="H27" s="31">
         <x:v>46121.2464636111</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="31">
         <x:v>46121.3217277662</x:v>
       </x:c>
-      <x:c r="J27" s="31" t="s">
+      <x:c r="J27" s="30" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="K27" s="33" t="n">
+      <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L27" s="34">
+      <x:c r="L27" s="33">
         <x:v>46121.498248206</x:v>
       </x:c>
-      <x:c r="M27" s="30" t="s">
+      <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="30" t="s">
+      <x:c r="B28" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C28" s="30" t="s">
+      <x:c r="C28" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D28" s="31" t="s">
+      <x:c r="D28" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E28" s="30" t="s">
+      <x:c r="E28" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F28" s="30" t="s">
+      <x:c r="F28" s="29" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="G28" s="30" t="s">
+      <x:c r="G28" s="29" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="H28" s="32">
+      <x:c r="H28" s="31">
         <x:v>46121.4966047917</x:v>
       </x:c>
-      <x:c r="I28" s="32">
+      <x:c r="I28" s="31">
         <x:v>46121.4974146412</x:v>
       </x:c>
-      <x:c r="J28" s="31" t="s">
+      <x:c r="J28" s="30" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="K28" s="33" t="n">
+      <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L28" s="34">
+      <x:c r="L28" s="33">
         <x:v>46121.4980146875</x:v>
       </x:c>
-      <x:c r="M28" s="30" t="s">
+      <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="30" t="s">
+      <x:c r="B29" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C29" s="30" t="s">
+      <x:c r="C29" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D29" s="31" t="s">
+      <x:c r="D29" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E29" s="30" t="s">
+      <x:c r="E29" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F29" s="30" t="s">
+      <x:c r="F29" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G29" s="30" t="s">
+      <x:c r="G29" s="29" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="H29" s="32">
+      <x:c r="H29" s="31">
         <x:v>46121.5149441551</x:v>
       </x:c>
-      <x:c r="I29" s="32">
+      <x:c r="I29" s="31">
         <x:v>46122.2067431944</x:v>
       </x:c>
-      <x:c r="J29" s="31" t="s">
+      <x:c r="J29" s="30" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="K29" s="33" t="n">
+      <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L29" s="34">
+      <x:c r="L29" s="33">
         <x:v>46122.2310990278</x:v>
       </x:c>
-      <x:c r="M29" s="30" t="s">
+      <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="30" t="s">
+      <x:c r="B30" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C30" s="30" t="s">
+      <x:c r="C30" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D30" s="31" t="s">
+      <x:c r="D30" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E30" s="30" t="s">
+      <x:c r="E30" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F30" s="30" t="s">
+      <x:c r="F30" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G30" s="30" t="s">
+      <x:c r="G30" s="29" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H30" s="32">
+      <x:c r="H30" s="31">
         <x:v>46121.5178724884</x:v>
       </x:c>
-      <x:c r="I30" s="32">
+      <x:c r="I30" s="31">
         <x:v>46122.2064690394</x:v>
       </x:c>
-      <x:c r="J30" s="31" t="s">
+      <x:c r="J30" s="30" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="K30" s="33" t="n">
+      <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L30" s="34">
+      <x:c r="L30" s="33">
         <x:v>46122.230922581</x:v>
       </x:c>
-      <x:c r="M30" s="30" t="s">
+      <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="30" t="s">
+      <x:c r="B31" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C31" s="30" t="s">
+      <x:c r="C31" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D31" s="31" t="s">
+      <x:c r="D31" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E31" s="30" t="s">
+      <x:c r="E31" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F31" s="30" t="s">
+      <x:c r="F31" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G31" s="30" t="s">
+      <x:c r="G31" s="29" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H31" s="32">
+      <x:c r="H31" s="31">
         <x:v>46119.8023724884</x:v>
       </x:c>
-      <x:c r="I31" s="32">
+      <x:c r="I31" s="31">
         <x:v>46119.8046602662</x:v>
       </x:c>
-      <x:c r="J31" s="31" t="s">
+      <x:c r="J31" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K31" s="33" t="n">
+      <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L31" s="34">
+      <x:c r="L31" s="33">
         <x:v>46119.8055532407</x:v>
       </x:c>
-      <x:c r="M31" s="30" t="s">
+      <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="30" t="s">
+      <x:c r="B32" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C32" s="30" t="s">
+      <x:c r="C32" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D32" s="31" t="s">
+      <x:c r="D32" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E32" s="30" t="s">
+      <x:c r="E32" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F32" s="30" t="s">
+      <x:c r="F32" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G32" s="30" t="s">
+      <x:c r="G32" s="29" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="H32" s="32">
+      <x:c r="H32" s="31">
         <x:v>46122.1299166204</x:v>
       </x:c>
-      <x:c r="I32" s="32">
+      <x:c r="I32" s="31">
         <x:v>46122.2059087963</x:v>
       </x:c>
-      <x:c r="J32" s="31" t="s">
+      <x:c r="J32" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K32" s="33" t="n">
+      <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L32" s="34">
+      <x:c r="L32" s="33">
         <x:v>46122.2086237847</x:v>
       </x:c>
-      <x:c r="M32" s="30" t="s">
+      <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="30" t="s">
+      <x:c r="B33" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C33" s="30" t="s">
+      <x:c r="C33" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D33" s="31" t="s">
+      <x:c r="D33" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E33" s="30" t="s">
+      <x:c r="E33" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F33" s="30" t="s">
+      <x:c r="F33" s="29" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G33" s="30" t="s">
+      <x:c r="G33" s="29" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="H33" s="32">
+      <x:c r="H33" s="31">
         <x:v>46122.1996025926</x:v>
       </x:c>
-      <x:c r="I33" s="32">
+      <x:c r="I33" s="31">
         <x:v>46122.2050823032</x:v>
       </x:c>
-      <x:c r="J33" s="31" t="s">
+      <x:c r="J33" s="30" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="K33" s="33" t="n">
+      <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L33" s="34">
+      <x:c r="L33" s="33">
         <x:v>46122.2083635185</x:v>
       </x:c>
-      <x:c r="M33" s="30" t="s">
+      <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="30" t="s">
+      <x:c r="B34" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C34" s="30" t="s">
+      <x:c r="C34" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D34" s="31" t="s">
+      <x:c r="D34" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E34" s="30" t="s">
+      <x:c r="E34" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F34" s="30" t="s">
+      <x:c r="F34" s="29" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G34" s="30" t="s">
+      <x:c r="G34" s="29" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="H34" s="32">
+      <x:c r="H34" s="31">
         <x:v>46121.2273626852</x:v>
       </x:c>
-      <x:c r="I34" s="32">
+      <x:c r="I34" s="31">
         <x:v>46121.228379213</x:v>
       </x:c>
-      <x:c r="J34" s="31" t="s">
+      <x:c r="J34" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K34" s="33" t="n">
+      <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L34" s="34">
+      <x:c r="L34" s="33">
         <x:v>46121.2291153125</x:v>
       </x:c>
-      <x:c r="M34" s="30" t="s">
+      <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="30" t="s">
+      <x:c r="B35" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C35" s="30" t="s">
+      <x:c r="C35" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D35" s="31" t="s">
+      <x:c r="D35" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E35" s="30" t="s">
+      <x:c r="E35" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F35" s="30" t="s">
+      <x:c r="F35" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G35" s="30" t="s">
+      <x:c r="G35" s="29" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="H35" s="32">
+      <x:c r="H35" s="31">
         <x:v>46119.8017436343</x:v>
       </x:c>
-      <x:c r="I35" s="32">
+      <x:c r="I35" s="31">
         <x:v>46119.8048384144</x:v>
       </x:c>
-      <x:c r="J35" s="31" t="s">
+      <x:c r="J35" s="30" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K35" s="33" t="n">
+      <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L35" s="34">
+      <x:c r="L35" s="33">
         <x:v>46119.8080510417</x:v>
       </x:c>
-      <x:c r="M35" s="30" t="s">
+      <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="30" t="s">
+      <x:c r="B36" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C36" s="30" t="s">
+      <x:c r="C36" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D36" s="31" t="s">
+      <x:c r="D36" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E36" s="30" t="s">
+      <x:c r="E36" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F36" s="30" t="s">
+      <x:c r="F36" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G36" s="30" t="s">
+      <x:c r="G36" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H36" s="32">
+      <x:c r="H36" s="31">
         <x:v>46119.5434206134</x:v>
       </x:c>
-      <x:c r="I36" s="32">
+      <x:c r="I36" s="31">
         <x:v>46119.545474919</x:v>
       </x:c>
-      <x:c r="J36" s="31" t="s">
+      <x:c r="J36" s="30" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="K36" s="33" t="n">
+      <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L36" s="34">
+      <x:c r="L36" s="33">
         <x:v>46119.5469447569</x:v>
       </x:c>
-      <x:c r="M36" s="30" t="s">
+      <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="30" t="s">
+      <x:c r="B37" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C37" s="30" t="s">
+      <x:c r="C37" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D37" s="31" t="s">
+      <x:c r="D37" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E37" s="30" t="s">
+      <x:c r="E37" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F37" s="30" t="s">
+      <x:c r="F37" s="29" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G37" s="30" t="s">
+      <x:c r="G37" s="29" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="H37" s="32">
+      <x:c r="H37" s="31">
         <x:v>46119.729231331</x:v>
       </x:c>
-      <x:c r="I37" s="32">
+      <x:c r="I37" s="31">
         <x:v>46119.7316308565</x:v>
       </x:c>
-      <x:c r="J37" s="31" t="s">
+      <x:c r="J37" s="30" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="K37" s="33" t="n">
+      <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L37" s="34">
+      <x:c r="L37" s="33">
         <x:v>46119.7327704398</x:v>
       </x:c>
-      <x:c r="M37" s="30" t="s">
+      <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="30" t="s">
+      <x:c r="B38" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C38" s="30" t="s">
+      <x:c r="C38" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D38" s="31" t="s">
+      <x:c r="D38" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E38" s="30" t="s">
+      <x:c r="E38" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F38" s="30" t="s">
+      <x:c r="F38" s="29" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="G38" s="30" t="s">
+      <x:c r="G38" s="29" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="H38" s="32">
+      <x:c r="H38" s="31">
         <x:v>46118.4219285995</x:v>
       </x:c>
-      <x:c r="I38" s="32">
+      <x:c r="I38" s="31">
         <x:v>46118.4229350116</x:v>
       </x:c>
-      <x:c r="J38" s="31" t="s">
+      <x:c r="J38" s="30" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="K38" s="33" t="n">
+      <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L38" s="34">
+      <x:c r="L38" s="33">
         <x:v>46118.4241364815</x:v>
       </x:c>
-      <x:c r="M38" s="30" t="s">
+      <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="30" t="s">
+      <x:c r="B39" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C39" s="30" t="s">
+      <x:c r="C39" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D39" s="31" t="s">
+      <x:c r="D39" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E39" s="30" t="s">
+      <x:c r="E39" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F39" s="30" t="s">
+      <x:c r="F39" s="29" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="G39" s="30" t="s">
+      <x:c r="G39" s="29" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H39" s="32">
+      <x:c r="H39" s="31">
         <x:v>46118.7424944097</x:v>
       </x:c>
-      <x:c r="I39" s="32">
+      <x:c r="I39" s="31">
         <x:v>46118.7432728009</x:v>
       </x:c>
-      <x:c r="J39" s="31" t="s">
+      <x:c r="J39" s="30" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="K39" s="33" t="n">
+      <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L39" s="34">
+      <x:c r="L39" s="33">
         <x:v>46118.743899213</x:v>
       </x:c>
-      <x:c r="M39" s="30" t="s">
+      <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="30" t="s">
+      <x:c r="B40" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C40" s="30" t="s">
+      <x:c r="C40" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D40" s="31" t="s">
+      <x:c r="D40" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E40" s="30" t="s">
+      <x:c r="E40" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F40" s="30" t="s">
+      <x:c r="F40" s="29" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G40" s="30" t="s">
+      <x:c r="G40" s="29" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="H40" s="32">
+      <x:c r="H40" s="31">
         <x:v>46118.7562945255</x:v>
       </x:c>
-      <x:c r="I40" s="32">
+      <x:c r="I40" s="31">
         <x:v>46118.7571720255</x:v>
       </x:c>
-      <x:c r="J40" s="31" t="s">
+      <x:c r="J40" s="30" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="K40" s="33" t="n">
+      <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L40" s="34">
+      <x:c r="L40" s="33">
         <x:v>46118.7577859143</x:v>
       </x:c>
-      <x:c r="M40" s="30" t="s">
+      <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="30" t="s">
+      <x:c r="B41" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C41" s="30" t="s">
+      <x:c r="C41" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D41" s="31" t="s">
+      <x:c r="D41" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E41" s="30" t="s">
+      <x:c r="E41" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F41" s="30" t="s">
+      <x:c r="F41" s="29" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G41" s="30" t="s">
+      <x:c r="G41" s="29" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="H41" s="32">
+      <x:c r="H41" s="31">
         <x:v>46119.0668949653</x:v>
       </x:c>
-      <x:c r="I41" s="32">
+      <x:c r="I41" s="31">
         <x:v>46119.0755180324</x:v>
       </x:c>
-      <x:c r="J41" s="31" t="s">
+      <x:c r="J41" s="30" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="K41" s="33" t="n">
+      <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L41" s="34">
+      <x:c r="L41" s="33">
         <x:v>46119.076169375</x:v>
       </x:c>
-      <x:c r="M41" s="30" t="s">
+      <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="30" t="s">
+      <x:c r="B42" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C42" s="30" t="s">
+      <x:c r="C42" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D42" s="31" t="s">
+      <x:c r="D42" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E42" s="30" t="s">
+      <x:c r="E42" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F42" s="30" t="s">
+      <x:c r="F42" s="29" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G42" s="30" t="s">
+      <x:c r="G42" s="29" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H42" s="32">
+      <x:c r="H42" s="31">
         <x:v>46119.0739296412</x:v>
       </x:c>
-      <x:c r="I42" s="32">
+      <x:c r="I42" s="31">
         <x:v>46119.0753097685</x:v>
       </x:c>
-      <x:c r="J42" s="31" t="s">
+      <x:c r="J42" s="30" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="K42" s="33" t="n">
+      <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L42" s="34">
+      <x:c r="L42" s="33">
         <x:v>46119.0764109954</x:v>
       </x:c>
-      <x:c r="M42" s="30" t="s">
+      <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B43" s="30" t="s">
+      <x:c r="B43" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C43" s="30" t="s">
+      <x:c r="C43" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D43" s="31" t="s">
+      <x:c r="D43" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E43" s="30" t="s">
+      <x:c r="E43" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F43" s="30" t="s">
+      <x:c r="F43" s="29" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G43" s="30" t="s">
+      <x:c r="G43" s="29" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H43" s="32">
+      <x:c r="H43" s="31">
         <x:v>46119.1921340856</x:v>
       </x:c>
-      <x:c r="I43" s="32">
+      <x:c r="I43" s="31">
         <x:v>46119.1932160417</x:v>
       </x:c>
-      <x:c r="J43" s="31" t="s">
+      <x:c r="J43" s="30" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="K43" s="33" t="n">
+      <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L43" s="34">
+      <x:c r="L43" s="33">
         <x:v>46119.193627581</x:v>
       </x:c>
-      <x:c r="M43" s="30" t="s">
+      <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="30" t="s">
+      <x:c r="B44" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C44" s="30" t="s">
+      <x:c r="C44" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D44" s="31" t="s">
+      <x:c r="D44" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E44" s="30" t="s">
+      <x:c r="E44" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F44" s="30" t="s">
+      <x:c r="F44" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G44" s="30" t="s">
+      <x:c r="G44" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H44" s="32">
+      <x:c r="H44" s="31">
         <x:v>46119.7297941435</x:v>
       </x:c>
-      <x:c r="I44" s="32">
+      <x:c r="I44" s="31">
         <x:v>46119.731450544</x:v>
       </x:c>
-      <x:c r="J44" s="31" t="s">
+      <x:c r="J44" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K44" s="33" t="n">
+      <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L44" s="34">
+      <x:c r="L44" s="33">
         <x:v>46119.7324832755</x:v>
       </x:c>
-      <x:c r="M44" s="30" t="s">
+      <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="30" t="s">
+      <x:c r="B45" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C45" s="30" t="s">
+      <x:c r="C45" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D45" s="31" t="s">
+      <x:c r="D45" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E45" s="30" t="s">
+      <x:c r="E45" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F45" s="30" t="s">
+      <x:c r="F45" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G45" s="30" t="s">
+      <x:c r="G45" s="29" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="H45" s="32">
+      <x:c r="H45" s="31">
         <x:v>46119.4681336458</x:v>
       </x:c>
-      <x:c r="I45" s="32">
+      <x:c r="I45" s="31">
         <x:v>46119.4697068056</x:v>
       </x:c>
-      <x:c r="J45" s="31" t="s">
+      <x:c r="J45" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K45" s="33" t="n">
+      <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L45" s="34">
+      <x:c r="L45" s="33">
         <x:v>46119.470392037</x:v>
       </x:c>
-      <x:c r="M45" s="30" t="s">
+      <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B46" s="30" t="s">
+      <x:c r="B46" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C46" s="30" t="s">
+      <x:c r="C46" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D46" s="31" t="s">
+      <x:c r="D46" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E46" s="30" t="s">
+      <x:c r="E46" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F46" s="30" t="s">
+      <x:c r="F46" s="29" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="G46" s="30" t="s">
+      <x:c r="G46" s="29" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="H46" s="32">
+      <x:c r="H46" s="31">
         <x:v>46119.5424612384</x:v>
       </x:c>
-      <x:c r="I46" s="32">
+      <x:c r="I46" s="31">
         <x:v>46119.5457934491</x:v>
       </x:c>
-      <x:c r="J46" s="31" t="s">
+      <x:c r="J46" s="30" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="K46" s="33" t="n">
+      <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L46" s="34">
+      <x:c r="L46" s="33">
         <x:v>46119.5465567708</x:v>
       </x:c>
-      <x:c r="M46" s="30" t="s">
+      <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B47" s="30" t="s">
+      <x:c r="B47" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C47" s="30" t="s">
+      <x:c r="C47" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D47" s="31" t="s">
+      <x:c r="D47" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E47" s="30" t="s">
+      <x:c r="E47" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F47" s="30" t="s">
+      <x:c r="F47" s="29" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="G47" s="30" t="s">
+      <x:c r="G47" s="29" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="H47" s="32">
+      <x:c r="H47" s="31">
         <x:v>46119.542956794</x:v>
       </x:c>
-      <x:c r="I47" s="32">
+      <x:c r="I47" s="31">
         <x:v>46119.5456356481</x:v>
       </x:c>
-      <x:c r="J47" s="31" t="s">
+      <x:c r="J47" s="30" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="K47" s="33" t="n">
+      <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L47" s="34">
+      <x:c r="L47" s="33">
         <x:v>46119.5477968982</x:v>
       </x:c>
-      <x:c r="M47" s="30" t="s">
+      <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B48" s="30" t="s">
+      <x:c r="B48" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C48" s="30" t="s">
+      <x:c r="C48" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D48" s="31" t="s">
+      <x:c r="D48" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E48" s="30" t="s">
+      <x:c r="E48" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F48" s="30" t="s">
+      <x:c r="F48" s="29" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="G48" s="30" t="s">
+      <x:c r="G48" s="29" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="H48" s="32">
+      <x:c r="H48" s="31">
         <x:v>46122.2429836343</x:v>
       </x:c>
-      <x:c r="I48" s="32">
+      <x:c r="I48" s="31">
         <x:v>46122.244317963</x:v>
       </x:c>
-      <x:c r="J48" s="31" t="s">
+      <x:c r="J48" s="30" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="K48" s="33" t="n">
+      <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L48" s="34">
+      <x:c r="L48" s="33">
         <x:v>46122.2448800694</x:v>
       </x:c>
-      <x:c r="M48" s="30" t="s">
+      <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B49" s="30" t="s">
+      <x:c r="B49" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C49" s="30" t="s">
+      <x:c r="C49" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D49" s="31" t="s">
+      <x:c r="D49" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E49" s="30" t="s">
+      <x:c r="E49" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F49" s="30" t="s">
+      <x:c r="F49" s="29" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G49" s="30" t="s">
+      <x:c r="G49" s="29" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H49" s="32">
+      <x:c r="H49" s="31">
         <x:v>46119.5439653357</x:v>
       </x:c>
-      <x:c r="I49" s="32">
+      <x:c r="I49" s="31">
         <x:v>46119.5452984143</x:v>
       </x:c>
-      <x:c r="J49" s="31" t="s">
+      <x:c r="J49" s="30" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="K49" s="33" t="n">
+      <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L49" s="34">
+      <x:c r="L49" s="33">
         <x:v>46119.5467543982</x:v>
       </x:c>
-      <x:c r="M49" s="30" t="s">
+      <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B50" s="30" t="s">
+      <x:c r="B50" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C50" s="30" t="s">
+      <x:c r="C50" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D50" s="31" t="s">
+      <x:c r="D50" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E50" s="30" t="s">
+      <x:c r="E50" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F50" s="30" t="s">
+      <x:c r="F50" s="29" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="G50" s="30" t="s">
+      <x:c r="G50" s="29" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H50" s="32">
+      <x:c r="H50" s="31">
         <x:v>46119.7254171991</x:v>
       </x:c>
-      <x:c r="I50" s="32">
+      <x:c r="I50" s="31">
         <x:v>46119.7262936574</x:v>
       </x:c>
-      <x:c r="J50" s="31" t="s">
+      <x:c r="J50" s="30" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="K50" s="33" t="n">
+      <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L50" s="34">
+      <x:c r="L50" s="33">
         <x:v>46119.7267657407</x:v>
       </x:c>
-      <x:c r="M50" s="30" t="s">
+      <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B51" s="30" t="s">
+      <x:c r="B51" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C51" s="30" t="s">
+      <x:c r="C51" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D51" s="31" t="s">
+      <x:c r="D51" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E51" s="30" t="s">
+      <x:c r="E51" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F51" s="30" t="s">
+      <x:c r="F51" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G51" s="30" t="s">
+      <x:c r="G51" s="29" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="H51" s="32">
+      <x:c r="H51" s="31">
         <x:v>46119.7285584838</x:v>
       </x:c>
-      <x:c r="I51" s="32">
+      <x:c r="I51" s="31">
         <x:v>46119.7318005208</x:v>
       </x:c>
-      <x:c r="J51" s="31" t="s">
+      <x:c r="J51" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K51" s="33" t="n">
+      <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L51" s="34">
+      <x:c r="L51" s="33">
         <x:v>46119.7339888773</x:v>
       </x:c>
-      <x:c r="M51" s="30" t="s">
+      <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B52" s="30" t="s">
+      <x:c r="B52" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C52" s="30" t="s">
+      <x:c r="C52" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D52" s="31" t="s">
+      <x:c r="D52" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E52" s="30" t="s">
+      <x:c r="E52" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F52" s="30" t="s">
+      <x:c r="F52" s="29" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="G52" s="30" t="s">
+      <x:c r="G52" s="29" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="H52" s="32">
+      <x:c r="H52" s="31">
         <x:v>46119.5267212153</x:v>
       </x:c>
-      <x:c r="I52" s="32">
+      <x:c r="I52" s="31">
         <x:v>46119.5274664236</x:v>
       </x:c>
-      <x:c r="J52" s="31" t="s">
+      <x:c r="J52" s="30" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="K52" s="33" t="n">
+      <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L52" s="34">
+      <x:c r="L52" s="33">
         <x:v>46119.5279398495</x:v>
       </x:c>
-      <x:c r="M52" s="30" t="s">
+      <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B53" s="30" t="s">
+      <x:c r="B53" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C53" s="30" t="s">
+      <x:c r="C53" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D53" s="31" t="s">
+      <x:c r="D53" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E53" s="30" t="s">
+      <x:c r="E53" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F53" s="30" t="s">
+      <x:c r="F53" s="29" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G53" s="30" t="s">
+      <x:c r="G53" s="29" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="H53" s="32">
+      <x:c r="H53" s="31">
         <x:v>46122.3569147569</x:v>
       </x:c>
-      <x:c r="I53" s="32">
+      <x:c r="I53" s="31">
         <x:v>46122.3577305324</x:v>
       </x:c>
-      <x:c r="J53" s="31" t="s">
+      <x:c r="J53" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K53" s="33" t="n">
+      <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L53" s="34">
+      <x:c r="L53" s="33">
         <x:v>46122.3582679861</x:v>
       </x:c>
-      <x:c r="M53" s="30" t="s">
+      <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B54" s="30" t="s">
+      <x:c r="B54" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C54" s="30" t="s">
+      <x:c r="C54" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D54" s="31" t="s">
+      <x:c r="D54" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E54" s="30" t="s">
+      <x:c r="E54" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F54" s="30" t="s">
+      <x:c r="F54" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G54" s="30" t="s">
+      <x:c r="G54" s="29" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="H54" s="32">
+      <x:c r="H54" s="31">
         <x:v>46122.36782125</x:v>
       </x:c>
-      <x:c r="I54" s="32">
+      <x:c r="I54" s="31">
         <x:v>46122.3686719907</x:v>
       </x:c>
-      <x:c r="J54" s="31" t="s">
+      <x:c r="J54" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K54" s="33" t="n">
+      <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L54" s="34">
+      <x:c r="L54" s="33">
         <x:v>46122.3692180787</x:v>
       </x:c>
-      <x:c r="M54" s="30" t="s">
+      <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B55" s="30" t="s">
+      <x:c r="B55" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C55" s="30" t="s">
+      <x:c r="C55" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D55" s="31" t="s">
+      <x:c r="D55" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E55" s="30" t="s">
+      <x:c r="E55" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F55" s="30" t="s">
+      <x:c r="F55" s="29" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G55" s="30" t="s">
+      <x:c r="G55" s="29" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="H55" s="32">
+      <x:c r="H55" s="31">
         <x:v>46122.3767795718</x:v>
       </x:c>
-      <x:c r="I55" s="32">
+      <x:c r="I55" s="31">
         <x:v>46122.3776183449</x:v>
       </x:c>
-      <x:c r="J55" s="31" t="s">
+      <x:c r="J55" s="30" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="K55" s="33" t="n">
+      <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L55" s="34">
+      <x:c r="L55" s="33">
         <x:v>46122.3780755324</x:v>
       </x:c>
-      <x:c r="M55" s="30" t="s">
+      <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B56" s="30" t="s">
+      <x:c r="B56" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C56" s="30" t="s">
+      <x:c r="C56" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D56" s="31" t="s">
+      <x:c r="D56" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E56" s="30" t="s">
+      <x:c r="E56" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F56" s="30" t="s">
+      <x:c r="F56" s="29" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G56" s="30" t="s">
+      <x:c r="G56" s="29" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="H56" s="32">
+      <x:c r="H56" s="31">
         <x:v>46127.1221474769</x:v>
       </x:c>
-      <x:c r="I56" s="32">
+      <x:c r="I56" s="31">
         <x:v>46127.1231965625</x:v>
       </x:c>
-      <x:c r="J56" s="31" t="s">
+      <x:c r="J56" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K56" s="33" t="n">
+      <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L56" s="34">
+      <x:c r="L56" s="33">
         <x:v>46128.1095700579</x:v>
       </x:c>
-      <x:c r="M56" s="30" t="s">
+      <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B57" s="30" t="s">
+      <x:c r="B57" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C57" s="30" t="s">
+      <x:c r="C57" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D57" s="31" t="s">
+      <x:c r="D57" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E57" s="30" t="s">
+      <x:c r="E57" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F57" s="30" t="s">
+      <x:c r="F57" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G57" s="30" t="s">
+      <x:c r="G57" s="29" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="H57" s="32">
+      <x:c r="H57" s="31">
         <x:v>46126.5341923727</x:v>
       </x:c>
-      <x:c r="I57" s="32">
+      <x:c r="I57" s="31">
         <x:v>46126.5348242708</x:v>
       </x:c>
-      <x:c r="J57" s="31" t="s">
+      <x:c r="J57" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K57" s="33" t="n">
+      <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L57" s="34">
+      <x:c r="L57" s="33">
         <x:v>46126.5353594213</x:v>
       </x:c>
-      <x:c r="M57" s="30" t="s">
+      <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B58" s="30" t="s">
+      <x:c r="B58" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C58" s="30" t="s">
+      <x:c r="C58" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D58" s="31" t="s">
+      <x:c r="D58" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E58" s="30" t="s">
+      <x:c r="E58" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F58" s="30" t="s">
+      <x:c r="F58" s="29" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="G58" s="30" t="s">
+      <x:c r="G58" s="29" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="H58" s="32">
+      <x:c r="H58" s="31">
         <x:v>46124.7035032407</x:v>
       </x:c>
-      <x:c r="I58" s="32">
+      <x:c r="I58" s="31">
         <x:v>46124.704475463</x:v>
       </x:c>
-      <x:c r="J58" s="31" t="s">
+      <x:c r="J58" s="30" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="K58" s="33" t="n">
+      <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L58" s="34">
+      <x:c r="L58" s="33">
         <x:v>46124.7056197917</x:v>
       </x:c>
-      <x:c r="M58" s="30" t="s">
+      <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B59" s="30" t="s">
+      <x:c r="B59" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C59" s="30" t="s">
+      <x:c r="C59" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D59" s="31" t="s">
+      <x:c r="D59" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E59" s="30" t="s">
+      <x:c r="E59" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F59" s="30" t="s">
+      <x:c r="F59" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G59" s="30" t="s">
+      <x:c r="G59" s="29" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="H59" s="32">
+      <x:c r="H59" s="31">
         <x:v>46124.7029179398</x:v>
       </x:c>
-      <x:c r="I59" s="32">
+      <x:c r="I59" s="31">
         <x:v>46124.7046092014</x:v>
       </x:c>
-      <x:c r="J59" s="31" t="s">
+      <x:c r="J59" s="30" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="K59" s="33" t="n">
+      <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L59" s="34">
+      <x:c r="L59" s="33">
         <x:v>46124.7058091204</x:v>
       </x:c>
-      <x:c r="M59" s="30" t="s">
+      <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B60" s="30" t="s">
+      <x:c r="B60" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C60" s="30" t="s">
+      <x:c r="C60" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D60" s="31" t="s">
+      <x:c r="D60" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E60" s="30" t="s">
+      <x:c r="E60" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F60" s="30" t="s">
+      <x:c r="F60" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G60" s="30" t="s">
+      <x:c r="G60" s="29" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="H60" s="32">
+      <x:c r="H60" s="31">
         <x:v>46124.7023532986</x:v>
       </x:c>
-      <x:c r="I60" s="32">
+      <x:c r="I60" s="31">
         <x:v>46124.7048005093</x:v>
       </x:c>
-      <x:c r="J60" s="31" t="s">
+      <x:c r="J60" s="30" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="K60" s="33" t="n">
+      <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L60" s="34">
+      <x:c r="L60" s="33">
         <x:v>46124.7059938426</x:v>
       </x:c>
-      <x:c r="M60" s="30" t="s">
+      <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B61" s="30" t="s">
+      <x:c r="B61" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C61" s="30" t="s">
+      <x:c r="C61" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D61" s="31" t="s">
+      <x:c r="D61" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E61" s="30" t="s">
+      <x:c r="E61" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F61" s="30" t="s">
+      <x:c r="F61" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G61" s="30" t="s">
+      <x:c r="G61" s="29" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="H61" s="32">
+      <x:c r="H61" s="31">
         <x:v>46124.701771875</x:v>
       </x:c>
-      <x:c r="I61" s="32">
+      <x:c r="I61" s="31">
         <x:v>46124.7049218519</x:v>
       </x:c>
-      <x:c r="J61" s="31" t="s">
+      <x:c r="J61" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K61" s="33" t="n">
+      <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L61" s="34">
+      <x:c r="L61" s="33">
         <x:v>46124.7061899306</x:v>
       </x:c>
-      <x:c r="M61" s="30" t="s">
+      <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B62" s="30" t="s">
+      <x:c r="B62" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C62" s="30" t="s">
+      <x:c r="C62" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D62" s="31" t="s">
+      <x:c r="D62" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E62" s="30" t="s">
+      <x:c r="E62" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F62" s="30" t="s">
+      <x:c r="F62" s="29" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="G62" s="30" t="s">
+      <x:c r="G62" s="29" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="H62" s="32">
+      <x:c r="H62" s="31">
         <x:v>46124.6975491551</x:v>
       </x:c>
-      <x:c r="I62" s="32">
+      <x:c r="I62" s="31">
         <x:v>46124.6983328357</x:v>
       </x:c>
-      <x:c r="J62" s="31" t="s">
+      <x:c r="J62" s="30" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="K62" s="33" t="n">
+      <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L62" s="34">
+      <x:c r="L62" s="33">
         <x:v>46124.6990752199</x:v>
       </x:c>
-      <x:c r="M62" s="30" t="s">
+      <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B63" s="30" t="s">
+      <x:c r="B63" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C63" s="30" t="s">
+      <x:c r="C63" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D63" s="31" t="s">
+      <x:c r="D63" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E63" s="30" t="s">
+      <x:c r="E63" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F63" s="30" t="s">
+      <x:c r="F63" s="29" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="G63" s="30" t="s">
+      <x:c r="G63" s="29" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="H63" s="32">
+      <x:c r="H63" s="31">
         <x:v>46124.6761778356</x:v>
       </x:c>
-      <x:c r="I63" s="32">
+      <x:c r="I63" s="31">
         <x:v>46124.6772295602</x:v>
       </x:c>
-      <x:c r="J63" s="31" t="s">
+      <x:c r="J63" s="30" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="K63" s="33" t="n">
+      <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L63" s="34">
+      <x:c r="L63" s="33">
         <x:v>46124.6777516435</x:v>
       </x:c>
-      <x:c r="M63" s="30" t="s">
+      <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B64" s="30" t="s">
+      <x:c r="B64" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C64" s="30" t="s">
+      <x:c r="C64" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D64" s="31" t="s">
+      <x:c r="D64" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E64" s="30" t="s">
+      <x:c r="E64" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F64" s="30" t="s">
+      <x:c r="F64" s="29" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="G64" s="30" t="s">
+      <x:c r="G64" s="29" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="H64" s="32">
+      <x:c r="H64" s="31">
         <x:v>46124.5490358102</x:v>
       </x:c>
-      <x:c r="I64" s="32">
+      <x:c r="I64" s="31">
         <x:v>46124.6984689583</x:v>
       </x:c>
-      <x:c r="J64" s="31" t="s">
+      <x:c r="J64" s="30" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="K64" s="33" t="n">
+      <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L64" s="34">
+      <x:c r="L64" s="33">
         <x:v>46124.6992754861</x:v>
       </x:c>
-      <x:c r="M64" s="30" t="s">
+      <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B65" s="30" t="s">
+      <x:c r="B65" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C65" s="30" t="s">
+      <x:c r="C65" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D65" s="31" t="s">
+      <x:c r="D65" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E65" s="30" t="s">
+      <x:c r="E65" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F65" s="30" t="s">
+      <x:c r="F65" s="29" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="G65" s="30" t="s">
+      <x:c r="G65" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H65" s="32">
+      <x:c r="H65" s="31">
         <x:v>46124.1518079282</x:v>
       </x:c>
-      <x:c r="I65" s="32">
+      <x:c r="I65" s="31">
         <x:v>46124.1529164583</x:v>
       </x:c>
-      <x:c r="J65" s="31" t="s">
+      <x:c r="J65" s="30" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="K65" s="33" t="n">
+      <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L65" s="34">
+      <x:c r="L65" s="33">
         <x:v>46124.1538595949</x:v>
       </x:c>
-      <x:c r="M65" s="30" t="s">
+      <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B66" s="30" t="s">
+      <x:c r="B66" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C66" s="30" t="s">
+      <x:c r="C66" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D66" s="31" t="s">
+      <x:c r="D66" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E66" s="30" t="s">
+      <x:c r="E66" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F66" s="30" t="s">
+      <x:c r="F66" s="29" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G66" s="30" t="s">
+      <x:c r="G66" s="29" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="H66" s="32">
+      <x:c r="H66" s="31">
         <x:v>46118.3446055671</x:v>
       </x:c>
-      <x:c r="I66" s="32">
+      <x:c r="I66" s="31">
         <x:v>46118.476906412</x:v>
       </x:c>
-      <x:c r="J66" s="31" t="s">
+      <x:c r="J66" s="30" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="K66" s="33" t="n">
+      <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L66" s="34">
+      <x:c r="L66" s="33">
         <x:v>46118.3476865394</x:v>
       </x:c>
-      <x:c r="M66" s="30" t="s">
+      <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B67" s="30" t="s">
+      <x:c r="B67" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C67" s="30" t="s">
+      <x:c r="C67" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D67" s="31" t="s">
+      <x:c r="D67" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E67" s="30" t="s">
+      <x:c r="E67" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F67" s="30" t="s">
+      <x:c r="F67" s="29" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G67" s="30" t="s">
+      <x:c r="G67" s="29" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="H67" s="32">
+      <x:c r="H67" s="31">
         <x:v>46124.150742662</x:v>
       </x:c>
-      <x:c r="I67" s="32">
+      <x:c r="I67" s="31">
         <x:v>46124.153253125</x:v>
       </x:c>
-      <x:c r="J67" s="31" t="s">
+      <x:c r="J67" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K67" s="33" t="n">
+      <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L67" s="34">
+      <x:c r="L67" s="33">
         <x:v>46124.1542643171</x:v>
       </x:c>
-      <x:c r="M67" s="30" t="s">
+      <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B68" s="30" t="s">
+      <x:c r="B68" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C68" s="30" t="s">
+      <x:c r="C68" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D68" s="31" t="s">
+      <x:c r="D68" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E68" s="30" t="s">
+      <x:c r="E68" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F68" s="30" t="s">
+      <x:c r="F68" s="29" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="G68" s="30" t="s">
+      <x:c r="G68" s="29" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="H68" s="32">
+      <x:c r="H68" s="31">
         <x:v>46124.1487218981</x:v>
       </x:c>
-      <x:c r="I68" s="32">
+      <x:c r="I68" s="31">
         <x:v>46124.1494313773</x:v>
       </x:c>
-      <x:c r="J68" s="31" t="s">
+      <x:c r="J68" s="30" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="K68" s="33" t="n">
+      <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L68" s="34">
+      <x:c r="L68" s="33">
         <x:v>46124.1498205093</x:v>
       </x:c>
-      <x:c r="M68" s="30" t="s">
+      <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B69" s="30" t="s">
+      <x:c r="B69" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C69" s="30" t="s">
+      <x:c r="C69" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D69" s="31" t="s">
+      <x:c r="D69" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E69" s="30" t="s">
+      <x:c r="E69" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F69" s="30" t="s">
+      <x:c r="F69" s="29" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="G69" s="30" t="s">
+      <x:c r="G69" s="29" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="H69" s="32">
+      <x:c r="H69" s="31">
         <x:v>46124.1449755903</x:v>
       </x:c>
-      <x:c r="I69" s="32">
+      <x:c r="I69" s="31">
         <x:v>46124.1465040046</x:v>
       </x:c>
-      <x:c r="J69" s="31" t="s">
+      <x:c r="J69" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K69" s="33" t="n">
+      <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L69" s="34">
+      <x:c r="L69" s="33">
         <x:v>46124.1471056481</x:v>
       </x:c>
-      <x:c r="M69" s="30" t="s">
+      <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B70" s="30" t="s">
+      <x:c r="B70" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C70" s="30" t="s">
+      <x:c r="C70" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D70" s="31" t="s">
+      <x:c r="D70" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E70" s="30" t="s">
+      <x:c r="E70" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F70" s="30" t="s">
+      <x:c r="F70" s="29" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="G70" s="30" t="s">
+      <x:c r="G70" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="H70" s="32">
+      <x:c r="H70" s="31">
         <x:v>46124.1410094907</x:v>
       </x:c>
-      <x:c r="I70" s="32">
+      <x:c r="I70" s="31">
         <x:v>46124.1426461806</x:v>
       </x:c>
-      <x:c r="J70" s="31" t="s">
+      <x:c r="J70" s="30" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="K70" s="33" t="n">
+      <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L70" s="34">
+      <x:c r="L70" s="33">
         <x:v>46124.1434541782</x:v>
       </x:c>
-      <x:c r="M70" s="30" t="s">
+      <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B71" s="30" t="s">
+      <x:c r="B71" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C71" s="30" t="s">
+      <x:c r="C71" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D71" s="31" t="s">
+      <x:c r="D71" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E71" s="30" t="s">
+      <x:c r="E71" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F71" s="30" t="s">
+      <x:c r="F71" s="29" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G71" s="30" t="s">
+      <x:c r="G71" s="29" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="H71" s="32">
+      <x:c r="H71" s="31">
         <x:v>46124.1512647338</x:v>
       </x:c>
-      <x:c r="I71" s="32">
+      <x:c r="I71" s="31">
         <x:v>46124.1530803935</x:v>
       </x:c>
-      <x:c r="J71" s="31" t="s">
+      <x:c r="J71" s="30" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="K71" s="33" t="n">
+      <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L71" s="34">
+      <x:c r="L71" s="33">
         <x:v>46124.1540594444</x:v>
       </x:c>
-      <x:c r="M71" s="30" t="s">
+      <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B72" s="30" t="s">
+      <x:c r="B72" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C72" s="30" t="s">
+      <x:c r="C72" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D72" s="31" t="s">
+      <x:c r="D72" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E72" s="30" t="s">
+      <x:c r="E72" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F72" s="30" t="s">
+      <x:c r="F72" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G72" s="30" t="s">
+      <x:c r="G72" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="H72" s="32">
+      <x:c r="H72" s="31">
         <x:v>46123.4162791088</x:v>
       </x:c>
-      <x:c r="I72" s="32">
+      <x:c r="I72" s="31">
         <x:v>46123.4173169792</x:v>
       </x:c>
-      <x:c r="J72" s="31" t="s">
+      <x:c r="J72" s="30" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="K72" s="33" t="n">
+      <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L72" s="34">
+      <x:c r="L72" s="33">
         <x:v>46123.417862662</x:v>
       </x:c>
-      <x:c r="M72" s="30" t="s">
+      <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B73" s="30" t="s">
+      <x:c r="B73" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C73" s="30" t="s">
+      <x:c r="C73" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D73" s="31" t="s">
+      <x:c r="D73" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E73" s="30" t="s">
+      <x:c r="E73" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F73" s="30" t="s">
+      <x:c r="F73" s="29" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="G73" s="30" t="s">
+      <x:c r="G73" s="29" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="H73" s="32">
+      <x:c r="H73" s="31">
         <x:v>46122.3879258681</x:v>
       </x:c>
-      <x:c r="I73" s="32">
+      <x:c r="I73" s="31">
         <x:v>46122.3894281713</x:v>
       </x:c>
-      <x:c r="J73" s="31" t="s">
+      <x:c r="J73" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K73" s="33" t="n">
+      <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L73" s="34">
+      <x:c r="L73" s="33">
         <x:v>46122.3900310185</x:v>
       </x:c>
-      <x:c r="M73" s="30" t="s">
+      <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B74" s="30" t="s">
+      <x:c r="B74" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C74" s="30" t="s">
+      <x:c r="C74" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D74" s="31" t="s">
+      <x:c r="D74" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E74" s="30" t="s">
+      <x:c r="E74" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F74" s="30" t="s">
+      <x:c r="F74" s="29" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="G74" s="30" t="s">
+      <x:c r="G74" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="H74" s="32">
+      <x:c r="H74" s="31">
         <x:v>46122.3885020718</x:v>
       </x:c>
-      <x:c r="I74" s="32">
+      <x:c r="I74" s="31">
         <x:v>46122.3892655903</x:v>
       </x:c>
-      <x:c r="J74" s="31" t="s">
+      <x:c r="J74" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K74" s="33" t="n">
+      <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L74" s="34">
+      <x:c r="L74" s="33">
         <x:v>46122.3902404514</x:v>
       </x:c>
-      <x:c r="M74" s="30" t="s">
+      <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B75" s="30" t="s">
+      <x:c r="B75" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C75" s="30" t="s">
+      <x:c r="C75" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D75" s="31" t="s">
+      <x:c r="D75" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E75" s="30" t="s">
+      <x:c r="E75" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F75" s="30" t="s">
+      <x:c r="F75" s="29" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="G75" s="30" t="s">
+      <x:c r="G75" s="29" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="H75" s="32">
+      <x:c r="H75" s="31">
         <x:v>46122.3974322338</x:v>
       </x:c>
-      <x:c r="I75" s="32">
+      <x:c r="I75" s="31">
         <x:v>46122.3980999421</x:v>
       </x:c>
-      <x:c r="J75" s="31" t="s">
+      <x:c r="J75" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K75" s="33" t="n">
+      <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L75" s="34">
+      <x:c r="L75" s="33">
         <x:v>46122.398526713</x:v>
       </x:c>
-      <x:c r="M75" s="30" t="s">
+      <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B76" s="30" t="s">
+      <x:c r="B76" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C76" s="30" t="s">
+      <x:c r="C76" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D76" s="31" t="s">
+      <x:c r="D76" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E76" s="30" t="s">
+      <x:c r="E76" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F76" s="30" t="s">
+      <x:c r="F76" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G76" s="30" t="s">
+      <x:c r="G76" s="29" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H76" s="32">
+      <x:c r="H76" s="31">
         <x:v>46122.5587807523</x:v>
       </x:c>
-      <x:c r="I76" s="32">
+      <x:c r="I76" s="31">
         <x:v>46122.5602428125</x:v>
       </x:c>
-      <x:c r="J76" s="31" t="s">
+      <x:c r="J76" s="30" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="K76" s="33" t="n">
+      <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L76" s="34">
+      <x:c r="L76" s="33">
         <x:v>46122.5607516551</x:v>
       </x:c>
-      <x:c r="M76" s="30" t="s">
+      <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B77" s="30" t="s">
+      <x:c r="B77" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C77" s="30" t="s">
+      <x:c r="C77" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D77" s="31" t="s">
+      <x:c r="D77" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E77" s="30" t="s">
+      <x:c r="E77" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F77" s="30" t="s">
+      <x:c r="F77" s="29" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="G77" s="30" t="s">
+      <x:c r="G77" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="H77" s="32">
+      <x:c r="H77" s="31">
         <x:v>46123.4191184375</x:v>
       </x:c>
-      <x:c r="I77" s="32">
+      <x:c r="I77" s="31">
         <x:v>46123.4205974074</x:v>
       </x:c>
-      <x:c r="J77" s="31" t="s">
+      <x:c r="J77" s="30" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="K77" s="33" t="n">
+      <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L77" s="34">
+      <x:c r="L77" s="33">
         <x:v>46123.4214065278</x:v>
       </x:c>
-      <x:c r="M77" s="30" t="s">
+      <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B78" s="30" t="s">
+      <x:c r="B78" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C78" s="30" t="s">
+      <x:c r="C78" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D78" s="31" t="s">
+      <x:c r="D78" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E78" s="30" t="s">
+      <x:c r="E78" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F78" s="30" t="s">
+      <x:c r="F78" s="29" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="G78" s="30" t="s">
+      <x:c r="G78" s="29" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="H78" s="32">
+      <x:c r="H78" s="31">
         <x:v>46122.5911383796</x:v>
       </x:c>
-      <x:c r="I78" s="32">
+      <x:c r="I78" s="31">
         <x:v>46122.5921380556</x:v>
       </x:c>
-      <x:c r="J78" s="31" t="s">
+      <x:c r="J78" s="30" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="K78" s="33" t="n">
+      <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L78" s="34">
+      <x:c r="L78" s="33">
         <x:v>46122.5928339699</x:v>
       </x:c>
-      <x:c r="M78" s="30" t="s">
+      <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B79" s="30" t="s">
+      <x:c r="B79" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C79" s="30" t="s">
+      <x:c r="C79" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D79" s="31" t="s">
+      <x:c r="D79" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E79" s="30" t="s">
+      <x:c r="E79" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F79" s="30" t="s">
+      <x:c r="F79" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G79" s="30" t="s">
+      <x:c r="G79" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="H79" s="32">
+      <x:c r="H79" s="31">
         <x:v>46122.5945434491</x:v>
       </x:c>
-      <x:c r="I79" s="32">
+      <x:c r="I79" s="31">
         <x:v>46122.5999534606</x:v>
       </x:c>
-      <x:c r="J79" s="31" t="s">
+      <x:c r="J79" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K79" s="33" t="n">
+      <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L79" s="34">
+      <x:c r="L79" s="33">
         <x:v>46122.6007489699</x:v>
       </x:c>
-      <x:c r="M79" s="30" t="s">
+      <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B80" s="30" t="s">
+      <x:c r="B80" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C80" s="30" t="s">
+      <x:c r="C80" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D80" s="31" t="s">
+      <x:c r="D80" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E80" s="30" t="s">
+      <x:c r="E80" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F80" s="30" t="s">
+      <x:c r="F80" s="29" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G80" s="30" t="s">
+      <x:c r="G80" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="H80" s="32">
+      <x:c r="H80" s="31">
         <x:v>46122.6182774306</x:v>
       </x:c>
-      <x:c r="I80" s="32">
+      <x:c r="I80" s="31">
         <x:v>46122.6193276968</x:v>
       </x:c>
-      <x:c r="J80" s="31" t="s">
+      <x:c r="J80" s="30" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="K80" s="33" t="n">
+      <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L80" s="34">
+      <x:c r="L80" s="33">
         <x:v>46122.6199813426</x:v>
       </x:c>
-      <x:c r="M80" s="30" t="s">
+      <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B81" s="30" t="s">
+      <x:c r="B81" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C81" s="30" t="s">
+      <x:c r="C81" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D81" s="31" t="s">
+      <x:c r="D81" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E81" s="30" t="s">
+      <x:c r="E81" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F81" s="30" t="s">
+      <x:c r="F81" s="29" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G81" s="30" t="s">
+      <x:c r="G81" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="H81" s="32">
+      <x:c r="H81" s="31">
         <x:v>46122.5623107755</x:v>
       </x:c>
-      <x:c r="I81" s="32">
+      <x:c r="I81" s="31">
         <x:v>46122.5630093981</x:v>
       </x:c>
-      <x:c r="J81" s="31" t="s">
+      <x:c r="J81" s="30" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="K81" s="33" t="n">
+      <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L81" s="34">
+      <x:c r="L81" s="33">
         <x:v>46122.5634620023</x:v>
       </x:c>
-      <x:c r="M81" s="30" t="s">
+      <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B82" s="30" t="s">
+      <x:c r="B82" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C82" s="30" t="s">
+      <x:c r="C82" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D82" s="31" t="s">
+      <x:c r="D82" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E82" s="30" t="s">
+      <x:c r="E82" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F82" s="30" t="s">
+      <x:c r="F82" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G82" s="30" t="s">
+      <x:c r="G82" s="29" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="H82" s="32">
+      <x:c r="H82" s="31">
         <x:v>46128.4605351157</x:v>
       </x:c>
-      <x:c r="I82" s="32">
+      <x:c r="I82" s="31">
         <x:v>46128.4612873727</x:v>
       </x:c>
-      <x:c r="J82" s="31" t="s">
+      <x:c r="J82" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K82" s="33" t="n">
+      <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L82" s="34">
+      <x:c r="L82" s="33">
         <x:v>46128.4617054051</x:v>
       </x:c>
-      <x:c r="M82" s="30" t="s">
+      <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B83" s="30" t="s">
+      <x:c r="B83" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C83" s="30" t="s">
+      <x:c r="C83" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D83" s="31" t="s">
+      <x:c r="D83" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E83" s="30" t="s">
+      <x:c r="E83" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F83" s="30" t="s">
+      <x:c r="F83" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G83" s="30" t="s">
+      <x:c r="G83" s="29" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="H83" s="32">
+      <x:c r="H83" s="31">
         <x:v>46123.061368912</x:v>
       </x:c>
-      <x:c r="I83" s="32">
+      <x:c r="I83" s="31">
         <x:v>46123.0623472106</x:v>
       </x:c>
-      <x:c r="J83" s="31" t="s">
+      <x:c r="J83" s="30" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="K83" s="33" t="n">
+      <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L83" s="34">
+      <x:c r="L83" s="33">
         <x:v>46123.0628773958</x:v>
       </x:c>
-      <x:c r="M83" s="30" t="s">
+      <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B84" s="30" t="s">
+      <x:c r="B84" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C84" s="30" t="s">
+      <x:c r="C84" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D84" s="31" t="s">
+      <x:c r="D84" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E84" s="30" t="s">
+      <x:c r="E84" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F84" s="30" t="s">
+      <x:c r="F84" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G84" s="30" t="s">
+      <x:c r="G84" s="29" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="H84" s="32">
+      <x:c r="H84" s="31">
         <x:v>46122.6819179514</x:v>
       </x:c>
-      <x:c r="I84" s="32">
+      <x:c r="I84" s="31">
         <x:v>46122.6826717361</x:v>
       </x:c>
-      <x:c r="J84" s="31" t="s">
+      <x:c r="J84" s="30" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="K84" s="33" t="n">
+      <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L84" s="34">
+      <x:c r="L84" s="33">
         <x:v>46122.6831438079</x:v>
       </x:c>
-      <x:c r="M84" s="30" t="s">
+      <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B85" s="30" t="s">
+      <x:c r="B85" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C85" s="30" t="s">
+      <x:c r="C85" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D85" s="31" t="s">
+      <x:c r="D85" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E85" s="30" t="s">
+      <x:c r="E85" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F85" s="30" t="s">
+      <x:c r="F85" s="29" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="G85" s="30" t="s">
+      <x:c r="G85" s="29" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="H85" s="32">
+      <x:c r="H85" s="31">
         <x:v>46122.7261372338</x:v>
       </x:c>
-      <x:c r="I85" s="32">
+      <x:c r="I85" s="31">
         <x:v>46122.727234375</x:v>
       </x:c>
-      <x:c r="J85" s="31" t="s">
+      <x:c r="J85" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K85" s="33" t="n">
+      <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L85" s="34">
+      <x:c r="L85" s="33">
         <x:v>46122.7277720023</x:v>
       </x:c>
-      <x:c r="M85" s="30" t="s">
+      <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B86" s="30" t="s">
+      <x:c r="B86" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C86" s="30" t="s">
+      <x:c r="C86" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D86" s="31" t="s">
+      <x:c r="D86" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E86" s="30" t="s">
+      <x:c r="E86" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F86" s="30" t="s">
+      <x:c r="F86" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G86" s="30" t="s">
+      <x:c r="G86" s="29" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="H86" s="32">
+      <x:c r="H86" s="31">
         <x:v>46122.9452935995</x:v>
       </x:c>
-      <x:c r="I86" s="32">
+      <x:c r="I86" s="31">
         <x:v>46123.0460683681</x:v>
       </x:c>
-      <x:c r="J86" s="31" t="s">
+      <x:c r="J86" s="30" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="K86" s="33" t="n">
+      <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L86" s="34">
+      <x:c r="L86" s="33">
         <x:v>46123.0466478819</x:v>
       </x:c>
-      <x:c r="M86" s="30" t="s">
+      <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B87" s="30" t="s">
+      <x:c r="B87" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C87" s="30" t="s">
+      <x:c r="C87" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D87" s="31" t="s">
+      <x:c r="D87" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E87" s="30" t="s">
+      <x:c r="E87" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F87" s="30" t="s">
+      <x:c r="F87" s="29" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="G87" s="30" t="s">
+      <x:c r="G87" s="29" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H87" s="32">
+      <x:c r="H87" s="31">
         <x:v>46123.0476912847</x:v>
       </x:c>
-      <x:c r="I87" s="32">
+      <x:c r="I87" s="31">
         <x:v>46123.0484775694</x:v>
       </x:c>
-      <x:c r="J87" s="31" t="s">
+      <x:c r="J87" s="30" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="K87" s="33" t="n">
+      <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L87" s="34">
+      <x:c r="L87" s="33">
         <x:v>46123.049084375</x:v>
       </x:c>
-      <x:c r="M87" s="30" t="s">
+      <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B88" s="30" t="s">
+      <x:c r="B88" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C88" s="30" t="s">
+      <x:c r="C88" s="29" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D88" s="31" t="s">
+      <x:c r="D88" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E88" s="30" t="s">
+      <x:c r="E88" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F88" s="30" t="s">
+      <x:c r="F88" s="29" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="G88" s="30" t="s">
+      <x:c r="G88" s="29" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="H88" s="32">
+      <x:c r="H88" s="31">
         <x:v>46122.6795081481</x:v>
       </x:c>
-      <x:c r="I88" s="32">
+      <x:c r="I88" s="31">
         <x:v>46122.6802186921</x:v>
       </x:c>
-      <x:c r="J88" s="31" t="s">
+      <x:c r="J88" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K88" s="33" t="n">
+      <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L88" s="34">
+      <x:c r="L88" s="33">
         <x:v>46122.6809879398</x:v>
       </x:c>
-      <x:c r="M88" s="30" t="s">
+      <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B89" s="30" t="s">
+      <x:c r="B89" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C89" s="30" t="s">
+      <x:c r="C89" s="29" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="D89" s="31" t="s">
+      <x:c r="D89" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E89" s="30" t="s">
+      <x:c r="E89" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F89" s="30" t="s">
+      <x:c r="F89" s="29" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="G89" s="30" t="s">
+      <x:c r="G89" s="29" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="H89" s="32">
+      <x:c r="H89" s="31">
         <x:v>46118.5788871875</x:v>
       </x:c>
-      <x:c r="I89" s="32">
+      <x:c r="I89" s="31">
         <x:v>46118.5789284722</x:v>
       </x:c>
-      <x:c r="J89" s="31" t="s">
+      <x:c r="J89" s="30" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="K89" s="33" t="n">
+      <x:c r="K89" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L89" s="34">
+      <x:c r="L89" s="33">
         <x:v>46118.5806122685</x:v>
       </x:c>
-      <x:c r="M89" s="30" t="s">
+      <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B90" s="30" t="s">
+      <x:c r="B90" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C90" s="30" t="s">
+      <x:c r="C90" s="29" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="D90" s="31" t="s">
+      <x:c r="D90" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E90" s="30" t="s">
+      <x:c r="E90" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F90" s="30" t="s">
+      <x:c r="F90" s="29" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="G90" s="30" t="s">
+      <x:c r="G90" s="29" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="H90" s="32">
+      <x:c r="H90" s="31">
         <x:v>46118.6064654514</x:v>
       </x:c>
-      <x:c r="I90" s="32">
+      <x:c r="I90" s="31">
         <x:v>46118.6065117477</x:v>
       </x:c>
-      <x:c r="J90" s="31" t="s">
+      <x:c r="J90" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K90" s="33" t="n">
+      <x:c r="K90" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L90" s="34">
+      <x:c r="L90" s="33">
         <x:v>46118.6077792245</x:v>
       </x:c>
-      <x:c r="M90" s="30" t="s">
+      <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B91" s="30" t="s">
+      <x:c r="B91" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C91" s="30" t="s">
+      <x:c r="C91" s="29" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="D91" s="31" t="s">
+      <x:c r="D91" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E91" s="30" t="s">
+      <x:c r="E91" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F91" s="30" t="s">
+      <x:c r="F91" s="29" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="G91" s="30" t="s">
+      <x:c r="G91" s="29" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="H91" s="32">
+      <x:c r="H91" s="31">
         <x:v>46118.7029973032</x:v>
       </x:c>
-      <x:c r="I91" s="32">
+      <x:c r="I91" s="31">
         <x:v>46118.7030397569</x:v>
       </x:c>
-      <x:c r="J91" s="31" t="s">
+      <x:c r="J91" s="30" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="K91" s="33" t="n">
+      <x:c r="K91" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L91" s="34">
+      <x:c r="L91" s="33">
         <x:v>46118.7054991898</x:v>
       </x:c>
-      <x:c r="M91" s="30" t="s">
+      <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B92" s="30" t="s">
+      <x:c r="B92" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C92" s="30" t="s">
+      <x:c r="C92" s="29" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D92" s="31" t="s">
+      <x:c r="D92" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E92" s="30" t="s">
+      <x:c r="E92" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F92" s="30" t="s">
+      <x:c r="F92" s="29" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="G92" s="30" t="s">
+      <x:c r="G92" s="29" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="H92" s="32">
+      <x:c r="H92" s="31">
         <x:v>46118.7372774306</x:v>
       </x:c>
-      <x:c r="I92" s="32">
+      <x:c r="I92" s="31">
         <x:v>46118.7373236806</x:v>
       </x:c>
-      <x:c r="J92" s="31" t="s">
+      <x:c r="J92" s="30" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="K92" s="33" t="n">
+      <x:c r="K92" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L92" s="34">
+      <x:c r="L92" s="33">
         <x:v>46118.7388858565</x:v>
       </x:c>
-      <x:c r="M92" s="30" t="s">
+      <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B93" s="30" t="s">
+      <x:c r="B93" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C93" s="30" t="s">
+      <x:c r="C93" s="29" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="D93" s="31" t="s">
+      <x:c r="D93" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E93" s="30" t="s">
+      <x:c r="E93" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F93" s="30" t="s">
+      <x:c r="F93" s="29" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="G93" s="30" t="s">
+      <x:c r="G93" s="29" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="H93" s="32">
+      <x:c r="H93" s="31">
         <x:v>46118.6471475926</x:v>
       </x:c>
-      <x:c r="I93" s="32">
+      <x:c r="I93" s="31">
         <x:v>46118.647188044</x:v>
       </x:c>
-      <x:c r="J93" s="31" t="s">
+      <x:c r="J93" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K93" s="33" t="n">
+      <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L93" s="34">
+      <x:c r="L93" s="33">
         <x:v>46118.6489296181</x:v>
       </x:c>
-      <x:c r="M93" s="30" t="s">
+      <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B94" s="30" t="s">
+      <x:c r="B94" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C94" s="30" t="s">
+      <x:c r="C94" s="29" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="D94" s="31" t="s">
+      <x:c r="D94" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E94" s="30" t="s">
+      <x:c r="E94" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F94" s="30" t="s">
+      <x:c r="F94" s="29" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G94" s="30" t="s">
+      <x:c r="G94" s="29" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="H94" s="32">
+      <x:c r="H94" s="31">
         <x:v>46118.7761679514</x:v>
       </x:c>
-      <x:c r="I94" s="32">
+      <x:c r="I94" s="31">
         <x:v>46118.7762103819</x:v>
       </x:c>
-      <x:c r="J94" s="31" t="s">
+      <x:c r="J94" s="30" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K94" s="33" t="n">
+      <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L94" s="34">
+      <x:c r="L94" s="33">
         <x:v>46118.7774822107</x:v>
       </x:c>
-      <x:c r="M94" s="30" t="s">
+      <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B95" s="30" t="s">
+      <x:c r="B95" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C95" s="30" t="s">
+      <x:c r="C95" s="29" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="D95" s="31" t="s">
+      <x:c r="D95" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E95" s="30" t="s">
+      <x:c r="E95" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F95" s="30" t="s">
+      <x:c r="F95" s="29" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G95" s="30" t="s">
+      <x:c r="G95" s="29" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H95" s="32">
+      <x:c r="H95" s="31">
         <x:v>46118.439490081</x:v>
       </x:c>
-      <x:c r="I95" s="32">
+      <x:c r="I95" s="31">
         <x:v>46118.4395309375</x:v>
       </x:c>
-      <x:c r="J95" s="31" t="s">
+      <x:c r="J95" s="30" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="K95" s="33" t="n">
+      <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L95" s="34">
+      <x:c r="L95" s="33">
         <x:v>46118.4416909375</x:v>
       </x:c>
-      <x:c r="M95" s="30" t="s">
+      <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B96" s="30" t="s">
+      <x:c r="B96" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C96" s="30" t="s">
+      <x:c r="C96" s="29" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="D96" s="31" t="s">
+      <x:c r="D96" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E96" s="30" t="s">
+      <x:c r="E96" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F96" s="30" t="s">
+      <x:c r="F96" s="29" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G96" s="30" t="s">
+      <x:c r="G96" s="29" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="H96" s="32">
+      <x:c r="H96" s="31">
         <x:v>46119.4833706713</x:v>
       </x:c>
-      <x:c r="I96" s="32">
+      <x:c r="I96" s="31">
         <x:v>46119.4833991435</x:v>
       </x:c>
-      <x:c r="J96" s="31" t="s">
+      <x:c r="J96" s="30" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K96" s="33" t="n">
+      <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L96" s="34">
+      <x:c r="L96" s="33">
         <x:v>46119.4846717477</x:v>
       </x:c>
-      <x:c r="M96" s="30" t="s">
+      <x:c r="M96" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B97" s="30" t="s">
+      <x:c r="B97" s="29" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="C97" s="30" t="s">
+      <x:c r="C97" s="29" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="D97" s="31" t="s"/>
-      <x:c r="E97" s="30" t="s">
+      <x:c r="D97" s="30" t="s"/>
+      <x:c r="E97" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F97" s="30" t="s">
+      <x:c r="F97" s="29" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="G97" s="30" t="s">
+      <x:c r="G97" s="29" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="H97" s="32">
+      <x:c r="H97" s="31">
         <x:v>46124.1588481829</x:v>
       </x:c>
-      <x:c r="I97" s="32">
+      <x:c r="I97" s="31">
         <x:v>46124.1588689236</x:v>
       </x:c>
-      <x:c r="J97" s="31" t="s">
+      <x:c r="J97" s="30" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="K97" s="33" t="n">
+      <x:c r="K97" s="32" t="n">
         <x:v>5070</x:v>
       </x:c>
-      <x:c r="L97" s="34">
+      <x:c r="L97" s="33">
         <x:v>46124.1622106481</x:v>
       </x:c>
-      <x:c r="M97" s="30" t="s">
+      <x:c r="M97" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B98" s="30" t="s">
+      <x:c r="B98" s="29" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="C98" s="30" t="s">
+      <x:c r="C98" s="29" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="D98" s="31" t="s">
+      <x:c r="D98" s="30" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E98" s="30" t="s">
+      <x:c r="E98" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F98" s="30" t="s">
+      <x:c r="F98" s="29" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G98" s="30" t="s">
+      <x:c r="G98" s="29" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="H98" s="32">
+      <x:c r="H98" s="31">
         <x:v>46124.1607868981</x:v>
       </x:c>
-      <x:c r="I98" s="32">
+      <x:c r="I98" s="31">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J98" s="31" t="s">
+      <x:c r="J98" s="30" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="K98" s="33" t="n">
+      <x:c r="K98" s="32" t="n">
         <x:v>3100</x:v>
       </x:c>
-      <x:c r="L98" s="34">
+      <x:c r="L98" s="33">
         <x:v>46124.1624131829</x:v>
       </x:c>
-      <x:c r="M98" s="30" t="s">
+      <x:c r="M98" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B101" s="18" t="s">
+      <x:c r="B101" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C101" s="19" t="s"/>
-      <x:c r="D101" s="19" t="s"/>
-      <x:c r="E101" s="20" t="s"/>
-      <x:c r="F101" s="20" t="s"/>
+      <x:c r="C101" s="18" t="s"/>
+      <x:c r="D101" s="18" t="s"/>
+      <x:c r="E101" s="19" t="s"/>
+      <x:c r="F101" s="19" t="s"/>
     </x:row>
     <x:row r="102" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B102" s="21" t="s">
+      <x:c r="B102" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C102" s="22" t="s"/>
-      <x:c r="D102" s="22" t="s"/>
-      <x:c r="E102" s="22" t="s"/>
-      <x:c r="F102" s="23" t="s">
+      <x:c r="C102" s="21" t="s"/>
+      <x:c r="D102" s="21" t="s"/>
+      <x:c r="E102" s="21" t="s"/>
+      <x:c r="F102" s="22" t="s">
         <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B103" s="24" t="s">
+      <x:c r="B103" s="23" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C103" s="25" t="s"/>
-      <x:c r="D103" s="25" t="s"/>
-      <x:c r="E103" s="25" t="s"/>
-      <x:c r="F103" s="26" t="n">
+      <x:c r="C103" s="24" t="s"/>
+      <x:c r="D103" s="24" t="s"/>
+      <x:c r="E103" s="24" t="s"/>
+      <x:c r="F103" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B104" s="24" t="s">
+      <x:c r="B104" s="23" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C104" s="25" t="s"/>
-      <x:c r="D104" s="25" t="s"/>
-      <x:c r="E104" s="25" t="s"/>
-      <x:c r="F104" s="26" t="n">
+      <x:c r="C104" s="24" t="s"/>
+      <x:c r="D104" s="24" t="s"/>
+      <x:c r="E104" s="24" t="s"/>
+      <x:c r="F104" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B105" s="24" t="s">
+      <x:c r="B105" s="23" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C105" s="25" t="s"/>
-      <x:c r="D105" s="25" t="s"/>
-      <x:c r="E105" s="25" t="s"/>
-      <x:c r="F105" s="26" t="n">
+      <x:c r="C105" s="24" t="s"/>
+      <x:c r="D105" s="24" t="s"/>
+      <x:c r="E105" s="24" t="s"/>
+      <x:c r="F105" s="25" t="n">
         <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B106" s="24" t="s">
+      <x:c r="B106" s="23" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="C106" s="25" t="s"/>
-      <x:c r="D106" s="25" t="s"/>
-      <x:c r="E106" s="25" t="s"/>
-      <x:c r="F106" s="26" t="n">
+      <x:c r="C106" s="24" t="s"/>
+      <x:c r="D106" s="24" t="s"/>
+      <x:c r="E106" s="24" t="s"/>
+      <x:c r="F106" s="25" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B107" s="24" t="s">
+      <x:c r="B107" s="23" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="C107" s="25" t="s"/>
-      <x:c r="D107" s="25" t="s"/>
-      <x:c r="E107" s="25" t="s"/>
-      <x:c r="F107" s="26" t="n">
+      <x:c r="C107" s="24" t="s"/>
+      <x:c r="D107" s="24" t="s"/>
+      <x:c r="E107" s="24" t="s"/>
+      <x:c r="F107" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B108" s="24" t="s">
+      <x:c r="B108" s="23" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="C108" s="25" t="s"/>
-      <x:c r="D108" s="25" t="s"/>
-      <x:c r="E108" s="25" t="s"/>
-      <x:c r="F108" s="26" t="n">
+      <x:c r="C108" s="24" t="s"/>
+      <x:c r="D108" s="24" t="s"/>
+      <x:c r="E108" s="24" t="s"/>
+      <x:c r="F108" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B109" s="27" t="s">
+      <x:c r="B109" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C109" s="28" t="s"/>
-      <x:c r="D109" s="28" t="s"/>
-      <x:c r="E109" s="28" t="s"/>
-      <x:c r="F109" s="29" t="n">
+      <x:c r="C109" s="27" t="s"/>
+      <x:c r="D109" s="27" t="s"/>
+      <x:c r="E109" s="27" t="s"/>
+      <x:c r="F109" s="28" t="n">
         <x:v>91</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -189,6 +189,15 @@
     <x:t>zxcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1316-566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>szdasdqweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08340</x:t>
   </x:si>
   <x:si>
@@ -234,6 +243,15 @@
     <x:t>123wesdasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08292</x:t>
   </x:si>
   <x:si>
@@ -252,22 +270,34 @@
     <x:t>asd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1316-566</x:t>
-  </x:si>
-  <x:si>
-    <x:t>szdasdqweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08134</x:t>
@@ -279,42 +309,60 @@
     <x:t>resdxcv</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08148</x:t>
   </x:si>
   <x:si>
@@ -324,6 +372,12 @@
     <x:t>df</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
   </x:si>
   <x:si>
@@ -333,58 +387,148 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -393,150 +537,6 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
   </x:si>
   <x:si>
@@ -552,43 +552,124 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08369</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1334-994</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08212</x:t>
@@ -597,72 +678,48 @@
     <x:t>61-4-2026-1312-712</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08188</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1299-939</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08187</x:t>
   </x:si>
   <x:si>
@@ -672,13 +729,64 @@
     <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
@@ -690,93 +798,6 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08180</x:t>
   </x:si>
   <x:si>
@@ -792,21 +813,6 @@
     <x:t>tesg213</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -886,6 +892,15 @@
   </x:si>
   <x:si>
     <x:t>61-4-2026-1239-459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1343-633</x:t>
+  </x:si>
+  <x:si>
+    <x:t>czxc</x:t>
   </x:si>
   <x:si>
     <x:t>Permit to PURCHASE/POSSESS</x:t>
@@ -5863,19 +5878,19 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46124.9835281713</x:v>
       </x:c>
       <x:c r="I11" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46125.0608962963</x:v>
       </x:c>
       <x:c r="J11" s="30" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="K11" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L11" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.1641622569</x:v>
       </x:c>
       <x:c r="M11" s="29" t="s">
         <x:v>21</x:v>
@@ -5901,10 +5916,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>59</x:v>
@@ -5913,7 +5928,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
@@ -5939,10 +5954,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>62</x:v>
@@ -5951,7 +5966,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
@@ -5977,10 +5992,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>65</x:v>
@@ -5989,7 +6004,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
@@ -6015,10 +6030,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>68</x:v>
@@ -6027,7 +6042,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
@@ -6053,10 +6068,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>71</x:v>
@@ -6065,7 +6080,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -6091,10 +6106,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>74</x:v>
@@ -6103,7 +6118,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -6129,19 +6144,19 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46124.9835281713</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46125.0608962963</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
-        <x:v>240</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.1641622569</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -6167,10 +6182,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
         <x:v>80</x:v>
@@ -6179,7 +6194,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -6205,19 +6220,19 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -6243,19 +6258,19 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -6281,10 +6296,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
         <x:v>88</x:v>
@@ -6293,7 +6308,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -6319,19 +6334,19 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -6351,25 +6366,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G24" s="29" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G24" s="29" t="s">
+      <x:c r="H24" s="31">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I24" s="31">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J24" s="30" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="H24" s="31">
-        <x:v>46120.7129542245</x:v>
-      </x:c>
-      <x:c r="I24" s="31">
-        <x:v>46121.100944213</x:v>
-      </x:c>
-      <x:c r="J24" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -6395,19 +6410,19 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -6433,10 +6448,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
         <x:v>98</x:v>
@@ -6445,7 +6460,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -6471,10 +6486,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>101</x:v>
@@ -6483,7 +6498,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -6509,10 +6524,10 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
         <x:v>104</x:v>
@@ -6521,7 +6536,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -6547,10 +6562,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>107</x:v>
@@ -6559,7 +6574,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -6585,19 +6600,19 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -6617,16 +6632,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="H31" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>53</x:v>
@@ -6635,7 +6650,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -6655,25 +6670,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="G32" s="29" t="s">
+      <x:c r="H32" s="31">
+        <x:v>46121.5183984954</x:v>
+      </x:c>
+      <x:c r="I32" s="31">
+        <x:v>46122.2061737153</x:v>
+      </x:c>
+      <x:c r="J32" s="30" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="H32" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I32" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J32" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -6699,19 +6714,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>117</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -6731,25 +6746,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G34" s="29" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="G34" s="29" t="s">
+      <x:c r="H34" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I34" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="H34" s="31">
-        <x:v>46121.2273626852</x:v>
-      </x:c>
-      <x:c r="I34" s="31">
-        <x:v>46121.228379213</x:v>
-      </x:c>
-      <x:c r="J34" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -6775,19 +6790,19 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -6813,10 +6828,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
         <x:v>124</x:v>
@@ -6825,7 +6840,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -6851,19 +6866,19 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -6883,10 +6898,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G38" s="29" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="G38" s="29" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="H38" s="31">
         <x:v>46118.4219285995</x:v>
@@ -6895,7 +6910,7 @@
         <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
@@ -6921,10 +6936,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G39" s="29" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="G39" s="29" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="H39" s="31">
         <x:v>46118.7424944097</x:v>
@@ -6933,7 +6948,7 @@
         <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
@@ -6959,10 +6974,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="G40" s="29" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="H40" s="31">
         <x:v>46118.7562945255</x:v>
@@ -6971,7 +6986,7 @@
         <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>136</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
@@ -6997,10 +7012,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="G41" s="29" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="H41" s="31">
         <x:v>46119.0668949653</x:v>
@@ -7009,7 +7024,7 @@
         <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>139</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
@@ -7035,10 +7050,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="G42" s="29" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="H42" s="31">
         <x:v>46119.0739296412</x:v>
@@ -7047,7 +7062,7 @@
         <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>142</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
@@ -7073,10 +7088,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="G43" s="29" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="H43" s="31">
         <x:v>46119.1921340856</x:v>
@@ -7085,7 +7100,7 @@
         <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>145</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
@@ -7111,25 +7126,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
-        <x:v>147</x:v>
-      </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -7149,25 +7164,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
+      <x:c r="H45" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -7269,19 +7284,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>91</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -7301,25 +7316,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G49" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>160</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -7351,7 +7366,7 @@
         <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
@@ -7421,10 +7436,10 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
         <x:v>167</x:v>
@@ -7433,7 +7448,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -7459,19 +7474,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -7573,19 +7588,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -7611,19 +7626,19 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -7649,10 +7664,10 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
         <x:v>181</x:v>
@@ -7661,7 +7676,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -7687,10 +7702,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
         <x:v>184</x:v>
@@ -7699,7 +7714,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -7725,10 +7740,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>187</x:v>
@@ -7737,7 +7752,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -7763,19 +7778,19 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -7795,25 +7810,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -7833,25 +7848,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G63" s="29" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -7871,25 +7886,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="G64" s="29" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -7909,25 +7924,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G65" s="29" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -7947,25 +7962,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="G66" s="29" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -7985,25 +8000,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G67" s="29" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -8023,25 +8038,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G68" s="29" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
-        <x:v>209</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -8061,25 +8076,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="G69" s="29" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -8099,25 +8114,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="G70" s="29" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -8143,19 +8158,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>217</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -8175,25 +8190,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G72" s="29" t="s">
-        <x:v>219</x:v>
-      </x:c>
       <x:c r="H72" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>220</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -8213,25 +8228,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -8251,25 +8266,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G74" s="29" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H74" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I74" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J74" s="30" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="G74" s="29" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H74" s="31">
-        <x:v>46122.3885020718</x:v>
-      </x:c>
-      <x:c r="I74" s="31">
-        <x:v>46122.3892655903</x:v>
-      </x:c>
-      <x:c r="J74" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -8289,25 +8304,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="G75" s="29" t="s">
-        <x:v>226</x:v>
-      </x:c>
       <x:c r="H75" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -8327,25 +8342,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G76" s="29" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G76" s="29" t="s">
-        <x:v>228</x:v>
-      </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>229</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -8365,25 +8380,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G77" s="29" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H77" s="31">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I77" s="31">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J77" s="30" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="G77" s="29" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H77" s="31">
-        <x:v>46123.4191184375</x:v>
-      </x:c>
-      <x:c r="I77" s="31">
-        <x:v>46123.4205974074</x:v>
-      </x:c>
-      <x:c r="J77" s="30" t="s">
-        <x:v>232</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -8403,25 +8418,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="H78" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="G78" s="29" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46122.5911383796</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46122.5921380556</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -8441,25 +8456,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="H79" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="G79" s="29" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -8479,25 +8494,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
-        <x:v>239</x:v>
-      </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -8517,25 +8532,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>241</x:v>
-      </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -8555,25 +8570,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>243</x:v>
-      </x:c>
       <x:c r="H82" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -8593,25 +8608,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="G83" s="29" t="s">
+      <x:c r="H83" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I83" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J83" s="30" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="H83" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I83" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J83" s="30" t="s">
-        <x:v>246</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -8631,25 +8646,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>248</x:v>
-      </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>249</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -8669,25 +8684,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H85" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="G85" s="29" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -8707,25 +8722,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G86" s="29" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="G86" s="29" t="s">
+      <x:c r="H86" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I86" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J86" s="30" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="H86" s="31">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I86" s="31">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J86" s="30" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -8745,25 +8760,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="G87" s="29" t="s">
+      <x:c r="H87" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I87" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="H87" s="31">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I87" s="31">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J87" s="30" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -8783,16 +8798,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="G88" s="29" t="s">
-        <x:v>259</x:v>
-      </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
         <x:v>30</x:v>
@@ -8801,7 +8816,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -8809,10 +8824,10 @@
     </x:row>
     <x:row r="89" spans="1:28" ht="30" customHeight="1">
       <x:c r="B89" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C89" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D89" s="30" t="s">
         <x:v>16</x:v>
@@ -8821,25 +8836,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -8847,10 +8862,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C90" s="29" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D90" s="30" t="s">
         <x:v>16</x:v>
@@ -8859,25 +8874,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H90" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="G90" s="29" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="H90" s="31">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I90" s="31">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J90" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -8885,10 +8900,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>16</x:v>
@@ -8897,25 +8912,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="G91" s="29" t="s">
-        <x:v>270</x:v>
-      </x:c>
       <x:c r="H91" s="31">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>271</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -8923,10 +8938,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>16</x:v>
@@ -8935,25 +8950,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G92" s="29" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H92" s="31">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I92" s="31">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J92" s="30" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="G92" s="29" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H92" s="31">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I92" s="31">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J92" s="30" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -8961,10 +8976,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>16</x:v>
@@ -8973,25 +8988,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>277</x:v>
-      </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
@@ -8999,10 +9014,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>16</x:v>
@@ -9011,25 +9026,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="G94" s="29" t="s">
-        <x:v>281</x:v>
-      </x:c>
       <x:c r="H94" s="31">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I94" s="31">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J94" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
@@ -9037,10 +9052,10 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>16</x:v>
@@ -9055,19 +9070,19 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>284</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
@@ -9075,10 +9090,10 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>16</x:v>
@@ -9087,25 +9102,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
+      <x:c r="H96" s="31">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>21</x:v>
@@ -9113,35 +9128,37 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>287</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D97" s="30" t="s"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D97" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E97" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
-        <x:v>289</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="G97" s="29" t="s">
-        <x:v>290</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="H97" s="31">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>291</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>21</x:v>
@@ -9149,10 +9166,10 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>292</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>293</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>41</x:v>
@@ -9161,132 +9178,214 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
-        <x:v>294</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G98" s="29" t="s">
-        <x:v>295</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H98" s="31">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46132.3879904745</x:v>
       </x:c>
       <x:c r="I98" s="31">
         <x:v>46023</x:v>
       </x:c>
       <x:c r="J98" s="30" t="s">
-        <x:v>296</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="101" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B101" s="17" t="s">
+    <x:row r="99" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B99" s="29" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C99" s="29" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="D99" s="30" t="s"/>
+      <x:c r="E99" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F99" s="29" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G99" s="29" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H99" s="31">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I99" s="31">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J99" s="30" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="K99" s="32" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L99" s="33">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M99" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B100" s="29" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C100" s="29" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E100" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F100" s="29" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G100" s="29" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="H100" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I100" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J100" s="30" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="K100" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L100" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M100" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B103" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C101" s="18" t="s"/>
-      <x:c r="D101" s="18" t="s"/>
-      <x:c r="E101" s="19" t="s"/>
-      <x:c r="F101" s="19" t="s"/>
-    </x:row>
-    <x:row r="102" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B102" s="20" t="s">
+      <x:c r="C103" s="18" t="s"/>
+      <x:c r="D103" s="18" t="s"/>
+      <x:c r="E103" s="19" t="s"/>
+      <x:c r="F103" s="19" t="s"/>
+    </x:row>
+    <x:row r="104" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B104" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C102" s="21" t="s"/>
-      <x:c r="D102" s="21" t="s"/>
-      <x:c r="E102" s="21" t="s"/>
-      <x:c r="F102" s="22" t="s">
+      <x:c r="C104" s="21" t="s"/>
+      <x:c r="D104" s="21" t="s"/>
+      <x:c r="E104" s="21" t="s"/>
+      <x:c r="F104" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B103" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C103" s="24" t="s"/>
-      <x:c r="D103" s="24" t="s"/>
-      <x:c r="E103" s="24" t="s"/>
-      <x:c r="F103" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B104" s="23" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C104" s="24" t="s"/>
-      <x:c r="D104" s="24" t="s"/>
-      <x:c r="E104" s="24" t="s"/>
-      <x:c r="F104" s="25" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:28" ht="18" customHeight="1">
       <x:c r="B105" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C105" s="24" t="s"/>
       <x:c r="D105" s="24" t="s"/>
       <x:c r="E105" s="24" t="s"/>
       <x:c r="F105" s="25" t="n">
-        <x:v>78</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="23" t="s">
-        <x:v>260</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C106" s="24" t="s"/>
       <x:c r="D106" s="24" t="s"/>
       <x:c r="E106" s="24" t="s"/>
       <x:c r="F106" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="23" t="s">
-        <x:v>287</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s"/>
       <x:c r="D107" s="24" t="s"/>
       <x:c r="E107" s="24" t="s"/>
       <x:c r="F107" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="23" t="s">
-        <x:v>292</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s"/>
       <x:c r="D108" s="24" t="s"/>
       <x:c r="E108" s="24" t="s"/>
       <x:c r="F108" s="25" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B109" s="23" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C109" s="24" t="s"/>
+      <x:c r="D109" s="24" t="s"/>
+      <x:c r="E109" s="24" t="s"/>
+      <x:c r="F109" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B109" s="26" t="s">
+    <x:row r="110" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B110" s="23" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C110" s="24" t="s"/>
+      <x:c r="D110" s="24" t="s"/>
+      <x:c r="E110" s="24" t="s"/>
+      <x:c r="F110" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B111" s="23" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C111" s="24" t="s"/>
+      <x:c r="D111" s="24" t="s"/>
+      <x:c r="E111" s="24" t="s"/>
+      <x:c r="F111" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B112" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C109" s="27" t="s"/>
-      <x:c r="D109" s="27" t="s"/>
-      <x:c r="E109" s="27" t="s"/>
-      <x:c r="F109" s="28" t="n">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C112" s="27" t="s"/>
+      <x:c r="D112" s="27" t="s"/>
+      <x:c r="E112" s="27" t="s"/>
+      <x:c r="F112" s="28" t="n">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
     <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10169,20 +10268,21 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="13">
+  <x:mergeCells count="14">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B101:F101"/>
-    <x:mergeCell ref="B102:E102"/>
-    <x:mergeCell ref="B103:E103"/>
+    <x:mergeCell ref="B103:F103"/>
     <x:mergeCell ref="B104:E104"/>
     <x:mergeCell ref="B105:E105"/>
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
     <x:mergeCell ref="B109:E109"/>
+    <x:mergeCell ref="B110:E110"/>
+    <x:mergeCell ref="B111:E111"/>
+    <x:mergeCell ref="B112:E112"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -198,6 +198,60 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08292</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1322-790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1323-538</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1324-430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wesdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1325-890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdxzcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08340</x:t>
   </x:si>
   <x:si>
@@ -207,15 +261,6 @@
     <x:t>aszxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08338</x:t>
   </x:si>
   <x:si>
@@ -225,51 +270,6 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1325-890</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdxzcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08335</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1324-430</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wesdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08296</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1323-538</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08292</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1322-790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
@@ -315,6 +315,30 @@
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
   </x:si>
   <x:si>
@@ -324,6 +348,36 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08145</x:t>
   </x:si>
   <x:si>
@@ -333,60 +387,6 @@
     <x:t>sdf</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08101</x:t>
   </x:si>
   <x:si>
@@ -543,6 +543,45 @@
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
   </x:si>
   <x:si>
@@ -552,45 +591,6 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08209</x:t>
   </x:si>
   <x:si>
@@ -765,54 +765,54 @@
     <x:t>zsdasdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08178</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -870,22 +870,31 @@
     <x:t>61-4-2026-1228-788</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08621-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1342-777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08034-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1223-617</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123431</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08045-26</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1233-011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08034-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1223-617</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123431</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5916,10 +5925,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>59</x:v>
@@ -5928,7 +5937,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
@@ -5954,10 +5963,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>62</x:v>
@@ -5966,7 +5975,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
@@ -5992,10 +6001,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>65</x:v>
@@ -6004,7 +6013,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
@@ -6068,10 +6077,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>71</x:v>
@@ -6080,7 +6089,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -6106,10 +6115,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
         <x:v>74</x:v>
@@ -6118,7 +6127,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -6144,10 +6153,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
         <x:v>77</x:v>
@@ -6156,7 +6165,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -6182,10 +6191,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
         <x:v>80</x:v>
@@ -6194,7 +6203,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -6448,19 +6457,19 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -6480,25 +6489,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G27" s="29" t="s">
+      <x:c r="H27" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46121.4966047917</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46121.4974146412</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -6518,10 +6527,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="G28" s="29" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="H28" s="31">
         <x:v>46121.5149441551</x:v>
@@ -6530,7 +6539,7 @@
         <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
@@ -6556,25 +6565,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="G29" s="29" t="s">
+      <x:c r="H29" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I29" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J29" s="30" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="H29" s="31">
-        <x:v>46121.5178724884</x:v>
-      </x:c>
-      <x:c r="I29" s="31">
-        <x:v>46122.2064690394</x:v>
-      </x:c>
-      <x:c r="J29" s="30" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -6594,25 +6603,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G30" s="29" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="H30" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -6632,10 +6641,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="G31" s="29" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="H31" s="31">
         <x:v>46119.8029380671</x:v>
@@ -6670,10 +6679,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="G32" s="29" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="31">
         <x:v>46121.5183984954</x:v>
@@ -6682,7 +6691,7 @@
         <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
@@ -6708,25 +6717,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="G33" s="29" t="s">
+      <x:c r="H33" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I33" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J33" s="30" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="H33" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I33" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J33" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -6752,10 +6761,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
         <x:v>119</x:v>
@@ -6764,7 +6773,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -7366,7 +7375,7 @@
         <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
@@ -7480,7 +7489,7 @@
         <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
@@ -7550,19 +7559,19 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -7582,25 +7591,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="G56" s="29" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="G56" s="29" t="s">
+      <x:c r="H56" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I56" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J56" s="30" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="H56" s="31">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I56" s="31">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J56" s="30" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -7740,10 +7749,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
         <x:v>187</x:v>
@@ -7752,7 +7761,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -8652,10 +8661,10 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
         <x:v>30</x:v>
@@ -8664,7 +8673,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -8690,10 +8699,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
         <x:v>250</x:v>
@@ -8702,7 +8711,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -8766,10 +8775,10 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
         <x:v>256</x:v>
@@ -8778,7 +8787,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -8804,19 +8813,19 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -8836,25 +8845,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>261</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -9055,34 +9064,34 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E95" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G95" s="29" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G95" s="29" t="s">
+      <x:c r="H95" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I95" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J95" s="30" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="H95" s="31">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I95" s="31">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J95" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="K95" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
@@ -9093,7 +9102,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>16</x:v>
@@ -9102,10 +9111,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="G96" s="29" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="H96" s="31">
         <x:v>46118.439490081</x:v>
@@ -9114,7 +9123,7 @@
         <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J96" s="30" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
@@ -9131,7 +9140,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>16</x:v>
@@ -9140,25 +9149,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="G97" s="29" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="H97" s="31">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>21</x:v>
@@ -9166,37 +9175,37 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>289</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E98" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G98" s="29" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="H98" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I98" s="31">
-        <x:v>46023</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J98" s="30" t="s">
-        <x:v>291</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>21</x:v>
@@ -9207,32 +9216,34 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="D99" s="30" t="s"/>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="D99" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="E99" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G99" s="29" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H99" s="31">
+        <x:v>46132.3879904745</x:v>
+      </x:c>
+      <x:c r="I99" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J99" s="30" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G99" s="29" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H99" s="31">
-        <x:v>46124.1588481829</x:v>
-      </x:c>
-      <x:c r="I99" s="31">
-        <x:v>46124.1588689236</x:v>
-      </x:c>
-      <x:c r="J99" s="30" t="s">
-        <x:v>296</x:v>
-      </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>21</x:v>
@@ -9240,117 +9251,142 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="D100" s="30" t="s">
-        <x:v>41</x:v>
-      </x:c>
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="s"/>
       <x:c r="E100" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="G100" s="29" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="H100" s="31">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I100" s="31">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J100" s="30" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="G100" s="29" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="H100" s="31">
-        <x:v>46124.1607868981</x:v>
-      </x:c>
-      <x:c r="I100" s="31">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="J100" s="30" t="s">
-        <x:v>301</x:v>
-      </x:c>
       <x:c r="K100" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B101" s="29" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C101" s="29" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="D101" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E101" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F101" s="29" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G101" s="29" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H101" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I101" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J101" s="30" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="K101" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L101" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M101" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="103" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B103" s="17" t="s">
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B104" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C103" s="18" t="s"/>
-      <x:c r="D103" s="18" t="s"/>
-      <x:c r="E103" s="19" t="s"/>
-      <x:c r="F103" s="19" t="s"/>
-    </x:row>
-    <x:row r="104" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B104" s="20" t="s">
+      <x:c r="C104" s="18" t="s"/>
+      <x:c r="D104" s="18" t="s"/>
+      <x:c r="E104" s="19" t="s"/>
+      <x:c r="F104" s="19" t="s"/>
+    </x:row>
+    <x:row r="105" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B105" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C104" s="21" t="s"/>
-      <x:c r="D104" s="21" t="s"/>
-      <x:c r="E104" s="21" t="s"/>
-      <x:c r="F104" s="22" t="s">
+      <x:c r="C105" s="21" t="s"/>
+      <x:c r="D105" s="21" t="s"/>
+      <x:c r="E105" s="21" t="s"/>
+      <x:c r="F105" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B105" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C105" s="24" t="s"/>
-      <x:c r="D105" s="24" t="s"/>
-      <x:c r="E105" s="24" t="s"/>
-      <x:c r="F105" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:28" ht="18" customHeight="1">
       <x:c r="B106" s="23" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C106" s="24" t="s"/>
       <x:c r="D106" s="24" t="s"/>
       <x:c r="E106" s="24" t="s"/>
       <x:c r="F106" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s"/>
       <x:c r="D107" s="24" t="s"/>
       <x:c r="E107" s="24" t="s"/>
       <x:c r="F107" s="25" t="n">
-        <x:v>79</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="23" t="s">
-        <x:v>262</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s"/>
       <x:c r="D108" s="24" t="s"/>
       <x:c r="E108" s="24" t="s"/>
       <x:c r="F108" s="25" t="n">
-        <x:v>8</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
       <x:c r="B109" s="23" t="s">
-        <x:v>289</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C109" s="24" t="s"/>
       <x:c r="D109" s="24" t="s"/>
       <x:c r="E109" s="24" t="s"/>
       <x:c r="F109" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
@@ -9366,7 +9402,7 @@
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>297</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
@@ -9375,18 +9411,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B112" s="26" t="s">
+    <x:row r="112" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B112" s="23" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C112" s="24" t="s"/>
+      <x:c r="D112" s="24" t="s"/>
+      <x:c r="E112" s="24" t="s"/>
+      <x:c r="F112" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B113" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C112" s="27" t="s"/>
-      <x:c r="D112" s="27" t="s"/>
-      <x:c r="E112" s="27" t="s"/>
-      <x:c r="F112" s="28" t="n">
-        <x:v>93</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C113" s="27" t="s"/>
+      <x:c r="D113" s="27" t="s"/>
+      <x:c r="E113" s="27" t="s"/>
+      <x:c r="F113" s="28" t="n">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
     <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10273,8 +10319,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B103:F103"/>
-    <x:mergeCell ref="B104:E104"/>
+    <x:mergeCell ref="B104:F104"/>
     <x:mergeCell ref="B105:E105"/>
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
@@ -10283,6 +10328,7 @@
     <x:mergeCell ref="B110:E110"/>
     <x:mergeCell ref="B111:E111"/>
     <x:mergeCell ref="B112:E112"/>
+    <x:mergeCell ref="B113:E113"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -198,6 +198,15 @@
     <x:t>szdasdqweq</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1321-473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08292</x:t>
   </x:si>
   <x:si>
@@ -234,13 +243,10 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08281</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1321-473</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asd</x:t>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08339</x:t>
@@ -270,6 +276,12 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
   </x:si>
   <x:si>
@@ -315,28 +327,223 @@
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08153</x:t>
@@ -348,199 +555,139 @@
     <x:t>zxcasdadasdxasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08168</x:t>
@@ -549,147 +696,6 @@
     <x:t>61-4-2026-1282-165</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
   </x:si>
   <x:si>
@@ -765,6 +771,39 @@
     <x:t>zsdasdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08180</x:t>
   </x:si>
   <x:si>
@@ -780,39 +819,6 @@
     <x:t>tesg213</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
-  </x:si>
-  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -882,6 +888,12 @@
     <x:t>TEST</x:t>
   </x:si>
   <x:si>
+    <x:t>MPDP-ROXIV-08045-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1233-011</x:t>
+  </x:si>
+  <x:si>
     <x:t>MPDP-ROXIV-08034-26</x:t>
   </x:si>
   <x:si>
@@ -889,12 +901,6 @@
   </x:si>
   <x:si>
     <x:t>123431</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPDP-ROXIV-08045-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1233-011</x:t>
   </x:si>
   <x:si>
     <x:t>MPDP-ROXIV-08088-26</x:t>
@@ -5925,10 +5931,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="31">
-        <x:v>46126.1914900926</x:v>
+        <x:v>46126.1388059144</x:v>
       </x:c>
       <x:c r="I12" s="31">
-        <x:v>46126.2594011574</x:v>
+        <x:v>46126.1498425347</x:v>
       </x:c>
       <x:c r="J12" s="30" t="s">
         <x:v>59</x:v>
@@ -5937,7 +5943,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L12" s="33">
-        <x:v>46126.2601296875</x:v>
+        <x:v>46126.176386169</x:v>
       </x:c>
       <x:c r="M12" s="29" t="s">
         <x:v>21</x:v>
@@ -5963,10 +5969,10 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="31">
-        <x:v>46126.2608066551</x:v>
+        <x:v>46126.1914900926</x:v>
       </x:c>
       <x:c r="I13" s="31">
-        <x:v>46126.2618529282</x:v>
+        <x:v>46126.2594011574</x:v>
       </x:c>
       <x:c r="J13" s="30" t="s">
         <x:v>62</x:v>
@@ -5975,7 +5981,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L13" s="33">
-        <x:v>46126.2624254167</x:v>
+        <x:v>46126.2601296875</x:v>
       </x:c>
       <x:c r="M13" s="29" t="s">
         <x:v>21</x:v>
@@ -6001,10 +6007,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H14" s="31">
-        <x:v>46126.4381590509</x:v>
+        <x:v>46126.2608066551</x:v>
       </x:c>
       <x:c r="I14" s="31">
-        <x:v>46126.4434486343</x:v>
+        <x:v>46126.2618529282</x:v>
       </x:c>
       <x:c r="J14" s="30" t="s">
         <x:v>65</x:v>
@@ -6013,7 +6019,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L14" s="33">
-        <x:v>46126.444417662</x:v>
+        <x:v>46126.2624254167</x:v>
       </x:c>
       <x:c r="M14" s="29" t="s">
         <x:v>21</x:v>
@@ -6039,10 +6045,10 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="H15" s="31">
-        <x:v>46126.4485157523</x:v>
+        <x:v>46126.4381590509</x:v>
       </x:c>
       <x:c r="I15" s="31">
-        <x:v>46126.4527227431</x:v>
+        <x:v>46126.4434486343</x:v>
       </x:c>
       <x:c r="J15" s="30" t="s">
         <x:v>68</x:v>
@@ -6051,7 +6057,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L15" s="33">
-        <x:v>46126.4533495949</x:v>
+        <x:v>46126.444417662</x:v>
       </x:c>
       <x:c r="M15" s="29" t="s">
         <x:v>21</x:v>
@@ -6077,10 +6083,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="31">
-        <x:v>46126.1388059144</x:v>
+        <x:v>46126.4485157523</x:v>
       </x:c>
       <x:c r="I16" s="31">
-        <x:v>46126.1498425347</x:v>
+        <x:v>46126.4527227431</x:v>
       </x:c>
       <x:c r="J16" s="30" t="s">
         <x:v>71</x:v>
@@ -6089,7 +6095,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L16" s="33">
-        <x:v>46126.176386169</x:v>
+        <x:v>46126.4533495949</x:v>
       </x:c>
       <x:c r="M16" s="29" t="s">
         <x:v>21</x:v>
@@ -6115,19 +6121,19 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
-        <x:v>74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -6147,25 +6153,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G18" s="29" t="s">
+      <x:c r="H18" s="31">
+        <x:v>46126.4716621296</x:v>
+      </x:c>
+      <x:c r="I18" s="31">
+        <x:v>46126.4737503704</x:v>
+      </x:c>
+      <x:c r="J18" s="30" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="H18" s="31">
-        <x:v>46126.4798427199</x:v>
-      </x:c>
-      <x:c r="I18" s="31">
-        <x:v>46126.4809562153</x:v>
-      </x:c>
-      <x:c r="J18" s="30" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -6185,25 +6191,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G19" s="29" t="s">
+      <x:c r="H19" s="31">
+        <x:v>46126.4798427199</x:v>
+      </x:c>
+      <x:c r="I19" s="31">
+        <x:v>46126.4809562153</x:v>
+      </x:c>
+      <x:c r="J19" s="30" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="H19" s="31">
-        <x:v>46126.455832662</x:v>
-      </x:c>
-      <x:c r="I19" s="31">
-        <x:v>46126.4740829051</x:v>
-      </x:c>
-      <x:c r="J19" s="30" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -6214,34 +6220,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="s">
+      <x:c r="H20" s="31">
+        <x:v>46126.455832662</x:v>
+      </x:c>
+      <x:c r="I20" s="31">
+        <x:v>46126.4740829051</x:v>
+      </x:c>
+      <x:c r="J20" s="30" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H20" s="31">
-        <x:v>46120.2349196412</x:v>
-      </x:c>
-      <x:c r="I20" s="31">
-        <x:v>46120.5229746296</x:v>
-      </x:c>
-      <x:c r="J20" s="30" t="s">
-        <x:v>83</x:v>
-      </x:c>
       <x:c r="K20" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -6261,25 +6267,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G21" s="29" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G21" s="29" t="s">
-        <x:v>85</x:v>
-      </x:c>
       <x:c r="H21" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -6299,25 +6305,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G22" s="29" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G22" s="29" t="s">
+      <x:c r="H22" s="31">
+        <x:v>46120.2349196412</x:v>
+      </x:c>
+      <x:c r="I22" s="31">
+        <x:v>46120.5229746296</x:v>
+      </x:c>
+      <x:c r="J22" s="30" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="H22" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I22" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J22" s="30" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -6337,25 +6343,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G23" s="29" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G23" s="29" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -6375,25 +6381,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G24" s="29" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G24" s="29" t="s">
+      <x:c r="H24" s="31">
+        <x:v>46120.2374046412</x:v>
+      </x:c>
+      <x:c r="I24" s="31">
+        <x:v>46120.5224942245</x:v>
+      </x:c>
+      <x:c r="J24" s="30" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="H24" s="31">
-        <x:v>46121.0999663542</x:v>
-      </x:c>
-      <x:c r="I24" s="31">
-        <x:v>46121.1007466204</x:v>
-      </x:c>
-      <x:c r="J24" s="30" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -6413,16 +6419,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G25" s="29" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G25" s="29" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="H25" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
         <x:v>30</x:v>
@@ -6431,7 +6437,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -6451,25 +6457,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="G26" s="29" t="s">
+      <x:c r="H26" s="31">
+        <x:v>46121.0999663542</x:v>
+      </x:c>
+      <x:c r="I26" s="31">
+        <x:v>46121.1007466204</x:v>
+      </x:c>
+      <x:c r="J26" s="30" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="H26" s="31">
-        <x:v>46122.2429836343</x:v>
-      </x:c>
-      <x:c r="I26" s="31">
-        <x:v>46122.244317963</x:v>
-      </x:c>
-      <x:c r="J26" s="30" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -6495,19 +6501,19 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -6527,25 +6533,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G28" s="29" t="s">
+      <x:c r="H28" s="31">
+        <x:v>46121.2464636111</x:v>
+      </x:c>
+      <x:c r="I28" s="31">
+        <x:v>46121.3217277662</x:v>
+      </x:c>
+      <x:c r="J28" s="30" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="H28" s="31">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I28" s="31">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J28" s="30" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -6565,25 +6571,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G29" s="29" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G29" s="29" t="s">
+      <x:c r="H29" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I29" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J29" s="30" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="H29" s="31">
-        <x:v>46122.1996025926</x:v>
-      </x:c>
-      <x:c r="I29" s="31">
-        <x:v>46122.2050823032</x:v>
-      </x:c>
-      <x:c r="J29" s="30" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -6603,25 +6609,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="29" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G30" s="29" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G30" s="29" t="s">
+      <x:c r="H30" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I30" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J30" s="30" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="H30" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I30" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J30" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -6647,19 +6653,19 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -6679,10 +6685,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G32" s="29" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="31">
         <x:v>46121.5183984954</x:v>
@@ -6691,7 +6697,7 @@
         <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
@@ -6717,25 +6723,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G33" s="29" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>116</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -6761,19 +6767,19 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>119</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -6793,10 +6799,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G35" s="29" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="G35" s="29" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="31">
         <x:v>46119.8023724884</x:v>
@@ -6831,25 +6837,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G36" s="29" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G36" s="29" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>124</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -6869,10 +6875,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H37" s="31">
         <x:v>46119.7297941435</x:v>
@@ -6881,7 +6887,7 @@
         <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
@@ -6907,25 +6913,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G38" s="29" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="H38" s="31">
+        <x:v>46119.729231331</x:v>
+      </x:c>
+      <x:c r="I38" s="31">
+        <x:v>46119.7316308565</x:v>
+      </x:c>
+      <x:c r="J38" s="30" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="G38" s="29" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H38" s="31">
-        <x:v>46118.4219285995</x:v>
-      </x:c>
-      <x:c r="I38" s="31">
-        <x:v>46118.4229350116</x:v>
-      </x:c>
-      <x:c r="J38" s="30" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -6945,25 +6951,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G39" s="29" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H39" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I39" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J39" s="30" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="G39" s="29" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H39" s="31">
-        <x:v>46118.7424944097</x:v>
-      </x:c>
-      <x:c r="I39" s="31">
-        <x:v>46118.7432728009</x:v>
-      </x:c>
-      <x:c r="J39" s="30" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -6983,25 +6989,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G40" s="29" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="H40" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I40" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J40" s="30" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="G40" s="29" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="H40" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I40" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J40" s="30" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -7021,25 +7027,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="H41" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="G41" s="29" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -7059,25 +7065,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H42" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I42" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="G42" s="29" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="H42" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I42" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J42" s="30" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -7097,25 +7103,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H43" s="31">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I43" s="31">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="G43" s="29" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="H43" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I43" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J43" s="30" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -7135,25 +7141,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="H44" s="31">
+        <x:v>46119.1921340856</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46119.1932160417</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="G44" s="29" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -7173,25 +7179,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
-        <x:v>148</x:v>
-      </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -7211,25 +7217,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="G46" s="29" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="H46" s="31">
+        <x:v>46119.5267212153</x:v>
+      </x:c>
+      <x:c r="I46" s="31">
+        <x:v>46119.5274664236</x:v>
+      </x:c>
+      <x:c r="J46" s="30" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="G46" s="29" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H46" s="31">
-        <x:v>46119.5424612384</x:v>
-      </x:c>
-      <x:c r="I46" s="31">
-        <x:v>46119.5457934491</x:v>
-      </x:c>
-      <x:c r="J46" s="30" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -7249,25 +7255,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="G47" s="29" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -7287,25 +7293,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="G48" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -7325,25 +7331,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G49" s="29" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -7363,25 +7369,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G50" s="29" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H50" s="31">
+        <x:v>46119.5434206134</x:v>
+      </x:c>
+      <x:c r="I50" s="31">
+        <x:v>46119.545474919</x:v>
+      </x:c>
+      <x:c r="J50" s="30" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="G50" s="29" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="H50" s="31">
-        <x:v>46119.7254171991</x:v>
-      </x:c>
-      <x:c r="I50" s="31">
-        <x:v>46119.7262936574</x:v>
-      </x:c>
-      <x:c r="J50" s="30" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -7401,25 +7407,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="G51" s="29" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G51" s="29" t="s">
+      <x:c r="H51" s="31">
+        <x:v>46119.5439653357</x:v>
+      </x:c>
+      <x:c r="I51" s="31">
+        <x:v>46119.5452984143</x:v>
+      </x:c>
+      <x:c r="J51" s="30" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="H51" s="31">
-        <x:v>46119.7285584838</x:v>
-      </x:c>
-      <x:c r="I51" s="31">
-        <x:v>46119.7318005208</x:v>
-      </x:c>
-      <x:c r="J51" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -7445,19 +7451,19 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -7477,25 +7483,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G53" s="29" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="G53" s="29" t="s">
-        <x:v>169</x:v>
-      </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>71</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -7515,25 +7521,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G54" s="29" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="G54" s="29" t="s">
-        <x:v>171</x:v>
-      </x:c>
       <x:c r="H54" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -7553,25 +7559,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G55" s="29" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="G55" s="29" t="s">
-        <x:v>173</x:v>
-      </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -7591,25 +7597,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G56" s="29" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="G56" s="29" t="s">
+      <x:c r="H56" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I56" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J56" s="30" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="H56" s="31">
-        <x:v>46118.3446055671</x:v>
-      </x:c>
-      <x:c r="I56" s="31">
-        <x:v>46118.476906412</x:v>
-      </x:c>
-      <x:c r="J56" s="30" t="s">
-        <x:v>176</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -7629,25 +7635,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G57" s="29" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="G57" s="29" t="s">
+      <x:c r="H57" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I57" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J57" s="30" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="H57" s="31">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I57" s="31">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J57" s="30" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -7673,19 +7679,19 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>181</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -7705,25 +7711,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="G59" s="29" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="G59" s="29" t="s">
+      <x:c r="H59" s="31">
+        <x:v>46124.1512647338</x:v>
+      </x:c>
+      <x:c r="I59" s="31">
+        <x:v>46124.1530803935</x:v>
+      </x:c>
+      <x:c r="J59" s="30" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="H59" s="31">
-        <x:v>46124.1518079282</x:v>
-      </x:c>
-      <x:c r="I59" s="31">
-        <x:v>46124.1529164583</x:v>
-      </x:c>
-      <x:c r="J59" s="30" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -7743,25 +7749,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G60" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G60" s="29" t="s">
+      <x:c r="H60" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I60" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J60" s="30" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="H60" s="31">
-        <x:v>46122.3767795718</x:v>
-      </x:c>
-      <x:c r="I60" s="31">
-        <x:v>46122.3776183449</x:v>
-      </x:c>
-      <x:c r="J60" s="30" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -7781,25 +7787,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G61" s="29" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="G61" s="29" t="s">
+      <x:c r="H61" s="31">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I61" s="31">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J61" s="30" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="H61" s="31">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I61" s="31">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J61" s="30" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -7819,25 +7825,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="G62" s="29" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="G62" s="29" t="s">
+      <x:c r="H62" s="31">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I62" s="31">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J62" s="30" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="H62" s="31">
-        <x:v>46124.6761778356</x:v>
-      </x:c>
-      <x:c r="I62" s="31">
-        <x:v>46124.6772295602</x:v>
-      </x:c>
-      <x:c r="J62" s="30" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -7857,25 +7863,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G63" s="29" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="G63" s="29" t="s">
+      <x:c r="H63" s="31">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I63" s="31">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J63" s="30" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="H63" s="31">
-        <x:v>46124.1487218981</x:v>
-      </x:c>
-      <x:c r="I63" s="31">
-        <x:v>46124.1494313773</x:v>
-      </x:c>
-      <x:c r="J63" s="30" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -7895,25 +7901,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G64" s="29" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G64" s="29" t="s">
+      <x:c r="H64" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I64" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J64" s="30" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="H64" s="31">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I64" s="31">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J64" s="30" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -7933,25 +7939,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G65" s="29" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G65" s="29" t="s">
+      <x:c r="H65" s="31">
+        <x:v>46124.6975491551</x:v>
+      </x:c>
+      <x:c r="I65" s="31">
+        <x:v>46124.6983328357</x:v>
+      </x:c>
+      <x:c r="J65" s="30" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="H65" s="31">
-        <x:v>46124.7023532986</x:v>
-      </x:c>
-      <x:c r="I65" s="31">
-        <x:v>46124.7048005093</x:v>
-      </x:c>
-      <x:c r="J65" s="30" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -7971,25 +7977,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G66" s="29" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="G66" s="29" t="s">
+      <x:c r="H66" s="31">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I66" s="31">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J66" s="30" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="H66" s="31">
-        <x:v>46124.7029179398</x:v>
-      </x:c>
-      <x:c r="I66" s="31">
-        <x:v>46124.7046092014</x:v>
-      </x:c>
-      <x:c r="J66" s="30" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -8009,25 +8015,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G67" s="29" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="G67" s="29" t="s">
+      <x:c r="H67" s="31">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I67" s="31">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J67" s="30" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="H67" s="31">
-        <x:v>46124.7035032407</x:v>
-      </x:c>
-      <x:c r="I67" s="31">
-        <x:v>46124.704475463</x:v>
-      </x:c>
-      <x:c r="J67" s="30" t="s">
-        <x:v>208</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -8047,25 +8053,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G68" s="29" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="G68" s="29" t="s">
+      <x:c r="H68" s="31">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I68" s="31">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J68" s="30" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="H68" s="31">
-        <x:v>46126.5341923727</x:v>
-      </x:c>
-      <x:c r="I68" s="31">
-        <x:v>46126.5348242708</x:v>
-      </x:c>
-      <x:c r="J68" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -8091,10 +8097,10 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
         <x:v>30</x:v>
@@ -8103,7 +8109,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -8129,10 +8135,10 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
         <x:v>30</x:v>
@@ -8141,7 +8147,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -8167,19 +8173,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -8205,19 +8211,19 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -8243,19 +8249,19 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -8281,19 +8287,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>223</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -8313,25 +8319,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="G75" s="29" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="G75" s="29" t="s">
+      <x:c r="H75" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I75" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J75" s="30" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="H75" s="31">
-        <x:v>46122.3885020718</x:v>
-      </x:c>
-      <x:c r="I75" s="31">
-        <x:v>46122.3892655903</x:v>
-      </x:c>
-      <x:c r="J75" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -8357,19 +8363,19 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -8395,19 +8401,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>230</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -8427,25 +8433,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
+      <x:c r="H78" s="31">
+        <x:v>46122.5587807523</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46122.5602428125</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46124.1410094907</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46124.1426461806</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -8465,25 +8471,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F79" s="29" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G79" s="29" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="G79" s="29" t="s">
+      <x:c r="H79" s="31">
+        <x:v>46124.1410094907</x:v>
+      </x:c>
+      <x:c r="I79" s="31">
+        <x:v>46124.1426461806</x:v>
+      </x:c>
+      <x:c r="J79" s="30" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="H79" s="31">
-        <x:v>46122.5911383796</x:v>
-      </x:c>
-      <x:c r="I79" s="31">
-        <x:v>46122.5921380556</x:v>
-      </x:c>
-      <x:c r="J79" s="30" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -8503,25 +8509,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
+      <x:c r="H80" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I80" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J80" s="30" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="H80" s="31">
-        <x:v>46122.5945434491</x:v>
-      </x:c>
-      <x:c r="I80" s="31">
-        <x:v>46122.5999534606</x:v>
-      </x:c>
-      <x:c r="J80" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -8547,19 +8553,19 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>83</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -8585,19 +8591,19 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>149</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -8623,19 +8629,19 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>245</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -8655,25 +8661,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="G84" s="29" t="s">
+      <x:c r="H84" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I84" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J84" s="30" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="H84" s="31">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I84" s="31">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J84" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -8699,10 +8705,10 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
         <x:v>250</x:v>
@@ -8711,7 +8717,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -8737,19 +8743,19 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>253</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -8769,25 +8775,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="G87" s="29" t="s">
+      <x:c r="H87" s="31">
+        <x:v>46123.0476912847</x:v>
+      </x:c>
+      <x:c r="I87" s="31">
+        <x:v>46123.0484775694</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="H87" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I87" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J87" s="30" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -8807,25 +8813,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="G88" s="29" t="s">
+      <x:c r="H88" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I88" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J88" s="30" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="H88" s="31">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I88" s="31">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J88" s="30" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -8845,16 +8851,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G89" s="29" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="G89" s="29" t="s">
-        <x:v>261</x:v>
-      </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
         <x:v>30</x:v>
@@ -8863,7 +8869,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -8871,10 +8877,10 @@
     </x:row>
     <x:row r="90" spans="1:28" ht="30" customHeight="1">
       <x:c r="B90" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C90" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D90" s="30" t="s">
         <x:v>16</x:v>
@@ -8883,25 +8889,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G90" s="29" t="s">
-        <x:v>265</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -8909,10 +8915,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>16</x:v>
@@ -8921,25 +8927,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G91" s="29" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H91" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I91" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J91" s="30" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="G91" s="29" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H91" s="31">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I91" s="31">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J91" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -8947,10 +8953,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>16</x:v>
@@ -8959,25 +8965,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G92" s="29" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="G92" s="29" t="s">
-        <x:v>272</x:v>
-      </x:c>
       <x:c r="H92" s="31">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>273</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -8985,10 +8991,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>16</x:v>
@@ -8997,25 +9003,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
@@ -9023,10 +9029,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>16</x:v>
@@ -9035,25 +9041,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H94" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I94" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J94" s="30" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="G94" s="29" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H94" s="31">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I94" s="31">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J94" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
@@ -9061,16 +9067,16 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>46</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E95" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
         <x:v>281</x:v>
@@ -9079,19 +9085,19 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46132.3798789699</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46132.3799006944</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>283</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
-        <x:v>3031</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46133.1738098148</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
@@ -9099,37 +9105,37 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E96" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="H96" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46118.439490081</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46118.4395309375</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>287</x:v>
-      </x:c>
       <x:c r="K96" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>21</x:v>
@@ -9137,10 +9143,10 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>16</x:v>
@@ -9149,10 +9155,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="G97" s="29" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="G97" s="29" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="H97" s="31">
         <x:v>46118.7761679514</x:v>
@@ -9175,10 +9181,10 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>16</x:v>
@@ -9187,25 +9193,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G98" s="29" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="G98" s="29" t="s">
+      <x:c r="H98" s="31">
+        <x:v>46118.439490081</x:v>
+      </x:c>
+      <x:c r="I98" s="31">
+        <x:v>46118.4395309375</x:v>
+      </x:c>
+      <x:c r="J98" s="30" t="s">
         <x:v>291</x:v>
-      </x:c>
-      <x:c r="H98" s="31">
-        <x:v>46119.4833706713</x:v>
-      </x:c>
-      <x:c r="I98" s="31">
-        <x:v>46119.4833991435</x:v>
-      </x:c>
-      <x:c r="J98" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>21</x:v>
@@ -9213,37 +9219,37 @@
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
       <x:c r="B99" s="29" t="s">
-        <x:v>292</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>284</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D99" s="30" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E99" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="G99" s="29" t="s">
         <x:v>293</x:v>
       </x:c>
       <x:c r="H99" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I99" s="31">
-        <x:v>46023</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J99" s="30" t="s">
-        <x:v>294</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>21</x:v>
@@ -9251,35 +9257,37 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D100" s="30" t="s"/>
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D100" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="E100" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G100" s="29" t="s">
-        <x:v>298</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="H100" s="31">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46132.3879904745</x:v>
       </x:c>
       <x:c r="I100" s="31">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46023</x:v>
       </x:c>
       <x:c r="J100" s="30" t="s">
-        <x:v>299</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>21</x:v>
@@ -9287,122 +9295,147 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="D101" s="30" t="s">
-        <x:v>41</x:v>
-      </x:c>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D101" s="30" t="s"/>
       <x:c r="E101" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F101" s="29" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="G101" s="29" t="s">
-        <x:v>303</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H101" s="31">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46124.1588481829</x:v>
       </x:c>
       <x:c r="I101" s="31">
-        <x:v>46023</x:v>
+        <x:v>46124.1588689236</x:v>
       </x:c>
       <x:c r="J101" s="30" t="s">
-        <x:v>304</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B102" s="29" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C102" s="29" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="D102" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E102" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F102" s="29" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G102" s="29" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H102" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I102" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J102" s="30" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="K102" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L102" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M102" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B104" s="17" t="s">
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B105" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C104" s="18" t="s"/>
-      <x:c r="D104" s="18" t="s"/>
-      <x:c r="E104" s="19" t="s"/>
-      <x:c r="F104" s="19" t="s"/>
-    </x:row>
-    <x:row r="105" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B105" s="20" t="s">
+      <x:c r="C105" s="18" t="s"/>
+      <x:c r="D105" s="18" t="s"/>
+      <x:c r="E105" s="19" t="s"/>
+      <x:c r="F105" s="19" t="s"/>
+    </x:row>
+    <x:row r="106" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B106" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C105" s="21" t="s"/>
-      <x:c r="D105" s="21" t="s"/>
-      <x:c r="E105" s="21" t="s"/>
-      <x:c r="F105" s="22" t="s">
+      <x:c r="C106" s="21" t="s"/>
+      <x:c r="D106" s="21" t="s"/>
+      <x:c r="E106" s="21" t="s"/>
+      <x:c r="F106" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B106" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C106" s="24" t="s"/>
-      <x:c r="D106" s="24" t="s"/>
-      <x:c r="E106" s="24" t="s"/>
-      <x:c r="F106" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:28" ht="18" customHeight="1">
       <x:c r="B107" s="23" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C107" s="24" t="s"/>
       <x:c r="D107" s="24" t="s"/>
       <x:c r="E107" s="24" t="s"/>
       <x:c r="F107" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:28" ht="18" customHeight="1">
       <x:c r="B108" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C108" s="24" t="s"/>
       <x:c r="D108" s="24" t="s"/>
       <x:c r="E108" s="24" t="s"/>
       <x:c r="F108" s="25" t="n">
-        <x:v>79</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
       <x:c r="B109" s="23" t="s">
-        <x:v>262</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C109" s="24" t="s"/>
       <x:c r="D109" s="24" t="s"/>
       <x:c r="E109" s="24" t="s"/>
       <x:c r="F109" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
       <x:c r="B110" s="23" t="s">
-        <x:v>292</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s"/>
       <x:c r="D110" s="24" t="s"/>
       <x:c r="E110" s="24" t="s"/>
       <x:c r="F110" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
@@ -9413,7 +9446,7 @@
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>300</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
@@ -9422,18 +9455,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B113" s="26" t="s">
+    <x:row r="113" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B113" s="23" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C113" s="24" t="s"/>
+      <x:c r="D113" s="24" t="s"/>
+      <x:c r="E113" s="24" t="s"/>
+      <x:c r="F113" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B114" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C113" s="27" t="s"/>
-      <x:c r="D113" s="27" t="s"/>
-      <x:c r="E113" s="27" t="s"/>
-      <x:c r="F113" s="28" t="n">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C114" s="27" t="s"/>
+      <x:c r="D114" s="27" t="s"/>
+      <x:c r="E114" s="27" t="s"/>
+      <x:c r="F114" s="28" t="n">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
     <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10319,8 +10362,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B104:F104"/>
-    <x:mergeCell ref="B105:E105"/>
+    <x:mergeCell ref="B105:F105"/>
     <x:mergeCell ref="B106:E106"/>
     <x:mergeCell ref="B107:E107"/>
     <x:mergeCell ref="B108:E108"/>
@@ -10329,6 +10371,7 @@
     <x:mergeCell ref="B111:E111"/>
     <x:mergeCell ref="B112:E112"/>
     <x:mergeCell ref="B113:E113"/>
+    <x:mergeCell ref="B114:E114"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -243,37 +243,163 @@
     <x:t>asdxzcasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1326-920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08682</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1346-976</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08338</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1326-920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe</x:t>
+    <x:t>26-1RTG-XIV-08117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1255-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08118</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1256-775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08120</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1257-399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1258-667</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1259-834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>resdxcv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1261-591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08138</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1262-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08102</x:t>
@@ -282,100 +408,163 @@
     <x:t>61-4-2026-1253-632</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08117</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1255-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08118</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1256-775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08120</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1257-399</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIAAVAA-A0A8A131AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1258-667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1259-834</x:t>
-  </x:si>
-  <x:si>
-    <x:t>resdxcv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08137</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1261-591</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08138</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1262-573</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1251-149</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1280-364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1281-501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08154</x:t>
@@ -384,100 +573,94 @@
     <x:t>61-4-2026-1275-174</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1251-149</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
+    <x:t>26-1RTG-XIV-08027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1221-509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1234565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08625</x:t>
@@ -486,133 +669,31 @@
     <x:t>61-4-2026-1344-095</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1280-364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1221-509</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234565</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1281-501</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08189</x:t>
@@ -624,64 +705,40 @@
     <x:t>zsdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08187</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1298-649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sczxcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08188</x:t>
@@ -690,10 +747,37 @@
     <x:t>61-4-2026-1299-939</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1290-287</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08185</x:t>
@@ -705,63 +789,6 @@
     <x:t>sxdasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1298-649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sczxcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1286-997</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08179</x:t>
   </x:si>
   <x:si>
@@ -771,6 +798,15 @@
     <x:t>zsdasdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08184</x:t>
   </x:si>
   <x:si>
@@ -780,10 +816,13 @@
     <x:t>test12</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1290-287</x:t>
+    <x:t>26-1RTG-XIV-08181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1293-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tesg213</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08182</x:t>
@@ -793,30 +832,6 @@
   </x:si>
   <x:si>
     <x:t>sdasqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1292-028</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1293-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tesg213</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -6121,19 +6136,19 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="H17" s="31">
-        <x:v>46133.5419909606</x:v>
+        <x:v>46126.455832662</x:v>
       </x:c>
       <x:c r="I17" s="31">
-        <x:v>46133.5429334722</x:v>
+        <x:v>46126.4740829051</x:v>
       </x:c>
       <x:c r="J17" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K17" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L17" s="33">
-        <x:v>46133.5457238194</x:v>
+        <x:v>46126.4751368866</x:v>
       </x:c>
       <x:c r="M17" s="29" t="s">
         <x:v>21</x:v>
@@ -6153,25 +6168,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="29" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G18" s="29" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -6235,10 +6250,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46126.455832662</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46126.4740829051</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
         <x:v>82</x:v>
@@ -6247,7 +6262,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46126.4751368866</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -6258,13 +6273,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D21" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
         <x:v>83</x:v>
@@ -6273,19 +6288,19 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="H21" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46133.0575652778</x:v>
       </x:c>
       <x:c r="I21" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="L21" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46134.4615905556</x:v>
       </x:c>
       <x:c r="M21" s="29" t="s">
         <x:v>21</x:v>
@@ -6296,34 +6311,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D22" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H22" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46133.5419909606</x:v>
       </x:c>
       <x:c r="I22" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46133.5429334722</x:v>
       </x:c>
       <x:c r="J22" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K22" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L22" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46133.5457238194</x:v>
       </x:c>
       <x:c r="M22" s="29" t="s">
         <x:v>21</x:v>
@@ -6349,19 +6364,19 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -6381,25 +6396,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G24" s="29" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H24" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I24" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J24" s="30" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="G24" s="29" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="H24" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I24" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J24" s="30" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -6425,19 +6440,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -6457,25 +6472,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F26" s="29" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G26" s="29" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>97</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -6501,19 +6516,19 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -6533,25 +6548,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F28" s="29" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G28" s="29" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>102</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -6577,10 +6592,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>105</x:v>
@@ -6589,7 +6604,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -6615,10 +6630,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
         <x:v>108</x:v>
@@ -6627,7 +6642,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -6653,10 +6668,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
         <x:v>111</x:v>
@@ -6665,7 +6680,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -6691,10 +6706,10 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
         <x:v>114</x:v>
@@ -6703,7 +6718,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -6729,19 +6744,19 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -6761,25 +6776,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="G34" s="29" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
-        <x:v>92</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -6799,25 +6814,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G35" s="29" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -6837,25 +6852,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G36" s="29" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -6875,25 +6890,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -6913,25 +6928,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F38" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G38" s="29" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -6951,25 +6966,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>130</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -6995,19 +7010,19 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>133</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -7027,25 +7042,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G41" s="29" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="G41" s="29" t="s">
+      <x:c r="H41" s="31">
+        <x:v>46118.4219285995</x:v>
+      </x:c>
+      <x:c r="I41" s="31">
+        <x:v>46118.4229350116</x:v>
+      </x:c>
+      <x:c r="J41" s="30" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="H41" s="31">
-        <x:v>46118.7562945255</x:v>
-      </x:c>
-      <x:c r="I41" s="31">
-        <x:v>46118.7571720255</x:v>
-      </x:c>
-      <x:c r="J41" s="30" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -7065,25 +7080,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G42" s="29" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="G42" s="29" t="s">
+      <x:c r="H42" s="31">
+        <x:v>46118.7424944097</x:v>
+      </x:c>
+      <x:c r="I42" s="31">
+        <x:v>46118.7432728009</x:v>
+      </x:c>
+      <x:c r="J42" s="30" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="H42" s="31">
-        <x:v>46119.0668949653</x:v>
-      </x:c>
-      <x:c r="I42" s="31">
-        <x:v>46119.0755180324</x:v>
-      </x:c>
-      <x:c r="J42" s="30" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -7103,25 +7118,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G43" s="29" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G43" s="29" t="s">
+      <x:c r="H43" s="31">
+        <x:v>46118.7562945255</x:v>
+      </x:c>
+      <x:c r="I43" s="31">
+        <x:v>46118.7571720255</x:v>
+      </x:c>
+      <x:c r="J43" s="30" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="H43" s="31">
-        <x:v>46119.0739296412</x:v>
-      </x:c>
-      <x:c r="I43" s="31">
-        <x:v>46119.0753097685</x:v>
-      </x:c>
-      <x:c r="J43" s="30" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -7141,25 +7156,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G44" s="29" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="G44" s="29" t="s">
+      <x:c r="H44" s="31">
+        <x:v>46119.0668949653</x:v>
+      </x:c>
+      <x:c r="I44" s="31">
+        <x:v>46119.0755180324</x:v>
+      </x:c>
+      <x:c r="J44" s="30" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="H44" s="31">
-        <x:v>46119.1921340856</x:v>
-      </x:c>
-      <x:c r="I44" s="31">
-        <x:v>46119.1932160417</x:v>
-      </x:c>
-      <x:c r="J44" s="30" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -7179,25 +7194,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G45" s="29" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G45" s="29" t="s">
+      <x:c r="H45" s="31">
+        <x:v>46119.0739296412</x:v>
+      </x:c>
+      <x:c r="I45" s="31">
+        <x:v>46119.0753097685</x:v>
+      </x:c>
+      <x:c r="J45" s="30" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="H45" s="31">
-        <x:v>46119.4681336458</x:v>
-      </x:c>
-      <x:c r="I45" s="31">
-        <x:v>46119.4697068056</x:v>
-      </x:c>
-      <x:c r="J45" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -7223,10 +7238,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
         <x:v>150</x:v>
@@ -7235,7 +7250,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -7261,19 +7276,19 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -7299,10 +7314,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
         <x:v>155</x:v>
@@ -7311,7 +7326,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -7337,10 +7352,10 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
         <x:v>158</x:v>
@@ -7349,7 +7364,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -7375,10 +7390,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
         <x:v>161</x:v>
@@ -7387,7 +7402,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -7413,10 +7428,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
         <x:v>164</x:v>
@@ -7425,7 +7440,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -7451,19 +7466,19 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -7483,25 +7498,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G53" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -7521,25 +7536,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -7559,25 +7574,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -7597,25 +7612,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>175</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -7635,25 +7650,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -7673,25 +7688,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -7711,25 +7726,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -7749,25 +7764,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -7787,25 +7802,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -7825,25 +7840,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>192</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -7869,10 +7884,10 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
         <x:v>195</x:v>
@@ -7881,7 +7896,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -7907,10 +7922,10 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
         <x:v>198</x:v>
@@ -7919,7 +7934,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -7983,19 +7998,19 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
-        <x:v>204</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -8015,25 +8030,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="G67" s="29" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="G67" s="29" t="s">
-        <x:v>206</x:v>
-      </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
-        <x:v>207</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -8053,25 +8068,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F68" s="29" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G68" s="29" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="H68" s="31">
+        <x:v>46124.7029179398</x:v>
+      </x:c>
+      <x:c r="I68" s="31">
+        <x:v>46124.7046092014</x:v>
+      </x:c>
+      <x:c r="J68" s="30" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="G68" s="29" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H68" s="31">
-        <x:v>46124.7035032407</x:v>
-      </x:c>
-      <x:c r="I68" s="31">
-        <x:v>46124.704475463</x:v>
-      </x:c>
-      <x:c r="J68" s="30" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="K68" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -8091,25 +8106,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F69" s="29" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G69" s="29" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H69" s="31">
+        <x:v>46124.7035032407</x:v>
+      </x:c>
+      <x:c r="I69" s="31">
+        <x:v>46124.704475463</x:v>
+      </x:c>
+      <x:c r="J69" s="30" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="G69" s="29" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="H69" s="31">
-        <x:v>46128.4605351157</x:v>
-      </x:c>
-      <x:c r="I69" s="31">
-        <x:v>46128.4612873727</x:v>
-      </x:c>
-      <x:c r="J69" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K69" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -8129,25 +8144,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F70" s="29" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G70" s="29" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G70" s="29" t="s">
-        <x:v>214</x:v>
-      </x:c>
       <x:c r="H70" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -8167,16 +8182,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G71" s="29" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="G71" s="29" t="s">
-        <x:v>216</x:v>
-      </x:c>
       <x:c r="H71" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
         <x:v>30</x:v>
@@ -8185,7 +8200,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -8205,25 +8220,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G72" s="29" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G72" s="29" t="s">
-        <x:v>218</x:v>
-      </x:c>
       <x:c r="H72" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -8243,25 +8258,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G73" s="29" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="G73" s="29" t="s">
-        <x:v>220</x:v>
-      </x:c>
       <x:c r="H73" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -8281,25 +8296,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G74" s="29" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="G74" s="29" t="s">
+      <x:c r="H74" s="31">
+        <x:v>46124.7023532986</x:v>
+      </x:c>
+      <x:c r="I74" s="31">
+        <x:v>46124.7048005093</x:v>
+      </x:c>
+      <x:c r="J74" s="30" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="H74" s="31">
-        <x:v>46122.3879258681</x:v>
-      </x:c>
-      <x:c r="I74" s="31">
-        <x:v>46122.3894281713</x:v>
-      </x:c>
-      <x:c r="J74" s="30" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -8325,10 +8340,10 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
         <x:v>225</x:v>
@@ -8337,7 +8352,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -8401,19 +8416,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -8433,25 +8448,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G78" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>232</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -8477,10 +8492,10 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
         <x:v>235</x:v>
@@ -8489,7 +8504,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -8515,19 +8530,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>238</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -8547,25 +8562,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F81" s="29" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="G81" s="29" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="G81" s="29" t="s">
-        <x:v>240</x:v>
-      </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -8585,25 +8600,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G82" s="29" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="G82" s="29" t="s">
-        <x:v>242</x:v>
-      </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -8623,25 +8638,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G83" s="29" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="G83" s="29" t="s">
-        <x:v>244</x:v>
-      </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -8661,25 +8676,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G84" s="29" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G84" s="29" t="s">
-        <x:v>246</x:v>
-      </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>247</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -8699,25 +8714,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="G85" s="29" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="H85" s="31">
+        <x:v>46122.5911383796</x:v>
+      </x:c>
+      <x:c r="I85" s="31">
+        <x:v>46122.5921380556</x:v>
+      </x:c>
+      <x:c r="J85" s="30" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="G85" s="29" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H85" s="31">
-        <x:v>46123.4162791088</x:v>
-      </x:c>
-      <x:c r="I85" s="31">
-        <x:v>46123.4173169792</x:v>
-      </x:c>
-      <x:c r="J85" s="30" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -8737,16 +8752,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
         <x:v>30</x:v>
@@ -8755,7 +8770,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -8775,25 +8790,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G87" s="29" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H87" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I87" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J87" s="30" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="G87" s="29" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H87" s="31">
-        <x:v>46123.0476912847</x:v>
-      </x:c>
-      <x:c r="I87" s="31">
-        <x:v>46123.0484775694</x:v>
-      </x:c>
-      <x:c r="J87" s="30" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -8813,25 +8828,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G88" s="29" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H88" s="31">
+        <x:v>46122.6819179514</x:v>
+      </x:c>
+      <x:c r="I88" s="31">
+        <x:v>46122.6826717361</x:v>
+      </x:c>
+      <x:c r="J88" s="30" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="G88" s="29" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H88" s="31">
-        <x:v>46123.061368912</x:v>
-      </x:c>
-      <x:c r="I88" s="31">
-        <x:v>46123.0623472106</x:v>
-      </x:c>
-      <x:c r="J88" s="30" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -8851,25 +8866,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G89" s="29" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H89" s="31">
+        <x:v>46123.061368912</x:v>
+      </x:c>
+      <x:c r="I89" s="31">
+        <x:v>46123.0623472106</x:v>
+      </x:c>
+      <x:c r="J89" s="30" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="G89" s="29" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="H89" s="31">
-        <x:v>46122.7261372338</x:v>
-      </x:c>
-      <x:c r="I89" s="31">
-        <x:v>46122.727234375</x:v>
-      </x:c>
-      <x:c r="J89" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -8889,25 +8904,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G90" s="29" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="G90" s="29" t="s">
+      <x:c r="H90" s="31">
+        <x:v>46123.4162791088</x:v>
+      </x:c>
+      <x:c r="I90" s="31">
+        <x:v>46123.4173169792</x:v>
+      </x:c>
+      <x:c r="J90" s="30" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="H90" s="31">
-        <x:v>46122.9452935995</x:v>
-      </x:c>
-      <x:c r="I90" s="31">
-        <x:v>46123.0460683681</x:v>
-      </x:c>
-      <x:c r="J90" s="30" t="s">
-        <x:v>263</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -8915,10 +8930,10 @@
     </x:row>
     <x:row r="91" spans="1:28" ht="30" customHeight="1">
       <x:c r="B91" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C91" s="29" t="s">
-        <x:v>265</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D91" s="30" t="s">
         <x:v>16</x:v>
@@ -8927,25 +8942,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
-        <x:v>266</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G91" s="29" t="s">
-        <x:v>267</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46118.5788871875</x:v>
+        <x:v>46122.9452935995</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46118.5789284722</x:v>
+        <x:v>46123.0460683681</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>268</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -8953,10 +8968,10 @@
     </x:row>
     <x:row r="92" spans="1:28" ht="30" customHeight="1">
       <x:c r="B92" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C92" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D92" s="30" t="s">
         <x:v>16</x:v>
@@ -8965,25 +8980,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
-        <x:v>270</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G92" s="29" t="s">
-        <x:v>271</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46118.6064654514</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46118.6065117477</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -8991,10 +9006,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>16</x:v>
@@ -9003,25 +9018,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.7029973032</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.7030397569</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="K93" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
@@ -9029,10 +9044,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>16</x:v>
@@ -9041,25 +9056,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="G94" s="29" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="H94" s="31">
-        <x:v>46118.7372774306</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I94" s="31">
-        <x:v>46118.7373236806</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J94" s="30" t="s">
-        <x:v>279</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
@@ -9067,10 +9082,10 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
-        <x:v>280</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="D95" s="30" t="s">
         <x:v>16</x:v>
@@ -9079,25 +9094,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F95" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G95" s="29" t="s">
-        <x:v>282</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46118.6471475926</x:v>
+        <x:v>46118.7029973032</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46118.647188044</x:v>
+        <x:v>46118.7030397569</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
@@ -9105,37 +9120,37 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>46</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E96" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
+      <x:c r="H96" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46132.3798789699</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46132.3799006944</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>285</x:v>
-      </x:c>
       <x:c r="K96" s="32" t="n">
-        <x:v>3031</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46133.1738098148</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>21</x:v>
@@ -9143,10 +9158,10 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>286</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>16</x:v>
@@ -9155,25 +9170,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="G97" s="29" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="G97" s="29" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="H97" s="31">
-        <x:v>46118.7761679514</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I97" s="31">
-        <x:v>46118.7762103819</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J97" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>21</x:v>
@@ -9181,37 +9196,37 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>286</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E98" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G98" s="29" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="G98" s="29" t="s">
+      <x:c r="H98" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I98" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J98" s="30" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="H98" s="31">
-        <x:v>46118.439490081</x:v>
-      </x:c>
-      <x:c r="I98" s="31">
-        <x:v>46118.4395309375</x:v>
-      </x:c>
-      <x:c r="J98" s="30" t="s">
-        <x:v>291</x:v>
-      </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>21</x:v>
@@ -9219,10 +9234,10 @@
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
       <x:c r="B99" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D99" s="30" t="s">
         <x:v>16</x:v>
@@ -9237,19 +9252,19 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="H99" s="31">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I99" s="31">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J99" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K99" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>21</x:v>
@@ -9257,37 +9272,37 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>294</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>286</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D100" s="30" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E100" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
-        <x:v>265</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G100" s="29" t="s">
         <x:v>295</x:v>
       </x:c>
       <x:c r="H100" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46118.439490081</x:v>
       </x:c>
       <x:c r="I100" s="31">
-        <x:v>46023</x:v>
+        <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J100" s="30" t="s">
         <x:v>296</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>21</x:v>
@@ -9295,35 +9310,37 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>297</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="D101" s="30" t="s"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D101" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="E101" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F101" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G101" s="29" t="s">
-        <x:v>300</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="H101" s="31">
-        <x:v>46124.1588481829</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I101" s="31">
-        <x:v>46124.1588689236</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J101" s="30" t="s">
-        <x:v>301</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>21</x:v>
@@ -9331,10 +9348,10 @@
     </x:row>
     <x:row r="102" spans="1:28" ht="30" customHeight="1">
       <x:c r="B102" s="29" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C102" s="29" t="s">
-        <x:v>303</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="D102" s="30" t="s">
         <x:v>41</x:v>
@@ -9343,121 +9360,173 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F102" s="29" t="s">
-        <x:v>304</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="G102" s="29" t="s">
-        <x:v>305</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="H102" s="31">
-        <x:v>46124.1607868981</x:v>
+        <x:v>46132.3879904745</x:v>
       </x:c>
       <x:c r="I102" s="31">
         <x:v>46023</x:v>
       </x:c>
       <x:c r="J102" s="30" t="s">
-        <x:v>306</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="K102" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L102" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M102" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="105" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B105" s="17" t="s">
+    <x:row r="103" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B103" s="29" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C103" s="29" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="D103" s="30" t="s"/>
+      <x:c r="E103" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F103" s="29" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="G103" s="29" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="H103" s="31">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I103" s="31">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J103" s="30" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="K103" s="32" t="n">
+        <x:v>5070</x:v>
+      </x:c>
+      <x:c r="L103" s="33">
+        <x:v>46124.1622106481</x:v>
+      </x:c>
+      <x:c r="M103" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B104" s="29" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C104" s="29" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="D104" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E104" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F104" s="29" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G104" s="29" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="H104" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I104" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J104" s="30" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="K104" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L104" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M104" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B107" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C105" s="18" t="s"/>
-      <x:c r="D105" s="18" t="s"/>
-      <x:c r="E105" s="19" t="s"/>
-      <x:c r="F105" s="19" t="s"/>
-    </x:row>
-    <x:row r="106" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B106" s="20" t="s">
+      <x:c r="C107" s="18" t="s"/>
+      <x:c r="D107" s="18" t="s"/>
+      <x:c r="E107" s="19" t="s"/>
+      <x:c r="F107" s="19" t="s"/>
+    </x:row>
+    <x:row r="108" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B108" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C106" s="21" t="s"/>
-      <x:c r="D106" s="21" t="s"/>
-      <x:c r="E106" s="21" t="s"/>
-      <x:c r="F106" s="22" t="s">
+      <x:c r="C108" s="21" t="s"/>
+      <x:c r="D108" s="21" t="s"/>
+      <x:c r="E108" s="21" t="s"/>
+      <x:c r="F108" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B107" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C107" s="24" t="s"/>
-      <x:c r="D107" s="24" t="s"/>
-      <x:c r="E107" s="24" t="s"/>
-      <x:c r="F107" s="25" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B108" s="23" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C108" s="24" t="s"/>
-      <x:c r="D108" s="24" t="s"/>
-      <x:c r="E108" s="24" t="s"/>
-      <x:c r="F108" s="25" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:28" ht="18" customHeight="1">
       <x:c r="B109" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C109" s="24" t="s"/>
       <x:c r="D109" s="24" t="s"/>
       <x:c r="E109" s="24" t="s"/>
       <x:c r="F109" s="25" t="n">
-        <x:v>80</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
       <x:c r="B110" s="23" t="s">
-        <x:v>264</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s"/>
       <x:c r="D110" s="24" t="s"/>
       <x:c r="E110" s="24" t="s"/>
       <x:c r="F110" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>294</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
       <x:c r="E111" s="24" t="s"/>
       <x:c r="F111" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>297</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
       <x:c r="E112" s="24" t="s"/>
       <x:c r="F112" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:28" ht="18" customHeight="1">
       <x:c r="B113" s="23" t="s">
-        <x:v>302</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C113" s="24" t="s"/>
       <x:c r="D113" s="24" t="s"/>
@@ -9466,19 +9535,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B114" s="26" t="s">
+    <x:row r="114" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B114" s="23" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C114" s="24" t="s"/>
+      <x:c r="D114" s="24" t="s"/>
+      <x:c r="E114" s="24" t="s"/>
+      <x:c r="F114" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B115" s="23" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="C115" s="24" t="s"/>
+      <x:c r="D115" s="24" t="s"/>
+      <x:c r="E115" s="24" t="s"/>
+      <x:c r="F115" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B116" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C114" s="27" t="s"/>
-      <x:c r="D114" s="27" t="s"/>
-      <x:c r="E114" s="27" t="s"/>
-      <x:c r="F114" s="28" t="n">
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C116" s="27" t="s"/>
+      <x:c r="D116" s="27" t="s"/>
+      <x:c r="E116" s="27" t="s"/>
+      <x:c r="F116" s="28" t="n">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
     <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10362,9 +10451,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B105:F105"/>
-    <x:mergeCell ref="B106:E106"/>
-    <x:mergeCell ref="B107:E107"/>
+    <x:mergeCell ref="B107:F107"/>
     <x:mergeCell ref="B108:E108"/>
     <x:mergeCell ref="B109:E109"/>
     <x:mergeCell ref="B110:E110"/>
@@ -10372,6 +10459,8 @@
     <x:mergeCell ref="B112:E112"/>
     <x:mergeCell ref="B113:E113"/>
     <x:mergeCell ref="B114:E114"/>
+    <x:mergeCell ref="B115:E115"/>
+    <x:mergeCell ref="B116:E116"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -252,43 +252,58 @@
     <x:t>asdqwe</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08339</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1327-230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qweasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1348-304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08729</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1347-280</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08339</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1327-230</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qweasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
+    <x:t>26-1RTG-XIV-08344</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1332-041</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08117</x:t>
@@ -336,6 +351,63 @@
     <x:t>61-4-2026-1261-591</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1269-505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1253-632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIaV-08146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1270-571</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08147</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1271-966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1272-162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>df</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1273-639</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08153</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1274-495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdadasdxasd</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08138</x:t>
   </x:si>
   <x:si>
@@ -345,55 +417,16 @@
     <x:t>cxcasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1269-505</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIaV-08146</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1270-571</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1271-966</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08148</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1272-162</x:t>
-  </x:si>
-  <x:si>
-    <x:t>df</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1273-639</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08153</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1274-495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdadasdxasd</x:t>
+    <x:t>26-1RTG-XIV-08101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1252-337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
@@ -402,16 +435,130 @@
     <x:t>61-4-2026-1279-279</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08102</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1253-632</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08101</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1252-337</x:t>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -420,144 +567,48 @@
     <x:t>61-4-2026-1251-149</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1249-913</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08163</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1280-364</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1275-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1282-165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1301-555</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1302-585</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scawdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1303-365</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdweq</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08165</x:t>
   </x:si>
   <x:si>
@@ -567,10 +618,118 @@
     <x:t>zscasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08154</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1275-174</x:t>
+    <x:t>26-1RTG-XIV-08209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1309-422</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1310-349</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1300-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1311-081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwedszxczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1313-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zscasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1314-175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1315-598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08625</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1344-095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1339-442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1334-994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1312-712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1299-939</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1284-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08185</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1297-182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sxdasdasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1283-909</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08027</x:t>
@@ -582,133 +741,13 @@
     <x:t>1234565</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1302-585</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scawdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1303-365</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdweq</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1282-165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1309-422</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqwezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1310-349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1311-081</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwedszxczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1301-555</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08212</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1312-712</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1314-175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1315-598</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08625</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1344-095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08482</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1339-442</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08369</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1334-994</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08344</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1332-041</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1313-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zscasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1300-860</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1283-909</x:t>
+    <x:t>26-1RTG-XIV-08173</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1285-609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdazcxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08187</x:t>
@@ -720,19 +759,25 @@
     <x:t>sczxcasdasd</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1284-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08173</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1285-609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdazcxc</x:t>
+    <x:t>26-1RTG-XIV-08175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1287-637</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdadqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1288-384</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1289-340</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08174</x:t>
@@ -741,22 +786,22 @@
     <x:t>61-4-2026-1286-997</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1299-939</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1288-384</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1289-340</x:t>
+    <x:t>26-1RTG-XIV-08179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1291-157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasdqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08184</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1296-884</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test12</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08178</x:t>
@@ -765,13 +810,22 @@
     <x:t>61-4-2026-1290-287</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1287-637</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdadqwe</x:t>
+    <x:t>26-1RTG-XIV-08182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1294-405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sdasqwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1295-514</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsdasd</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08180</x:t>
@@ -780,42 +834,6 @@
     <x:t>61-4-2026-1292-028</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08185</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1297-182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sxdasdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1291-157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasdqwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1295-514</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsdasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08184</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1296-884</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test12</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08181</x:t>
   </x:si>
   <x:si>
@@ -823,15 +841,6 @@
   </x:si>
   <x:si>
     <x:t>tesg213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08182</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1294-405</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sdasqwe</x:t>
   </x:si>
   <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
@@ -6174,19 +6183,19 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H18" s="31">
-        <x:v>46134.4519824769</x:v>
+        <x:v>46126.4716621296</x:v>
       </x:c>
       <x:c r="I18" s="31">
-        <x:v>46134.4543351736</x:v>
+        <x:v>46126.4737503704</x:v>
       </x:c>
       <x:c r="J18" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K18" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L18" s="33">
-        <x:v>46134.4551470833</x:v>
+        <x:v>46126.4748429977</x:v>
       </x:c>
       <x:c r="M18" s="29" t="s">
         <x:v>21</x:v>
@@ -6206,25 +6215,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="29" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G19" s="29" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46126.4798427199</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46126.4809562153</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46126.4814216667</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -6244,25 +6253,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="29" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G20" s="29" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H20" s="31">
-        <x:v>46126.4716621296</x:v>
+        <x:v>46126.4798427199</x:v>
       </x:c>
       <x:c r="I20" s="31">
-        <x:v>46126.4737503704</x:v>
+        <x:v>46126.4809562153</x:v>
       </x:c>
       <x:c r="J20" s="30" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K20" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L20" s="33">
-        <x:v>46126.4748429977</x:v>
+        <x:v>46126.4814216667</x:v>
       </x:c>
       <x:c r="M20" s="29" t="s">
         <x:v>21</x:v>
@@ -6282,10 +6291,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="29" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G21" s="29" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H21" s="31">
         <x:v>46133.0575652778</x:v>
@@ -6294,7 +6303,7 @@
         <x:v>46134.4546264699</x:v>
       </x:c>
       <x:c r="J21" s="30" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K21" s="32" t="n">
         <x:v>361</x:v>
@@ -6320,10 +6329,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="29" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G22" s="29" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H22" s="31">
         <x:v>46133.5419909606</x:v>
@@ -6349,34 +6358,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D23" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="29" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G23" s="29" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H23" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46134.4519824769</x:v>
       </x:c>
       <x:c r="I23" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46134.4543351736</x:v>
       </x:c>
       <x:c r="J23" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K23" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L23" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46134.4551470833</x:v>
       </x:c>
       <x:c r="M23" s="29" t="s">
         <x:v>21</x:v>
@@ -6402,19 +6411,19 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -6440,19 +6449,19 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2374046412</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5224942245</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -6478,19 +6487,19 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2362105324</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5226826273</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -6516,10 +6525,10 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H27" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I27" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J27" s="30" t="s">
         <x:v>100</x:v>
@@ -6528,7 +6537,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -6554,10 +6563,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
         <x:v>30</x:v>
@@ -6566,7 +6575,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -6592,10 +6601,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
         <x:v>105</x:v>
@@ -6604,7 +6613,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -6630,19 +6639,19 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>108</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -6662,25 +6671,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G31" s="29" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="G31" s="29" t="s">
+      <x:c r="H31" s="31">
+        <x:v>46121.4966047917</x:v>
+      </x:c>
+      <x:c r="I31" s="31">
+        <x:v>46121.4974146412</x:v>
+      </x:c>
+      <x:c r="J31" s="30" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="H31" s="31">
-        <x:v>46121.5149441551</x:v>
-      </x:c>
-      <x:c r="I31" s="31">
-        <x:v>46122.2067431944</x:v>
-      </x:c>
-      <x:c r="J31" s="30" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -6700,25 +6709,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F32" s="29" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G32" s="29" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G32" s="29" t="s">
-        <x:v>113</x:v>
-      </x:c>
       <x:c r="H32" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>114</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -6738,25 +6747,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G33" s="29" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H33" s="31">
+        <x:v>46121.5149441551</x:v>
+      </x:c>
+      <x:c r="I33" s="31">
+        <x:v>46122.2067431944</x:v>
+      </x:c>
+      <x:c r="J33" s="30" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="G33" s="29" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="H33" s="31">
-        <x:v>46121.5183984954</x:v>
-      </x:c>
-      <x:c r="I33" s="31">
-        <x:v>46122.2061737153</x:v>
-      </x:c>
-      <x:c r="J33" s="30" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -6776,25 +6785,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F34" s="29" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="G34" s="29" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H34" s="31">
+        <x:v>46121.5178724884</x:v>
+      </x:c>
+      <x:c r="I34" s="31">
+        <x:v>46122.2064690394</x:v>
+      </x:c>
+      <x:c r="J34" s="30" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="G34" s="29" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="H34" s="31">
-        <x:v>46122.1299166204</x:v>
-      </x:c>
-      <x:c r="I34" s="31">
-        <x:v>46122.2059087963</x:v>
-      </x:c>
-      <x:c r="J34" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K34" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -6814,25 +6823,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F35" s="29" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="G35" s="29" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="G35" s="29" t="s">
+      <x:c r="H35" s="31">
+        <x:v>46121.5183984954</x:v>
+      </x:c>
+      <x:c r="I35" s="31">
+        <x:v>46122.2061737153</x:v>
+      </x:c>
+      <x:c r="J35" s="30" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="H35" s="31">
-        <x:v>46122.1996025926</x:v>
-      </x:c>
-      <x:c r="I35" s="31">
-        <x:v>46122.2050823032</x:v>
-      </x:c>
-      <x:c r="J35" s="30" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="K35" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -6852,25 +6861,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F36" s="29" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="G36" s="29" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G36" s="29" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="H36" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -6890,25 +6899,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="G37" s="29" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="G37" s="29" t="s">
+      <x:c r="H37" s="31">
+        <x:v>46122.1996025926</x:v>
+      </x:c>
+      <x:c r="I37" s="31">
+        <x:v>46122.2050823032</x:v>
+      </x:c>
+      <x:c r="J37" s="30" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="H37" s="31">
-        <x:v>46119.8029380671</x:v>
-      </x:c>
-      <x:c r="I37" s="31">
-        <x:v>46120.5237086343</x:v>
-      </x:c>
-      <x:c r="J37" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -6934,19 +6943,19 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K38" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -6966,25 +6975,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F39" s="29" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G39" s="29" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -7004,10 +7013,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H40" s="31">
         <x:v>46119.7297941435</x:v>
@@ -7016,7 +7025,7 @@
         <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
@@ -7042,25 +7051,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>135</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -7086,10 +7095,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
         <x:v>138</x:v>
@@ -7098,7 +7107,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -7124,10 +7133,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
         <x:v>141</x:v>
@@ -7136,7 +7145,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -7162,10 +7171,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
         <x:v>144</x:v>
@@ -7174,7 +7183,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -7200,10 +7209,10 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
         <x:v>147</x:v>
@@ -7212,7 +7221,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -7238,10 +7247,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
         <x:v>150</x:v>
@@ -7250,7 +7259,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -7276,19 +7285,19 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -7308,25 +7317,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="G48" s="29" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>155</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -7352,10 +7361,10 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
         <x:v>158</x:v>
@@ -7364,7 +7373,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -7390,10 +7399,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
         <x:v>161</x:v>
@@ -7402,7 +7411,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -7428,10 +7437,10 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
         <x:v>164</x:v>
@@ -7440,7 +7449,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -7466,10 +7475,10 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
         <x:v>167</x:v>
@@ -7478,7 +7487,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -7504,19 +7513,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -7536,25 +7545,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -7574,25 +7583,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>174</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -7618,19 +7627,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -7650,25 +7659,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>179</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -7694,19 +7703,19 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -7732,19 +7741,19 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>184</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -7764,25 +7773,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G60" s="29" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="G60" s="29" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="H60" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>187</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -7802,25 +7811,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -7840,25 +7849,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>191</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>192</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -7878,25 +7887,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F63" s="29" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G63" s="29" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H63" s="31">
+        <x:v>46124.1518079282</x:v>
+      </x:c>
+      <x:c r="I63" s="31">
+        <x:v>46124.1529164583</x:v>
+      </x:c>
+      <x:c r="J63" s="30" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="G63" s="29" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H63" s="31">
-        <x:v>46124.5490358102</x:v>
-      </x:c>
-      <x:c r="I63" s="31">
-        <x:v>46124.6984689583</x:v>
-      </x:c>
-      <x:c r="J63" s="30" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="K63" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -7916,25 +7925,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F64" s="29" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G64" s="29" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="H64" s="31">
+        <x:v>46122.3767795718</x:v>
+      </x:c>
+      <x:c r="I64" s="31">
+        <x:v>46122.3776183449</x:v>
+      </x:c>
+      <x:c r="J64" s="30" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="G64" s="29" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="H64" s="31">
-        <x:v>46124.6761778356</x:v>
-      </x:c>
-      <x:c r="I64" s="31">
-        <x:v>46124.6772295602</x:v>
-      </x:c>
-      <x:c r="J64" s="30" t="s">
-        <x:v>198</x:v>
       </x:c>
       <x:c r="K64" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -7954,25 +7963,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="29" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G65" s="29" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="H65" s="31">
+        <x:v>46124.5490358102</x:v>
+      </x:c>
+      <x:c r="I65" s="31">
+        <x:v>46124.6984689583</x:v>
+      </x:c>
+      <x:c r="J65" s="30" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="G65" s="29" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H65" s="31">
-        <x:v>46124.6975491551</x:v>
-      </x:c>
-      <x:c r="I65" s="31">
-        <x:v>46124.6983328357</x:v>
-      </x:c>
-      <x:c r="J65" s="30" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="K65" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -7992,25 +8001,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="29" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G66" s="29" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="H66" s="31">
+        <x:v>46124.6761778356</x:v>
+      </x:c>
+      <x:c r="I66" s="31">
+        <x:v>46124.6772295602</x:v>
+      </x:c>
+      <x:c r="J66" s="30" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="G66" s="29" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="H66" s="31">
-        <x:v>46124.150742662</x:v>
-      </x:c>
-      <x:c r="I66" s="31">
-        <x:v>46124.153253125</x:v>
-      </x:c>
-      <x:c r="J66" s="30" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K66" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -8030,25 +8039,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F67" s="29" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G67" s="29" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="G67" s="29" t="s">
+      <x:c r="H67" s="31">
+        <x:v>46124.1487218981</x:v>
+      </x:c>
+      <x:c r="I67" s="31">
+        <x:v>46124.1494313773</x:v>
+      </x:c>
+      <x:c r="J67" s="30" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="H67" s="31">
-        <x:v>46124.701771875</x:v>
-      </x:c>
-      <x:c r="I67" s="31">
-        <x:v>46124.7049218519</x:v>
-      </x:c>
-      <x:c r="J67" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K67" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -8074,10 +8083,10 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
         <x:v>208</x:v>
@@ -8086,7 +8095,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -8112,10 +8121,10 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
         <x:v>211</x:v>
@@ -8124,7 +8133,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -8150,19 +8159,19 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K70" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -8182,25 +8191,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F71" s="29" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="G71" s="29" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="K71" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -8220,25 +8229,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F72" s="29" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G72" s="29" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -8258,16 +8267,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
         <x:v>30</x:v>
@@ -8276,7 +8285,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -8296,25 +8305,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
-        <x:v>222</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K74" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -8334,25 +8343,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>225</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -8378,19 +8387,19 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -8416,19 +8425,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>230</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -8448,25 +8457,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G78" s="29" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="G78" s="29" t="s">
+      <x:c r="H78" s="31">
+        <x:v>46123.4191184375</x:v>
+      </x:c>
+      <x:c r="I78" s="31">
+        <x:v>46123.4205974074</x:v>
+      </x:c>
+      <x:c r="J78" s="30" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="H78" s="31">
-        <x:v>46122.3974322338</x:v>
-      </x:c>
-      <x:c r="I78" s="31">
-        <x:v>46122.3980999421</x:v>
-      </x:c>
-      <x:c r="J78" s="30" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -8492,19 +8501,19 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>235</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -8524,25 +8533,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G80" s="29" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="G80" s="29" t="s">
+      <x:c r="H80" s="31">
+        <x:v>46118.3446055671</x:v>
+      </x:c>
+      <x:c r="I80" s="31">
+        <x:v>46118.476906412</x:v>
+      </x:c>
+      <x:c r="J80" s="30" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="H80" s="31">
-        <x:v>46122.5623107755</x:v>
-      </x:c>
-      <x:c r="I80" s="31">
-        <x:v>46122.5630093981</x:v>
-      </x:c>
-      <x:c r="J80" s="30" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -8568,19 +8577,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="K81" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -8600,25 +8609,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F82" s="29" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G82" s="29" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K82" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -8638,25 +8647,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F83" s="29" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="G83" s="29" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
-        <x:v>90</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="K83" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -8676,16 +8685,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="29" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="G84" s="29" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
         <x:v>30</x:v>
@@ -8694,7 +8703,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -8714,25 +8723,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>248</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -8752,25 +8761,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.7261372338</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.727234375</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.7277720023</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -8790,25 +8799,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -8828,25 +8837,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F88" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="G88" s="29" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K88" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -8866,25 +8875,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F89" s="29" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="G89" s="29" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46123.061368912</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46123.0623472106</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>259</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46123.0628773958</x:v>
+        <x:v>46122.6809879398</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -8904,25 +8913,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="G90" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46123.0476912847</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46123.0484775694</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46123.049084375</x:v>
       </x:c>
       <x:c r="M90" s="29" t="s">
         <x:v>21</x:v>
@@ -8942,25 +8951,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F91" s="29" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G91" s="29" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="H91" s="31">
-        <x:v>46122.9452935995</x:v>
+        <x:v>46123.061368912</x:v>
       </x:c>
       <x:c r="I91" s="31">
-        <x:v>46123.0460683681</x:v>
+        <x:v>46123.0623472106</x:v>
       </x:c>
       <x:c r="J91" s="30" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="K91" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L91" s="33">
-        <x:v>46123.0466478819</x:v>
+        <x:v>46123.0628773958</x:v>
       </x:c>
       <x:c r="M91" s="29" t="s">
         <x:v>21</x:v>
@@ -8980,25 +8989,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F92" s="29" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="G92" s="29" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="H92" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.7261372338</x:v>
       </x:c>
       <x:c r="I92" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.727234375</x:v>
       </x:c>
       <x:c r="J92" s="30" t="s">
-        <x:v>268</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K92" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L92" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.7277720023</x:v>
       </x:c>
       <x:c r="M92" s="29" t="s">
         <x:v>21</x:v>
@@ -9006,10 +9015,10 @@
     </x:row>
     <x:row r="93" spans="1:28" ht="30" customHeight="1">
       <x:c r="B93" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C93" s="29" t="s">
-        <x:v>270</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D93" s="30" t="s">
         <x:v>16</x:v>
@@ -9018,25 +9027,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F93" s="29" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="G93" s="29" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="H93" s="31">
+        <x:v>46122.9452935995</x:v>
+      </x:c>
+      <x:c r="I93" s="31">
+        <x:v>46123.0460683681</x:v>
+      </x:c>
+      <x:c r="J93" s="30" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="G93" s="29" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="H93" s="31">
-        <x:v>46118.5788871875</x:v>
-      </x:c>
-      <x:c r="I93" s="31">
-        <x:v>46118.5789284722</x:v>
-      </x:c>
-      <x:c r="J93" s="30" t="s">
-        <x:v>273</x:v>
-      </x:c>
       <x:c r="K93" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L93" s="33">
-        <x:v>46118.5806122685</x:v>
+        <x:v>46123.0466478819</x:v>
       </x:c>
       <x:c r="M93" s="29" t="s">
         <x:v>21</x:v>
@@ -9044,10 +9053,10 @@
     </x:row>
     <x:row r="94" spans="1:28" ht="30" customHeight="1">
       <x:c r="B94" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C94" s="29" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="D94" s="30" t="s">
         <x:v>16</x:v>
@@ -9056,25 +9065,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F94" s="29" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G94" s="29" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="G94" s="29" t="s">
+      <x:c r="H94" s="31">
+        <x:v>46118.5788871875</x:v>
+      </x:c>
+      <x:c r="I94" s="31">
+        <x:v>46118.5789284722</x:v>
+      </x:c>
+      <x:c r="J94" s="30" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="H94" s="31">
-        <x:v>46118.6064654514</x:v>
-      </x:c>
-      <x:c r="I94" s="31">
-        <x:v>46118.6065117477</x:v>
-      </x:c>
-      <x:c r="J94" s="30" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="K94" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L94" s="33">
-        <x:v>46118.6077792245</x:v>
+        <x:v>46118.5806122685</x:v>
       </x:c>
       <x:c r="M94" s="29" t="s">
         <x:v>21</x:v>
@@ -9082,7 +9091,7 @@
     </x:row>
     <x:row r="95" spans="1:28" ht="30" customHeight="1">
       <x:c r="B95" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C95" s="29" t="s">
         <x:v>277</x:v>
@@ -9100,19 +9109,19 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="H95" s="31">
-        <x:v>46118.7029973032</x:v>
+        <x:v>46118.6064654514</x:v>
       </x:c>
       <x:c r="I95" s="31">
-        <x:v>46118.7030397569</x:v>
+        <x:v>46118.6065117477</x:v>
       </x:c>
       <x:c r="J95" s="30" t="s">
-        <x:v>280</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K95" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L95" s="33">
-        <x:v>46118.7054991898</x:v>
+        <x:v>46118.6077792245</x:v>
       </x:c>
       <x:c r="M95" s="29" t="s">
         <x:v>21</x:v>
@@ -9120,10 +9129,10 @@
     </x:row>
     <x:row r="96" spans="1:28" ht="30" customHeight="1">
       <x:c r="B96" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C96" s="29" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D96" s="30" t="s">
         <x:v>16</x:v>
@@ -9132,25 +9141,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F96" s="29" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G96" s="29" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="G96" s="29" t="s">
+      <x:c r="H96" s="31">
+        <x:v>46118.7029973032</x:v>
+      </x:c>
+      <x:c r="I96" s="31">
+        <x:v>46118.7030397569</x:v>
+      </x:c>
+      <x:c r="J96" s="30" t="s">
         <x:v>283</x:v>
-      </x:c>
-      <x:c r="H96" s="31">
-        <x:v>46118.7372774306</x:v>
-      </x:c>
-      <x:c r="I96" s="31">
-        <x:v>46118.7373236806</x:v>
-      </x:c>
-      <x:c r="J96" s="30" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="K96" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L96" s="33">
-        <x:v>46118.7388858565</x:v>
+        <x:v>46118.7054991898</x:v>
       </x:c>
       <x:c r="M96" s="29" t="s">
         <x:v>21</x:v>
@@ -9158,10 +9167,10 @@
     </x:row>
     <x:row r="97" spans="1:28" ht="30" customHeight="1">
       <x:c r="B97" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C97" s="29" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="D97" s="30" t="s">
         <x:v>16</x:v>
@@ -9170,25 +9179,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F97" s="29" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G97" s="29" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="G97" s="29" t="s">
+      <x:c r="H97" s="31">
+        <x:v>46118.7372774306</x:v>
+      </x:c>
+      <x:c r="I97" s="31">
+        <x:v>46118.7373236806</x:v>
+      </x:c>
+      <x:c r="J97" s="30" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="H97" s="31">
-        <x:v>46118.6471475926</x:v>
-      </x:c>
-      <x:c r="I97" s="31">
-        <x:v>46118.647188044</x:v>
-      </x:c>
-      <x:c r="J97" s="30" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K97" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L97" s="33">
-        <x:v>46118.6489296181</x:v>
+        <x:v>46118.7388858565</x:v>
       </x:c>
       <x:c r="M97" s="29" t="s">
         <x:v>21</x:v>
@@ -9196,37 +9205,37 @@
     </x:row>
     <x:row r="98" spans="1:28" ht="30" customHeight="1">
       <x:c r="B98" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C98" s="29" t="s">
-        <x:v>46</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D98" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E98" s="29" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F98" s="29" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="G98" s="29" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="H98" s="31">
-        <x:v>46132.3798789699</x:v>
+        <x:v>46118.6471475926</x:v>
       </x:c>
       <x:c r="I98" s="31">
-        <x:v>46132.3799006944</x:v>
+        <x:v>46118.647188044</x:v>
       </x:c>
       <x:c r="J98" s="30" t="s">
-        <x:v>290</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K98" s="32" t="n">
-        <x:v>3031</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L98" s="33">
-        <x:v>46133.1738098148</x:v>
+        <x:v>46118.6489296181</x:v>
       </x:c>
       <x:c r="M98" s="29" t="s">
         <x:v>21</x:v>
@@ -9234,37 +9243,37 @@
     </x:row>
     <x:row r="99" spans="1:28" ht="30" customHeight="1">
       <x:c r="B99" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C99" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D99" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E99" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F99" s="29" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G99" s="29" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="G99" s="29" t="s">
+      <x:c r="H99" s="31">
+        <x:v>46132.3798789699</x:v>
+      </x:c>
+      <x:c r="I99" s="31">
+        <x:v>46132.3799006944</x:v>
+      </x:c>
+      <x:c r="J99" s="30" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="H99" s="31">
-        <x:v>46118.7761679514</x:v>
-      </x:c>
-      <x:c r="I99" s="31">
-        <x:v>46118.7762103819</x:v>
-      </x:c>
-      <x:c r="J99" s="30" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="K99" s="32" t="n">
-        <x:v>3530</x:v>
+        <x:v>3031</x:v>
       </x:c>
       <x:c r="L99" s="33">
-        <x:v>46118.7774822107</x:v>
+        <x:v>46133.1738098148</x:v>
       </x:c>
       <x:c r="M99" s="29" t="s">
         <x:v>21</x:v>
@@ -9272,10 +9281,10 @@
     </x:row>
     <x:row r="100" spans="1:28" ht="30" customHeight="1">
       <x:c r="B100" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C100" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D100" s="30" t="s">
         <x:v>16</x:v>
@@ -9284,25 +9293,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F100" s="29" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="G100" s="29" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="H100" s="31">
-        <x:v>46118.439490081</x:v>
+        <x:v>46118.7761679514</x:v>
       </x:c>
       <x:c r="I100" s="31">
-        <x:v>46118.4395309375</x:v>
+        <x:v>46118.7762103819</x:v>
       </x:c>
       <x:c r="J100" s="30" t="s">
-        <x:v>296</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K100" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L100" s="33">
-        <x:v>46118.4416909375</x:v>
+        <x:v>46118.7774822107</x:v>
       </x:c>
       <x:c r="M100" s="29" t="s">
         <x:v>21</x:v>
@@ -9310,10 +9319,10 @@
     </x:row>
     <x:row r="101" spans="1:28" ht="30" customHeight="1">
       <x:c r="B101" s="29" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C101" s="29" t="s">
-        <x:v>50</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="D101" s="30" t="s">
         <x:v>16</x:v>
@@ -9328,19 +9337,19 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="H101" s="31">
-        <x:v>46119.4833706713</x:v>
+        <x:v>46118.439490081</x:v>
       </x:c>
       <x:c r="I101" s="31">
-        <x:v>46119.4833991435</x:v>
+        <x:v>46118.4395309375</x:v>
       </x:c>
       <x:c r="J101" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="K101" s="32" t="n">
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L101" s="33">
-        <x:v>46119.4846717477</x:v>
+        <x:v>46118.4416909375</x:v>
       </x:c>
       <x:c r="M101" s="29" t="s">
         <x:v>21</x:v>
@@ -9348,37 +9357,37 @@
     </x:row>
     <x:row r="102" spans="1:28" ht="30" customHeight="1">
       <x:c r="B102" s="29" t="s">
-        <x:v>299</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C102" s="29" t="s">
-        <x:v>291</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D102" s="30" t="s">
-        <x:v>41</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E102" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F102" s="29" t="s">
-        <x:v>270</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G102" s="29" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="H102" s="31">
-        <x:v>46132.3879904745</x:v>
+        <x:v>46119.4833706713</x:v>
       </x:c>
       <x:c r="I102" s="31">
-        <x:v>46023</x:v>
+        <x:v>46119.4833991435</x:v>
       </x:c>
       <x:c r="J102" s="30" t="s">
-        <x:v>301</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K102" s="32" t="n">
-        <x:v>5281</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L102" s="33">
-        <x:v>46132.4226006481</x:v>
+        <x:v>46119.4846717477</x:v>
       </x:c>
       <x:c r="M102" s="29" t="s">
         <x:v>21</x:v>
@@ -9389,32 +9398,34 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="C103" s="29" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="D103" s="30" t="s"/>
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D103" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="E103" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F103" s="29" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G103" s="29" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H103" s="31">
+        <x:v>46132.3879904745</x:v>
+      </x:c>
+      <x:c r="I103" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J103" s="30" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="G103" s="29" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="H103" s="31">
-        <x:v>46124.1588481829</x:v>
-      </x:c>
-      <x:c r="I103" s="31">
-        <x:v>46124.1588689236</x:v>
-      </x:c>
-      <x:c r="J103" s="30" t="s">
-        <x:v>306</x:v>
-      </x:c>
       <x:c r="K103" s="32" t="n">
-        <x:v>5070</x:v>
+        <x:v>5281</x:v>
       </x:c>
       <x:c r="L103" s="33">
-        <x:v>46124.1622106481</x:v>
+        <x:v>46132.4226006481</x:v>
       </x:c>
       <x:c r="M103" s="29" t="s">
         <x:v>21</x:v>
@@ -9422,117 +9433,142 @@
     </x:row>
     <x:row r="104" spans="1:28" ht="30" customHeight="1">
       <x:c r="B104" s="29" t="s">
-        <x:v>307</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C104" s="29" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="D104" s="30" t="s">
-        <x:v>41</x:v>
-      </x:c>
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="D104" s="30" t="s"/>
       <x:c r="E104" s="29" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="F104" s="29" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G104" s="29" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="H104" s="31">
+        <x:v>46124.1588481829</x:v>
+      </x:c>
+      <x:c r="I104" s="31">
+        <x:v>46124.1588689236</x:v>
+      </x:c>
+      <x:c r="J104" s="30" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="G104" s="29" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="H104" s="31">
-        <x:v>46124.1607868981</x:v>
-      </x:c>
-      <x:c r="I104" s="31">
-        <x:v>46023</x:v>
-      </x:c>
-      <x:c r="J104" s="30" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="K104" s="32" t="n">
-        <x:v>3100</x:v>
+        <x:v>5070</x:v>
       </x:c>
       <x:c r="L104" s="33">
-        <x:v>46124.1624131829</x:v>
+        <x:v>46124.1622106481</x:v>
       </x:c>
       <x:c r="M104" s="29" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B105" s="29" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="C105" s="29" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="D105" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E105" s="29" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F105" s="29" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="G105" s="29" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="H105" s="31">
+        <x:v>46124.1607868981</x:v>
+      </x:c>
+      <x:c r="I105" s="31">
+        <x:v>46023</x:v>
+      </x:c>
+      <x:c r="J105" s="30" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="K105" s="32" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="L105" s="33">
+        <x:v>46124.1624131829</x:v>
+      </x:c>
+      <x:c r="M105" s="29" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="107" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B107" s="17" t="s">
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B108" s="17" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C107" s="18" t="s"/>
-      <x:c r="D107" s="18" t="s"/>
-      <x:c r="E107" s="19" t="s"/>
-      <x:c r="F107" s="19" t="s"/>
-    </x:row>
-    <x:row r="108" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B108" s="20" t="s">
+      <x:c r="C108" s="18" t="s"/>
+      <x:c r="D108" s="18" t="s"/>
+      <x:c r="E108" s="19" t="s"/>
+      <x:c r="F108" s="19" t="s"/>
+    </x:row>
+    <x:row r="109" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B109" s="20" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C108" s="21" t="s"/>
-      <x:c r="D108" s="21" t="s"/>
-      <x:c r="E108" s="21" t="s"/>
-      <x:c r="F108" s="22" t="s">
+      <x:c r="C109" s="21" t="s"/>
+      <x:c r="D109" s="21" t="s"/>
+      <x:c r="E109" s="21" t="s"/>
+      <x:c r="F109" s="22" t="s">
         <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B109" s="23" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C109" s="24" t="s"/>
-      <x:c r="D109" s="24" t="s"/>
-      <x:c r="E109" s="24" t="s"/>
-      <x:c r="F109" s="25" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:28" ht="18" customHeight="1">
       <x:c r="B110" s="23" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C110" s="24" t="s"/>
       <x:c r="D110" s="24" t="s"/>
       <x:c r="E110" s="24" t="s"/>
       <x:c r="F110" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:28" ht="18" customHeight="1">
       <x:c r="B111" s="23" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C111" s="24" t="s"/>
       <x:c r="D111" s="24" t="s"/>
       <x:c r="E111" s="24" t="s"/>
       <x:c r="F111" s="25" t="n">
-        <x:v>82</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:28" ht="18" customHeight="1">
       <x:c r="B112" s="23" t="s">
-        <x:v>269</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C112" s="24" t="s"/>
       <x:c r="D112" s="24" t="s"/>
       <x:c r="E112" s="24" t="s"/>
       <x:c r="F112" s="25" t="n">
-        <x:v>9</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:28" ht="18" customHeight="1">
       <x:c r="B113" s="23" t="s">
-        <x:v>299</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C113" s="24" t="s"/>
       <x:c r="D113" s="24" t="s"/>
       <x:c r="E113" s="24" t="s"/>
       <x:c r="F113" s="25" t="n">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:28" ht="18" customHeight="1">
@@ -9548,7 +9584,7 @@
     </x:row>
     <x:row r="115" spans="1:28" ht="18" customHeight="1">
       <x:c r="B115" s="23" t="s">
-        <x:v>307</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C115" s="24" t="s"/>
       <x:c r="D115" s="24" t="s"/>
@@ -9557,18 +9593,28 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B116" s="26" t="s">
+    <x:row r="116" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B116" s="23" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="C116" s="24" t="s"/>
+      <x:c r="D116" s="24" t="s"/>
+      <x:c r="E116" s="24" t="s"/>
+      <x:c r="F116" s="25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B117" s="26" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C116" s="27" t="s"/>
-      <x:c r="D116" s="27" t="s"/>
-      <x:c r="E116" s="27" t="s"/>
-      <x:c r="F116" s="28" t="n">
-        <x:v>97</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C117" s="27" t="s"/>
+      <x:c r="D117" s="27" t="s"/>
+      <x:c r="E117" s="27" t="s"/>
+      <x:c r="F117" s="28" t="n">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
     <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
@@ -10451,8 +10497,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B107:F107"/>
-    <x:mergeCell ref="B108:E108"/>
+    <x:mergeCell ref="B108:F108"/>
     <x:mergeCell ref="B109:E109"/>
     <x:mergeCell ref="B110:E110"/>
     <x:mergeCell ref="B111:E111"/>
@@ -10461,6 +10506,7 @@
     <x:mergeCell ref="B114:E114"/>
     <x:mergeCell ref="B115:E115"/>
     <x:mergeCell ref="B116:E116"/>
+    <x:mergeCell ref="B117:E117"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
+++ b/reports/service-tracking-report-EVALUATOR-EDGE-evaluator-cache-serviceTracking-EVALUATOR-EDGE-XIV-202501-202612.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="315">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="318">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -261,6 +261,45 @@
     <x:t>123qweasd</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1354-199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>edwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1328-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aszxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08635</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1345-593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1346-976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08729</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1347-280</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08756</x:t>
   </x:si>
   <x:si>
@@ -270,36 +309,6 @@
     <x:t>1555</x:t>
   </x:si>
   <x:si>
-    <x:t>26-1RTG-XIV-08340</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1328-100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>aszxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1345-593</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08682</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1346-976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08729</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1347-280</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-XIV-08344</x:t>
   </x:si>
   <x:si>
@@ -423,142 +432,142 @@
     <x:t>61-4-2026-1252-337</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1248-677</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcasdqwezxc</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08098</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1249-913</x:t>
   </x:si>
   <x:si>
+    <x:t>26-1RTG-XIV-08033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1222-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123437</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1231-932</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wqeasdzxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1232-155</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zxcasdqweq2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1234-926</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123qwe123qwe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1235-550</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123wezxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08082</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1237-114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdqwe123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1238-244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08089</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1240-813</x:t>
+  </x:si>
+  <x:si>
+    <x:t>xzczxcasd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08091</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1242-068</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zdd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1243-710</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zsd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1244-026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zcx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08094</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1245-872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zczxc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1246-201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-XIV-08096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1247-499</x:t>
+  </x:si>
+  <x:si>
     <x:t>26-1RTG-XIV-08160</x:t>
   </x:si>
   <x:si>
     <x:t>61-4-2026-1279-279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1222-213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123437</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1231-932</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wqeasdzxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08044</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1232-155</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zxcasdqweq2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1234-926</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123qwe123qwe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1235-550</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123wezxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08082</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1237-114</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdqwe123</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1238-244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08089</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1240-813</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xzczxcasd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08091</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1242-068</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zdd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08092</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1243-710</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zsd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1244-026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08094</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1245-872</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zczxc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08095</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1246-201</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08096</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1247-499</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26-1RTG-XIV-08097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1248-677</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zcasdqwezxc</x:t>
   </x:si>
   <x:si>
     <x:t>26-1RTG-XIV-08100</x:t>
@@ -6221,19 +6230,19 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="H19" s="31">
-        <x:v>46134.9871842824</x:v>
+        <x:v>46139.4236006019</x:v>
       </x:c>
       <x:c r="I19" s="31">
-        <x:v>46135.0270460764</x:v>
+        <x:v>46139.424377581</x:v>
       </x:c>
       <x:c r="J19" s="30" t="s">
         <x:v>80</x:v>
       </x:c>
       <x:c r="K19" s="32" t="n">
-        <x:v>270</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L19" s="33">
-        <x:v>46135.0715283333</x:v>
+        <x:v>46139.4248658449</x:v>
       </x:c>
       <x:c r="M19" s="29" t="s">
         <x:v>21</x:v>
@@ -6396,13 +6405,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="29" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D24" s="30" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="29" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F24" s="29" t="s">
         <x:v>91</x:v>
@@ -6411,19 +6420,19 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H24" s="31">
-        <x:v>46126.5341923727</x:v>
+        <x:v>46134.9871842824</x:v>
       </x:c>
       <x:c r="I24" s="31">
-        <x:v>46126.5348242708</x:v>
+        <x:v>46135.0270460764</x:v>
       </x:c>
       <x:c r="J24" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K24" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L24" s="33">
-        <x:v>46126.5353594213</x:v>
+        <x:v>46135.0715283333</x:v>
       </x:c>
       <x:c r="M24" s="29" t="s">
         <x:v>21</x:v>
@@ -6443,25 +6452,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F25" s="29" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G25" s="29" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="31">
-        <x:v>46120.2349196412</x:v>
+        <x:v>46126.5341923727</x:v>
       </x:c>
       <x:c r="I25" s="31">
-        <x:v>46120.5229746296</x:v>
+        <x:v>46126.5348242708</x:v>
       </x:c>
       <x:c r="J25" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K25" s="32" t="n">
-        <x:v>0</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L25" s="33">
-        <x:v>46120.5255047106</x:v>
+        <x:v>46126.5353594213</x:v>
       </x:c>
       <x:c r="M25" s="29" t="s">
         <x:v>21</x:v>
@@ -6487,19 +6496,19 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H26" s="31">
-        <x:v>46120.2362105324</x:v>
+        <x:v>46120.2349196412</x:v>
       </x:c>
       <x:c r="I26" s="31">
-        <x:v>46120.5226826273</x:v>
+        <x:v>46120.5229746296</x:v>
       </x:c>
       <x:c r="J26" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K26" s="32" t="n">
-        <x:v>210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L26" s="33">
-        <x:v>46120.5252627315</x:v>
+        <x:v>46120.5255047106</x:v>
       </x:c>
       <x:c r="M26" s="29" t="s">
         <x:v>21</x:v>
@@ -6519,25 +6528,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F27" s="29" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H27" s="31">
+        <x:v>46120.2362105324</x:v>
+      </x:c>
+      <x:c r="I27" s="31">
+        <x:v>46120.5226826273</x:v>
+      </x:c>
+      <x:c r="J27" s="30" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="G27" s="29" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H27" s="31">
-        <x:v>46120.2374046412</x:v>
-      </x:c>
-      <x:c r="I27" s="31">
-        <x:v>46120.5224942245</x:v>
-      </x:c>
-      <x:c r="J27" s="30" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="K27" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L27" s="33">
-        <x:v>46120.5250032292</x:v>
+        <x:v>46120.5252627315</x:v>
       </x:c>
       <x:c r="M27" s="29" t="s">
         <x:v>21</x:v>
@@ -6563,19 +6572,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="H28" s="31">
-        <x:v>46120.7129542245</x:v>
+        <x:v>46120.2374046412</x:v>
       </x:c>
       <x:c r="I28" s="31">
-        <x:v>46121.100944213</x:v>
+        <x:v>46120.5224942245</x:v>
       </x:c>
       <x:c r="J28" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K28" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L28" s="33">
-        <x:v>46121.1029720949</x:v>
+        <x:v>46120.5250032292</x:v>
       </x:c>
       <x:c r="M28" s="29" t="s">
         <x:v>21</x:v>
@@ -6595,25 +6604,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F29" s="29" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G29" s="29" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H29" s="31">
-        <x:v>46121.0999663542</x:v>
+        <x:v>46120.7129542245</x:v>
       </x:c>
       <x:c r="I29" s="31">
-        <x:v>46121.1007466204</x:v>
+        <x:v>46121.100944213</x:v>
       </x:c>
       <x:c r="J29" s="30" t="s">
-        <x:v>105</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K29" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L29" s="33">
-        <x:v>46121.1027298958</x:v>
+        <x:v>46121.1029720949</x:v>
       </x:c>
       <x:c r="M29" s="29" t="s">
         <x:v>21</x:v>
@@ -6639,19 +6648,19 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="H30" s="31">
-        <x:v>46121.2273626852</x:v>
+        <x:v>46121.0999663542</x:v>
       </x:c>
       <x:c r="I30" s="31">
-        <x:v>46121.228379213</x:v>
+        <x:v>46121.1007466204</x:v>
       </x:c>
       <x:c r="J30" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K30" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L30" s="33">
-        <x:v>46121.2291153125</x:v>
+        <x:v>46121.1027298958</x:v>
       </x:c>
       <x:c r="M30" s="29" t="s">
         <x:v>21</x:v>
@@ -6671,25 +6680,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F31" s="29" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="G31" s="29" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H31" s="31">
-        <x:v>46121.4966047917</x:v>
+        <x:v>46121.2273626852</x:v>
       </x:c>
       <x:c r="I31" s="31">
-        <x:v>46121.4974146412</x:v>
+        <x:v>46121.228379213</x:v>
       </x:c>
       <x:c r="J31" s="30" t="s">
-        <x:v>110</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K31" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L31" s="33">
-        <x:v>46121.4980146875</x:v>
+        <x:v>46121.2291153125</x:v>
       </x:c>
       <x:c r="M31" s="29" t="s">
         <x:v>21</x:v>
@@ -6715,19 +6724,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H32" s="31">
-        <x:v>46119.8029380671</x:v>
+        <x:v>46121.4966047917</x:v>
       </x:c>
       <x:c r="I32" s="31">
-        <x:v>46120.5237086343</x:v>
+        <x:v>46121.4974146412</x:v>
       </x:c>
       <x:c r="J32" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K32" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L32" s="33">
-        <x:v>46120.5257164468</x:v>
+        <x:v>46121.4980146875</x:v>
       </x:c>
       <x:c r="M32" s="29" t="s">
         <x:v>21</x:v>
@@ -6747,25 +6756,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F33" s="29" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G33" s="29" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H33" s="31">
-        <x:v>46121.5149441551</x:v>
+        <x:v>46119.8029380671</x:v>
       </x:c>
       <x:c r="I33" s="31">
-        <x:v>46122.2067431944</x:v>
+        <x:v>46120.5237086343</x:v>
       </x:c>
       <x:c r="J33" s="30" t="s">
-        <x:v>115</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K33" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L33" s="33">
-        <x:v>46122.2310990278</x:v>
+        <x:v>46120.5257164468</x:v>
       </x:c>
       <x:c r="M33" s="29" t="s">
         <x:v>21</x:v>
@@ -6791,10 +6800,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H34" s="31">
-        <x:v>46121.5178724884</x:v>
+        <x:v>46121.5149441551</x:v>
       </x:c>
       <x:c r="I34" s="31">
-        <x:v>46122.2064690394</x:v>
+        <x:v>46122.2067431944</x:v>
       </x:c>
       <x:c r="J34" s="30" t="s">
         <x:v>118</x:v>
@@ -6803,7 +6812,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L34" s="33">
-        <x:v>46122.230922581</x:v>
+        <x:v>46122.2310990278</x:v>
       </x:c>
       <x:c r="M34" s="29" t="s">
         <x:v>21</x:v>
@@ -6829,10 +6838,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="H35" s="31">
-        <x:v>46121.5183984954</x:v>
+        <x:v>46121.5178724884</x:v>
       </x:c>
       <x:c r="I35" s="31">
-        <x:v>46122.2061737153</x:v>
+        <x:v>46122.2064690394</x:v>
       </x:c>
       <x:c r="J35" s="30" t="s">
         <x:v>121</x:v>
@@ -6841,7 +6850,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L35" s="33">
-        <x:v>46122.2307100926</x:v>
+        <x:v>46122.230922581</x:v>
       </x:c>
       <x:c r="M35" s="29" t="s">
         <x:v>21</x:v>
@@ -6867,19 +6876,19 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="H36" s="31">
-        <x:v>46122.1299166204</x:v>
+        <x:v>46121.5183984954</x:v>
       </x:c>
       <x:c r="I36" s="31">
-        <x:v>46122.2059087963</x:v>
+        <x:v>46122.2061737153</x:v>
       </x:c>
       <x:c r="J36" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K36" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L36" s="33">
-        <x:v>46122.2086237847</x:v>
+        <x:v>46122.2307100926</x:v>
       </x:c>
       <x:c r="M36" s="29" t="s">
         <x:v>21</x:v>
@@ -6899,25 +6908,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F37" s="29" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G37" s="29" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="H37" s="31">
-        <x:v>46122.1996025926</x:v>
+        <x:v>46122.1299166204</x:v>
       </x:c>
       <x:c r="I37" s="31">
-        <x:v>46122.2050823032</x:v>
+        <x:v>46122.2059087963</x:v>
       </x:c>
       <x:c r="J37" s="30" t="s">
-        <x:v>126</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K37" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L37" s="33">
-        <x:v>46122.2083635185</x:v>
+        <x:v>46122.2086237847</x:v>
       </x:c>
       <x:c r="M37" s="29" t="s">
         <x:v>21</x:v>
@@ -6943,10 +6952,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="H38" s="31">
-        <x:v>46121.2464636111</x:v>
+        <x:v>46122.1996025926</x:v>
       </x:c>
       <x:c r="I38" s="31">
-        <x:v>46121.3217277662</x:v>
+        <x:v>46122.2050823032</x:v>
       </x:c>
       <x:c r="J38" s="30" t="s">
         <x:v>129</x:v>
@@ -6955,7 +6964,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L38" s="33">
-        <x:v>46121.498248206</x:v>
+        <x:v>46122.2083635185</x:v>
       </x:c>
       <x:c r="M38" s="29" t="s">
         <x:v>21</x:v>
@@ -6981,19 +6990,19 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H39" s="31">
-        <x:v>46119.8023724884</x:v>
+        <x:v>46121.2464636111</x:v>
       </x:c>
       <x:c r="I39" s="31">
-        <x:v>46119.8046602662</x:v>
+        <x:v>46121.3217277662</x:v>
       </x:c>
       <x:c r="J39" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K39" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="33">
-        <x:v>46119.8055532407</x:v>
+        <x:v>46121.498248206</x:v>
       </x:c>
       <x:c r="M39" s="29" t="s">
         <x:v>21</x:v>
@@ -7013,25 +7022,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F40" s="29" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G40" s="29" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H40" s="31">
-        <x:v>46119.7297941435</x:v>
+        <x:v>46119.8023724884</x:v>
       </x:c>
       <x:c r="I40" s="31">
-        <x:v>46119.731450544</x:v>
+        <x:v>46119.8046602662</x:v>
       </x:c>
       <x:c r="J40" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K40" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L40" s="33">
-        <x:v>46119.7324832755</x:v>
+        <x:v>46119.8055532407</x:v>
       </x:c>
       <x:c r="M40" s="29" t="s">
         <x:v>21</x:v>
@@ -7051,25 +7060,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F41" s="29" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G41" s="29" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H41" s="31">
-        <x:v>46122.3569147569</x:v>
+        <x:v>46119.729231331</x:v>
       </x:c>
       <x:c r="I41" s="31">
-        <x:v>46122.3577305324</x:v>
+        <x:v>46119.7316308565</x:v>
       </x:c>
       <x:c r="J41" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K41" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="33">
-        <x:v>46122.3582679861</x:v>
+        <x:v>46119.7327704398</x:v>
       </x:c>
       <x:c r="M41" s="29" t="s">
         <x:v>21</x:v>
@@ -7089,25 +7098,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F42" s="29" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G42" s="29" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="H42" s="31">
-        <x:v>46118.4219285995</x:v>
+        <x:v>46119.7297941435</x:v>
       </x:c>
       <x:c r="I42" s="31">
-        <x:v>46118.4229350116</x:v>
+        <x:v>46119.731450544</x:v>
       </x:c>
       <x:c r="J42" s="30" t="s">
-        <x:v>138</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K42" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L42" s="33">
-        <x:v>46118.4241364815</x:v>
+        <x:v>46119.7324832755</x:v>
       </x:c>
       <x:c r="M42" s="29" t="s">
         <x:v>21</x:v>
@@ -7127,25 +7136,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F43" s="29" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="G43" s="29" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H43" s="31">
-        <x:v>46118.7424944097</x:v>
+        <x:v>46118.4219285995</x:v>
       </x:c>
       <x:c r="I43" s="31">
-        <x:v>46118.7432728009</x:v>
+        <x:v>46118.4229350116</x:v>
       </x:c>
       <x:c r="J43" s="30" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K43" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L43" s="33">
-        <x:v>46118.743899213</x:v>
+        <x:v>46118.4241364815</x:v>
       </x:c>
       <x:c r="M43" s="29" t="s">
         <x:v>21</x:v>
@@ -7165,25 +7174,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F44" s="29" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G44" s="29" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="H44" s="31">
-        <x:v>46118.7562945255</x:v>
+        <x:v>46118.7424944097</x:v>
       </x:c>
       <x:c r="I44" s="31">
-        <x:v>46118.7571720255</x:v>
+        <x:v>46118.7432728009</x:v>
       </x:c>
       <x:c r="J44" s="30" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="K44" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L44" s="33">
-        <x:v>46118.7577859143</x:v>
+        <x:v>46118.743899213</x:v>
       </x:c>
       <x:c r="M44" s="29" t="s">
         <x:v>21</x:v>
@@ -7203,25 +7212,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F45" s="29" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G45" s="29" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H45" s="31">
-        <x:v>46119.0668949653</x:v>
+        <x:v>46118.7562945255</x:v>
       </x:c>
       <x:c r="I45" s="31">
-        <x:v>46119.0755180324</x:v>
+        <x:v>46118.7571720255</x:v>
       </x:c>
       <x:c r="J45" s="30" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="K45" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L45" s="33">
-        <x:v>46119.076169375</x:v>
+        <x:v>46118.7577859143</x:v>
       </x:c>
       <x:c r="M45" s="29" t="s">
         <x:v>21</x:v>
@@ -7241,25 +7250,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F46" s="29" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="G46" s="29" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H46" s="31">
-        <x:v>46119.0739296412</x:v>
+        <x:v>46119.0668949653</x:v>
       </x:c>
       <x:c r="I46" s="31">
-        <x:v>46119.0753097685</x:v>
+        <x:v>46119.0755180324</x:v>
       </x:c>
       <x:c r="J46" s="30" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="K46" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L46" s="33">
-        <x:v>46119.0764109954</x:v>
+        <x:v>46119.076169375</x:v>
       </x:c>
       <x:c r="M46" s="29" t="s">
         <x:v>21</x:v>
@@ -7279,25 +7288,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F47" s="29" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G47" s="29" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H47" s="31">
-        <x:v>46119.1921340856</x:v>
+        <x:v>46119.0739296412</x:v>
       </x:c>
       <x:c r="I47" s="31">
-        <x:v>46119.1932160417</x:v>
+        <x:v>46119.0753097685</x:v>
       </x:c>
       <x:c r="J47" s="30" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K47" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L47" s="33">
-        <x:v>46119.193627581</x:v>
+        <x:v>46119.0764109954</x:v>
       </x:c>
       <x:c r="M47" s="29" t="s">
         <x:v>21</x:v>
@@ -7317,25 +7326,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F48" s="29" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G48" s="29" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="H48" s="31">
-        <x:v>46119.4681336458</x:v>
+        <x:v>46119.1921340856</x:v>
       </x:c>
       <x:c r="I48" s="31">
-        <x:v>46119.4697068056</x:v>
+        <x:v>46119.1932160417</x:v>
       </x:c>
       <x:c r="J48" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K48" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L48" s="33">
-        <x:v>46119.470392037</x:v>
+        <x:v>46119.193627581</x:v>
       </x:c>
       <x:c r="M48" s="29" t="s">
         <x:v>21</x:v>
@@ -7355,25 +7364,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F49" s="29" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G49" s="29" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H49" s="31">
-        <x:v>46119.5267212153</x:v>
+        <x:v>46119.4681336458</x:v>
       </x:c>
       <x:c r="I49" s="31">
-        <x:v>46119.5274664236</x:v>
+        <x:v>46119.4697068056</x:v>
       </x:c>
       <x:c r="J49" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K49" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L49" s="33">
-        <x:v>46119.5279398495</x:v>
+        <x:v>46119.470392037</x:v>
       </x:c>
       <x:c r="M49" s="29" t="s">
         <x:v>21</x:v>
@@ -7393,25 +7402,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F50" s="29" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="G50" s="29" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="H50" s="31">
-        <x:v>46119.5424612384</x:v>
+        <x:v>46119.5267212153</x:v>
       </x:c>
       <x:c r="I50" s="31">
-        <x:v>46119.5457934491</x:v>
+        <x:v>46119.5274664236</x:v>
       </x:c>
       <x:c r="J50" s="30" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K50" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L50" s="33">
-        <x:v>46119.5465567708</x:v>
+        <x:v>46119.5279398495</x:v>
       </x:c>
       <x:c r="M50" s="29" t="s">
         <x:v>21</x:v>
@@ -7431,25 +7440,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="29" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G51" s="29" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="H51" s="31">
-        <x:v>46119.542956794</x:v>
+        <x:v>46119.5424612384</x:v>
       </x:c>
       <x:c r="I51" s="31">
-        <x:v>46119.5456356481</x:v>
+        <x:v>46119.5457934491</x:v>
       </x:c>
       <x:c r="J51" s="30" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K51" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L51" s="33">
-        <x:v>46119.5477968982</x:v>
+        <x:v>46119.5465567708</x:v>
       </x:c>
       <x:c r="M51" s="29" t="s">
         <x:v>21</x:v>
@@ -7469,25 +7478,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F52" s="29" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G52" s="29" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H52" s="31">
-        <x:v>46119.5434206134</x:v>
+        <x:v>46119.542956794</x:v>
       </x:c>
       <x:c r="I52" s="31">
-        <x:v>46119.545474919</x:v>
+        <x:v>46119.5456356481</x:v>
       </x:c>
       <x:c r="J52" s="30" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="K52" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L52" s="33">
-        <x:v>46119.5469447569</x:v>
+        <x:v>46119.5477968982</x:v>
       </x:c>
       <x:c r="M52" s="29" t="s">
         <x:v>21</x:v>
@@ -7507,25 +7516,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F53" s="29" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G53" s="29" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="H53" s="31">
-        <x:v>46119.5439653357</x:v>
+        <x:v>46119.5434206134</x:v>
       </x:c>
       <x:c r="I53" s="31">
-        <x:v>46119.5452984143</x:v>
+        <x:v>46119.545474919</x:v>
       </x:c>
       <x:c r="J53" s="30" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="K53" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L53" s="33">
-        <x:v>46119.5467543982</x:v>
+        <x:v>46119.5469447569</x:v>
       </x:c>
       <x:c r="M53" s="29" t="s">
         <x:v>21</x:v>
@@ -7545,25 +7554,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="29" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G54" s="29" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H54" s="31">
-        <x:v>46119.7254171991</x:v>
+        <x:v>46119.5439653357</x:v>
       </x:c>
       <x:c r="I54" s="31">
-        <x:v>46119.7262936574</x:v>
+        <x:v>46119.5452984143</x:v>
       </x:c>
       <x:c r="J54" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="K54" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L54" s="33">
-        <x:v>46119.7267657407</x:v>
+        <x:v>46119.5467543982</x:v>
       </x:c>
       <x:c r="M54" s="29" t="s">
         <x:v>21</x:v>
@@ -7583,25 +7592,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F55" s="29" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G55" s="29" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="H55" s="31">
-        <x:v>46119.7285584838</x:v>
+        <x:v>46119.7254171991</x:v>
       </x:c>
       <x:c r="I55" s="31">
-        <x:v>46119.7318005208</x:v>
+        <x:v>46119.7262936574</x:v>
       </x:c>
       <x:c r="J55" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K55" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L55" s="33">
-        <x:v>46119.7339888773</x:v>
+        <x:v>46119.7267657407</x:v>
       </x:c>
       <x:c r="M55" s="29" t="s">
         <x:v>21</x:v>
@@ -7621,25 +7630,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F56" s="29" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="G56" s="29" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H56" s="31">
-        <x:v>46119.729231331</x:v>
+        <x:v>46119.7285584838</x:v>
       </x:c>
       <x:c r="I56" s="31">
-        <x:v>46119.7316308565</x:v>
+        <x:v>46119.7318005208</x:v>
       </x:c>
       <x:c r="J56" s="30" t="s">
-        <x:v>177</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K56" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L56" s="33">
-        <x:v>46119.7327704398</x:v>
+        <x:v>46119.7339888773</x:v>
       </x:c>
       <x:c r="M56" s="29" t="s">
         <x:v>21</x:v>
@@ -7659,25 +7668,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F57" s="29" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="G57" s="29" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="H57" s="31">
-        <x:v>46119.8017436343</x:v>
+        <x:v>46122.3569147569</x:v>
       </x:c>
       <x:c r="I57" s="31">
-        <x:v>46119.8048384144</x:v>
+        <x:v>46122.3577305324</x:v>
       </x:c>
       <x:c r="J57" s="30" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K57" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L57" s="33">
-        <x:v>46119.8080510417</x:v>
+        <x:v>46122.3582679861</x:v>
       </x:c>
       <x:c r="M57" s="29" t="s">
         <x:v>21</x:v>
@@ -7697,25 +7706,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F58" s="29" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G58" s="29" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="H58" s="31">
-        <x:v>46122.36782125</x:v>
+        <x:v>46119.8017436343</x:v>
       </x:c>
       <x:c r="I58" s="31">
-        <x:v>46122.3686719907</x:v>
+        <x:v>46119.8048384144</x:v>
       </x:c>
       <x:c r="J58" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K58" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L58" s="33">
-        <x:v>46122.3692180787</x:v>
+        <x:v>46119.8080510417</x:v>
       </x:c>
       <x:c r="M58" s="29" t="s">
         <x:v>21</x:v>
@@ -7735,25 +7744,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F59" s="29" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G59" s="29" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H59" s="31">
-        <x:v>46122.2429836343</x:v>
+        <x:v>46122.36782125</x:v>
       </x:c>
       <x:c r="I59" s="31">
-        <x:v>46122.244317963</x:v>
+        <x:v>46122.3686719907</x:v>
       </x:c>
       <x:c r="J59" s="30" t="s">
-        <x:v>100</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K59" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L59" s="33">
-        <x:v>46122.2448800694</x:v>
+        <x:v>46122.3692180787</x:v>
       </x:c>
       <x:c r="M59" s="29" t="s">
         <x:v>21</x:v>
@@ -7773,25 +7782,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="29" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G60" s="29" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="H60" s="31">
-        <x:v>46122.3879258681</x:v>
+        <x:v>46122.2429836343</x:v>
       </x:c>
       <x:c r="I60" s="31">
-        <x:v>46122.3894281713</x:v>
+        <x:v>46122.244317963</x:v>
       </x:c>
       <x:c r="J60" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K60" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L60" s="33">
-        <x:v>46122.3900310185</x:v>
+        <x:v>46122.2448800694</x:v>
       </x:c>
       <x:c r="M60" s="29" t="s">
         <x:v>21</x:v>
@@ -7811,25 +7820,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F61" s="29" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="G61" s="29" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="H61" s="31">
-        <x:v>46124.150742662</x:v>
+        <x:v>46122.3879258681</x:v>
       </x:c>
       <x:c r="I61" s="31">
-        <x:v>46124.153253125</x:v>
+        <x:v>46122.3894281713</x:v>
       </x:c>
       <x:c r="J61" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K61" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L61" s="33">
-        <x:v>46124.1542643171</x:v>
+        <x:v>46122.3900310185</x:v>
       </x:c>
       <x:c r="M61" s="29" t="s">
         <x:v>21</x:v>
@@ -7849,25 +7858,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F62" s="29" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="G62" s="29" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="H62" s="31">
-        <x:v>46124.1512647338</x:v>
+        <x:v>46124.150742662</x:v>
       </x:c>
       <x:c r="I62" s="31">
-        <x:v>46124.1530803935</x:v>
+        <x:v>46124.153253125</x:v>
       </x:c>
       <x:c r="J62" s="30" t="s">
-        <x:v>190</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K62" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L62" s="33">
-        <x:v>46124.1540594444</x:v>
+        <x:v>46124.1542643171</x:v>
       </x:c>
       <x:c r="M62" s="29" t="s">
         <x:v>21</x:v>
@@ -7893,10 +7902,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="H63" s="31">
-        <x:v>46124.1518079282</x:v>
+        <x:v>46124.1512647338</x:v>
       </x:c>
       <x:c r="I63" s="31">
-        <x:v>46124.1529164583</x:v>
+        <x:v>46124.1530803935</x:v>
       </x:c>
       <x:c r="J63" s="30" t="s">
         <x:v>193</x:v>
@@ -7905,7 +7914,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L63" s="33">
-        <x:v>46124.1538595949</x:v>
+        <x:v>46124.1540594444</x:v>
       </x:c>
       <x:c r="M63" s="29" t="s">
         <x:v>21</x:v>
@@ -7931,10 +7940,10 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="H64" s="31">
-        <x:v>46122.3767795718</x:v>
+        <x:v>46124.1518079282</x:v>
       </x:c>
       <x:c r="I64" s="31">
-        <x:v>46122.3776183449</x:v>
+        <x:v>46124.1529164583</x:v>
       </x:c>
       <x:c r="J64" s="30" t="s">
         <x:v>196</x:v>
@@ -7943,7 +7952,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L64" s="33">
-        <x:v>46122.3780755324</x:v>
+        <x:v>46124.1538595949</x:v>
       </x:c>
       <x:c r="M64" s="29" t="s">
         <x:v>21</x:v>
@@ -7969,10 +7978,10 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="H65" s="31">
-        <x:v>46124.5490358102</x:v>
+        <x:v>46122.3767795718</x:v>
       </x:c>
       <x:c r="I65" s="31">
-        <x:v>46124.6984689583</x:v>
+        <x:v>46122.3776183449</x:v>
       </x:c>
       <x:c r="J65" s="30" t="s">
         <x:v>199</x:v>
@@ -7981,7 +7990,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L65" s="33">
-        <x:v>46124.6992754861</x:v>
+        <x:v>46122.3780755324</x:v>
       </x:c>
       <x:c r="M65" s="29" t="s">
         <x:v>21</x:v>
@@ -8007,10 +8016,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="H66" s="31">
-        <x:v>46124.6761778356</x:v>
+        <x:v>46124.5490358102</x:v>
       </x:c>
       <x:c r="I66" s="31">
-        <x:v>46124.6772295602</x:v>
+        <x:v>46124.6984689583</x:v>
       </x:c>
       <x:c r="J66" s="30" t="s">
         <x:v>202</x:v>
@@ -8019,7 +8028,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L66" s="33">
-        <x:v>46124.6777516435</x:v>
+        <x:v>46124.6992754861</x:v>
       </x:c>
       <x:c r="M66" s="29" t="s">
         <x:v>21</x:v>
@@ -8045,10 +8054,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="H67" s="31">
-        <x:v>46124.1487218981</x:v>
+        <x:v>46124.6761778356</x:v>
       </x:c>
       <x:c r="I67" s="31">
-        <x:v>46124.1494313773</x:v>
+        <x:v>46124.6772295602</x:v>
       </x:c>
       <x:c r="J67" s="30" t="s">
         <x:v>205</x:v>
@@ -8057,7 +8066,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L67" s="33">
-        <x:v>46124.1498205093</x:v>
+        <x:v>46124.6777516435</x:v>
       </x:c>
       <x:c r="M67" s="29" t="s">
         <x:v>21</x:v>
@@ -8083,10 +8092,10 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="H68" s="31">
-        <x:v>46124.6975491551</x:v>
+        <x:v>46124.1487218981</x:v>
       </x:c>
       <x:c r="I68" s="31">
-        <x:v>46124.6983328357</x:v>
+        <x:v>46124.1494313773</x:v>
       </x:c>
       <x:c r="J68" s="30" t="s">
         <x:v>208</x:v>
@@ -8095,7 +8104,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L68" s="33">
-        <x:v>46124.6990752199</x:v>
+        <x:v>46124.1498205093</x:v>
       </x:c>
       <x:c r="M68" s="29" t="s">
         <x:v>21</x:v>
@@ -8121,10 +8130,10 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="H69" s="31">
-        <x:v>46124.7023532986</x:v>
+        <x:v>46124.6975491551</x:v>
       </x:c>
       <x:c r="I69" s="31">
-        <x:v>46124.7048005093</x:v>
+        <x:v>46124.6983328357</x:v>
       </x:c>
       <x:c r="J69" s="30" t="s">
         <x:v>211</x:v>
@@ -8133,7 +8142,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L69" s="33">
-        <x:v>46124.7059938426</x:v>
+        <x:v>46124.6990752199</x:v>
       </x:c>
       <x:c r="M69" s="29" t="s">
         <x:v>21</x:v>
@@ -8159,10 +8168,10 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="H70" s="31">
-        <x:v>46124.7029179398</x:v>
+        <x:v>46124.7023532986</x:v>
       </x:c>
       <x:c r="I70" s="31">
-        <x:v>46124.7046092014</x:v>
+        <x:v>46124.7048005093</x:v>
       </x:c>
       <x:c r="J70" s="30" t="s">
         <x:v>214</x:v>
@@ -8171,7 +8180,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L70" s="33">
-        <x:v>46124.7058091204</x:v>
+        <x:v>46124.7059938426</x:v>
       </x:c>
       <x:c r="M70" s="29" t="s">
         <x:v>21</x:v>
@@ -8197,10 +8206,10 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="H71" s="31">
-        <x:v>46124.7035032407</x:v>
+        <x:v>46124.7029179398</x:v>
       </x:c>
       <x:c r="I71" s="31">
-        <x:v>46124.704475463</x:v>
+        <x:v>46124.7046092014</x:v>
       </x:c>
       <x:c r="J71" s="30" t="s">
         <x:v>217</x:v>
@@ -8209,7 +8218,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L71" s="33">
-        <x:v>46124.7056197917</x:v>
+        <x:v>46124.7058091204</x:v>
       </x:c>
       <x:c r="M71" s="29" t="s">
         <x:v>21</x:v>
@@ -8235,19 +8244,19 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="H72" s="31">
-        <x:v>46132.4200429282</x:v>
+        <x:v>46124.7035032407</x:v>
       </x:c>
       <x:c r="I72" s="31">
-        <x:v>46132.4214079282</x:v>
+        <x:v>46124.704475463</x:v>
       </x:c>
       <x:c r="J72" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K72" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L72" s="33">
-        <x:v>46132.422405787</x:v>
+        <x:v>46124.7056197917</x:v>
       </x:c>
       <x:c r="M72" s="29" t="s">
         <x:v>21</x:v>
@@ -8267,25 +8276,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F73" s="29" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="G73" s="29" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="H73" s="31">
-        <x:v>46128.4605351157</x:v>
+        <x:v>46132.4200429282</x:v>
       </x:c>
       <x:c r="I73" s="31">
-        <x:v>46128.4612873727</x:v>
+        <x:v>46132.4214079282</x:v>
       </x:c>
       <x:c r="J73" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K73" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L73" s="33">
-        <x:v>46128.4617054051</x:v>
+        <x:v>46132.422405787</x:v>
       </x:c>
       <x:c r="M73" s="29" t="s">
         <x:v>21</x:v>
@@ -8305,16 +8314,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F74" s="29" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="G74" s="29" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="H74" s="31">
-        <x:v>46127.1221474769</x:v>
+        <x:v>46128.4605351157</x:v>
       </x:c>
       <x:c r="I74" s="31">
-        <x:v>46127.1231965625</x:v>
+        <x:v>46128.4612873727</x:v>
       </x:c>
       <x:c r="J74" s="30" t="s">
         <x:v>30</x:v>
@@ -8323,7 +8332,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L74" s="33">
-        <x:v>46128.1095700579</x:v>
+        <x:v>46128.4617054051</x:v>
       </x:c>
       <x:c r="M74" s="29" t="s">
         <x:v>21</x:v>
@@ -8343,25 +8352,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="29" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="G75" s="29" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="H75" s="31">
-        <x:v>46124.701771875</x:v>
+        <x:v>46127.1221474769</x:v>
       </x:c>
       <x:c r="I75" s="31">
-        <x:v>46124.7049218519</x:v>
+        <x:v>46127.1231965625</x:v>
       </x:c>
       <x:c r="J75" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K75" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L75" s="33">
-        <x:v>46124.7061899306</x:v>
+        <x:v>46128.1095700579</x:v>
       </x:c>
       <x:c r="M75" s="29" t="s">
         <x:v>21</x:v>
@@ -8381,25 +8390,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F76" s="29" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G76" s="29" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H76" s="31">
-        <x:v>46124.1449755903</x:v>
+        <x:v>46124.701771875</x:v>
       </x:c>
       <x:c r="I76" s="31">
-        <x:v>46124.1465040046</x:v>
+        <x:v>46124.7049218519</x:v>
       </x:c>
       <x:c r="J76" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K76" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L76" s="33">
-        <x:v>46124.1471056481</x:v>
+        <x:v>46124.7061899306</x:v>
       </x:c>
       <x:c r="M76" s="29" t="s">
         <x:v>21</x:v>
@@ -8419,25 +8428,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F77" s="29" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="G77" s="29" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="H77" s="31">
-        <x:v>46122.3974322338</x:v>
+        <x:v>46124.1449755903</x:v>
       </x:c>
       <x:c r="I77" s="31">
-        <x:v>46122.3980999421</x:v>
+        <x:v>46124.1465040046</x:v>
       </x:c>
       <x:c r="J77" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K77" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L77" s="33">
-        <x:v>46122.398526713</x:v>
+        <x:v>46124.1471056481</x:v>
       </x:c>
       <x:c r="M77" s="29" t="s">
         <x:v>21</x:v>
@@ -8457,25 +8466,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="29" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="G78" s="29" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="H78" s="31">
-        <x:v>46123.4191184375</x:v>
+        <x:v>46122.3974322338</x:v>
       </x:c>
       <x:c r="I78" s="31">
-        <x:v>46123.4205974074</x:v>
+        <x:v>46122.3980999421</x:v>
       </x:c>
       <x:c r="J78" s="30" t="s">
-        <x:v>232</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K78" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L78" s="33">
-        <x:v>46123.4214065278</x:v>
+        <x:v>46122.398526713</x:v>
       </x:c>
       <x:c r="M78" s="29" t="s">
         <x:v>21</x:v>
@@ -8501,19 +8510,19 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="H79" s="31">
-        <x:v>46122.3885020718</x:v>
+        <x:v>46123.4191184375</x:v>
       </x:c>
       <x:c r="I79" s="31">
-        <x:v>46122.3892655903</x:v>
+        <x:v>46123.4205974074</x:v>
       </x:c>
       <x:c r="J79" s="30" t="s">
-        <x:v>53</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K79" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L79" s="33">
-        <x:v>46122.3902404514</x:v>
+        <x:v>46123.4214065278</x:v>
       </x:c>
       <x:c r="M79" s="29" t="s">
         <x:v>21</x:v>
@@ -8533,25 +8542,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F80" s="29" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="G80" s="29" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="H80" s="31">
-        <x:v>46118.3446055671</x:v>
+        <x:v>46122.3885020718</x:v>
       </x:c>
       <x:c r="I80" s="31">
-        <x:v>46118.476906412</x:v>
+        <x:v>46122.3892655903</x:v>
       </x:c>
       <x:c r="J80" s="30" t="s">
-        <x:v>237</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K80" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L80" s="33">
-        <x:v>46118.3476865394</x:v>
+        <x:v>46122.3902404514</x:v>
       </x:c>
       <x:c r="M80" s="29" t="s">
         <x:v>21</x:v>
@@ -8577,10 +8586,10 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="H81" s="31">
-        <x:v>46122.5587807523</x:v>
+        <x:v>46118.3446055671</x:v>
       </x:c>
       <x:c r="I81" s="31">
-        <x:v>46122.5602428125</x:v>
+        <x:v>46118.476906412</x:v>
       </x:c>
       <x:c r="J81" s="30" t="s">
         <x:v>240</x:v>
@@ -8589,7 +8598,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L81" s="33">
-        <x:v>46122.5607516551</x:v>
+        <x:v>46118.3476865394</x:v>
       </x:c>
       <x:c r="M81" s="29" t="s">
         <x:v>21</x:v>
@@ -8615,10 +8624,10 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="H82" s="31">
-        <x:v>46124.1410094907</x:v>
+        <x:v>46122.5587807523</x:v>
       </x:c>
       <x:c r="I82" s="31">
-        <x:v>46124.1426461806</x:v>
+        <x:v>46122.5602428125</x:v>
       </x:c>
       <x:c r="J82" s="30" t="s">
         <x:v>243</x:v>
@@ -8627,7 +8636,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L82" s="33">
-        <x:v>46124.1434541782</x:v>
+        <x:v>46122.5607516551</x:v>
       </x:c>
       <x:c r="M82" s="29" t="s">
         <x:v>21</x:v>
@@ -8653,10 +8662,10 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="H83" s="31">
-        <x:v>46122.5911383796</x:v>
+        <x:v>46124.1410094907</x:v>
       </x:c>
       <x:c r="I83" s="31">
-        <x:v>46122.5921380556</x:v>
+        <x:v>46124.1426461806</x:v>
       </x:c>
       <x:c r="J83" s="30" t="s">
         <x:v>246</x:v>
@@ -8665,7 +8674,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L83" s="33">
-        <x:v>46122.5928339699</x:v>
+        <x:v>46124.1434541782</x:v>
       </x:c>
       <x:c r="M83" s="29" t="s">
         <x:v>21</x:v>
@@ -8691,19 +8700,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="H84" s="31">
-        <x:v>46122.5945434491</x:v>
+        <x:v>46122.5911383796</x:v>
       </x:c>
       <x:c r="I84" s="31">
-        <x:v>46122.5999534606</x:v>
+        <x:v>46122.5921380556</x:v>
       </x:c>
       <x:c r="J84" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K84" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L84" s="33">
-        <x:v>46122.6007489699</x:v>
+        <x:v>46122.5928339699</x:v>
       </x:c>
       <x:c r="M84" s="29" t="s">
         <x:v>21</x:v>
@@ -8723,25 +8732,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F85" s="29" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G85" s="29" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="H85" s="31">
-        <x:v>46122.6182774306</x:v>
+        <x:v>46122.5945434491</x:v>
       </x:c>
       <x:c r="I85" s="31">
-        <x:v>46122.6193276968</x:v>
+        <x:v>46122.5999534606</x:v>
       </x:c>
       <x:c r="J85" s="30" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K85" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L85" s="33">
-        <x:v>46122.6199813426</x:v>
+        <x:v>46122.6007489699</x:v>
       </x:c>
       <x:c r="M85" s="29" t="s">
         <x:v>21</x:v>
@@ -8761,25 +8770,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F86" s="29" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="G86" s="29" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="H86" s="31">
-        <x:v>46122.5623107755</x:v>
+        <x:v>46122.6182774306</x:v>
       </x:c>
       <x:c r="I86" s="31">
-        <x:v>46122.5630093981</x:v>
+        <x:v>46122.6193276968</x:v>
       </x:c>
       <x:c r="J86" s="30" t="s">
-        <x:v>158</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K86" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L86" s="33">
-        <x:v>46122.5634620023</x:v>
+        <x:v>46122.6199813426</x:v>
       </x:c>
       <x:c r="M86" s="29" t="s">
         <x:v>21</x:v>
@@ -8799,25 +8808,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F87" s="29" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="G87" s="29" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="H87" s="31">
-        <x:v>46122.6819179514</x:v>
+        <x:v>46122.5623107755</x:v>
       </x:c>
       <x:c r="I87" s="31">
-        <x:v>46122.6826717361</x:v>
+        <x:v>46122.5630093981</x:v>
       </x:c>
       <x:c r="J87" s="30" t="s">
-        <x:v>255</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="K87" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L87" s="33">
-        <x:v>46122.6831438079</x:v>
+        <x:v>46122.5634620023</x:v>
       </x:c>
       <x:c r="M87" s="29" t="s">
         <x:v>21</x:v>
@@ -8843,10 +8852,10 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="H88" s="31">
-        <x:v>46123.4162791088</x:v>
+        <x:v>46122.6819179514</x:v>
       </x:c>
       <x:c r="I88" s="31">
-        <x:v>46123.4173169792</x:v>
+        <x:v>46122.6826717361</x:v>
       </x:c>
       <x:c r="J88" s="30" t="s">
         <x:v>258</x:v>
@@ -8855,7 +8864,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L88" s="33">
-        <x:v>46123.417862662</x:v>
+        <x:v>46122.6831438079</x:v>
       </x:c>
       <x:c r="M88" s="29" t="s">
         <x:v>21</x:v>
@@ -8881,19 +8890,19 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="H89" s="31">
-        <x:v>46122.6795081481</x:v>
+        <x:v>46123.4162791088</x:v>
       </x:c>
       <x:c r="I89" s="31">
-        <x:v>46122.6802186921</x:v>
+        <x:v>46123.4173169792</x:v>
       </x:c>
       <x:c r="J89" s="30" t="s">
-        <x:v>30</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="K89" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L89" s="33">
-        <x:v>46122.6809879398</x:v>
+        <x:v>46123.417862662</x:v>
       </x:c>
       <x:c r="M89" s="29" t="s">
         <x:v>21</x:v>
@@ -8913,25 +8922,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F90" s="29" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="G90" s="29" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="H90" s="31">
-        <x:v>46123.0476912847</x:v>
+        <x:v>46122.6795081481</x:v>
       </x:c>
       <x:c r="I90" s="31">
-        <x:v>46123.0484775694</x:v>
+        <x:v>46122.6802186921</x:v>
       </x:c>
       <x:c r="J90" s="30" t="s">
-        <x:v>263</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K90" s="32" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L90" s="33">
-        <x:v>46123.049084375</x:v>
+        <x:v>46122.680987939